--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F228BACA-7AAB-4E17-808A-4B7A9C56CE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080A1A3A-A494-4054-8799-3E3BEBFAD6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="560">
   <si>
     <t>Sales</t>
   </si>
@@ -1386,10 +1386,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3282,6 +3278,13 @@
   </si>
   <si>
     <t>DCF</t>
+  </si>
+  <si>
+    <t>昆仑能源是中国国内销售规模最大的
+天然气终端利用企业和 LPG 销售企业之一。</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -5069,7 +5072,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C1" s="33">
         <f>Thesis!C1</f>
@@ -5080,16 +5083,16 @@
         <v>INT</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F1" s="307" t="str">
         <f>Thesis!F1</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -5103,7 +5106,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -5112,7 +5115,7 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C5" s="359" t="str">
         <f>Thesis!C5</f>
@@ -5121,7 +5124,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C6" s="34">
         <f>Common_Shares</f>
@@ -5131,7 +5134,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C7" s="360">
         <f>Thesis!C7</f>
@@ -5142,7 +5145,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -5155,14 +5158,14 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C11" s="365" t="str">
         <f>Thesis!C11</f>
@@ -5173,18 +5176,18 @@
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.76</v>
+        <v>7.72</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C13" s="32" t="str">
         <f>Market_currency</f>
@@ -5195,11 +5198,11 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>67192.301254079997</v>
+        <v>66845.949185759993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5209,7 +5212,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -5223,11 +5226,11 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0942481800000001</v>
+        <v>1.09186545</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5238,7 +5241,7 @@
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
       <c r="B18" s="371" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C18" s="371"/>
       <c r="D18" s="371"/>
@@ -5247,21 +5250,21 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E21" s="363" t="str">
         <f>valuation_method</f>
@@ -5270,7 +5273,7 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C22" s="32" t="str">
         <f>Thesis!C22</f>
@@ -5287,7 +5290,7 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C23" s="253" t="str">
         <f>Thesis!C23</f>
@@ -5296,7 +5299,7 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C24" s="253" t="str">
         <f>Thesis!C24</f>
@@ -5305,7 +5308,7 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C25" s="32" t="str">
         <f>Reporting_currency</f>
@@ -5327,14 +5330,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>13.950006223203813</v>
+        <v>12.955428203627237</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25315453740124205</v>
+        <v>0.2264478139311954</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5343,7 +5346,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5354,7 +5357,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F28" s="361">
         <f>Thesis!F28</f>
@@ -5363,18 +5366,18 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>6.255904177578377</v>
+        <v>5.8503896992892184</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F29" s="362">
         <f>Thesis!F29</f>
@@ -5383,18 +5386,18 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.8169432851566398</v>
+        <v>7.3062505252398662</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F30" s="224">
         <f>Thesis!F30</f>
@@ -5403,18 +5406,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>12.12785192627685</v>
+        <v>11.325299029666908</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F31" s="224">
         <f>Thesis!F31</f>
@@ -5423,18 +5426,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.832519704946716</v>
+        <v>10.117830170604076</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F32" s="224">
         <f>Thesis!F32</f>
@@ -5447,7 +5450,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -5457,7 +5460,7 @@
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
       <c r="B36" s="371" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C36" s="371"/>
       <c r="D36" s="371"/>
@@ -5466,7 +5469,7 @@
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="374" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="374"/>
       <c r="D37" s="374"/>
@@ -5475,7 +5478,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -5484,7 +5487,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="B40" s="367" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C40" s="367"/>
       <c r="D40" s="367"/>
@@ -5510,7 +5513,7 @@
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
       <c r="B43" s="367" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C43" s="367"/>
       <c r="D43" s="367"/>
@@ -5545,7 +5548,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="B47" s="367" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C47" s="367"/>
       <c r="D47" s="367"/>
@@ -5567,7 +5570,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="367" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C50" s="367"/>
       <c r="D50" s="367"/>
@@ -5576,11 +5579,11 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61776536198528</v>
+        <v>279.60690627024144</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5591,7 +5594,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -5610,7 +5613,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38223463801478</v>
+        <v>-523.39309372975856</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5619,7 +5622,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="2:6">
@@ -5650,7 +5653,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7312559290367</v>
+        <v>-4449.7285411561006</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="367" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C61" s="373"/>
       <c r="D61" s="373"/>
@@ -5681,7 +5684,7 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="371" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C64" s="371"/>
       <c r="D64" s="371"/>
@@ -5690,7 +5693,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="371" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C65" s="371"/>
       <c r="D65" s="371"/>
@@ -5699,11 +5702,11 @@
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060629860687</v>
+        <v>10305.03755922756</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5716,7 +5719,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3316978747062</v>
+        <v>7230.3235535558979</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5725,52 +5728,52 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11774827105977852</v>
+        <v>0.11810050686108982</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4531388562371134E-2</v>
+        <v>4.4664651439119164E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41383529837571015</v>
+        <v>0.41293463541208869</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.2003593743875291</v>
+        <v>0.20035925214863964</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.1911415616576877</v>
+        <v>0.19114130195562065</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5780,11 +5783,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688940854644052E-2</v>
+        <v>9.7688881254799131E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780132319646975E-2</v>
+        <v>9.0780008977618121E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5817,7 +5820,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5831,7 +5834,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
       <c r="B80" s="371" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C80" s="371"/>
       <c r="D80" s="371"/>
@@ -5849,12 +5852,12 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5863,7 +5866,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5884,13 +5887,13 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
       <c r="B89" s="371" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C89" s="371"/>
       <c r="D89" s="371"/>
@@ -5899,7 +5902,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="B90" s="371" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C90" s="371"/>
       <c r="D90" s="371"/>
@@ -5920,7 +5923,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.183021112318418</v>
+        <v>12.156478839568178</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5929,7 +5932,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5942,7 +5945,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="371" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C97" s="371"/>
       <c r="D97" s="371"/>
@@ -5956,12 +5959,12 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="371" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C101" s="371"/>
       <c r="D101" s="371"/>
@@ -5987,7 +5990,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0682365133358012</v>
+        <v>3.0615554154632685</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5996,7 +5999,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6005,7 +6008,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6014,7 +6017,7 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="108" spans="2:6">
@@ -6036,7 +6039,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.223463801474</v>
+        <v>17131.309372975855</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6049,7 +6052,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1648163891938452</v>
+        <v>2.1602394243918974</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6058,7 +6061,7 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -6080,7 +6083,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0017655740038342E-2</v>
+        <v>1.9974067210732804E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6089,7 +6092,7 @@
     </row>
     <row r="116" spans="1:6">
       <c r="B116" s="371" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C116" s="371"/>
       <c r="D116" s="371"/>
@@ -6098,11 +6101,11 @@
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6111,11 +6114,11 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1955836830910833</v>
+        <v>-3.1886252862224569</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6124,7 +6127,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -6134,7 +6137,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="367" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C123" s="367"/>
       <c r="D123" s="367"/>
@@ -6143,19 +6146,19 @@
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="C125" s="233" t="s">
         <v>523</v>
-      </c>
-      <c r="C125" s="233" t="s">
-        <v>524</v>
       </c>
       <c r="D125" s="233" t="s">
         <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
+        <v>524</v>
+      </c>
+      <c r="F125" s="233" t="s">
         <v>525</v>
-      </c>
-      <c r="F125" s="233" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -6169,11 +6172,11 @@
       </c>
       <c r="D126" s="230">
         <f>DCF!D74</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>15.25 HKD</v>
+        <v>12.89 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6191,11 +6194,11 @@
       </c>
       <c r="D127" s="220">
         <f>DCF!D75</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>15.67 HKD</v>
+        <v>14.06 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6213,11 +6216,11 @@
       </c>
       <c r="D128" s="220">
         <f>DCF!D76</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.98 HKD</v>
+        <v>13.03 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6235,11 +6238,11 @@
       </c>
       <c r="D129" s="220">
         <f>DCF!D77</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.53 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6257,11 +6260,11 @@
       </c>
       <c r="D130" s="220">
         <f>DCF!D78</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.3 HKD</v>
+        <v>11.28 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6274,7 +6277,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>13.950006223203813</v>
+        <v>12.955428203627237</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6283,7 +6286,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C134" s="369"/>
       <c r="D134" s="369"/>
@@ -6292,7 +6295,7 @@
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -6302,7 +6305,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="370" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C138" s="370"/>
       <c r="D138" s="370"/>
@@ -6311,7 +6314,7 @@
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C139" s="371"/>
       <c r="D139" s="371"/>
@@ -6320,12 +6323,12 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -6334,7 +6337,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -6343,11 +6346,11 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6356,7 +6359,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -6369,7 +6372,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -6383,7 +6386,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58603424994384601</v>
+        <v>0.58475815790742269</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6393,7 +6396,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.6698699276345312</v>
+        <v>5.2656315413817953</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6402,7 +6405,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>6.255904177578377</v>
+        <v>5.8503896992892184</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6411,7 +6414,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -6424,21 +6427,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55154828768659714</v>
+        <v>0.5484217420423636</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -6452,7 +6455,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67454009887628796</v>
+        <v>0.67307128498271995</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6462,7 +6465,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>7.1424031862803519</v>
+        <v>6.6331792402571459</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6471,7 +6474,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.8169432851566398</v>
+        <v>7.3062505252398662</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6480,7 +6483,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -6493,21 +6496,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43964589261943932</v>
+        <v>0.43604716027878754</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -6521,7 +6524,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89864697218420275</v>
+        <v>0.89669016463435369</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6531,16 +6534,16 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>11.229204954092648</v>
+        <v>10.428608865032555</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>12.12785192627685</v>
+        <v>11.325299029666908</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -6562,21 +6565,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.13062032143728175</v>
+        <v>0.12582595868995883</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -6590,7 +6593,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83370776184420992</v>
+        <v>0.83189235969715858</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6600,16 +6603,16 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.9988119431025062</v>
+        <v>9.2859378109069173</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.832519704946716</v>
+        <v>10.117830170604076</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6618,7 +6621,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -6631,16 +6634,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22345991530747344</v>
+        <v>0.22261918959240934</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -6650,7 +6653,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="B179" s="372" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C179" s="371"/>
       <c r="D179" s="371"/>
@@ -6659,12 +6662,12 @@
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="B182" s="373" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C182" s="373"/>
       <c r="D182" s="373"/>
@@ -6673,27 +6676,27 @@
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
       <c r="B188" s="367" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C188" s="367"/>
       <c r="D188" s="367"/>
@@ -6702,12 +6705,12 @@
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="B191" s="368" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C191" s="368"/>
       <c r="D191" s="368"/>
@@ -6716,7 +6719,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="B192" s="368" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C192" s="368"/>
       <c r="D192" s="368"/>
@@ -6725,22 +6728,22 @@
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -6818,13 +6821,13 @@
         <v>45867</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>279</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -6843,7 +6846,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -6852,15 +6855,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C6" s="51">
         <v>8658801708</v>
@@ -6869,7 +6872,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -6879,7 +6882,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -6892,48 +6895,48 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C12" s="50">
-        <v>7.76</v>
+        <v>7.72</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>67192.301254079997</v>
+        <v>66845.949185759993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -6943,7 +6946,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -6957,10 +6960,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0942481800000001</v>
+        <v>1.09186545</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -6971,7 +6974,7 @@
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
       <c r="B18" s="371" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C18" s="371"/>
       <c r="D18" s="371"/>
@@ -6980,24 +6983,24 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -7005,7 +7008,7 @@
         <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
@@ -7015,26 +7018,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -7052,14 +7055,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>13.950006223203813</v>
+        <v>12.955428203627237</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25315453740124205</v>
+        <v>0.2264478139311954</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7068,7 +7071,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -7079,7 +7082,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -7087,18 +7090,18 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>6.255904177578377</v>
+        <v>5.8503896992892184</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F29" s="302">
         <v>0.35</v>
@@ -7106,18 +7109,18 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.8169432851566398</v>
+        <v>7.3062505252398662</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F30" s="312">
         <v>0.25</v>
@@ -7125,18 +7128,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>12.12785192627685</v>
+        <v>11.325299029666908</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -7144,18 +7147,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.832519704946716</v>
+        <v>10.117830170604076</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -7167,7 +7170,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -7177,7 +7180,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="B36" s="371" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C36" s="371"/>
       <c r="D36" s="371"/>
@@ -7186,7 +7189,7 @@
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="374" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="374"/>
       <c r="D37" s="374"/>
@@ -7296,11 +7299,11 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61776536198528</v>
+        <v>279.60690627024144</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7311,7 +7314,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -7330,7 +7333,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38223463801478</v>
+        <v>-523.39309372975856</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7370,7 +7373,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7312559290367</v>
+        <v>-4449.7285411561006</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="367" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C61" s="373"/>
       <c r="D61" s="373"/>
@@ -7401,7 +7404,7 @@
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
       <c r="B64" s="371" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C64" s="371"/>
       <c r="D64" s="371"/>
@@ -7410,7 +7413,7 @@
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
       <c r="B65" s="371" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C65" s="371"/>
       <c r="D65" s="371"/>
@@ -7423,7 +7426,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060629860687</v>
+        <v>10305.03755922756</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7436,7 +7439,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3316978747062</v>
+        <v>7230.3235535558979</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7445,52 +7448,52 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11774827105977852</v>
+        <v>0.11810050686108982</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4531388562371134E-2</v>
+        <v>4.4664651439119164E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41383529837571015</v>
+        <v>0.41293463541208869</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C72" s="323" t="s">
+        <v>431</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>432</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.2003593743875291</v>
+        <v>0.20035925214863964</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.1911415616576877</v>
+        <v>0.19114130195562065</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -7500,11 +7503,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688940854644052E-2</v>
+        <v>9.7688881254799131E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780132319646975E-2</v>
+        <v>9.0780008977618121E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -7537,7 +7540,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -7551,7 +7554,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
       <c r="B80" s="371" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C80" s="371"/>
       <c r="D80" s="371"/>
@@ -7574,7 +7577,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -7583,7 +7586,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -7604,13 +7607,13 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
       <c r="B89" s="371" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C89" s="371"/>
       <c r="D89" s="371"/>
@@ -7619,7 +7622,7 @@
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
       <c r="B90" s="371" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C90" s="371"/>
       <c r="D90" s="371"/>
@@ -7640,7 +7643,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.183021112318418</v>
+        <v>12.156478839568178</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -7649,7 +7652,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -7662,7 +7665,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="371" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C97" s="371"/>
       <c r="D97" s="371"/>
@@ -7681,7 +7684,7 @@
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
       <c r="B101" s="371" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C101" s="371"/>
       <c r="D101" s="371"/>
@@ -7707,7 +7710,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0682365133358012</v>
+        <v>3.0615554154632685</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -7716,7 +7719,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -7725,7 +7728,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -7756,7 +7759,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.223463801474</v>
+        <v>17131.309372975855</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7769,7 +7772,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1648163891938452</v>
+        <v>2.1602394243918974</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -7800,7 +7803,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0017655740038342E-2</v>
+        <v>1.9974067210732804E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -7809,7 +7812,7 @@
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
       <c r="B116" s="371" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C116" s="371"/>
       <c r="D116" s="371"/>
@@ -7818,11 +7821,11 @@
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -7831,11 +7834,11 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1955836830910833</v>
+        <v>-3.1886252862224569</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -7844,7 +7847,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -7854,7 +7857,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="367" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C123" s="367"/>
       <c r="D123" s="367"/>
@@ -7889,11 +7892,11 @@
       </c>
       <c r="D126" s="230">
         <f>DCF!D74</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>15.25 HKD</v>
+        <v>12.89 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -7911,11 +7914,11 @@
       </c>
       <c r="D127" s="220">
         <f>DCF!D75</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>15.67 HKD</v>
+        <v>14.06 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -7933,11 +7936,11 @@
       </c>
       <c r="D128" s="220">
         <f>DCF!D76</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.98 HKD</v>
+        <v>13.03 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -7955,11 +7958,11 @@
       </c>
       <c r="D129" s="220">
         <f>DCF!D77</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.53 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -7977,11 +7980,11 @@
       </c>
       <c r="D130" s="220">
         <f>DCF!D78</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.3 HKD</v>
+        <v>11.28 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -7994,7 +7997,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>13.950006223203813</v>
+        <v>12.955428203627237</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -8003,7 +8006,7 @@
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
       <c r="B134" s="369" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C134" s="369"/>
       <c r="D134" s="369"/>
@@ -8012,7 +8015,7 @@
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="370" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C138" s="370"/>
       <c r="D138" s="370"/>
@@ -8031,7 +8034,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C139" s="371"/>
       <c r="D139" s="371"/>
@@ -8067,7 +8070,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -8076,7 +8079,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -8089,7 +8092,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -8103,7 +8106,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58603424994384601</v>
+        <v>0.58475815790742269</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -8113,7 +8116,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.6698699276345312</v>
+        <v>5.2656315413817953</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -8122,7 +8125,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>6.255904177578377</v>
+        <v>5.8503896992892184</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -8131,7 +8134,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -8148,17 +8151,17 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55154828768659714</v>
+        <v>0.5484217420423636</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -8172,7 +8175,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67454009887628796</v>
+        <v>0.67307128498271995</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -8182,7 +8185,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>7.1424031862803519</v>
+        <v>6.6331792402571459</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -8191,7 +8194,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.8169432851566398</v>
+        <v>7.3062505252398662</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -8200,7 +8203,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -8217,17 +8220,17 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43964589261943932</v>
+        <v>0.43604716027878754</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -8241,7 +8244,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89864697218420275</v>
+        <v>0.89669016463435369</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -8251,16 +8254,16 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>11.229204954092648</v>
+        <v>10.428608865032555</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>12.12785192627685</v>
+        <v>11.325299029666908</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -8269,7 +8272,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -8286,17 +8289,17 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.13062032143728175</v>
+        <v>0.12582595868995883</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -8310,7 +8313,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83370776184420992</v>
+        <v>0.83189235969715858</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -8320,16 +8323,16 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.9988119431025062</v>
+        <v>9.2859378109069173</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.832519704946716</v>
+        <v>10.117830170604076</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -8355,12 +8358,12 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22345991530747344</v>
+        <v>0.22261918959240934</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -8370,7 +8373,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="B179" s="372" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C179" s="371"/>
       <c r="D179" s="371"/>
@@ -8379,12 +8382,12 @@
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="B182" s="373" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C182" s="373"/>
       <c r="D182" s="373"/>
@@ -8393,27 +8396,27 @@
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
       <c r="B188" s="367" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C188" s="367"/>
       <c r="D188" s="367"/>
@@ -8422,12 +8425,12 @@
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
       <c r="B191" s="368" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C191" s="368"/>
       <c r="D191" s="368"/>
@@ -8436,7 +8439,7 @@
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
       <c r="B192" s="368" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C192" s="368"/>
       <c r="D192" s="368"/>
@@ -8445,22 +8448,22 @@
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -9067,7 +9070,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C22" s="351">
         <v>12514</v>
@@ -9103,7 +9106,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C23" s="351">
         <v>-3491</v>
@@ -9139,7 +9142,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C24" s="351">
         <v>-8586</v>
@@ -9180,19 +9183,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.31054763348400005</v>
+        <v>0.30987141471000001</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27782961290200003</v>
+        <v>0.277224637755</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22738477180400005</v>
+        <v>0.22688964051000002</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -10512,7 +10515,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -10565,19 +10568,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.31054763348400005</v>
+        <v>0.30987141471000001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27782961290200003</v>
+        <v>0.277224637755</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22738477180400005</v>
+        <v>0.22688964051000002</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -11390,7 +11393,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -11888,7 +11891,7 @@
         <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>57</v>
@@ -11915,11 +11918,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2331455417156452</v>
+        <v>8.2152178327779772</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1955836830910833</v>
+        <v>-3.1886252862224569</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -12094,7 +12097,7 @@
         <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>57</v>
@@ -12110,7 +12113,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17130.223463801474</v>
+        <v>17131.309372975855</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -12161,7 +12164,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>92</v>
@@ -12173,52 +12176,52 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.930539628776</v>
+        <v>-14497.387585041586</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.888268099263</v>
+        <v>-13980.345313512073</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1102370008426452</v>
+        <v>3.1103534851014092</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2252600217747376</v>
+        <v>3.2253852811788817</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27961.776536198526</v>
+        <v>27960.690627024145</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -12226,7 +12229,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -12302,7 +12305,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -12313,23 +12316,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>285</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26567.251562220004</v>
+        <v>-26509.401260549999</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0682365133358016</v>
+        <v>-3.0615554154632685</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -12338,15 +12341,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18744.71584825806</v>
+        <v>18705.0848176135</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1648163891938452</v>
+        <v>2.1602394243918974</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -12359,11 +12362,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>173.32891171200004</v>
+        <v>172.95148728000001</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.0017655740038345E-2</v>
+        <v>1.9974067210732804E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -12372,15 +12375,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7649.2068022499443</v>
+        <v>-7631.3649556564988</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88340246840191805</v>
+        <v>-0.88134192386063825</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -12960,48 +12963,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.38223463801478</v>
+        <v>-523.39309372975856</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.939370139311</v>
+        <v>-208.96244077244023</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.50861380083563</v>
+        <v>-420.52956521087992</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.3297692585262</v>
+        <v>-366.35045576568484</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.96443298924373</v>
+        <v>-454.97717240983388</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.36533626928247</v>
+        <v>-503.37328335585096</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09121859934362</v>
+        <v>-818.09781708940352</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.0690127255707</v>
+        <v>-947.07611693932131</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1578362206624</v>
+        <v>-1014.1629175396502</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.58334047872603</v>
+        <v>-468.59174512482423</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.47636563814717</v>
+        <v>-437.48178410626201</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -13015,48 +13018,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.925023716147</v>
+        <v>17798.914164624402</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.060629860687</v>
+        <v>16980.03755922756</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.491386199163</v>
+        <v>17261.47043478912</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.670230741474</v>
+        <v>16973.649544234315</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.035567010756</v>
+        <v>14670.022827590166</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.634663730718</v>
+        <v>11589.626716644148</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.908781400656</v>
+        <v>20402.902182910595</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.930987274431</v>
+        <v>19208.923883060677</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.842163779336</v>
+        <v>16944.837082460348</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.416659521274</v>
+        <v>17752.408254875176</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.523634361853</v>
+        <v>11857.518215893739</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -13070,7 +13073,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7312559290367</v>
+        <v>-4449.7285411561006</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -13182,50 +13185,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3316978747062</v>
+        <v>7230.3235535558979</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.060629860687</v>
+        <v>10305.03755922756</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.491386199163</v>
+        <v>10350.47043478912</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.670230741474</v>
+        <v>10809.649544234315</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0355670107565</v>
+        <v>8651.0228275901663</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6346637307179</v>
+        <v>5607.6267166441485</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.908781400656</v>
+        <v>12308.902182910595</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.930987274431</v>
+        <v>11857.923883060677</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.842163779336</v>
+        <v>10224.837082460348</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.416659521274</v>
+        <v>11296.408254875176</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5236343618526</v>
+        <v>7067.5182158937387</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -13243,7 +13246,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -13268,7 +13271,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -13290,50 +13293,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3316978747062</v>
+        <v>7230.3235535558979</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.060629860687</v>
+        <v>10305.03755922756</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.491386199163</v>
+        <v>10350.47043478912</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.670230741474</v>
+        <v>10809.649544234315</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0355670107565</v>
+        <v>8651.0228275901663</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6346637307179</v>
+        <v>5607.6267166441485</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.908781400656</v>
+        <v>12308.902182910595</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.930987274431</v>
+        <v>11857.923883060677</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.842163779336</v>
+        <v>10224.837082460348</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.416659521274</v>
+        <v>11296.408254875176</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5236343618526</v>
+        <v>7067.5182158937387</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -13596,7 +13599,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -13656,7 +13659,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -13780,7 +13783,7 @@
         <v>-5900</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -13838,7 +13841,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -14146,48 +14149,48 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421606778595251</v>
+        <v>0.1842163180787626</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337842399114968</v>
+        <v>0.19337865870757606</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787922450763275</v>
+        <v>0.18787945348401833</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391230121262472</v>
+        <v>0.18391246092172567</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957488455079933</v>
+        <v>0.19957502140066719</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967741088534732</v>
+        <v>0.19967747546289613</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636699212980055</v>
+        <v>0.1963670647540191</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838199411191533</v>
+        <v>0.20838205660029324</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2084786579192314</v>
+        <v>0.20847875662073226</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986040933919701</v>
+        <v>0.21986050980765895</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -14285,52 +14288,52 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.61776536198528</v>
+        <v>279.60690627024144</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.060629860689</v>
+        <v>594.03755922755977</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.49138619916437</v>
+        <v>539.47043478912008</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.6702307414738</v>
+        <v>532.64954423431516</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.03556701075627</v>
+        <v>328.02282759016612</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.63466373071751</v>
+        <v>204.62671664414901</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90878140065635</v>
+        <v>169.90218291059645</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.9309872744293</v>
+        <v>182.92388306067866</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.84216377933757</v>
+        <v>130.83708246034982</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.41665952127397</v>
+        <v>216.40825487517577</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.52363436185286</v>
+        <v>139.51821589373796</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -14340,7 +14343,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -14401,48 +14404,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.38223463801478</v>
+        <v>-523.39309372975856</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.939370139311</v>
+        <v>-208.96244077244023</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.50861380083563</v>
+        <v>-420.52956521087992</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.3297692585262</v>
+        <v>-366.35045576568484</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.96443298924373</v>
+        <v>-454.97717240983388</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.36533626928247</v>
+        <v>-503.37328335585096</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09121859934362</v>
+        <v>-818.09781708940352</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.0690127255707</v>
+        <v>-947.07611693932131</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1578362206624</v>
+        <v>-1014.1629175396502</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.58334047872603</v>
+        <v>-468.59174512482423</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.47636563814717</v>
+        <v>-437.48178410626201</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -14472,7 +14475,7 @@
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -14499,7 +14502,7 @@
         <v>3.3073849829070391E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -14814,7 +14817,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -15375,7 +15378,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -15487,50 +15490,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8725698937322438E-3</v>
+        <v>2.8726294935771599E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.117048053095554E-3</v>
+        <v>1.1171713951244092E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3710128545216666E-3</v>
+        <v>2.3711309878033759E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1305178968648291E-3</v>
+        <v>2.1306382064258411E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2838273870184394E-3</v>
+        <v>3.2839193371912339E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074208590244706E-3</v>
+        <v>4.6074936005697977E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2197472364101522E-3</v>
+        <v>7.21980546882885E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795108820097721E-3</v>
+        <v>8.9795782396825761E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432798640685662E-2</v>
+        <v>1.1432855923383426E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7226660374529933E-3</v>
+        <v>5.7227686808434602E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0505904412433591E-2</v>
+        <v>1.0506034535824356E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -15544,50 +15547,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688940854644052E-2</v>
+        <v>9.7688881254799131E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780132319646975E-2</v>
+        <v>9.0780008977618121E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.732789441568368E-2</v>
+        <v>9.7327776282401982E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716269429241346E-2</v>
+        <v>9.8716149119680324E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1058849023581222</v>
+        <v>0.10588481040794941</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608264147450108</v>
+        <v>0.10608256873295575</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005797023643055</v>
+        <v>0.18005791200401186</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212696489309216</v>
+        <v>0.18212689753541933</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1910225031427337</v>
+        <v>0.19102244586003594</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680487359274656</v>
+        <v>0.2168047709493561</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475597690645882</v>
+        <v>0.28475584678306809</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -15601,7 +15604,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422235213661013E-2</v>
+        <v>2.4422220313699783E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -15716,50 +15719,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.968348901138697E-2</v>
+        <v>3.968344431150328E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093723628736713E-2</v>
+        <v>5.5093600286707865E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360631201998053E-2</v>
+        <v>5.8360513068716355E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867388398207991E-2</v>
+        <v>6.2867268088646969E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2441161244998135E-2</v>
+        <v>6.244106929482534E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327993919787623E-2</v>
+        <v>5.1327921178242288E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862750771227181</v>
+        <v>0.1086274494798531</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242942056769158</v>
+        <v>0.11242935321001875</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1152666354449455</v>
+        <v>0.11526657816224774</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795970615668002</v>
+        <v>0.13795960351328956</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972511789730921</v>
+        <v>0.16972498777391845</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -15823,50 +15826,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.968348901138697E-2</v>
+        <v>3.968344431150328E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093723628736713E-2</v>
+        <v>5.5093600286707865E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360631201998053E-2</v>
+        <v>5.8360513068716355E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867388398207991E-2</v>
+        <v>6.2867268088646969E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2441161244998135E-2</v>
+        <v>6.244106929482534E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327993919787623E-2</v>
+        <v>5.1327921178242288E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862750771227181</v>
+        <v>0.1086274494798531</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242942056769158</v>
+        <v>0.11242935321001875</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1152666354449455</v>
+        <v>0.11526657816224774</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795970615668002</v>
+        <v>0.13795960351328956</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972511789730921</v>
+        <v>0.16972498777391845</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -15892,24 +15895,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.31054763348400005</v>
+        <v>0.30987141471000001</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27782961290200003</v>
+        <v>0.277224637755</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22738477180400005</v>
+        <v>0.22688964051000002</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -15948,24 +15951,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2992.1664755453339</v>
+        <v>2985.6510204990423</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2992.1664755453339</v>
+        <v>2985.6510204990423</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2688.9703792266178</v>
+        <v>2683.1151349513243</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2405.6715267288164</v>
+        <v>2400.4331668926752</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1968.8796504696659</v>
+        <v>1964.5924067754941</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -16003,24 +16006,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41383529837571015</v>
+        <v>0.41293463541208869</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.29035893945883406</v>
+        <v>0.28972733028280578</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.2597915672691597</v>
+        <v>0.25922639476685683</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22254809586025667</v>
+        <v>0.22206392141297737</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22758889790924583</v>
+        <v>0.22709365654543673</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -16054,7 +16057,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C93" s="356">
         <v>0</v>
@@ -16075,28 +16078,28 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4531388562371134E-2</v>
+        <v>4.4664651439119164E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4531388562371134E-2</v>
+        <v>4.4664651439119164E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0019024933505162E-2</v>
+        <v>4.0138784288860106E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.5802785167783513E-2</v>
+        <v>3.5909927170336788E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.930216131494846E-2</v>
+        <v>2.9389849806994821E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -16216,46 +16219,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225057124674064E-2</v>
+        <v>4.8225841818108073E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6303965285611621E-2</v>
+        <v>-1.6304107846707883E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956919248755531E-2</v>
+        <v>1.6956924308159316E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702993037801605</v>
+        <v>0.15702952501966649</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578930161793846</v>
+        <v>0.26578907036946964</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196164880686727</v>
+        <v>-0.43196185460558734</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.215743056795886E-2</v>
+        <v>6.2157479883754529E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361522058521902</v>
+        <v>0.13361514127178542</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490961102966576E-2</v>
+        <v>-4.5490795435771503E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714368758048622</v>
+        <v>0.4971436629192747</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -16769,7 +16772,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -16821,49 +16824,49 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143548155105979</v>
+        <v>1.2143575341745789</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920112062709331</v>
+        <v>1.3920140239783747</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756201329538629</v>
+        <v>1.3756227654883972</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871171730884966</v>
+        <v>1.3871192157451198</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848592149304412</v>
+        <v>2.9848634450505576</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067770901272091</v>
+        <v>1.3067777906572411</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.435157618834449</v>
+        <v>1.4351584786533005</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994821618927388</v>
+        <v>1.2994828076813543</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941589155819454</v>
+        <v>1.3941599528507855</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917517212105108</v>
+        <v>1.8917531715635298</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -16935,48 +16938,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688940854644052E-2</v>
+        <v>9.7688881254799131E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780132319646975E-2</v>
+        <v>9.0780008977618121E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.732789441568368E-2</v>
+        <v>9.7327776282401982E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716269429241346E-2</v>
+        <v>9.8716149119680324E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1058849023581222</v>
+        <v>0.10588481040794941</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608264147450108</v>
+        <v>0.10608256873295575</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005797023643055</v>
+        <v>0.18005791200401186</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212696489309216</v>
+        <v>0.18212689753541933</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1910225031427337</v>
+        <v>0.19102244586003594</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680487359274656</v>
+        <v>0.2168047709493561</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475597690645882</v>
+        <v>0.28475584678306809</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -17100,50 +17103,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.2003593743875291</v>
+        <v>0.20035925214863964</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.1911415616576877</v>
+        <v>0.19114130195562065</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122275259899003</v>
+        <v>0.2012225083616698</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032527360835512</v>
+        <v>0.21032501727632916</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338046647171481</v>
+        <v>0.19338029854062252</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371116289911001</v>
+        <v>0.1371115349727797</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766128409926953</v>
+        <v>0.25766120076921883</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404529613482509</v>
+        <v>0.27404519478215933</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820711868616131</v>
+        <v>0.25820704125653865</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.2677468087344656</v>
+        <v>0.26774668197329193</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861275857974309</v>
+        <v>0.16861268152968742</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -17221,50 +17224,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91372658342388124</v>
+        <v>0.91173591296761336</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.3022926519493305</v>
+        <v>1.2994539950576844</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3080339224063582</v>
+        <v>1.3051830311059387</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.366062230696488</v>
+        <v>1.3630850159154255</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0932667410053585</v>
+        <v>1.0908845416658441</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70865972357618179</v>
+        <v>0.7071156119378228</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5555271371313966</v>
+        <v>1.5521391382057574</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.49853522911864</v>
+        <v>1.4952712665404526</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2921551163558302</v>
+        <v>1.2893408024233339</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4275743673379471</v>
+        <v>1.4244647583507173</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.893151862671971</v>
+        <v>0.89120633748320666</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -17278,50 +17281,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11774827105977852</v>
+        <v>0.11810050686108982</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.16782121803470754</v>
+        <v>0.16832305635462233</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16856107247504618</v>
+        <v>0.16906515946968118</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17603894725470207</v>
+        <v>0.17656541656935565</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14088488930481424</v>
+        <v>0.14130628778054977</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.1322129326827553E-2</v>
+        <v>9.1595286520443367E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20045452798085009</v>
+        <v>0.20105429251369916</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19311020993796907</v>
+        <v>0.19368798789384101</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.16651483458193689</v>
+        <v>0.16701305730872201</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18396576898684885</v>
+        <v>0.18451616040812402</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1150968895195839</v>
+        <v>0.11544123542528584</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17330,48 +17333,48 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1414894239750826</v>
+        <v>0.14222252979878772</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13773899430834011</v>
+        <v>0.13845266785397919</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12208243871543101</v>
+        <v>0.12271499021136589</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.39196454814681292</v>
+        <v>0.39399545254135604</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14483802189181696</v>
+        <v>0.14558847796379532</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14244191404917594</v>
+        <v>0.14317995505461209</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12223126528950809</v>
+        <v>0.12286458790758846</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1183022437338731</v>
+        <v>0.11891520872731287</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0809392389916067E-2</v>
+        <v>5.1072653490381953E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4527765185883207E-2</v>
+        <v>3.4706665523633898E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18121,7 +18124,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3316978747062</v>
+        <v>7230.3235535558979</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -18153,7 +18156,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.422638329415</v>
+        <v>96404.314047411972</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18187,7 +18190,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17130.223463801474</v>
+        <v>17131.309372975855</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18219,7 +18222,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89414.046102130887</v>
+        <v>89415.023420387821</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -18233,7 +18236,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0942481800000001</v>
+        <v>1.09186545</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -18247,7 +18250,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -18290,7 +18293,7 @@
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18300,7 +18303,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.94972380496737</v>
+        <v>13.015281616353727</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -18335,7 +18338,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7398084912256</v>
+        <v>7373.7315026360702</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -18347,7 +18350,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.292845108117</v>
+        <v>6859.2851187312281</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18357,7 +18360,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9923095243903</v>
+        <v>7519.9838389289371</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -18369,7 +18372,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2945890962819</v>
+        <v>6507.287259213791</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18379,7 +18382,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1456172871094</v>
+        <v>7669.1369786838613</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -18391,7 +18394,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3598237435081</v>
+        <v>6173.3528700085171</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -18411,7 +18414,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2572670667996</v>
+        <v>7821.248457123449</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -18423,7 +18426,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5615850969416</v>
+        <v>5856.5549882066935</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -18443,7 +18446,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3859353193875</v>
+        <v>7976.3769506375347</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -18455,7 +18458,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0204782027749</v>
+        <v>5556.0142198450712</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -18475,7 +18478,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5914623035187</v>
+        <v>8134.5822994173595</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -18487,7 +18490,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.9022360084382</v>
+        <v>5270.8962988108096</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18497,7 +18500,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9348751636953</v>
+        <v>8295.9255305386832</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -18509,7 +18512,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4154035345864</v>
+        <v>5000.4097710160631</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18519,7 +18522,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4784114712511</v>
+        <v>8460.4688815027348</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -18531,7 +18534,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8091408884038</v>
+        <v>4743.8037974137724</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18541,7 +18544,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2855432322449</v>
+        <v>8628.2758242440741</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -18553,7 +18556,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3711390196559</v>
+        <v>4500.3660697560526</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18563,7 +18566,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4210013715274</v>
+        <v>8799.4110896146449</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -18575,7 +18578,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4256424338573</v>
+        <v>4269.4208333095985</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18585,7 +18588,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9508007024397</v>
+        <v>8973.9406923534261</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -18597,7 +18600,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3315733738496</v>
+        <v>4050.3270110393692</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18607,7 +18610,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9422653917609</v>
+        <v>9151.9319565513597</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -18619,7 +18622,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.480752262742</v>
+        <v>3842.4764240535301</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18629,7 +18632,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4640549297274</v>
+        <v>9333.4535416213457</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -18641,7 +18644,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2962094683439</v>
+        <v>3645.2921033697971</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -18661,7 +18664,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5861906151658</v>
+        <v>9518.575468783336</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -18673,7 +18676,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2305837027798</v>
+        <v>3458.2266883168472</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -18693,7 +18696,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3800825659109</v>
+        <v>9707.3691480747311</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -18705,7 +18708,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.764602611403</v>
+        <v>3280.7609071249481</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -18725,7 +18728,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9185572649931</v>
+        <v>9899.9074058965252</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -18737,7 +18740,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4056413333228</v>
+        <v>3112.4021354881052</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -18747,7 +18750,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.275885653136</v>
+        <v>10096.264513105787</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -18759,7 +18762,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6863550322491</v>
+        <v>2952.6830290964526</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18769,7 +18772,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.527811778495</v>
+        <v>10296.516213665349</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -18781,7 +18784,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1633816017556</v>
+        <v>2801.16022634297</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18791,7 +18794,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.751582014602</v>
+        <v>10500.739753861733</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -18803,7 +18806,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.416110943785</v>
+        <v>2657.4131176033798</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18813,7 +18816,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.02597485785</v>
+        <v>10709.013912102597</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -18825,7 +18828,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0455174040922</v>
+        <v>2521.0426776729037</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -18835,19 +18838,19 @@
       </c>
       <c r="C41" s="123">
         <f t="shared" si="2"/>
-        <v>10921.43133131598</v>
+        <v>0</v>
       </c>
       <c r="D41" s="138">
         <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="124">
         <f t="shared" si="0"/>
-        <v>0.21898897494009908</v>
+        <v>0</v>
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>2391.6730521235681</v>
+        <v>0</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -18857,19 +18860,19 @@
       </c>
       <c r="C42" s="123">
         <f t="shared" si="2"/>
-        <v>11138.049585899302</v>
+        <v>0</v>
       </c>
       <c r="D42" s="138">
         <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="124">
         <f t="shared" si="0"/>
-        <v>0.20371067436288287</v>
+        <v>0</v>
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>2268.9395922307749</v>
+        <v>0</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -18879,19 +18882,19 @@
       </c>
       <c r="C43" s="123">
         <f t="shared" si="2"/>
-        <v>11358.964298226601</v>
+        <v>0</v>
       </c>
       <c r="D43" s="138">
         <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="124">
         <f t="shared" si="0"/>
-        <v>0.18949830173291429</v>
+        <v>0</v>
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>2152.5044439587455</v>
+        <v>0</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -18901,19 +18904,19 @@
       </c>
       <c r="C44" s="123">
         <f t="shared" si="2"/>
-        <v>11584.260685257917</v>
+        <v>0</v>
       </c>
       <c r="D44" s="138">
         <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="124">
         <f t="shared" si="0"/>
-        <v>0.17627748998410636</v>
+        <v>0</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>2042.0443969188295</v>
+        <v>0</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -18923,19 +18926,19 @@
       </c>
       <c r="C45" s="123">
         <f t="shared" si="2"/>
-        <v>11814.025654166657</v>
+        <v>0</v>
       </c>
       <c r="D45" s="138">
         <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="124">
         <f t="shared" si="0"/>
-        <v>0.16397906045033148</v>
+        <v>0</v>
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>1937.2528269063612</v>
+        <v>0</v>
       </c>
       <c r="H45" s="120"/>
     </row>
@@ -18945,19 +18948,19 @@
       </c>
       <c r="C46" s="123">
         <f t="shared" si="2"/>
-        <v>12048.34783586368</v>
+        <v>0</v>
       </c>
       <c r="D46" s="138">
         <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="124">
         <f t="shared" si="0"/>
-        <v>0.15253866088402931</v>
+        <v>0</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>1837.8388447476384</v>
+        <v>0</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18967,19 +18970,19 @@
       </c>
       <c r="C47" s="341">
         <f t="shared" si="2"/>
-        <v>12287.317619186306</v>
+        <v>0</v>
       </c>
       <c r="D47" s="138">
         <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E47" s="124">
         <f t="shared" si="0"/>
-        <v>0.14189642872932959</v>
+        <v>0</v>
       </c>
       <c r="F47" s="125">
         <f t="shared" si="1"/>
-        <v>1743.5264888255053</v>
+        <v>0</v>
       </c>
       <c r="G47" s="338"/>
       <c r="H47" s="339"/>
@@ -18999,19 +19002,19 @@
       </c>
       <c r="C48" s="341">
         <f t="shared" si="2"/>
-        <v>12531.027185765464</v>
+        <v>0</v>
       </c>
       <c r="D48" s="138">
         <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="124">
         <f t="shared" si="0"/>
-        <v>0.13199667788774846</v>
+        <v>0</v>
       </c>
       <c r="F48" s="125">
         <f t="shared" si="1"/>
-        <v>1654.0539590421031</v>
+        <v>0</v>
       </c>
       <c r="G48" s="338"/>
       <c r="H48" s="339"/>
@@ -19031,19 +19034,19 @@
       </c>
       <c r="C49" s="341">
         <f t="shared" si="2"/>
-        <v>12779.570545584364</v>
+        <v>0</v>
       </c>
       <c r="D49" s="138">
         <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="124">
         <f t="shared" si="0"/>
-        <v>0.1227876073374404</v>
+        <v>0</v>
       </c>
       <c r="F49" s="125">
         <f t="shared" si="1"/>
-        <v>1569.172890092332</v>
+        <v>0</v>
       </c>
       <c r="G49" s="338"/>
       <c r="H49" s="339"/>
@@ -19063,19 +19066,19 @@
       </c>
       <c r="C50" s="341">
         <f t="shared" si="2"/>
-        <v>13033.043573242485</v>
+        <v>0</v>
       </c>
       <c r="D50" s="138">
         <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="124">
         <f t="shared" si="0"/>
-        <v>0.11422103008133992</v>
+        <v>0</v>
       </c>
       <c r="F50" s="125">
         <f t="shared" si="1"/>
-        <v>1488.6476620307437</v>
+        <v>0</v>
       </c>
       <c r="G50" s="338"/>
       <c r="H50" s="339"/>
@@ -19095,7 +19098,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.530779883018</v>
+        <v>98316.420035147603</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -19103,11 +19106,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.11422103008133992</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>11229.815419702001</v>
+        <v>23144.977946522984</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19118,7 +19121,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>117374.74318744551</v>
+        <v>110204.15349294289</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19139,7 +19142,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>117374.74318744551</v>
+        <v>110204.15349294289</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -19169,19 +19172,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.422638329415</v>
+        <v>96404.314047411972</v>
       </c>
       <c r="C56" s="123">
-        <v>97922.046851661347</v>
+        <v>97921.936551276638</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.455402016611</v>
+        <v>99461.343367626512</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.12641905581</v>
+        <v>101023.01262558368</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.54549631022</v>
+        <v>102607.4299181324</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19190,19 +19193,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.422638329444</v>
+        <v>96404.314047411986</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.11724239515</v>
+        <v>99377.005303004422</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.89565749126</v>
+        <v>102492.78020845618</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.14701514522</v>
+        <v>105760.02788584513</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.7232108708</v>
+        <v>109187.60022071422</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -19211,19 +19214,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.42263832943</v>
+        <v>96404.314047412001</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.6071212228</v>
+        <v>101173.49315824767</v>
       </c>
       <c r="D58" s="123">
-        <v>106331.05402197571</v>
+        <v>106330.93424960022</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.76574935953</v>
+        <v>111913.63968856103</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.27477615344</v>
+        <v>117962.14190225315</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -19242,19 +19245,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.422638329444</v>
+        <v>96404.314047412015</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.15617938049</v>
+        <v>102998.04016121484</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.39673473871</v>
+        <v>110332.27245521027</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.73870812866</v>
+        <v>118504.60522319149</v>
       </c>
       <c r="F59" s="123">
-        <v>127626.07252387045</v>
+        <v>127625.92876457056</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -19273,19 +19276,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.422638329444</v>
+        <v>96404.314047412001</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.68723389968</v>
+        <v>104688.56931150272</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.75149397142</v>
+        <v>114140.62292467365</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.7212583268</v>
+        <v>124956.58050581119</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.52537556741</v>
+        <v>137367.37064339643</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -19304,19 +19307,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.422638329444</v>
+        <v>96404.314047412001</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.44503273178</v>
+        <v>106173.32543788859</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.84332652387</v>
+        <v>117578.71088452468</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.65392621746</v>
+        <v>130953.5064186962</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.94671063861</v>
+        <v>146703.78146182816</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -19396,23 +19399,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -19423,23 +19426,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.491407021727264</v>
+        <v>11.466507457959517</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.685948375289657</v>
+        <v>11.660624978252651</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.883303127804091</v>
+        <v>11.857549768147676</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.083532645710834</v>
+        <v>12.057343060390197</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -19450,23 +19453,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.299618643916505</v>
+        <v>11.275136915707542</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.675290217176963</v>
+        <v>11.649990040303253</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.069043876745374</v>
+        <v>12.04288585706467</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.481939791478265</v>
+        <v>12.454882225134602</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.915096611609483</v>
+        <v>12.88709535762402</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -19477,23 +19480,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.299618643916501</v>
+        <v>11.275136915707543</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.902319989492842</v>
+        <v>11.87652519916622</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.554087644523142</v>
+        <v>12.526872894835861</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.259597754716602</v>
+        <v>13.230845960842974</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.023972574406468</v>
+        <v>13.99355549203333</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -19504,23 +19507,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.299618643916505</v>
+        <v>11.275136915707545</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.132895715042158</v>
+        <v>12.106598585949095</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.059753685697389</v>
+        <v>13.031437277738185</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.09252595977053</v>
+        <v>14.061959525062246</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.245226213643571</v>
+        <v>15.212148473713411</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -19531,23 +19534,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.299618643916505</v>
+        <v>11.275136915707543</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.346535037436157</v>
+        <v>12.319772467701323</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.541031050004568</v>
+        <v>13.511666117631412</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.907889378524326</v>
+        <v>14.875546570119269</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.476293445923144</v>
+        <v>16.440533668265907</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -19557,23 +19560,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.299618643916505</v>
+        <v>11.275136915707543</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.534169952047</v>
+        <v>12.50699859560523</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.975516774162854</v>
+        <v>13.945205258960172</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.665746282830041</v>
+        <v>15.631752386039407</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.65617518916433</v>
+        <v>17.617844887927319</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -19604,11 +19607,11 @@
       </c>
       <c r="D74" s="145">
         <f>Scenarios!C55</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>15.245226213643571</v>
+        <v>12.88709535762402</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -19626,11 +19629,11 @@
       </c>
       <c r="D75" s="145">
         <f>Scenarios!C37</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>15.665746282830041</v>
+        <v>14.061959525062246</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -19649,11 +19652,11 @@
       </c>
       <c r="D76" s="145">
         <f>Scenarios!C25</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.975516774162854</v>
+        <v>13.031437277738185</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -19672,11 +19675,11 @@
       </c>
       <c r="D77" s="145">
         <f>Scenarios!C31</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.534169952047</v>
+        <v>12.106598585949095</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -19695,11 +19698,11 @@
       </c>
       <c r="D78" s="145">
         <f>Scenarios!C49</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.299618643916505</v>
+        <v>11.275136915707542</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -19715,7 +19718,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>102</v>
@@ -19852,7 +19855,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -19864,7 +19867,7 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -19877,11 +19880,11 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2992.1664755453339</v>
+        <v>2985.6510204990423</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -19909,11 +19912,11 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39895.553007271119</v>
+        <v>39808.680273320562</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -19925,11 +19928,11 @@
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0417641771338682</v>
+        <v>5.0198311575118559</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -19972,7 +19975,7 @@
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="120"/>
     </row>
@@ -19982,7 +19985,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.6097614319855342</v>
+        <v>5.2555900317547986</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -19998,7 +20001,7 @@
         <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D15" s="128" t="s">
         <v>114</v>
@@ -20007,7 +20010,7 @@
         <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -20017,7 +20020,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3051.5138137918184</v>
+        <v>3044.8691296676584</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -20029,7 +20032,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2838.6175012016915</v>
+        <v>2832.4363996908451</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -20039,7 +20042,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3112.0382611950718</v>
+        <v>3105.2617848329196</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -20051,7 +20054,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2692.948197897304</v>
+        <v>2687.0842919051765</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -20061,7 +20064,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3173.7631648167812</v>
+        <v>3166.8522822181876</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -20073,7 +20076,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2554.7542046395165</v>
+        <v>2549.1912166471384</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -20083,7 +20086,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3236.7123347897805</v>
+        <v>3229.6643801096325</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -20095,7 +20098,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2423.6519110243148</v>
+        <v>2418.3743988259803</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -20105,7 +20108,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3300.9100535027169</v>
+        <v>3293.7223080208983</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -20117,7 +20120,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2299.2773923786012</v>
+        <v>2294.2707062161048</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -20127,7 +20130,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3366.3810849668812</v>
+        <v>3359.0507760395371</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -20139,7 +20142,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2181.2853995477499</v>
+        <v>2176.535641444369</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -20149,7 +20152,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3433.150684368828</v>
+        <v>3425.6749843588295</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -20161,7 +20164,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2069.3484005242326</v>
+        <v>2064.8423857055641</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -20171,7 +20174,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3501.2446078124599</v>
+        <v>3493.620632998653</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -20183,7 +20186,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1963.1556712569738</v>
+        <v>1958.8808915515376</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -20193,7 +20196,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3570.6891222543422</v>
+        <v>3562.9139317191662</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -20205,7 +20208,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1862.4124331176338</v>
+        <v>1858.3570222356502</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -20215,7 +20218,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3641.5110156360765</v>
+        <v>3633.5816101311138</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -20227,7 +20230,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1766.8390346295234</v>
+        <v>1762.9917352234752</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -20237,7 +20240,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3713.7376072176376</v>
+        <v>3705.6509280066684</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -20249,7 +20252,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1676.1701751877267</v>
+        <v>1672.5203076032767</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -20259,7 +20262,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3787.3967581156721</v>
+        <v>3779.1496857947791</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -20271,7 +20274,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1590.1541686155751</v>
+        <v>1586.6916012460908</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -20281,7 +20284,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3862.5168820508097</v>
+        <v>3854.1062353450779</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -20293,7 +20296,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1508.5522445131774</v>
+        <v>1505.2673656755728</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -20303,7 +20306,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3939.1269563081414</v>
+        <v>3930.5494908444975</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -20315,7 +20318,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1431.1378854586462</v>
+        <v>1428.0215767124719</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -20325,7 +20328,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4017.2565329150902</v>
+        <v>4008.5089399707967</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -20337,7 +20340,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1357.6961982221585</v>
+        <v>1354.7398090578736</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -20347,7 +20350,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4096.9357500409888</v>
+        <v>4088.0146552673186</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -20359,7 +20362,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1288.0233172474193</v>
+        <v>1285.2186410735872</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -20369,7 +20372,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4178.1953436227532</v>
+        <v>4169.0973057433466</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -20381,7 +20384,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1221.9258387446589</v>
+        <v>1219.2650901074051</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -20391,7 +20394,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4261.0666592211519</v>
+        <v>4251.7881687045601</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -20403,7 +20406,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1159.2202838242758</v>
+        <v>1156.696076795778</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -20413,7 +20416,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4345.5816641122228</v>
+        <v>4336.1191418181206</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -20425,7 +20428,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1099.7325891808405</v>
+        <v>1097.3379168568536</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -20435,7 +20438,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4431.7729596185291</v>
+        <v>4422.1227554170719</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -20447,7 +20450,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1043.2976239136692</v>
+        <v>1041.0258389631765</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -20457,19 +20460,19 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>4519.6737936849786</v>
+        <v>0</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="124">
         <f t="shared" si="0"/>
-        <v>0.21898897494009908</v>
+        <v>0</v>
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>989.75873114270235</v>
+        <v>0</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -20479,19 +20482,19 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>4609.318073704093</v>
+        <v>0</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="124">
         <f t="shared" si="0"/>
-        <v>0.20371067436288287</v>
+        <v>0</v>
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>938.96729314728498</v>
+        <v>0</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -20501,19 +20504,19 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>4700.7403795956452</v>
+        <v>0</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="124">
         <f t="shared" si="0"/>
-        <v>0.18949830173291429</v>
+        <v>0</v>
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>890.78231882070963</v>
+        <v>0</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -20523,19 +20526,19 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>4793.9759771457193</v>
+        <v>0</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="124">
         <f t="shared" si="0"/>
-        <v>0.17627748998410636</v>
+        <v>0</v>
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>845.07005229535105</v>
+        <v>0</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -20545,19 +20548,19 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>4889.0608316103535</v>
+        <v>0</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="124">
         <f t="shared" si="0"/>
-        <v>0.16397906045033148</v>
+        <v>0</v>
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>801.70360165198201</v>
+        <v>0</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -20567,19 +20570,19 @@
       </c>
       <c r="C41" s="123">
         <f t="shared" si="2"/>
-        <v>4986.0316215889879</v>
+        <v>0</v>
       </c>
       <c r="D41" s="138">
         <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="124">
         <f t="shared" si="0"/>
-        <v>0.15253866088402931</v>
+        <v>0</v>
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>760.56258668260944</v>
+        <v>0</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -20589,19 +20592,19 @@
       </c>
       <c r="C42" s="123">
         <f t="shared" si="2"/>
-        <v>5084.9257531730855</v>
+        <v>0</v>
       </c>
       <c r="D42" s="138">
         <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="124">
         <f t="shared" si="0"/>
-        <v>0.14189642872932959</v>
+        <v>0</v>
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>721.53280472905726</v>
+        <v>0</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -20611,19 +20614,19 @@
       </c>
       <c r="C43" s="123">
         <f t="shared" si="2"/>
-        <v>5185.7813743753868</v>
+        <v>0</v>
       </c>
       <c r="D43" s="138">
         <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="124">
         <f t="shared" si="0"/>
-        <v>0.13199667788774846</v>
+        <v>0</v>
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>684.50591366971344</v>
+        <v>0</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -20633,19 +20636,19 @@
       </c>
       <c r="C44" s="123">
         <f t="shared" si="2"/>
-        <v>5288.6373898453421</v>
+        <v>0</v>
       </c>
       <c r="D44" s="138">
         <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="124">
         <f t="shared" si="0"/>
-        <v>0.1227876073374404</v>
+        <v>0</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>649.37913117443554</v>
+        <v>0</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -20655,19 +20658,19 @@
       </c>
       <c r="C45" s="123">
         <f t="shared" si="2"/>
-        <v>5393.5334758764357</v>
+        <v>0</v>
       </c>
       <c r="D45" s="138">
         <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="124">
         <f t="shared" si="0"/>
-        <v>0.11422103008133992</v>
+        <v>0</v>
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>616.05494939279617</v>
+        <v>0</v>
       </c>
       <c r="H45" s="120"/>
     </row>
@@ -20677,7 +20680,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40686.850850557581</v>
+        <v>40598.255062235447</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -20685,11 +20688,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.11422103008133992</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>4647.2940149165279</v>
+        <v>9557.3630299683027</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -20700,7 +20703,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>48573.811868748868</v>
+        <v>45507.111943506228</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -20721,7 +20724,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>48573.811868748868</v>
+        <v>45507.111943506228</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -20751,19 +20754,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39895.553007271126</v>
+        <v>39808.68027332057</v>
       </c>
       <c r="C51" s="123">
-        <v>40523.599476417541</v>
+        <v>40435.359168647097</v>
       </c>
       <c r="D51" s="123">
-        <v>41160.661073175928</v>
+        <v>41071.033561107426</v>
       </c>
       <c r="E51" s="123">
-        <v>41806.935664477052</v>
+        <v>41715.900886776239</v>
       </c>
       <c r="F51" s="123">
-        <v>42462.624206064793</v>
+        <v>42370.161663815445</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -20772,19 +20775,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39895.553007271126</v>
+        <v>39808.68027332057</v>
       </c>
       <c r="C52" s="123">
-        <v>41125.758965724526</v>
+        <v>41036.207453141338</v>
       </c>
       <c r="D52" s="123">
-        <v>42415.178055808421</v>
+        <v>42322.818827750198</v>
       </c>
       <c r="E52" s="123">
-        <v>43767.281996271602</v>
+        <v>43671.978556213806</v>
       </c>
       <c r="F52" s="123">
-        <v>45185.734013935173</v>
+        <v>45087.341888661518</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -20793,19 +20796,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39895.553007271126</v>
+        <v>39808.680273320577</v>
       </c>
       <c r="C53" s="123">
-        <v>41869.209890758109</v>
+        <v>41778.039510668459</v>
       </c>
       <c r="D53" s="123">
-        <v>44003.543467788077</v>
+        <v>43907.725567385438</v>
       </c>
       <c r="E53" s="123">
-        <v>46313.866641235538</v>
+        <v>46213.01800243582</v>
       </c>
       <c r="F53" s="123">
-        <v>48816.95317906695</v>
+        <v>48710.654058835964</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -20814,19 +20817,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39895.553007271134</v>
+        <v>39808.680273320577</v>
       </c>
       <c r="C54" s="123">
-        <v>42624.272694641913</v>
+        <v>42531.458162130926</v>
       </c>
       <c r="D54" s="123">
-        <v>45659.44032322782</v>
+        <v>45560.016700479493</v>
       </c>
       <c r="E54" s="123">
-        <v>49041.443902213992</v>
+        <v>48934.655952492089</v>
       </c>
       <c r="F54" s="123">
-        <v>52816.173803435944</v>
+        <v>52701.16636352714</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -20835,19 +20838,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39895.553007271134</v>
+        <v>39808.680273320577</v>
       </c>
       <c r="C55" s="123">
-        <v>43323.874118002263</v>
+        <v>43229.536200458562</v>
       </c>
       <c r="D55" s="123">
-        <v>47235.471951335443</v>
+        <v>47132.616513108806</v>
       </c>
       <c r="E55" s="123">
-        <v>51711.502025990121</v>
+        <v>51598.900013508457</v>
       </c>
       <c r="F55" s="123">
-        <v>56847.530850930874</v>
+        <v>56723.745114148151</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -20856,19 +20859,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39895.553007271141</v>
+        <v>39808.680273320584</v>
       </c>
       <c r="C56" s="123">
-        <v>43938.319304697608</v>
+        <v>43842.643430183583</v>
       </c>
       <c r="D56" s="123">
-        <v>48658.275710702888</v>
+        <v>48552.322111324589</v>
       </c>
       <c r="E56" s="123">
-        <v>54193.244445945704</v>
+        <v>54075.238428938937</v>
       </c>
       <c r="F56" s="123">
-        <v>60711.271559891429</v>
+        <v>60579.072511514743</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -20918,23 +20921,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0417641771338682</v>
+        <v>5.0198311575118559</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0417641771338682</v>
+        <v>5.0198311575118559</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0417641771338682</v>
+        <v>5.0198311575118559</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0417641771338682</v>
+        <v>5.0198311575118559</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0417641771338682</v>
+        <v>5.0198311575118559</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -20945,23 +20948,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.041764177133869</v>
+        <v>5.0198311575118568</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1211329776901797</v>
+        <v>5.0988546826052907</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2016410567880866</v>
+        <v>5.1790125300746359</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2833134196807627</v>
+        <v>5.2603295963935404</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3661754619673241</v>
+        <v>5.342831166683486</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -20972,23 +20975,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.041764177133869</v>
+        <v>5.0198311575118568</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1972303347453854</v>
+        <v>5.174620995849871</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3601794979394057</v>
+        <v>5.3368612866991798</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5310504020110045</v>
+        <v>5.5069888567392447</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.7103059839134804</v>
+        <v>5.6854646290240769</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -20999,23 +21002,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.041764177133869</v>
+        <v>5.0198311575118586</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2911832683118956</v>
+        <v>5.2681652090829703</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5609077303029979</v>
+        <v>5.5367162976854027</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8528727172619881</v>
+        <v>5.8274111590369833</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1691979988392207</v>
+        <v>6.1423603412243954</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -21026,23 +21029,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.041764177133869</v>
+        <v>5.0198311575118586</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3866036424927923</v>
+        <v>5.3631704791721804</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7701701873308053</v>
+        <v>5.7450684071811011</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1975678095260252</v>
+        <v>6.1706067356639087</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6745958630253304</v>
+        <v>6.6455595898301896</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -21053,23 +21056,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.041764177133869</v>
+        <v>5.0198311575118586</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.475015135220497</v>
+        <v>5.4511973583129167</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9693397489903415</v>
+        <v>5.9433715280967814</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5349939732106419</v>
+        <v>6.5065650054905282</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1840549384163088</v>
+        <v>7.1528023822883311</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -21079,23 +21082,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0417641771338708</v>
+        <v>5.0198311575118595</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5526650860941773</v>
+        <v>5.5285095111785338</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1491452782873735</v>
+        <v>6.1223948553582437</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8486219113300892</v>
+        <v>6.8188285783840135</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6723316516785811</v>
+        <v>7.6389549615457808</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -21126,11 +21129,11 @@
       </c>
       <c r="D69" s="145">
         <f>Scenarios!C55</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>6.6745958630253304</v>
+        <v>5.6854646290240769</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -21148,11 +21151,11 @@
       </c>
       <c r="D70" s="145">
         <f>Scenarios!C37</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.8486219113300892</v>
+        <v>6.1706067356639087</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -21171,11 +21174,11 @@
       </c>
       <c r="D71" s="145">
         <f>Scenarios!C25</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>6.1491452782873735</v>
+        <v>5.7450684071811011</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -21194,11 +21197,11 @@
       </c>
       <c r="D72" s="145">
         <f>Scenarios!C31</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.5526650860941773</v>
+        <v>5.3631704791721804</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -21217,11 +21220,11 @@
       </c>
       <c r="D73" s="145">
         <f>Scenarios!C49</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.041764177133869</v>
+        <v>5.0198311575118568</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -21237,7 +21240,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>102</v>
@@ -21308,7 +21311,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
@@ -21321,7 +21324,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.76</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21341,7 +21344,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -21350,7 +21353,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -21370,7 +21373,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>14.295569798447813</v>
+        <v>13.300239312737236</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -21387,7 +21390,7 @@
       </c>
       <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 20-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 昆仑能源(0135.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 昆仑能源(0135.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="377"/>
       <c r="H7" s="247">
@@ -21404,7 +21407,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060629860687</v>
+        <v>10305.03755922756</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -21426,7 +21429,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3316978747062</v>
+        <v>7230.3235535558979</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -21455,7 +21458,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E11" s="377"/>
       <c r="F11" s="377"/>
@@ -21510,7 +21513,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052768460979511E-2</v>
+        <v>6.0052497730721521E-2</v>
       </c>
       <c r="E14" s="377"/>
       <c r="F14" s="377"/>
@@ -21529,7 +21532,7 @@
         <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -21537,10 +21540,10 @@
         <v>129</v>
       </c>
       <c r="C18" s="150">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E18" s="377" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F18" s="378"/>
     </row>
@@ -21550,7 +21553,7 @@
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E20" s="378"/>
       <c r="F20" s="378"/>
@@ -21561,7 +21564,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.76</v>
+        <v>7.72</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -21576,7 +21579,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.299618643916499</v>
+        <v>11.275136915707538</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -21600,7 +21603,7 @@
       </c>
       <c r="C25" s="166">
         <f>C18</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D25" s="163"/>
       <c r="E25" s="376"/>
@@ -21623,7 +21626,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.975516774162854</v>
+        <v>13.031437277738185</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -21658,7 +21661,7 @@
       </c>
       <c r="C31" s="166">
         <f>C18</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D31" s="163"/>
       <c r="E31" s="376"/>
@@ -21681,7 +21684,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.534169952047</v>
+        <v>12.106598585949095</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -21716,7 +21719,7 @@
       </c>
       <c r="C37" s="166">
         <f>C18</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D37" s="163"/>
       <c r="E37" s="376"/>
@@ -21739,7 +21742,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>15.665746282830041</v>
+        <v>14.061959525062246</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -21766,7 +21769,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>14.025293311473122</v>
+        <v>13.052573988845179</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -21792,7 +21795,7 @@
         <v>129</v>
       </c>
       <c r="C46" s="150">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
@@ -21817,7 +21820,7 @@
       </c>
       <c r="C49" s="166">
         <f>C46</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D49" s="163"/>
       <c r="E49" s="376"/>
@@ -21840,7 +21843,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.299618643916505</v>
+        <v>11.275136915707542</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -21862,7 +21865,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
         <v>145</v>
@@ -21875,7 +21878,7 @@
       </c>
       <c r="C55" s="166">
         <f>C46</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D55" s="163"/>
       <c r="E55" s="376"/>
@@ -21898,7 +21901,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>15.245226213643571</v>
+        <v>12.88709535762402</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -21924,14 +21927,14 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>13.950006223203813</v>
+        <v>12.955428203627237</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -21940,7 +21943,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -21949,10 +21952,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -21961,11 +21964,11 @@
       </c>
       <c r="C64" s="166">
         <f>C18</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -21977,7 +21980,7 @@
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -21986,27 +21989,27 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.94972380496737</v>
+        <v>13.015281616353727</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -22016,19 +22019,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -22038,18 +22041,18 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.3326313570563578E-2</v>
+        <v>-6.8028776047238768E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -22068,7 +22071,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -22078,11 +22081,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.345563575244</v>
+        <v>0.34481110910999996</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -22091,12 +22094,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -22109,7 +22112,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58603424994384601</v>
+        <v>0.58475815790742269</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -22121,7 +22124,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.6698699276345312</v>
+        <v>5.2656315413817953</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -22131,7 +22134,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>6.255904177578377</v>
+        <v>5.8503896992892184</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -22142,7 +22145,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.55154828768659714</v>
+        <v>0.5484217420423636</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -22150,16 +22153,16 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.76</v>
+        <v>7.72</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22168,11 +22171,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.25315453740124205</v>
+        <v>0.2264478139311954</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22180,12 +22183,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -22198,7 +22201,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67454009887628796</v>
+        <v>0.67307128498271995</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -22210,7 +22213,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>7.1424031862803519</v>
+        <v>6.6331792402571459</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -22220,7 +22223,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.8169432851566398</v>
+        <v>7.3062505252398662</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -22231,19 +22234,19 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43964589261943932</v>
+        <v>0.43604716027878754</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -22258,7 +22261,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89864697218420275</v>
+        <v>0.89669016463435369</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -22270,7 +22273,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>11.229204954092648</v>
+        <v>10.428608865032555</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -22278,21 +22281,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>12.12785192627685</v>
+        <v>11.325299029666908</v>
       </c>
       <c r="D99" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E99" s="146" t="s">
         <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.13062032143728175</v>
+        <v>0.12582595868995883</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -22300,12 +22303,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -22318,7 +22321,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83370776184420992</v>
+        <v>0.83189235969715858</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -22328,27 +22331,27 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.9988119431025062</v>
+        <v>9.2859378109069173</v>
       </c>
       <c r="D104" s="116"/>
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.832519704946716</v>
+        <v>10.117830170604076</v>
       </c>
       <c r="D105" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E105" s="146" t="s">
         <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22345991530747344</v>
+        <v>0.22261918959240934</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -22356,32 +22359,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
+        <v>317</v>
+      </c>
+      <c r="F108" s="283" t="s">
         <v>318</v>
-      </c>
-      <c r="F108" s="283" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -22402,7 +22405,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
-  <dimension ref="B2:E2"/>
+  <dimension ref="B2:E4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -22412,11 +22415,16 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" t="s">
+        <v>558</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080A1A3A-A494-4054-8799-3E3BEBFAD6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5B061-315E-444E-ACCE-3DAF98270B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4737,6 +4737,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4746,16 +4755,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.72</v>
+        <v>7.54</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>66845.949185759993</v>
+        <v>65287.364878319997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.09186545</v>
+        <v>1.0887533899999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5240,13 +5240,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="368" t="s">
         <v>491</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="368"/>
+      <c r="D18" s="368"/>
+      <c r="E18" s="368"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.955428203627237</v>
+        <v>12.918660381570513</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2264478139311954</v>
+        <v>0.2352638333289685</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8503896992892184</v>
+        <v>5.8337790170666892</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3062505252398662</v>
+        <v>7.2855069971011268</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.325299029666908</v>
+        <v>11.293146615768574</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.117830170604076</v>
+        <v>10.089105373293357</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5459,22 +5459,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="368" t="s">
         <v>494</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="368"/>
+      <c r="D36" s="368"/>
+      <c r="E36" s="368"/>
+      <c r="F36" s="368"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="369" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.60690627024144</v>
+        <v>279.59272331831147</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.39309372975856</v>
+        <v>-523.40727668168847</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7285411561006</v>
+        <v>-4449.7249954181179</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5664,10 +5664,10 @@
       <c r="B61" s="367" t="s">
         <v>501</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="370"/>
+      <c r="D61" s="370"/>
+      <c r="E61" s="370"/>
+      <c r="F61" s="370"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5683,22 +5683,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="368" t="s">
         <v>502</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="368"/>
+      <c r="D64" s="368"/>
+      <c r="E64" s="368"/>
+      <c r="F64" s="368"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="368" t="s">
         <v>503</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="368"/>
+      <c r="D65" s="368"/>
+      <c r="E65" s="368"/>
+      <c r="F65" s="368"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.03755922756</v>
+        <v>10305.007426902648</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3235535558979</v>
+        <v>7230.3129163419508</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11810050686108982</v>
+        <v>0.12057505633899694</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5742,14 +5742,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4664651439119164E-2</v>
+        <v>4.5600573018832885E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>505</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41293463541208869</v>
+        <v>0.41175828540035703</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5769,11 +5769,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035925214863964</v>
+        <v>0.20035909249363959</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114130195562065</v>
+        <v>0.19114096276132886</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5783,11 +5783,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688881254799131E-2</v>
+        <v>9.7688803412033329E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780008977618121E-2</v>
+        <v>9.0779847881818629E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5833,22 +5833,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="368" t="s">
         <v>508</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="368"/>
+      <c r="D80" s="368"/>
+      <c r="E80" s="368"/>
+      <c r="F80" s="368"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5892,22 +5892,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="368" t="s">
         <v>509</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="368"/>
+      <c r="D89" s="368"/>
+      <c r="E89" s="368"/>
+      <c r="F89" s="368"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="368" t="s">
         <v>510</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="368"/>
+      <c r="D90" s="368"/>
+      <c r="E90" s="368"/>
+      <c r="F90" s="368"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.156478839568178</v>
+        <v>12.121812330613826</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5944,13 +5944,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="368" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="368"/>
+      <c r="D97" s="368"/>
+      <c r="E97" s="368"/>
+      <c r="F97" s="368"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5963,13 +5963,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="368" t="s">
         <v>513</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="368"/>
+      <c r="D101" s="368"/>
+      <c r="E101" s="368"/>
+      <c r="F101" s="368"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0615554154632685</v>
+        <v>3.0528292998542006</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17131.309372975855</v>
+        <v>17132.727668168856</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1602394243918974</v>
+        <v>2.1542605960627959</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9974067210732804E-2</v>
+        <v>1.9917136665303571E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6091,13 +6091,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="368" t="s">
         <v>518</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="368"/>
+      <c r="D116" s="368"/>
+      <c r="E116" s="368"/>
+      <c r="F116" s="368"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1886252862224569</v>
+        <v>-3.1795369931472965</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.89 HKD</v>
+        <v>12.85 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.06 HKD</v>
+        <v>14.02 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.03 HKD</v>
+        <v>12.99 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.11 HKD</v>
+        <v>12.07 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.28 HKD</v>
+        <v>11.24 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.955428203627237</v>
+        <v>12.918660381570513</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6285,13 +6285,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="372" t="s">
         <v>526</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6304,22 +6304,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="373" t="s">
         <v>528</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="368" t="s">
         <v>529</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="368"/>
+      <c r="D139" s="368"/>
+      <c r="E139" s="368"/>
+      <c r="F139" s="368"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58475815790742269</v>
+        <v>0.5830914667662227</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2656315413817953</v>
+        <v>5.2506875503004666</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8503896992892184</v>
+        <v>5.8337790170666892</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5484217420423636</v>
+        <v>0.54842229420404653</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67307128498271995</v>
+        <v>0.67115288173702392</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6331792402571459</v>
+        <v>6.6143541153641028</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3062505252398662</v>
+        <v>7.2855069971011268</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604716027878754</v>
+        <v>0.43604779583071351</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89669016463435369</v>
+        <v>0.8941343977184284</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.428608865032555</v>
+        <v>10.399012218050146</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.325299029666908</v>
+        <v>11.293146615768574</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582595868995883</v>
+        <v>0.12582680539546209</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83189235969715858</v>
+        <v>0.82952128097411704</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2859378109069173</v>
+        <v>9.2595840923192405</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.117830170604076</v>
+        <v>10.089105373293357</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261918959240934</v>
+        <v>0.22261992250730056</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6652,13 +6652,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="374" t="s">
         <v>536</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="368"/>
+      <c r="D179" s="368"/>
+      <c r="E179" s="368"/>
+      <c r="F179" s="368"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6666,13 +6666,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="370" t="s">
         <v>538</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="370"/>
+      <c r="D182" s="370"/>
+      <c r="E182" s="370"/>
+      <c r="F182" s="370"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6709,22 +6709,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="371" t="s">
         <v>545</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="371" t="s">
         <v>546</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6748,12 +6748,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6766,15 +6769,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -6915,7 +6915,7 @@
         <v>465</v>
       </c>
       <c r="C12" s="50">
-        <v>7.72</v>
+        <v>7.54</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>66845.949185759993</v>
+        <v>65287.364878319997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -6963,7 +6963,7 @@
         <v>469</v>
       </c>
       <c r="C16" s="50">
-        <v>1.09186545</v>
+        <v>1.0887533899999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -6973,13 +6973,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="368" t="s">
         <v>470</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="368"/>
+      <c r="D18" s="368"/>
+      <c r="E18" s="368"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.955428203627237</v>
+        <v>12.918660381570513</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2264478139311954</v>
+        <v>0.2352638333289685</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8503896992892184</v>
+        <v>5.8337790170666892</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3062505252398662</v>
+        <v>7.2855069971011268</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.325299029666908</v>
+        <v>11.293146615768574</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.117830170604076</v>
+        <v>10.089105373293357</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -7179,22 +7179,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="368" t="s">
         <v>471</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="368"/>
+      <c r="D36" s="368"/>
+      <c r="E36" s="368"/>
+      <c r="F36" s="368"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="369" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.60690627024144</v>
+        <v>279.59272331831147</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.39309372975856</v>
+        <v>-523.40727668168847</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7285411561006</v>
+        <v>-4449.7249954181179</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7384,10 +7384,10 @@
       <c r="B61" s="367" t="s">
         <v>330</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="370"/>
+      <c r="D61" s="370"/>
+      <c r="E61" s="370"/>
+      <c r="F61" s="370"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7403,22 +7403,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="368" t="s">
         <v>335</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="368"/>
+      <c r="D64" s="368"/>
+      <c r="E64" s="368"/>
+      <c r="F64" s="368"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="368" t="s">
         <v>350</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="368"/>
+      <c r="D65" s="368"/>
+      <c r="E65" s="368"/>
+      <c r="F65" s="368"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.03755922756</v>
+        <v>10305.007426902648</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3235535558979</v>
+        <v>7230.3129163419508</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11810050686108982</v>
+        <v>0.12057505633899694</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7462,14 +7462,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4664651439119164E-2</v>
+        <v>4.5600573018832885E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>426</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41293463541208869</v>
+        <v>0.41175828540035703</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -7489,11 +7489,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035925214863964</v>
+        <v>0.20035909249363959</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114130195562065</v>
+        <v>0.19114096276132886</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -7503,11 +7503,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688881254799131E-2</v>
+        <v>9.7688803412033329E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780008977618121E-2</v>
+        <v>9.0779847881818629E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -7553,22 +7553,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="368" t="s">
         <v>473</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="368"/>
+      <c r="D80" s="368"/>
+      <c r="E80" s="368"/>
+      <c r="F80" s="368"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7612,22 +7612,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="368" t="s">
         <v>351</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="368"/>
+      <c r="D89" s="368"/>
+      <c r="E89" s="368"/>
+      <c r="F89" s="368"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="368" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="368"/>
+      <c r="D90" s="368"/>
+      <c r="E90" s="368"/>
+      <c r="F90" s="368"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.156478839568178</v>
+        <v>12.121812330613826</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -7664,13 +7664,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="368" t="s">
         <v>353</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="368"/>
+      <c r="D97" s="368"/>
+      <c r="E97" s="368"/>
+      <c r="F97" s="368"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7683,13 +7683,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="368" t="s">
         <v>336</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="368"/>
+      <c r="D101" s="368"/>
+      <c r="E101" s="368"/>
+      <c r="F101" s="368"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0615554154632685</v>
+        <v>3.0528292998542006</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17131.309372975855</v>
+        <v>17132.727668168856</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1602394243918974</v>
+        <v>2.1542605960627959</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9974067210732804E-2</v>
+        <v>1.9917136665303571E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -7811,13 +7811,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="368" t="s">
         <v>354</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="368"/>
+      <c r="D116" s="368"/>
+      <c r="E116" s="368"/>
+      <c r="F116" s="368"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1886252862224569</v>
+        <v>-3.1795369931472965</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.89 HKD</v>
+        <v>12.85 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.06 HKD</v>
+        <v>14.02 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.03 HKD</v>
+        <v>12.99 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.11 HKD</v>
+        <v>12.07 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.28 HKD</v>
+        <v>11.24 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.955428203627237</v>
+        <v>12.918660381570513</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -8005,13 +8005,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="372" t="s">
         <v>476</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8024,22 +8024,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="373" t="s">
         <v>355</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="368" t="s">
         <v>478</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="368"/>
+      <c r="D139" s="368"/>
+      <c r="E139" s="368"/>
+      <c r="F139" s="368"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58475815790742269</v>
+        <v>0.5830914667662227</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2656315413817953</v>
+        <v>5.2506875503004666</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8503896992892184</v>
+        <v>5.8337790170666892</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5484217420423636</v>
+        <v>0.54842229420404653</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67307128498271995</v>
+        <v>0.67115288173702392</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6331792402571459</v>
+        <v>6.6143541153641028</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3062505252398662</v>
+        <v>7.2855069971011268</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604716027878754</v>
+        <v>0.43604779583071351</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89669016463435369</v>
+        <v>0.8941343977184284</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.428608865032555</v>
+        <v>10.399012218050146</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.325299029666908</v>
+        <v>11.293146615768574</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582595868995883</v>
+        <v>0.12582680539546209</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83189235969715858</v>
+        <v>0.82952128097411704</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2859378109069173</v>
+        <v>9.2595840923192405</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.117830170604076</v>
+        <v>10.089105373293357</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261918959240934</v>
+        <v>0.22261992250730056</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -8372,13 +8372,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="374" t="s">
         <v>479</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="368"/>
+      <c r="D179" s="368"/>
+      <c r="E179" s="368"/>
+      <c r="F179" s="368"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8386,13 +8386,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="370"/>
+      <c r="D182" s="370"/>
+      <c r="E182" s="370"/>
+      <c r="F182" s="370"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8429,22 +8429,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="371" t="s">
         <v>365</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="371" t="s">
         <v>366</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8468,6 +8468,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8484,17 +8495,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9183,19 +9183,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.30987141471000001</v>
+        <v>0.308988212082</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.277224637755</v>
+        <v>0.27643448572099999</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22688964051000002</v>
+        <v>0.22624295444199999</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -10568,19 +10568,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.30987141471000001</v>
+        <v>0.308988212082</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.277224637755</v>
+        <v>0.27643448572099999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22688964051000002</v>
+        <v>0.22624295444199999</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -11918,11 +11918,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2152178327779772</v>
+        <v>8.1918026301001419</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1886252862224569</v>
+        <v>-3.1795369931472965</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17131.309372975855</v>
+        <v>17132.727668168856</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -12180,11 +12180,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.387585041586</v>
+        <v>-14496.678437445085</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.345313512073</v>
+        <v>-13979.636165915572</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>343</v>
@@ -12196,11 +12196,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1103534851014092</v>
+        <v>3.1105056371759514</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2253852811788817</v>
+        <v>3.2255488958962317</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -12213,7 +12213,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27960.690627024145</v>
+        <v>27959.272331831144</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>344</v>
@@ -12328,11 +12328,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26509.401260549999</v>
+        <v>-26433.843555809999</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0615554154632685</v>
+        <v>-3.0528292998542006</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -12345,11 +12345,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18705.0848176135</v>
+        <v>18653.315328665638</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1602394243918974</v>
+        <v>2.1542605960627963</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>172.95148728000001</v>
+        <v>172.458536976</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9974067210732804E-2</v>
+        <v>1.9917136665303575E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -12379,11 +12379,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7631.3649556564988</v>
+        <v>-7608.0696901683614</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88134192386063825</v>
+        <v>-0.87865156712610071</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -12963,48 +12963,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.39309372975856</v>
+        <v>-523.40727668168847</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.96244077244023</v>
+        <v>-208.99257309735128</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.52956521087992</v>
+        <v>-420.55692963955698</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.35045576568484</v>
+        <v>-366.37747420733274</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.97717240983388</v>
+        <v>-454.9938112406042</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.37328335585096</v>
+        <v>-503.38366296672848</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09781708940352</v>
+        <v>-818.10643531176856</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.07611693932131</v>
+        <v>-947.08539568237848</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1629175396502</v>
+        <v>-1014.1695541999386</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.59174512482423</v>
+        <v>-468.60272234966135</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.48178410626201</v>
+        <v>-437.48886111367852</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -13018,48 +13018,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.914164624402</v>
+        <v>17798.899981672472</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.03755922756</v>
+        <v>16980.007426902648</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.47043478912</v>
+        <v>17261.443070360445</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.649544234315</v>
+        <v>16973.622525792667</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.022827590166</v>
+        <v>14670.006188759397</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.626716644148</v>
+        <v>11589.616337033272</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.902182910595</v>
+        <v>20402.893564688231</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.923883060677</v>
+        <v>19208.914604317622</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.837082460348</v>
+        <v>16944.83044580006</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.408254875176</v>
+        <v>17752.39727765034</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.518215893739</v>
+        <v>11857.511138886321</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7285411561006</v>
+        <v>-4449.7249954181179</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -13185,50 +13185,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3235535558979</v>
+        <v>7230.3129163419508</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.03755922756</v>
+        <v>10305.007426902648</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.47043478912</v>
+        <v>10350.443070360445</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.649544234315</v>
+        <v>10809.622525792667</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0228275901663</v>
+        <v>8651.0061887593965</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6267166441485</v>
+        <v>5607.6163370332724</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.902182910595</v>
+        <v>12308.893564688231</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.923883060677</v>
+        <v>11857.914604317622</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.837082460348</v>
+        <v>10224.83044580006</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.408254875176</v>
+        <v>11296.39727765034</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5182158937387</v>
+        <v>7067.5111388863206</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -13293,50 +13293,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3235535558979</v>
+        <v>7230.3129163419508</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.03755922756</v>
+        <v>10305.007426902648</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.47043478912</v>
+        <v>10350.443070360445</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.649544234315</v>
+        <v>10809.622525792667</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0228275901663</v>
+        <v>8651.0061887593965</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6267166441485</v>
+        <v>5607.6163370332724</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.902182910595</v>
+        <v>12308.893564688231</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.923883060677</v>
+        <v>11857.914604317622</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.837082460348</v>
+        <v>10224.83044580006</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.408254875176</v>
+        <v>11296.39727765034</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5182158937387</v>
+        <v>7067.5111388863206</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -14154,43 +14154,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.1842163180787626</v>
+        <v>0.18421664498474155</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337865870757606</v>
+        <v>0.19337896526922865</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787945348401833</v>
+        <v>0.18787975254864306</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391246092172567</v>
+        <v>0.18391266951661475</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957502140066719</v>
+        <v>0.19957520013920368</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967747546289613</v>
+        <v>0.19967755980705443</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1963670647540191</v>
+        <v>0.19636715960787085</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838205660029324</v>
+        <v>0.20838213821579976</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847875662073226</v>
+        <v>0.20847888553392349</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986050980765895</v>
+        <v>0.21986064102865807</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -14292,48 +14292,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.60690627024144</v>
+        <v>279.59272331831147</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.03755922755977</v>
+        <v>594.00742690264872</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.47043478912008</v>
+        <v>539.44307036044302</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.64954423431516</v>
+        <v>532.62252579266726</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.02282759016612</v>
+        <v>328.0061887593958</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.62671664414901</v>
+        <v>204.61633703327149</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90218291059645</v>
+        <v>169.89356468823146</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.92388306067866</v>
+        <v>182.91460431762147</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83708246034982</v>
+        <v>130.83044580006145</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.40825487517577</v>
+        <v>216.39727765033862</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.51821589373796</v>
+        <v>139.51113888632148</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -14404,48 +14404,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.39309372975856</v>
+        <v>-523.40727668168847</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.96244077244023</v>
+        <v>-208.99257309735128</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.52956521087992</v>
+        <v>-420.55692963955698</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.35045576568484</v>
+        <v>-366.37747420733274</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.97717240983388</v>
+        <v>-454.9938112406042</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.37328335585096</v>
+        <v>-503.38366296672848</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09781708940352</v>
+        <v>-818.10643531176856</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.07611693932131</v>
+        <v>-947.08539568237848</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1629175396502</v>
+        <v>-1014.1695541999386</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.59174512482423</v>
+        <v>-468.60272234966135</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.48178410626201</v>
+        <v>-437.48886111367852</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -15490,50 +15490,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8726294935771599E-3</v>
+        <v>2.8727073363429665E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1171713951244092E-3</v>
+        <v>1.1173324909238972E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3711309878033759E-3</v>
+        <v>2.3712852805099238E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1306382064258411E-3</v>
+        <v>2.130795341549183E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2839193371912339E-3</v>
+        <v>3.2840394323991441E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074936005697977E-3</v>
+        <v>4.6075886075800541E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.21980546882885E-3</v>
+        <v>7.2198815256128476E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795782396825761E-3</v>
+        <v>8.9796662148703757E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432855923383426E-2</v>
+        <v>1.1432930739746338E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7227686808434602E-3</v>
+        <v>5.7229027423568229E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0506034535824356E-2</v>
+        <v>1.050620448869332E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -15547,50 +15547,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688881254799131E-2</v>
+        <v>9.7688803412033329E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780008977618121E-2</v>
+        <v>9.0779847881818629E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327776282401982E-2</v>
+        <v>9.732762198969544E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716149119680324E-2</v>
+        <v>9.8715991984556994E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588481040794941</v>
+        <v>0.1058846903127415</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608256873295575</v>
+        <v>0.10608247372594551</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005791200401186</v>
+        <v>0.18005783594722785</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212689753541933</v>
+        <v>0.18212680956023156</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102244586003594</v>
+        <v>0.19102237104367303</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.2168047709493561</v>
+        <v>0.21680463688784274</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475584678306809</v>
+        <v>0.28475567683019909</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422220313699783E-2</v>
+        <v>2.4422200853008332E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -15719,50 +15719,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.968344431150328E-2</v>
+        <v>3.9683385929428931E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093600286707865E-2</v>
+        <v>5.5093439190908373E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360513068716355E-2</v>
+        <v>5.8360358776009813E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867268088646969E-2</v>
+        <v>6.2867110953523625E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.244106929482534E-2</v>
+        <v>6.2440949199617436E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327921178242288E-2</v>
+        <v>5.1327826171232049E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1086274494798531</v>
+        <v>0.10862737342306912</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242935321001875</v>
+        <v>0.11242926523483097</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526657816224774</v>
+        <v>0.11526650334588484</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795960351328956</v>
+        <v>0.1379594694517762</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972498777391845</v>
+        <v>0.16972481782104945</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -15826,50 +15826,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.968344431150328E-2</v>
+        <v>3.9683385929428931E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093600286707865E-2</v>
+        <v>5.5093439190908373E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360513068716355E-2</v>
+        <v>5.8360358776009813E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867268088646969E-2</v>
+        <v>6.2867110953523625E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.244106929482534E-2</v>
+        <v>6.2440949199617436E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327921178242288E-2</v>
+        <v>5.1327826171232049E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1086274494798531</v>
+        <v>0.10862737342306912</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242935321001875</v>
+        <v>0.11242926523483097</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526657816224774</v>
+        <v>0.11526650334588484</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795960351328956</v>
+        <v>0.1379594694517762</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972498777391845</v>
+        <v>0.16972481782104945</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -15895,24 +15895,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.30987141471000001</v>
+        <v>0.308988212082</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.277224637755</v>
+        <v>0.27643448572099999</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22688964051000002</v>
+        <v>0.22624295444199999</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -15951,24 +15951,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2985.6510204990423</v>
+        <v>2977.1412493410166</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2985.6510204990423</v>
+        <v>2977.1412493410166</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2683.1151349513243</v>
+        <v>2675.4676585274879</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2400.4331668926752</v>
+        <v>2393.5913971110963</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1964.5924067754941</v>
+        <v>1958.9928803453558</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -16006,24 +16006,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41293463541208869</v>
+        <v>0.41175828540035703</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28972733028280578</v>
+        <v>0.28890238754887038</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25922639476685683</v>
+        <v>0.25848822512622321</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22206392141297737</v>
+        <v>0.22143154318291747</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22709365654543673</v>
+        <v>0.22644682451975989</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -16082,24 +16082,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4664651439119164E-2</v>
+        <v>4.5600573018832885E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4664651439119164E-2</v>
+        <v>4.5600573018832885E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0138784288860106E-2</v>
+        <v>4.0979868976392574E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.5909927170336788E-2</v>
+        <v>3.6662398636737398E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.9389849806994821E-2</v>
+        <v>3.0005696875596816E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -16219,46 +16219,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225841818108073E-2</v>
+        <v>4.8226866701624349E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304107846707883E-2</v>
+        <v>-1.6304294044861667E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956924308159316E-2</v>
+        <v>1.6956930916214974E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702952501966649</v>
+        <v>0.15702899558408978</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578907036946964</v>
+        <v>0.26578876833766252</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196185460558734</v>
+        <v>-0.4319621233974531</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157479883754529E-2</v>
+        <v>6.2157544294680456E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361514127178542</v>
+        <v>0.13361503768122618</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490795435771503E-2</v>
+        <v>-4.5490579059256353E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.4971436629192747</v>
+        <v>0.49714363070947765</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -16830,43 +16830,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143575341745789</v>
+        <v>1.2143610850129491</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920140239783747</v>
+        <v>1.3920177041752719</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756227654883972</v>
+        <v>1.3756262038307934</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871192157451198</v>
+        <v>1.3871218836477179</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848634450505576</v>
+        <v>2.9848689699865045</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067777906572411</v>
+        <v>1.3067787056136928</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351584786533005</v>
+        <v>1.435159601655718</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994828076813543</v>
+        <v>1.2994836511404209</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941599528507855</v>
+        <v>1.3941613076196453</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917531715635298</v>
+        <v>1.8917550658585602</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -16938,48 +16938,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688881254799131E-2</v>
+        <v>9.7688803412033329E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780008977618121E-2</v>
+        <v>9.0779847881818629E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327776282401982E-2</v>
+        <v>9.732762198969544E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716149119680324E-2</v>
+        <v>9.8715991984556994E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588481040794941</v>
+        <v>0.1058846903127415</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608256873295575</v>
+        <v>0.10608247372594551</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005791200401186</v>
+        <v>0.18005783594722785</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212689753541933</v>
+        <v>0.18212680956023156</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102244586003594</v>
+        <v>0.19102237104367303</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.2168047709493561</v>
+        <v>0.21680463688784274</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475584678306809</v>
+        <v>0.28475567683019909</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -17103,50 +17103,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035925214863964</v>
+        <v>0.20035909249363959</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114130195562065</v>
+        <v>0.19114096276132886</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.2012225083616698</v>
+        <v>0.20122218936573033</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032501727632916</v>
+        <v>0.21032468248361463</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338029854062252</v>
+        <v>0.19338007920748998</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371115349727797</v>
+        <v>0.13711141217638473</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766120076921883</v>
+        <v>0.25766109193266695</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404519478215933</v>
+        <v>0.27404506240644882</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820704125653865</v>
+        <v>0.2582069401264771</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774668197329193</v>
+        <v>0.26774651641178138</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861268152968742</v>
+        <v>0.16861258089537456</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -17224,50 +17224,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91173591296761336</v>
+        <v>0.909135924796037</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2994539950576844</v>
+        <v>1.2957464725920984</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3051830311059387</v>
+        <v>1.3014595276440233</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3630850159154255</v>
+        <v>1.359196522389877</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0908845416658441</v>
+        <v>1.0877731853150749</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.7071156119378228</v>
+        <v>0.70509886964192359</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5521391382057574</v>
+        <v>1.5477141119101714</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4952712665404526</v>
+        <v>1.4910082433061442</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2893408024233339</v>
+        <v>1.2856650591449283</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4244647583507173</v>
+        <v>1.4204033358871528</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89120633748320666</v>
+        <v>0.88866531083809441</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -17281,50 +17281,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11810050686108982</v>
+        <v>0.12057505633899694</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.16832305635462233</v>
+        <v>0.17184966480001304</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16906515946968118</v>
+        <v>0.17260736440902166</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17656541656935565</v>
+        <v>0.18026479076788821</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14130628778054977</v>
+        <v>0.1442670007049171</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.1595286520443367E-2</v>
+        <v>9.3514438944552206E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20105429251369916</v>
+        <v>0.20526712359551344</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19368798789384101</v>
+        <v>0.19774645136686264</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.16701305730872201</v>
+        <v>0.17051260731365098</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18451616040812402</v>
+        <v>0.18838240529007333</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11544123542528584</v>
+        <v>0.11786012080080828</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17338,43 +17338,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14222252979878772</v>
+        <v>0.14561776260565532</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13845266785397919</v>
+        <v>0.14175790395659407</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12271499021136589</v>
+        <v>0.12564452578670354</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.39399545254135604</v>
+        <v>0.40340117952510191</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14558847796379532</v>
+        <v>0.14906406497088856</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14317995505461209</v>
+        <v>0.14659804416732167</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12286458790758846</v>
+        <v>0.1257976947807139</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11891520872731287</v>
+        <v>0.12175403333884023</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1072653490381953E-2</v>
+        <v>5.2291894555139079E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4706665523633898E-2</v>
+        <v>3.5535206610404997E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3235535558979</v>
+        <v>7230.3129163419508</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.314047411972</v>
+        <v>96404.172217892687</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17131.309372975855</v>
+        <v>17132.727668168856</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89415.023420387821</v>
+        <v>89416.299886061533</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.09186545</v>
+        <v>1.0887533899999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.015281616353727</v>
+        <v>12.97834311091939</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7315026360702</v>
+        <v>7373.7206544411038</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2851187312281</v>
+        <v>6859.2750273870734</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9838389289371</v>
+        <v>7519.9727755683034</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.287259213791</v>
+        <v>6507.2776857270346</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1369786838613</v>
+        <v>7669.1256958899139</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3528700085171</v>
+        <v>6173.343787804276</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.248457123449</v>
+        <v>7821.2369505438955</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5549882066935</v>
+        <v>5856.546372073828</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3769506375347</v>
+        <v>7976.3652158337582</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0142198450712</v>
+        <v>5556.0060458662019</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5822994173595</v>
+        <v>8134.5703318627066</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -18490,7 +18490,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.8962988108096</v>
+        <v>5270.8885442959236</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9255305386832</v>
+        <v>8295.913325616717</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4097710160631</v>
+        <v>5000.4024144395325</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4688815027348</v>
+        <v>8460.4564345054569</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8037974137724</v>
+        <v>4743.7968183545991</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2758242440741</v>
+        <v>8628.2631303701073</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3660697560526</v>
+        <v>4500.3594488411845</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4110896146449</v>
+        <v>8799.3981439673771</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4208333095985</v>
+        <v>4269.4145521601467</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9406923534261</v>
+        <v>8973.9274899391239</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3270110393692</v>
+        <v>4050.3210522195936</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9319565513597</v>
+        <v>9151.9184922772474</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4764240535301</v>
+        <v>3842.4707710224448</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4535416213457</v>
+        <v>9333.439810293632</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2921033697971</v>
+        <v>3645.2867404352455</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.575468783336</v>
+        <v>9518.5614651052183</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2266883168472</v>
+        <v>3458.2216005919495</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3691480747311</v>
+        <v>9707.3548666443457</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7609071249481</v>
+        <v>3280.7560804867735</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9074058965252</v>
+        <v>9899.8928412048699</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4021354881052</v>
+        <v>3112.3975565384694</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.264513105787</v>
+        <v>10096.249659534589</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6830290964526</v>
+        <v>2952.6786851247252</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.516213665349</v>
+        <v>10296.501065484903</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.16022634297</v>
+        <v>2801.1561052907919</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.739753861733</v>
+        <v>10500.72430522869</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4131176033798</v>
+        <v>2657.4092080311916</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.013912102597</v>
+        <v>10708.998157057709</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0426776729037</v>
+        <v>2521.038968728189</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.420035147603</v>
+        <v>98316.27539254805</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.977946522984</v>
+        <v>23144.94389575328</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.15349294289</v>
+        <v>110203.99136117246</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19142,7 +19142,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.15349294289</v>
+        <v>110203.99136117246</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -19172,19 +19172,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.314047411972</v>
+        <v>96404.172217892701</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.936551276638</v>
+        <v>97921.7924890391</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.343367626512</v>
+        <v>99461.197040621773</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.01262558368</v>
+        <v>101022.86400105935</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.4299181324</v>
+        <v>102607.2789626217</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19193,19 +19193,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.314047411986</v>
+        <v>96404.172217892716</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.005303004422</v>
+        <v>99376.859100077403</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.78020845618</v>
+        <v>102492.62942161753</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.02788584513</v>
+        <v>105759.87229224891</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.60022071422</v>
+        <v>109187.4395844916</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -19214,19 +19214,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.314047412001</v>
+        <v>96404.172217892701</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.49315824767</v>
+        <v>101173.3443123372</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.93424960022</v>
+        <v>106330.77781608954</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.63968856103</v>
+        <v>111913.4750418035</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.14190225315</v>
+        <v>117961.96835697099</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -19245,19 +19245,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.314047412015</v>
+        <v>96404.172217892701</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.04016121484</v>
+        <v>102997.88863104041</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.27245521027</v>
+        <v>110332.1101349519</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.60522319149</v>
+        <v>118504.43087984016</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.92876457056</v>
+        <v>127625.74100197603</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -19276,19 +19276,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.314047412001</v>
+        <v>96404.172217892701</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.56931150272</v>
+        <v>104688.41529423071</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.62292467365</v>
+        <v>114140.45500159009</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.58050581119</v>
+        <v>124956.39667034778</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.37064339643</v>
+        <v>137367.16854924388</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -19307,19 +19307,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.314047412001</v>
+        <v>96404.172217892701</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.32543788859</v>
+        <v>106173.1692362512</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.71088452468</v>
+        <v>117578.53790334422</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.5064186962</v>
+        <v>130953.31376058697</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.78146182816</v>
+        <v>146703.56563199722</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -19399,23 +19399,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -19426,23 +19426,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.466507457959517</v>
+        <v>11.433985576281023</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.660624978252651</v>
+        <v>11.627549533585709</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.857549768147676</v>
+        <v>11.823912755029676</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.057343060390197</v>
+        <v>12.023136298741727</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.275136915707542</v>
+        <v>11.243160763487728</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.649990040303253</v>
+        <v>11.616944923182349</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.04288585706467</v>
+        <v>12.008720322878126</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.454882225134602</v>
+        <v>12.419541805031562</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.88709535762402</v>
+        <v>12.850522399659859</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -19480,23 +19480,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.275136915707543</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.87652519916622</v>
+        <v>11.842834074001637</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.526872894835861</v>
+        <v>12.491327179661049</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.230845960842974</v>
+        <v>13.193292732726425</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.99355549203333</v>
+        <v>13.953827252785556</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -19507,23 +19507,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.275136915707545</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.106598585949095</v>
+        <v>12.072251362811706</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.031437277738185</v>
+        <v>12.994452701366082</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.061959525062246</v>
+        <v>14.022036218718577</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.212148473713411</v>
+        <v>15.168945185064517</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -19534,23 +19534,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.275136915707543</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.319772467701323</v>
+        <v>12.284817338740373</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.511666117631412</v>
+        <v>13.473312077486288</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.875546570119269</v>
+        <v>14.83330316574764</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.440533668265907</v>
+        <v>16.39382740586052</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -19560,23 +19560,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.275136915707543</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.50699859560523</v>
+        <v>12.471509555770487</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.945205258960172</v>
+        <v>13.905614899587803</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.631752386039407</v>
+        <v>15.587352517116257</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.617844887927319</v>
+        <v>17.567781298908123</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.88709535762402</v>
+        <v>12.850522399659859</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.061959525062246</v>
+        <v>14.022036218718577</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.031437277738185</v>
+        <v>12.994452701366082</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.106598585949095</v>
+        <v>12.072251362811706</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.275136915707542</v>
+        <v>11.243160763487728</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2985.6510204990423</v>
+        <v>2977.1412493410166</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39808.680273320562</v>
+        <v>39695.216657880221</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0198311575118559</v>
+        <v>4.9912566611984541</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2555900317547986</v>
+        <v>5.2406104282567458</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3044.8691296676584</v>
+        <v>3036.190573693867</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -20032,7 +20032,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2832.4363996908451</v>
+        <v>2824.363324366388</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3105.2617848329196</v>
+        <v>3096.4110963253684</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2687.0842919051765</v>
+        <v>2679.425502498967</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3166.8522822181876</v>
+        <v>3157.8260470594505</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2549.1912166471384</v>
+        <v>2541.9254532532336</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3229.6643801096325</v>
+        <v>3220.4591164658709</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2418.3743988259803</v>
+        <v>2411.4814925328005</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3293.7223080208983</v>
+        <v>3284.3344649987566</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2294.2707062161048</v>
+        <v>2287.7315231198845</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3359.0507760395371</v>
+        <v>3349.4767323164006</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2176.535641444369</v>
+        <v>2170.332029535673</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3425.6749843588295</v>
+        <v>3415.9110467859132</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2064.8423857055641</v>
+        <v>2058.9571244814274</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3493.620632998653</v>
+        <v>3483.6630351763847</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1958.8808915515376</v>
+        <v>1953.2976442133586</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3562.9139317191662</v>
+        <v>3552.7588325443121</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1858.3570222356502</v>
+        <v>1853.0602903401414</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3633.5816101311138</v>
+        <v>3623.2250923150905</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1762.9917352234752</v>
+        <v>1757.9668156607947</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3705.6509280066684</v>
+        <v>3695.0889965644628</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1672.5203076032767</v>
+        <v>1667.7532517829097</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3779.1496857947791</v>
+        <v>3768.3782665038993</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1586.6916012460908</v>
+        <v>1582.1691763771894</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3854.1062353450779</v>
+        <v>3843.121173173939</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -20296,7 +20296,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1505.2673656755728</v>
+        <v>1500.9770180342728</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3930.5494908444975</v>
+        <v>3919.3465483496343</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1428.0215767124719</v>
+        <v>1423.9513967942191</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4008.5089399707967</v>
+        <v>3997.0837956622872</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1354.7398090578736</v>
+        <v>1350.8784985180296</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4088.0146552673186</v>
+        <v>4076.3629019417858</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -20362,7 +20362,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1285.2186410735872</v>
+        <v>1281.5554813645408</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4169.0973057433466</v>
+        <v>4157.2144487839005</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1219.2650901074051</v>
+        <v>1215.7899127251374</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4251.7881687045601</v>
+        <v>4239.6696243470124</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1156.696076795778</v>
+        <v>1153.3992350532783</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4336.1191418181206</v>
+        <v>4323.7602353828197</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1097.3379168568536</v>
+        <v>1094.2102591060438</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4422.1227554170719</v>
+        <v>4409.5187195056651</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1041.0258389631765</v>
+        <v>1038.0586831910032</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40598.255062235447</v>
+        <v>40482.540982584898</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9557.3630299683027</v>
+        <v>9530.1224142028314</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45507.111943506228</v>
+        <v>45377.406527152118</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -20724,7 +20724,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45507.111943506228</v>
+        <v>45377.406527152118</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -20754,19 +20754,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39808.68027332057</v>
+        <v>39695.216657880228</v>
       </c>
       <c r="C51" s="123">
-        <v>40435.359168647097</v>
+        <v>40320.109378616296</v>
       </c>
       <c r="D51" s="123">
-        <v>41071.033561107426</v>
+        <v>40953.971957313493</v>
       </c>
       <c r="E51" s="123">
-        <v>41715.900886776239</v>
+        <v>41597.00126730965</v>
       </c>
       <c r="F51" s="123">
-        <v>42370.161663815445</v>
+        <v>42249.39725524524</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -20775,19 +20775,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39808.68027332057</v>
+        <v>39695.216657880235</v>
       </c>
       <c r="C52" s="123">
-        <v>41036.207453141338</v>
+        <v>40919.245111520737</v>
       </c>
       <c r="D52" s="123">
-        <v>42322.818827750198</v>
+        <v>42202.189356819428</v>
       </c>
       <c r="E52" s="123">
-        <v>43671.978556213806</v>
+        <v>43547.50367921713</v>
       </c>
       <c r="F52" s="123">
-        <v>45087.341888661518</v>
+        <v>44958.832910565332</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -20796,19 +20796,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39808.680273320577</v>
+        <v>39695.216657880228</v>
       </c>
       <c r="C53" s="123">
-        <v>41778.039510668459</v>
+        <v>41658.962782267925</v>
       </c>
       <c r="D53" s="123">
-        <v>43907.725567385438</v>
+        <v>43782.578758839358</v>
       </c>
       <c r="E53" s="123">
-        <v>46213.01800243582</v>
+        <v>46081.300596408662</v>
       </c>
       <c r="F53" s="123">
-        <v>48710.654058835964</v>
+        <v>48571.817833117544</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -20817,19 +20817,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39808.680273320577</v>
+        <v>39695.216657880235</v>
       </c>
       <c r="C54" s="123">
-        <v>42531.458162130926</v>
+        <v>42410.234022574121</v>
       </c>
       <c r="D54" s="123">
-        <v>45560.016700479493</v>
+        <v>45430.160493771153</v>
       </c>
       <c r="E54" s="123">
-        <v>48934.655952492089</v>
+        <v>48795.181271428111</v>
       </c>
       <c r="F54" s="123">
-        <v>52701.16636352714</v>
+        <v>52550.956287923706</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -20838,19 +20838,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39808.680273320577</v>
+        <v>39695.216657880235</v>
       </c>
       <c r="C55" s="123">
-        <v>43229.536200458562</v>
+        <v>43106.32238283295</v>
       </c>
       <c r="D55" s="123">
-        <v>47132.616513108806</v>
+        <v>46998.278046271342</v>
       </c>
       <c r="E55" s="123">
-        <v>51598.900013508457</v>
+        <v>51451.831642789286</v>
       </c>
       <c r="F55" s="123">
-        <v>56723.745114148151</v>
+        <v>56562.069792138536</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -20859,19 +20859,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39808.680273320584</v>
+        <v>39695.216657880243</v>
       </c>
       <c r="C56" s="123">
-        <v>43842.643430183583</v>
+        <v>43717.682120240723</v>
       </c>
       <c r="D56" s="123">
-        <v>48552.322111324589</v>
+        <v>48413.937166961907</v>
       </c>
       <c r="E56" s="123">
-        <v>54075.238428938937</v>
+        <v>53921.111941554271</v>
       </c>
       <c r="F56" s="123">
-        <v>60579.072511514743</v>
+        <v>60406.408646749929</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -20921,23 +20921,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0198311575118559</v>
+        <v>4.9912566611984541</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0198311575118559</v>
+        <v>4.9912566611984541</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0198311575118559</v>
+        <v>4.9912566611984541</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0198311575118559</v>
+        <v>4.9912566611984541</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0198311575118559</v>
+        <v>4.9912566611984541</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -20948,23 +20948,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0198311575118568</v>
+        <v>4.9912566611984559</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.0988546826052907</v>
+        <v>5.0698303589260663</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1790125300746359</v>
+        <v>5.1495319221011542</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2603295963935404</v>
+        <v>5.2303861054786118</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.342831166683486</v>
+        <v>5.31241805024887</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -20975,23 +20975,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0198311575118568</v>
+        <v>4.9912566611984568</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.174620995849871</v>
+        <v>5.145165385904126</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3368612866991798</v>
+        <v>5.3064821527449011</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5069888567392447</v>
+        <v>5.47564130184203</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6854646290240769</v>
+        <v>5.6531011325270057</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -21002,23 +21002,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0198311575118586</v>
+        <v>4.9912566611984559</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2681652090829703</v>
+        <v>5.2381771153360193</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5367162976854027</v>
+        <v>5.5051995246162919</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8274111590369833</v>
+        <v>5.7942396571566057</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1423603412243954</v>
+        <v>6.1073960471239355</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -21029,23 +21029,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0198311575118586</v>
+        <v>4.9912566611984568</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3631704791721804</v>
+        <v>5.3326415848176518</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7450684071811011</v>
+        <v>5.7123656267747176</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1706067356639087</v>
+        <v>6.1354816539854475</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6455595898301896</v>
+        <v>6.607730923478349</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -21056,23 +21056,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0198311575118586</v>
+        <v>4.9912566611984568</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4511973583129167</v>
+        <v>5.420167386600494</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9433715280967814</v>
+        <v>5.9095399424338559</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5065650054905282</v>
+        <v>6.4695275410961175</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1528023822883311</v>
+        <v>7.1120863265306946</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -21082,23 +21082,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0198311575118595</v>
+        <v>4.9912566611984586</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5285095111785338</v>
+        <v>5.4970394537824045</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1223948553582437</v>
+        <v>6.0875442112361133</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8188285783840135</v>
+        <v>6.7800136091229097</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6389549615457808</v>
+        <v>7.5954715686710461</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6854646290240769</v>
+        <v>5.6531011325270057</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1706067356639087</v>
+        <v>6.1354816539854475</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7450684071811011</v>
+        <v>5.7123656267747176</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3631704791721804</v>
+        <v>5.3326415848176518</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0198311575118568</v>
+        <v>4.9912566611984568</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.72</v>
+        <v>-7.54</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.300239312737236</v>
+        <v>13.262488702132513</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.03755922756</v>
+        <v>10305.007426902648</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3235535558979</v>
+        <v>7230.3129163419508</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052497730721521E-2</v>
+        <v>6.005214413120985E-2</v>
       </c>
       <c r="E14" s="377"/>
       <c r="F14" s="377"/>
@@ -21564,7 +21564,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.72</v>
+        <v>7.54</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.275136915707538</v>
+        <v>11.243160763487726</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.031437277738185</v>
+        <v>12.994452701366082</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.106598585949095</v>
+        <v>12.072251362811706</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.061959525062246</v>
+        <v>14.022036218718577</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.052573988845179</v>
+        <v>13.015529137125705</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.275136915707542</v>
+        <v>11.243160763487728</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.88709535762402</v>
+        <v>12.850522399659859</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.955428203627237</v>
+        <v>12.918660381570513</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.015281616353727</v>
+        <v>12.97834311091939</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8028776047238768E-2</v>
+        <v>-6.8014139328220632E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34481110910999996</v>
+        <v>0.34382832056199997</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58475815790742269</v>
+        <v>0.5830914667662227</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2656315413817953</v>
+        <v>5.2506875503004666</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8503896992892184</v>
+        <v>5.8337790170666892</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.5484217420423636</v>
+        <v>0.54842229420404653</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.72</v>
+        <v>7.54</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22175,7 +22175,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2264478139311954</v>
+        <v>0.2352638333289685</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67307128498271995</v>
+        <v>0.67115288173702392</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6331792402571459</v>
+        <v>6.6143541153641028</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3062505252398662</v>
+        <v>7.2855069971011268</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604716027878754</v>
+        <v>0.43604779583071351</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89669016463435369</v>
+        <v>0.8941343977184284</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.428608865032555</v>
+        <v>10.399012218050146</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -22285,7 +22285,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.325299029666908</v>
+        <v>11.293146615768574</v>
       </c>
       <c r="D99" t="s">
         <v>379</v>
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582595868995883</v>
+        <v>0.12582680539546209</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83189235969715858</v>
+        <v>0.82952128097411704</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2859378109069173</v>
+        <v>9.2595840923192405</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.117830170604076</v>
+        <v>10.089105373293357</v>
       </c>
       <c r="D105" t="s">
         <v>379</v>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261918959240934</v>
+        <v>0.22261992250730056</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5B061-315E-444E-ACCE-3DAF98270B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2806E7-246D-4974-A8E5-C240D3749C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4737,15 +4737,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4755,7 +4746,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0887533899999999</v>
+        <v>1.08868404</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5240,13 +5240,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="368" t="s">
+      <c r="B18" s="371" t="s">
         <v>491</v>
       </c>
-      <c r="C18" s="368"/>
-      <c r="D18" s="368"/>
-      <c r="E18" s="368"/>
-      <c r="F18" s="368"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.918660381570513</v>
+        <v>12.917841027032001</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2352638333289685</v>
+        <v>0.23523677184925385</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8337790170666892</v>
+        <v>5.8334088558780746</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2855069971011268</v>
+        <v>7.2850447373524485</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.293146615768574</v>
+        <v>11.292430114260537</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.089105373293357</v>
+        <v>10.088465254642657</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5459,22 +5459,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="368" t="s">
+      <c r="B36" s="371" t="s">
         <v>494</v>
       </c>
-      <c r="C36" s="368"/>
-      <c r="D36" s="368"/>
-      <c r="E36" s="368"/>
-      <c r="F36" s="368"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="374" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.59272331831147</v>
+        <v>279.59240726151421</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.40727668168847</v>
+        <v>-523.40759273848585</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7249954181179</v>
+        <v>-4449.7249164039185</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5664,10 +5664,10 @@
       <c r="B61" s="367" t="s">
         <v>501</v>
       </c>
-      <c r="C61" s="370"/>
-      <c r="D61" s="370"/>
-      <c r="E61" s="370"/>
-      <c r="F61" s="370"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5683,22 +5683,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="368" t="s">
+      <c r="B64" s="371" t="s">
         <v>502</v>
       </c>
-      <c r="C64" s="368"/>
-      <c r="D64" s="368"/>
-      <c r="E64" s="368"/>
-      <c r="F64" s="368"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="368" t="s">
+      <c r="B65" s="371" t="s">
         <v>503</v>
       </c>
-      <c r="C65" s="368"/>
-      <c r="D65" s="368"/>
-      <c r="E65" s="368"/>
-      <c r="F65" s="368"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.007426902648</v>
+        <v>10305.006755425642</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3129163419508</v>
+        <v>7230.3126792993517</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12057505633899694</v>
+        <v>0.12056737215284274</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5742,14 +5742,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5600573018832885E-2</v>
+        <v>4.5597668412732086E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>505</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41175828540035703</v>
+        <v>0.41173207125409761</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5769,11 +5769,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035909249363959</v>
+        <v>0.2003590889358437</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114096276132886</v>
+        <v>0.19114095520263008</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5783,11 +5783,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688803412033329E-2</v>
+        <v>9.768880167736374E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779847881818629E-2</v>
+        <v>9.0779844291915587E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5833,22 +5833,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="368" t="s">
+      <c r="B80" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C80" s="368"/>
-      <c r="D80" s="368"/>
-      <c r="E80" s="368"/>
-      <c r="F80" s="368"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="374" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5892,22 +5892,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="368" t="s">
+      <c r="B89" s="371" t="s">
         <v>509</v>
       </c>
-      <c r="C89" s="368"/>
-      <c r="D89" s="368"/>
-      <c r="E89" s="368"/>
-      <c r="F89" s="368"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="368" t="s">
+      <c r="B90" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C90" s="368"/>
-      <c r="D90" s="368"/>
-      <c r="E90" s="368"/>
-      <c r="F90" s="368"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.121812330613826</v>
+        <v>12.12103981376579</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5944,13 +5944,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="368" t="s">
+      <c r="B97" s="371" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="368"/>
-      <c r="D97" s="368"/>
-      <c r="E97" s="368"/>
-      <c r="F97" s="368"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5963,13 +5963,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="368" t="s">
+      <c r="B101" s="371" t="s">
         <v>513</v>
       </c>
-      <c r="C101" s="368"/>
-      <c r="D101" s="368"/>
-      <c r="E101" s="368"/>
-      <c r="F101" s="368"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0528292998542006</v>
+        <v>3.0526348446966884</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17132.727668168856</v>
+        <v>17132.75927384858</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1542605960627959</v>
+        <v>2.1541273505972445</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9917136665303571E-2</v>
+        <v>1.9915868009388996E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6091,13 +6091,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="368" t="s">
+      <c r="B116" s="371" t="s">
         <v>518</v>
       </c>
-      <c r="C116" s="368"/>
-      <c r="D116" s="368"/>
-      <c r="E116" s="368"/>
-      <c r="F116" s="368"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1795369931472965</v>
+        <v>-3.1793344671276307</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.918660381570513</v>
+        <v>12.917841027032001</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6285,13 +6285,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="369" t="s">
         <v>526</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6304,22 +6304,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="370" t="s">
         <v>528</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="368" t="s">
+      <c r="B139" s="371" t="s">
         <v>529</v>
       </c>
-      <c r="C139" s="368"/>
-      <c r="D139" s="368"/>
-      <c r="E139" s="368"/>
-      <c r="F139" s="368"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.5830914667662227</v>
+        <v>0.5830543257629508</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2506875503004666</v>
+        <v>5.250354530115124</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8337790170666892</v>
+        <v>5.8334088558780746</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842229420404653</v>
+        <v>0.54842230650841528</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67115288173702392</v>
+        <v>0.67111013151206389</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6143541153641028</v>
+        <v>6.6139346058403845</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2855069971011268</v>
+        <v>7.2850447373524485</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604779583071351</v>
+        <v>0.43604780999335013</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.8941343977184284</v>
+        <v>0.89407744430634128</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.399012218050146</v>
+        <v>10.398352669954194</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.293146615768574</v>
+        <v>11.292430114260537</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582680539546209</v>
+        <v>0.12582682426344416</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.82952128097411704</v>
+        <v>0.82946844320445867</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2595840923192405</v>
+        <v>9.2589968114381982</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.089105373293357</v>
+        <v>10.088465254642657</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261992250730056</v>
+        <v>0.22261993883957398</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6652,13 +6652,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="372" t="s">
         <v>536</v>
       </c>
-      <c r="C179" s="368"/>
-      <c r="D179" s="368"/>
-      <c r="E179" s="368"/>
-      <c r="F179" s="368"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6666,13 +6666,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="370" t="s">
+      <c r="B182" s="373" t="s">
         <v>538</v>
       </c>
-      <c r="C182" s="370"/>
-      <c r="D182" s="370"/>
-      <c r="E182" s="370"/>
-      <c r="F182" s="370"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6709,22 +6709,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="368" t="s">
         <v>545</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="368" t="s">
         <v>546</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6748,15 +6748,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6769,12 +6766,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -6963,7 +6963,7 @@
         <v>469</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0887533899999999</v>
+        <v>1.08868404</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -6973,13 +6973,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="368" t="s">
+      <c r="B18" s="371" t="s">
         <v>470</v>
       </c>
-      <c r="C18" s="368"/>
-      <c r="D18" s="368"/>
-      <c r="E18" s="368"/>
-      <c r="F18" s="368"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.918660381570513</v>
+        <v>12.917841027032001</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2352638333289685</v>
+        <v>0.23523677184925385</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8337790170666892</v>
+        <v>5.8334088558780746</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2855069971011268</v>
+        <v>7.2850447373524485</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.293146615768574</v>
+        <v>11.292430114260537</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.089105373293357</v>
+        <v>10.088465254642657</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -7179,22 +7179,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="368" t="s">
+      <c r="B36" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C36" s="368"/>
-      <c r="D36" s="368"/>
-      <c r="E36" s="368"/>
-      <c r="F36" s="368"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="374" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.59272331831147</v>
+        <v>279.59240726151421</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.40727668168847</v>
+        <v>-523.40759273848585</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7249954181179</v>
+        <v>-4449.7249164039185</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7384,10 +7384,10 @@
       <c r="B61" s="367" t="s">
         <v>330</v>
       </c>
-      <c r="C61" s="370"/>
-      <c r="D61" s="370"/>
-      <c r="E61" s="370"/>
-      <c r="F61" s="370"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7403,22 +7403,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="368" t="s">
+      <c r="B64" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C64" s="368"/>
-      <c r="D64" s="368"/>
-      <c r="E64" s="368"/>
-      <c r="F64" s="368"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="368" t="s">
+      <c r="B65" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C65" s="368"/>
-      <c r="D65" s="368"/>
-      <c r="E65" s="368"/>
-      <c r="F65" s="368"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.007426902648</v>
+        <v>10305.006755425642</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3129163419508</v>
+        <v>7230.3126792993517</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12057505633899694</v>
+        <v>0.12056737215284274</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7462,14 +7462,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5600573018832885E-2</v>
+        <v>4.5597668412732086E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>426</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41175828540035703</v>
+        <v>0.41173207125409761</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -7489,11 +7489,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035909249363959</v>
+        <v>0.2003590889358437</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114096276132886</v>
+        <v>0.19114095520263008</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -7503,11 +7503,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688803412033329E-2</v>
+        <v>9.768880167736374E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779847881818629E-2</v>
+        <v>9.0779844291915587E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -7553,22 +7553,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="368" t="s">
+      <c r="B80" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="C80" s="368"/>
-      <c r="D80" s="368"/>
-      <c r="E80" s="368"/>
-      <c r="F80" s="368"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="374" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7612,22 +7612,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="368" t="s">
+      <c r="B89" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C89" s="368"/>
-      <c r="D89" s="368"/>
-      <c r="E89" s="368"/>
-      <c r="F89" s="368"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="368" t="s">
+      <c r="B90" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="368"/>
-      <c r="D90" s="368"/>
-      <c r="E90" s="368"/>
-      <c r="F90" s="368"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.121812330613826</v>
+        <v>12.12103981376579</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -7664,13 +7664,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="368" t="s">
+      <c r="B97" s="371" t="s">
         <v>353</v>
       </c>
-      <c r="C97" s="368"/>
-      <c r="D97" s="368"/>
-      <c r="E97" s="368"/>
-      <c r="F97" s="368"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7683,13 +7683,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="368" t="s">
+      <c r="B101" s="371" t="s">
         <v>336</v>
       </c>
-      <c r="C101" s="368"/>
-      <c r="D101" s="368"/>
-      <c r="E101" s="368"/>
-      <c r="F101" s="368"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0528292998542006</v>
+        <v>3.0526348446966884</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17132.727668168856</v>
+        <v>17132.75927384858</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1542605960627959</v>
+        <v>2.1541273505972445</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9917136665303571E-2</v>
+        <v>1.9915868009388996E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -7811,13 +7811,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="368" t="s">
+      <c r="B116" s="371" t="s">
         <v>354</v>
       </c>
-      <c r="C116" s="368"/>
-      <c r="D116" s="368"/>
-      <c r="E116" s="368"/>
-      <c r="F116" s="368"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1795369931472965</v>
+        <v>-3.1793344671276307</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.918660381570513</v>
+        <v>12.917841027032001</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -8005,13 +8005,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="369" t="s">
         <v>476</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8024,22 +8024,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="370" t="s">
         <v>355</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="368" t="s">
+      <c r="B139" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C139" s="368"/>
-      <c r="D139" s="368"/>
-      <c r="E139" s="368"/>
-      <c r="F139" s="368"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.5830914667662227</v>
+        <v>0.5830543257629508</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2506875503004666</v>
+        <v>5.250354530115124</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8337790170666892</v>
+        <v>5.8334088558780746</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842229420404653</v>
+        <v>0.54842230650841528</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67115288173702392</v>
+        <v>0.67111013151206389</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6143541153641028</v>
+        <v>6.6139346058403845</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2855069971011268</v>
+        <v>7.2850447373524485</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604779583071351</v>
+        <v>0.43604780999335013</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.8941343977184284</v>
+        <v>0.89407744430634128</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.399012218050146</v>
+        <v>10.398352669954194</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.293146615768574</v>
+        <v>11.292430114260537</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582680539546209</v>
+        <v>0.12582682426344416</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.82952128097411704</v>
+        <v>0.82946844320445867</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2595840923192405</v>
+        <v>9.2589968114381982</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.089105373293357</v>
+        <v>10.088465254642657</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261992250730056</v>
+        <v>0.22261993883957398</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -8372,13 +8372,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="372" t="s">
         <v>479</v>
       </c>
-      <c r="C179" s="368"/>
-      <c r="D179" s="368"/>
-      <c r="E179" s="368"/>
-      <c r="F179" s="368"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8386,13 +8386,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="370" t="s">
+      <c r="B182" s="373" t="s">
         <v>364</v>
       </c>
-      <c r="C182" s="370"/>
-      <c r="D182" s="370"/>
-      <c r="E182" s="370"/>
-      <c r="F182" s="370"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8429,22 +8429,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="368" t="s">
         <v>365</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="368" t="s">
         <v>366</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8468,17 +8468,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8495,6 +8484,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9183,19 +9183,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.308988212082</v>
+        <v>0.30896853055199996</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27643448572099999</v>
+        <v>0.27641687775599999</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22624295444199999</v>
+        <v>0.226228543512</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -10568,19 +10568,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.308988212082</v>
+        <v>0.30896853055199996</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27643448572099999</v>
+        <v>0.27641687775599999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22624295444199999</v>
+        <v>0.226228543512</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -11918,11 +11918,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.1918026301001419</v>
+        <v>8.1912808392909326</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1795369931472965</v>
+        <v>-3.1793344671276307</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17132.727668168856</v>
+        <v>17132.75927384858</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -12180,11 +12180,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14496.678437445085</v>
+        <v>-14496.662634605224</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13979.636165915572</v>
+        <v>-13979.62036307571</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>343</v>
@@ -12196,11 +12196,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1105056371759514</v>
+        <v>3.1105090279441381</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2255488958962317</v>
+        <v>3.2255525421206173</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -12213,7 +12213,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27959.272331831144</v>
+        <v>27959.24072615142</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>344</v>
@@ -12328,11 +12328,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26433.843555809999</v>
+        <v>-26432.159807159998</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0528292998542006</v>
+        <v>-3.0526348446966884</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -12345,11 +12345,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18653.315328665638</v>
+        <v>18652.161582600937</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1542605960627963</v>
+        <v>2.1541273505972445</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>172.458536976</v>
+        <v>172.447551936</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9917136665303575E-2</v>
+        <v>1.9915868009388996E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -12379,11 +12379,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7608.0696901683614</v>
+        <v>-7607.5506726230615</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.87865156712610071</v>
+        <v>-0.87859162609005492</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -12963,48 +12963,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.40727668168847</v>
+        <v>-523.40759273848585</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.99257309735128</v>
+        <v>-208.99324457435773</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.55692963955698</v>
+        <v>-420.55753943600337</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.37747420733274</v>
+        <v>-366.378076293709</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.9938112406042</v>
+        <v>-454.99418202488022</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.38366296672848</v>
+        <v>-503.38389426882884</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.10643531176856</v>
+        <v>-818.10662736260338</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.08539568237848</v>
+        <v>-947.08560245243791</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1695541999386</v>
+        <v>-1014.1697020930997</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.60272234966135</v>
+        <v>-468.60296696915537</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.48886111367852</v>
+        <v>-437.48901881965605</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -13018,48 +13018,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.899981672472</v>
+        <v>17798.899665615674</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.007426902648</v>
+        <v>16980.006755425642</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.443070360445</v>
+        <v>17261.442460563998</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.622525792667</v>
+        <v>16973.621923706291</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.006188759397</v>
+        <v>14670.005817975119</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.616337033272</v>
+        <v>11589.616105731171</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.893564688231</v>
+        <v>20402.893372637398</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.914604317622</v>
+        <v>19208.914397547564</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.83044580006</v>
+        <v>16944.830297906901</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.39727765034</v>
+        <v>17752.397033030844</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.511138886321</v>
+        <v>11857.510981180343</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7249954181179</v>
+        <v>-4449.7249164039185</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -13185,50 +13185,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3129163419508</v>
+        <v>7230.3126792993517</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.007426902648</v>
+        <v>10305.006755425642</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.443070360445</v>
+        <v>10350.442460563998</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.622525792667</v>
+        <v>10809.621923706291</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0061887593965</v>
+        <v>8651.0058179751195</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6163370332724</v>
+        <v>5607.616105731171</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.893564688231</v>
+        <v>12308.893372637398</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.914604317622</v>
+        <v>11857.914397547564</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.83044580006</v>
+        <v>10224.830297906901</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.39727765034</v>
+        <v>11296.397033030844</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5111388863206</v>
+        <v>7067.5109811803432</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -13293,50 +13293,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3129163419508</v>
+        <v>7230.3126792993517</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.007426902648</v>
+        <v>10305.006755425642</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.443070360445</v>
+        <v>10350.442460563998</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.622525792667</v>
+        <v>10809.621923706291</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0061887593965</v>
+        <v>8651.0058179751195</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6163370332724</v>
+        <v>5607.616105731171</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.893564688231</v>
+        <v>12308.893372637398</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.914604317622</v>
+        <v>11857.914397547564</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.83044580006</v>
+        <v>10224.830297906901</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.39727765034</v>
+        <v>11296.397033030844</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5111388863206</v>
+        <v>7067.5109811803432</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -14154,43 +14154,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421664498474155</v>
+        <v>0.18421665226961742</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337896526922865</v>
+        <v>0.19337897210074381</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787975254864306</v>
+        <v>0.18787975921309216</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391266951661475</v>
+        <v>0.18391267416500598</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957520013920368</v>
+        <v>0.19957520412226601</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967755980705443</v>
+        <v>0.19967756168660361</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636715960787085</v>
+        <v>0.19636716172162119</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838213821579976</v>
+        <v>0.20838214003454283</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847888553392349</v>
+        <v>0.20847888840666229</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986064102865807</v>
+        <v>0.21986064395282465</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -14292,48 +14292,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.59272331831147</v>
+        <v>279.59240726151421</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.00742690264872</v>
+        <v>594.00675542564227</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.44307036044302</v>
+        <v>539.44246056399663</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.62252579266726</v>
+        <v>532.621923706291</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.0061887593958</v>
+        <v>328.00581797511978</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.61633703327149</v>
+        <v>204.61610573117113</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.89356468823146</v>
+        <v>169.89337263739665</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.91460431762147</v>
+        <v>182.91439754756209</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83044580006145</v>
+        <v>130.83029790690034</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.39727765033862</v>
+        <v>216.39703303084463</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.51113888632148</v>
+        <v>139.51098118034398</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -14404,48 +14404,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.40727668168847</v>
+        <v>-523.40759273848585</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.99257309735128</v>
+        <v>-208.99324457435773</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.55692963955698</v>
+        <v>-420.55753943600337</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.37747420733274</v>
+        <v>-366.378076293709</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.9938112406042</v>
+        <v>-454.99418202488022</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.38366296672848</v>
+        <v>-503.38389426882884</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.10643531176856</v>
+        <v>-818.10662736260338</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.08539568237848</v>
+        <v>-947.08560245243791</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1695541999386</v>
+        <v>-1014.1697020930997</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.60272234966135</v>
+        <v>-468.60296696915537</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.48886111367852</v>
+        <v>-437.48901881965605</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -15490,50 +15490,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8727073363429665E-3</v>
+        <v>2.8727090710125459E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1173324909238972E-3</v>
+        <v>1.1173360808269502E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3712852805099238E-3</v>
+        <v>2.3712887188109847E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.130795341549183E-3</v>
+        <v>2.1307988431914404E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2840394323991441E-3</v>
+        <v>3.2840421086337505E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6075886075800541E-3</v>
+        <v>4.607590724742372E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2198815256128476E-3</v>
+        <v>7.2198832204831169E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9796662148703757E-3</v>
+        <v>8.9796681753336292E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432930739746338E-2</v>
+        <v>1.1432932406974721E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7229027423568229E-3</v>
+        <v>5.7229057298204171E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.050620448869332E-2</v>
+        <v>1.0506208275969743E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -15547,50 +15547,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688803412033329E-2</v>
+        <v>9.768880167736374E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0779847881818629E-2</v>
+        <v>9.0779844291915587E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.732762198969544E-2</v>
+        <v>9.7327618551394379E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8715991984556994E-2</v>
+        <v>9.8715988482914727E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1058846903127415</v>
+        <v>0.10588468763650688</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608247372594551</v>
+        <v>0.10608247160878317</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005783594722785</v>
+        <v>0.18005783425235761</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212680956023156</v>
+        <v>0.18212680759976832</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102237104367303</v>
+        <v>0.19102236937644468</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680463688784274</v>
+        <v>0.21680463390037913</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475567683019909</v>
+        <v>0.28475567304292265</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422200853008332E-2</v>
+        <v>2.4422200419340935E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -15719,50 +15719,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683385929428931E-2</v>
+        <v>3.9683384628426736E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093439190908373E-2</v>
+        <v>5.5093435601005325E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360358776009813E-2</v>
+        <v>5.8360355337708752E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867110953523625E-2</v>
+        <v>6.2867107451881371E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2440949199617436E-2</v>
+        <v>6.244094652338282E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327826171232049E-2</v>
+        <v>5.1327824054069722E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862737342306912</v>
+        <v>0.10862737172819886</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242926523483097</v>
+        <v>0.11242926327436772</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526650334588484</v>
+        <v>0.11526650167865647</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1379594694517762</v>
+        <v>0.13795946646431259</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972481782104945</v>
+        <v>0.16972481403377304</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -15826,50 +15826,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683385929428931E-2</v>
+        <v>3.9683384628426736E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093439190908373E-2</v>
+        <v>5.5093435601005325E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360358776009813E-2</v>
+        <v>5.8360355337708752E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867110953523625E-2</v>
+        <v>6.2867107451881371E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2440949199617436E-2</v>
+        <v>6.244094652338282E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327826171232049E-2</v>
+        <v>5.1327824054069722E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862737342306912</v>
+        <v>0.10862737172819886</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242926523483097</v>
+        <v>0.11242926327436772</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526650334588484</v>
+        <v>0.11526650167865647</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1379594694517762</v>
+        <v>0.13795946646431259</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972481782104945</v>
+        <v>0.16972481403377304</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -15895,24 +15895,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.308988212082</v>
+        <v>0.30896853055199996</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27643448572099999</v>
+        <v>0.27641687775599999</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22624295444199999</v>
+        <v>0.226228543512</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -15951,24 +15951,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2977.1412493410166</v>
+        <v>2976.9516152626861</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2977.1412493410166</v>
+        <v>2976.9516152626861</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2675.4676585274879</v>
+        <v>2675.2972400619074</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2393.5913971110963</v>
+        <v>2393.4389332336796</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1958.9928803453558</v>
+        <v>1958.868098960058</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -16006,24 +16006,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41175828540035703</v>
+        <v>0.41173207125409761</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28890238754887038</v>
+        <v>0.28888400424340382</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25848822512622321</v>
+        <v>0.25847177550669947</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22143154318291747</v>
+        <v>0.22141745105670102</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22644682451975989</v>
+        <v>0.2264324103088578</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -16082,24 +16082,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5600573018832885E-2</v>
+        <v>4.5597668412732086E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5600573018832885E-2</v>
+        <v>4.5597668412732086E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0979868976392574E-2</v>
+        <v>4.0977258693899198E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6662398636737398E-2</v>
+        <v>3.6660063362864717E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0005696875596816E-2</v>
+        <v>3.0003785611671087E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -16219,46 +16219,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8226866701624349E-2</v>
+        <v>4.8226889540451401E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304294044861667E-2</v>
+        <v>-1.6304298194159128E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956930916214974E-2</v>
+        <v>1.6956931063470959E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702899558408978</v>
+        <v>0.1570289837859884</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578876833766252</v>
+        <v>0.26578876160709641</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.4319621233974531</v>
+        <v>-0.43196212938728751</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157544294680456E-2</v>
+        <v>6.2157545730032071E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361503768122618</v>
+        <v>0.13361503537278452</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490579059256353E-2</v>
+        <v>-4.5490574237459391E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714363070947765</v>
+        <v>0.49714362999170514</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -16830,43 +16830,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143610850129491</v>
+        <v>1.2143611641410434</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920177041752719</v>
+        <v>1.3920177861860126</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756262038307934</v>
+        <v>1.3756262804519559</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871218836477179</v>
+        <v>1.3871219431001096</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848689699865045</v>
+        <v>2.9848690931059285</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067787056136928</v>
+        <v>1.3067787260028483</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.435159601655718</v>
+        <v>1.4351596266810323</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994836511404209</v>
+        <v>1.2994836699363066</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941613076196453</v>
+        <v>1.3941613378097171</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917550658585602</v>
+        <v>1.8917551080715944</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -16938,48 +16938,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688803412033329E-2</v>
+        <v>9.768880167736374E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0779847881818629E-2</v>
+        <v>9.0779844291915587E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.732762198969544E-2</v>
+        <v>9.7327618551394379E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8715991984556994E-2</v>
+        <v>9.8715988482914727E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1058846903127415</v>
+        <v>0.10588468763650688</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608247372594551</v>
+        <v>0.10608247160878317</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005783594722785</v>
+        <v>0.18005783425235761</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212680956023156</v>
+        <v>0.18212680759976832</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102237104367303</v>
+        <v>0.19102236937644468</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680463688784274</v>
+        <v>0.21680463390037913</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475567683019909</v>
+        <v>0.28475567304292265</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -17103,50 +17103,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035909249363959</v>
+        <v>0.2003590889358437</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114096276132886</v>
+        <v>0.19114095520263008</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122218936573033</v>
+        <v>0.20122218225713717</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032468248361463</v>
+        <v>0.21032467502300178</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338007920748998</v>
+        <v>0.19338007431981016</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.13711141217638473</v>
+        <v>0.13711140943995612</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766109193266695</v>
+        <v>0.2576610895073233</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404506240644882</v>
+        <v>0.27404505945655211</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.2582069401264771</v>
+        <v>0.25820693787286708</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774651641178138</v>
+        <v>0.26774651272236316</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861258089537456</v>
+        <v>0.1686125786528119</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -17224,50 +17224,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.909135924796037</v>
+        <v>0.90907798603243428</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2957464725920984</v>
+        <v>1.2956638533896403</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3014595276440233</v>
+        <v>1.3013765522939902</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.359196522389877</v>
+        <v>1.3591098703531064</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0877731853150749</v>
+        <v>1.0877038511316208</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70509886964192359</v>
+        <v>0.70505392808753731</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5477141119101714</v>
+        <v>1.5476155034790997</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4910082433061442</v>
+        <v>1.4909132450012039</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2856650591449283</v>
+        <v>1.2855831479262336</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4204033358871528</v>
+        <v>1.4203128301230792</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.88866531083809441</v>
+        <v>0.88860868596019593</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -17281,50 +17281,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12057505633899694</v>
+        <v>0.12056737215284274</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17184966480001304</v>
+        <v>0.17183870734610615</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17260736440902166</v>
+        <v>0.17259635972068835</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18026479076788821</v>
+        <v>0.18025329845531915</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.1442670007049171</v>
+        <v>0.14425780518987014</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.3514438944552206E-2</v>
+        <v>9.3508478526198577E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20526712359551344</v>
+        <v>0.20525404555425725</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19774645136686264</v>
+        <v>0.19773385212217559</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17051260731365098</v>
+        <v>0.17050174375679492</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18838240529007333</v>
+        <v>0.18837040187308743</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11786012080080828</v>
+        <v>0.11785261087005251</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3129163419508</v>
+        <v>7230.3126792993517</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.172217892687</v>
+        <v>96404.169057324689</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17132.727668168856</v>
+        <v>17132.75927384858</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89416.299886061533</v>
+        <v>89416.328331173267</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0887533899999999</v>
+        <v>1.08868404</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>12.97834311091939</v>
+        <v>12.977519952831315</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7206544411038</v>
+        <v>7373.7204126969455</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2750273870734</v>
+        <v>6859.2748025087867</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9727755683034</v>
+        <v>7519.9725290293345</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2776857270346</v>
+        <v>6507.2774723888242</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1256958899139</v>
+        <v>7669.1254444610322</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.343787804276</v>
+        <v>6173.3435854139398</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2369505438955</v>
+        <v>7821.2366941281143</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.546372073828</v>
+        <v>5856.5461800695548</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3652158337582</v>
+        <v>7976.3649543321653</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0060458662019</v>
+        <v>5556.0058637150096</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5703318627066</v>
+        <v>8134.5700651744291</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -18490,7 +18490,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.8885442959236</v>
+        <v>5270.8883714921831</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.913325616717</v>
+        <v>8295.913053638882</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4024144395325</v>
+        <v>5000.40225050356</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4564345054569</v>
+        <v>8460.4561571331487</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.7968183545991</v>
+        <v>4743.796662831327</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2631303701073</v>
+        <v>8628.2628474963312</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3594488411845</v>
+        <v>4500.3593012988977</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.3981439673771</v>
+        <v>8799.3978554830155</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4145521601467</v>
+        <v>4269.4144121892859</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9274899391239</v>
+        <v>8973.9271957328947</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3210522195936</v>
+        <v>4050.3209194316159</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9184922772474</v>
+        <v>9151.918192235662</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4707710224448</v>
+        <v>3842.4706450487461</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.439810293632</v>
+        <v>9333.4395043009517</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2867404352455</v>
+        <v>3645.2866209261379</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5614651052183</v>
+        <v>9518.5611530434053</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2216005919495</v>
+        <v>3458.2214872156892</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3548666443457</v>
+        <v>9707.3545483930266</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7560804867735</v>
+        <v>3280.7559729286418</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.8928412048699</v>
+        <v>9899.8925166412773</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.3975565384694</v>
+        <v>3112.3974544998969</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.249659534589</v>
+        <v>10096.249328533526</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6786851247252</v>
+        <v>2952.6785883224652</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.501065484903</v>
+        <v>10296.500727918687</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1561052907919</v>
+        <v>2801.1560134561328</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.72430522869</v>
+        <v>10500.723960967105</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4092080311916</v>
+        <v>2657.4091209092103</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10708.998157057709</v>
+        <v>10708.99780596796</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.038968728189</v>
+        <v>2521.0388860770458</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.27539254805</v>
+        <v>98316.272169292613</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.94389575328</v>
+        <v>23144.943136956572</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110203.99136117246</v>
+        <v>110203.98774818353</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19142,7 +19142,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110203.99136117246</v>
+        <v>110203.98774818353</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -19172,19 +19172,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.172217892701</v>
+        <v>96404.169057324703</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.7924890391</v>
+        <v>97921.789278716606</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.197040621773</v>
+        <v>99461.193779830588</v>
       </c>
       <c r="E56" s="123">
-        <v>101022.86400105935</v>
+        <v>101022.86068906962</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.2789626217</v>
+        <v>102607.27559868761</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19193,19 +19193,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.172217892716</v>
+        <v>96404.169057324732</v>
       </c>
       <c r="C57" s="123">
-        <v>99376.859100077403</v>
+        <v>99376.855842051198</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.62942161753</v>
+        <v>102492.62606144218</v>
       </c>
       <c r="E57" s="123">
-        <v>105759.87229224891</v>
+        <v>105759.86882495845</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.4395844916</v>
+        <v>109187.43600482987</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -19214,19 +19214,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.172217892701</v>
+        <v>96404.169057324718</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.3443123372</v>
+        <v>101173.34099541401</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.77781608954</v>
+        <v>106330.7743300822</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.4750418035</v>
+        <v>111913.47137276991</v>
       </c>
       <c r="F58" s="123">
-        <v>117961.96835697099</v>
+        <v>117961.96448964026</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -19245,19 +19245,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.172217892701</v>
+        <v>96404.169057324732</v>
       </c>
       <c r="C59" s="341">
-        <v>102997.88863104041</v>
+        <v>102997.88525430034</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.1101349519</v>
+        <v>110332.10651776266</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.43087984016</v>
+        <v>118504.42699472501</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.74100197603</v>
+        <v>127625.73681782281</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -19276,19 +19276,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.172217892701</v>
+        <v>96404.169057324732</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.41529423071</v>
+        <v>104688.41186206749</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.45500159009</v>
+        <v>114140.45125954597</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.39667034778</v>
+        <v>124956.39257370782</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.16854924388</v>
+        <v>137367.16404572231</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -19307,19 +19307,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.172217892701</v>
+        <v>96404.169057324718</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.1692362512</v>
+        <v>106173.16575541096</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.53790334422</v>
+        <v>117578.53404858407</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.31376058697</v>
+        <v>130953.30946734073</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.56563199722</v>
+        <v>146703.56082238597</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -19399,23 +19399,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -19426,23 +19426,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675739</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.433985576281023</v>
+        <v>11.433260839302132</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.627549533585709</v>
+        <v>11.62681246087565</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.823912755029676</v>
+        <v>11.823163168192794</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.023136298741727</v>
+        <v>12.022374015491149</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.243160763487728</v>
+        <v>11.242448187675743</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.616944923182349</v>
+        <v>11.616208526298642</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.008720322878126</v>
+        <v>12.007958958350255</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.419541805031562</v>
+        <v>12.418754259062512</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.850522399659859</v>
+        <v>12.849707387519791</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -19480,23 +19480,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.243160763487726</v>
+        <v>11.242448187675741</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.842834074001637</v>
+        <v>11.842083281318846</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.491327179661049</v>
+        <v>12.490535058847097</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.193292732726425</v>
+        <v>13.192455876009815</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.953827252785556</v>
+        <v>13.952941927596228</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -19507,23 +19507,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.243160763487726</v>
+        <v>11.242448187675743</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.072251362811706</v>
+        <v>12.071485949483423</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>12.994452701366082</v>
+        <v>12.993628516622119</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.022036218718577</v>
+        <v>14.021146546607026</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.168945185064517</v>
+        <v>15.16798242103606</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -19534,23 +19534,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.243160763487726</v>
+        <v>11.242448187675743</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.284817338740373</v>
+        <v>12.284038378692074</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.473312077486288</v>
+        <v>13.472457375281254</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.83330316574764</v>
+        <v>14.832361792011968</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.39382740586052</v>
+        <v>16.392786580719864</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -19560,23 +19560,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.243160763487726</v>
+        <v>11.242448187675741</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.471509555770487</v>
+        <v>12.470718697923482</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.905614899587803</v>
+        <v>13.904732646946877</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.587352517116257</v>
+        <v>15.586363088204315</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.567781298908123</v>
+        <v>17.566665658291317</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.850522399659859</v>
+        <v>12.849707387519791</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.022036218718577</v>
+        <v>14.021146546607026</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.994452701366082</v>
+        <v>12.993628516622119</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.072251362811706</v>
+        <v>12.071485949483423</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.243160763487728</v>
+        <v>11.242448187675743</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2977.1412493410166</v>
+        <v>2976.9516152626861</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39695.216657880221</v>
+        <v>39692.688203502483</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>4.9912566611984541</v>
+        <v>4.9906208282751701</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2406104282567458</v>
+        <v>5.240276618657127</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3036.190573693867</v>
+        <v>3035.9971783683327</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -20032,7 +20032,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2824.363324366388</v>
+        <v>2824.1834217379837</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3096.4110963253684</v>
+        <v>3096.2138651511627</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2679.425502498967</v>
+        <v>2679.2548319317798</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3157.8260470594505</v>
+        <v>3157.6249039554427</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2541.9254532532336</v>
+        <v>2541.7635409856789</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3220.4591164658709</v>
+        <v>3220.2539838419193</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2411.4814925328005</v>
+        <v>2411.3278891153109</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3284.3344649987566</v>
+        <v>3284.125263725778</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2287.7315231198845</v>
+        <v>2287.5858021672925</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3349.4767323164006</v>
+        <v>3349.2633816958473</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2170.332029535673</v>
+        <v>2170.1937865436139</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3415.9110467859132</v>
+        <v>3415.6934645186425</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2058.9571244814274</v>
+        <v>2058.8259757034816</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3483.6630351763847</v>
+        <v>3483.4411373309144</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1953.2976442133586</v>
+        <v>1953.1732255958182</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3552.7588325443121</v>
+        <v>3552.5325335244424</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1853.0602903401414</v>
+        <v>1852.9422565114385</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3623.2250923150905</v>
+        <v>3622.994304826886</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1757.9668156607947</v>
+        <v>1757.85483897279</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3695.0889965644628</v>
+        <v>3694.8536315825804</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1667.7532517829097</v>
+        <v>1667.6470214013802</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3768.3782665038993</v>
+        <v>3768.1382332372455</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1582.1691763771894</v>
+        <v>1582.0683974189885</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3843.121173173939</v>
+        <v>3842.8763790306489</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -20296,7 +20296,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1500.9770180342728</v>
+        <v>1500.8814107487694</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3919.3465483496343</v>
+        <v>3919.0968989013531</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1423.9513967942191</v>
+        <v>1423.8606957867416</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>3997.0837956622872</v>
+        <v>3996.8291946077461</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1350.8784985180296</v>
+        <v>1350.7924520131619</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4076.3629019417858</v>
+        <v>4076.1032510696546</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -20362,7 +20362,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1281.5554813645408</v>
+        <v>1281.4738505072237</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4157.2144487839005</v>
+        <v>4156.9496479349009</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1215.7899127251374</v>
+        <v>1215.7124709176337</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4239.6696243470124</v>
+        <v>4239.3995713752847</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1153.3992350532783</v>
+        <v>1153.3257673261644</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4323.7602353828197</v>
+        <v>4323.484826116518</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1094.2102591060438</v>
+        <v>1094.1405615214799</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4409.5187195056651</v>
+        <v>4409.2378477067741</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1038.0586831910032</v>
+        <v>1037.992562276625</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40482.540982584898</v>
+        <v>40479.96237824444</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9530.1224142028314</v>
+        <v>9529.5153768374403</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45377.406527152118</v>
+        <v>45374.5161360208</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -20724,7 +20724,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45377.406527152118</v>
+        <v>45374.5161360208</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -20754,19 +20754,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39695.216657880228</v>
+        <v>39692.68820350249</v>
       </c>
       <c r="C51" s="123">
-        <v>40320.109378616296</v>
+        <v>40317.541120633279</v>
       </c>
       <c r="D51" s="123">
-        <v>40953.971957313493</v>
+        <v>40951.363324374819</v>
       </c>
       <c r="E51" s="123">
-        <v>41597.00126730965</v>
+        <v>41594.351675524784</v>
       </c>
       <c r="F51" s="123">
-        <v>42249.39725524524</v>
+        <v>42246.70610798768</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -20775,19 +20775,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39695.216657880235</v>
+        <v>39692.68820350249</v>
       </c>
       <c r="C52" s="123">
-        <v>40919.245111520737</v>
+        <v>40916.638690567604</v>
       </c>
       <c r="D52" s="123">
-        <v>42202.189356819428</v>
+        <v>42199.501216549295</v>
       </c>
       <c r="E52" s="123">
-        <v>43547.50367921713</v>
+        <v>43544.72984686181</v>
       </c>
       <c r="F52" s="123">
-        <v>44958.832910565332</v>
+        <v>44955.969181192835</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -20796,19 +20796,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39695.216657880228</v>
+        <v>39692.688203502483</v>
       </c>
       <c r="C53" s="123">
-        <v>41658.962782267925</v>
+        <v>41656.309243738913</v>
       </c>
       <c r="D53" s="123">
-        <v>43782.578758839358</v>
+        <v>43779.789952976775</v>
       </c>
       <c r="E53" s="123">
-        <v>46081.300596408662</v>
+        <v>46078.365369546715</v>
       </c>
       <c r="F53" s="123">
-        <v>48571.817833117544</v>
+        <v>48568.723968521888</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -20817,19 +20817,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39695.216657880235</v>
+        <v>39692.68820350249</v>
       </c>
       <c r="C54" s="123">
-        <v>42410.234022574121</v>
+        <v>42407.532630544956</v>
       </c>
       <c r="D54" s="123">
-        <v>45430.160493771153</v>
+        <v>45427.266742386142</v>
       </c>
       <c r="E54" s="123">
-        <v>48795.181271428111</v>
+        <v>48792.073179318133</v>
       </c>
       <c r="F54" s="123">
-        <v>52550.956287923706</v>
+        <v>52547.608965332533</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -20838,19 +20838,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39695.216657880235</v>
+        <v>39692.68820350249</v>
       </c>
       <c r="C55" s="123">
-        <v>43106.32238283295</v>
+        <v>43103.576652271084</v>
       </c>
       <c r="D55" s="123">
-        <v>46998.278046271342</v>
+        <v>46995.284410970235</v>
       </c>
       <c r="E55" s="123">
-        <v>51451.831642789286</v>
+        <v>51448.554330812854</v>
       </c>
       <c r="F55" s="123">
-        <v>56562.069792138536</v>
+        <v>56558.466974846648</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -20859,19 +20859,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39695.216657880243</v>
+        <v>39692.688203502497</v>
       </c>
       <c r="C56" s="123">
-        <v>43717.682120240723</v>
+        <v>43714.897448079981</v>
       </c>
       <c r="D56" s="123">
-        <v>48413.937166961907</v>
+        <v>48410.85335884396</v>
       </c>
       <c r="E56" s="123">
-        <v>53921.111941554271</v>
+        <v>53917.677344567026</v>
       </c>
       <c r="F56" s="123">
-        <v>60406.408646749929</v>
+        <v>60402.560957752452</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -20921,23 +20921,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>4.9912566611984541</v>
+        <v>4.9906208282751701</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>4.9912566611984541</v>
+        <v>4.9906208282751701</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>4.9912566611984541</v>
+        <v>4.9906208282751701</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>4.9912566611984541</v>
+        <v>4.9906208282751701</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>4.9912566611984541</v>
+        <v>4.9906208282751701</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -20948,23 +20948,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.9912566611984559</v>
+        <v>4.9906208282751718</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.0698303589260663</v>
+        <v>5.0691845165507932</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1495319221011542</v>
+        <v>5.1488759265958475</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2303861054786118</v>
+        <v>5.2297198100117406</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.31241805024887</v>
+        <v>5.3117413047861781</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -20975,23 +20975,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>4.9912566611984568</v>
+        <v>4.9906208282751718</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.145165385904126</v>
+        <v>5.144509946649011</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3064821527449011</v>
+        <v>5.3058061634523108</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.47564130184203</v>
+        <v>5.4749437634760181</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6531011325270057</v>
+        <v>5.652380987669166</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -21002,23 +21002,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>4.9912566611984559</v>
+        <v>4.990620828275171</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2381771153360193</v>
+        <v>5.2375098273774929</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5051995246162919</v>
+        <v>5.5044982208476005</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.7942396571566057</v>
+        <v>5.7935015327543757</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1073960471239355</v>
+        <v>6.106618029933899</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -21029,23 +21029,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>4.9912566611984568</v>
+        <v>4.9906208282751718</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3326415848176518</v>
+        <v>5.3319622630921097</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7123656267747176</v>
+        <v>5.7116379322516968</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1354816539854475</v>
+        <v>6.1347000589883134</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.607730923478349</v>
+        <v>6.6068891689554832</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -21056,23 +21056,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>4.9912566611984568</v>
+        <v>4.9906208282751718</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.420167386600494</v>
+        <v>5.4194769150202786</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9095399424338559</v>
+        <v>5.9087871300036579</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.4695275410961175</v>
+        <v>6.4687033922117898</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1120863265306946</v>
+        <v>7.1111803225027295</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -21082,23 +21082,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>4.9912566611984586</v>
+        <v>4.9906208282751736</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.4970394537824045</v>
+        <v>5.4963391895198024</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.0875442112361133</v>
+        <v>6.0867687229584728</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.7800136091229097</v>
+        <v>6.7791499076213393</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.5954715686710461</v>
+        <v>7.5945039865130726</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6531011325270057</v>
+        <v>5.652380987669166</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1354816539854475</v>
+        <v>6.1347000589883134</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7123656267747176</v>
+        <v>5.7116379322516968</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3326415848176518</v>
+        <v>5.3319622630921097</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>4.9912566611984568</v>
+        <v>4.9906208282751718</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.262488702132513</v>
+        <v>13.261647446864</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.007426902648</v>
+        <v>10305.006755425642</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3129163419508</v>
+        <v>7230.3126792993517</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.005214413120985E-2</v>
+        <v>6.0052136251482979E-2</v>
       </c>
       <c r="E14" s="377"/>
       <c r="F14" s="377"/>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.243160763487726</v>
+        <v>11.242448187675736</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>12.994452701366082</v>
+        <v>12.993628516622119</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.072251362811706</v>
+        <v>12.071485949483423</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.022036218718577</v>
+        <v>14.021146546607026</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.015529137125705</v>
+        <v>13.014703609191359</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.243160763487728</v>
+        <v>11.242448187675743</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.850522399659859</v>
+        <v>12.849707387519791</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.918660381570513</v>
+        <v>12.917841027032001</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>12.97834311091939</v>
+        <v>12.977519952831315</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8014139328220632E-2</v>
+        <v>-6.8013813163632031E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34382832056199997</v>
+        <v>0.34380641983199994</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.5830914667662227</v>
+        <v>0.5830543257629508</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2506875503004666</v>
+        <v>5.250354530115124</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8337790170666892</v>
+        <v>5.8334088558780746</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842229420404653</v>
+        <v>0.54842230650841528</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -22175,7 +22175,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2352638333289685</v>
+        <v>0.23523677184925385</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67115288173702392</v>
+        <v>0.67111013151206389</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6143541153641028</v>
+        <v>6.6139346058403845</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.2855069971011268</v>
+        <v>7.2850447373524485</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604779583071351</v>
+        <v>0.43604780999335013</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.8941343977184284</v>
+        <v>0.89407744430634128</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.399012218050146</v>
+        <v>10.398352669954194</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -22285,7 +22285,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.293146615768574</v>
+        <v>11.292430114260537</v>
       </c>
       <c r="D99" t="s">
         <v>379</v>
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582680539546209</v>
+        <v>0.12582682426344416</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.82952128097411704</v>
+        <v>0.82946844320445867</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2595840923192405</v>
+        <v>9.2589968114381982</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.089105373293357</v>
+        <v>10.088465254642657</v>
       </c>
       <c r="D105" t="s">
         <v>379</v>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261992250730056</v>
+        <v>0.22261993883957398</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2806E7-246D-4974-A8E5-C240D3749C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88BC6DA-21DB-402E-8E2A-DAA8C6CA1AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4737,6 +4737,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4746,16 +4755,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>65287.364878319997</v>
+        <v>65720.304963720002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.08868404</v>
+        <v>1.0942760599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5240,13 +5240,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="368" t="s">
         <v>491</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="368"/>
+      <c r="D18" s="368"/>
+      <c r="E18" s="368"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.917841027032001</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23523677184925385</v>
+        <v>0.23459463611465181</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8334088558780746</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2850447373524485</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.292430114260537</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.088465254642657</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5459,22 +5459,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="368" t="s">
         <v>494</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="368"/>
+      <c r="D36" s="368"/>
+      <c r="E36" s="368"/>
+      <c r="F36" s="368"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="369" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.59240726151421</v>
+        <v>279.61789242274239</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.40759273848585</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7249164039185</v>
+        <v>-4449.731287694226</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5664,10 +5664,10 @@
       <c r="B61" s="367" t="s">
         <v>501</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="370"/>
+      <c r="D61" s="370"/>
+      <c r="E61" s="370"/>
+      <c r="F61" s="370"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5683,22 +5683,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="368" t="s">
         <v>502</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="368"/>
+      <c r="D64" s="368"/>
+      <c r="E64" s="368"/>
+      <c r="F64" s="368"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="368" t="s">
         <v>503</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="368"/>
+      <c r="D65" s="368"/>
+      <c r="E65" s="368"/>
+      <c r="F65" s="368"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.006755425642</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3126792993517</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12056737215284274</v>
+        <v>0.12038865296639753</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5742,14 +5742,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5597668412732086E-2</v>
+        <v>4.5529957806060596E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>505</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41173207125409761</v>
+        <v>0.41384583689866911</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5769,11 +5769,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.2003590889358437</v>
+        <v>0.20035937581782973</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114095520263008</v>
+        <v>0.19114156469642632</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5783,11 +5783,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.768880167736374E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779844291915587E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5833,22 +5833,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="368" t="s">
         <v>508</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="368"/>
+      <c r="D80" s="368"/>
+      <c r="E80" s="368"/>
+      <c r="F80" s="368"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5892,22 +5892,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="368" t="s">
         <v>509</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="368"/>
+      <c r="D89" s="368"/>
+      <c r="E89" s="368"/>
+      <c r="F89" s="368"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="368" t="s">
         <v>510</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="368"/>
+      <c r="D90" s="368"/>
+      <c r="E90" s="368"/>
+      <c r="F90" s="368"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.12103981376579</v>
+        <v>12.18333168019943</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5944,13 +5944,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="368" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="368"/>
+      <c r="D97" s="368"/>
+      <c r="E97" s="368"/>
+      <c r="F97" s="368"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5963,13 +5963,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="368" t="s">
         <v>513</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="368"/>
+      <c r="D101" s="368"/>
+      <c r="E101" s="368"/>
+      <c r="F101" s="368"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0526348446966884</v>
+        <v>3.0683146879542789</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17132.75927384858</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1541273505972445</v>
+        <v>2.1648699400997713</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9915868009388996E-2</v>
+        <v>2.0018165763497582E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6091,13 +6091,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="368" t="s">
         <v>518</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="368"/>
+      <c r="D116" s="368"/>
+      <c r="E116" s="368"/>
+      <c r="F116" s="368"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1793344671276307</v>
+        <v>-3.1956651023474385</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.85 HKD</v>
+        <v>12.92 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.02 HKD</v>
+        <v>14.09 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>12.99 HKD</v>
+        <v>13.06 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.07 HKD</v>
+        <v>12.13 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.24 HKD</v>
+        <v>11.3 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.917841027032001</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6285,13 +6285,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="372" t="s">
         <v>526</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6304,22 +6304,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="373" t="s">
         <v>528</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="368" t="s">
         <v>529</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="368"/>
+      <c r="D139" s="368"/>
+      <c r="E139" s="368"/>
+      <c r="F139" s="368"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.5830543257629508</v>
+        <v>0.58604918132338757</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.250354530115124</v>
+        <v>5.2772069444640133</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8334088558780746</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842230650841528</v>
+        <v>0.5484213143271619</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67111013151206389</v>
+        <v>0.67455728526809577</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6139346058403845</v>
+        <v>6.6477609144246523</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2850447373524485</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604780999335013</v>
+        <v>0.43604666796787828</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89407744430634128</v>
+        <v>0.89866986852348141</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.398352669954194</v>
+        <v>10.45153400710732</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.292430114260537</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582682426344416</v>
+        <v>0.12582530281537296</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.82946844320445867</v>
+        <v>0.83372900361808255</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2589968114381982</v>
+        <v>9.3063510267411278</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.088465254642657</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261993883957398</v>
+        <v>0.22261862186231296</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6652,13 +6652,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="374" t="s">
         <v>536</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="368"/>
+      <c r="D179" s="368"/>
+      <c r="E179" s="368"/>
+      <c r="F179" s="368"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6666,13 +6666,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="370" t="s">
         <v>538</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="370"/>
+      <c r="D182" s="370"/>
+      <c r="E182" s="370"/>
+      <c r="F182" s="370"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6709,22 +6709,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="371" t="s">
         <v>545</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="371" t="s">
         <v>546</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6748,12 +6748,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6766,15 +6769,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -6915,7 +6915,7 @@
         <v>465</v>
       </c>
       <c r="C12" s="50">
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>65287.364878319997</v>
+        <v>65720.304963720002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -6963,7 +6963,7 @@
         <v>469</v>
       </c>
       <c r="C16" s="50">
-        <v>1.08868404</v>
+        <v>1.0942760599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -6973,13 +6973,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="368" t="s">
         <v>470</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="368"/>
+      <c r="D18" s="368"/>
+      <c r="E18" s="368"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.917841027032001</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23523677184925385</v>
+        <v>0.23459463611465181</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8334088558780746</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2850447373524485</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.292430114260537</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.088465254642657</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -7179,22 +7179,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="368" t="s">
         <v>471</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="368"/>
+      <c r="D36" s="368"/>
+      <c r="E36" s="368"/>
+      <c r="F36" s="368"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="369" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.59240726151421</v>
+        <v>279.61789242274239</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.40759273848585</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7249164039185</v>
+        <v>-4449.731287694226</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7384,10 +7384,10 @@
       <c r="B61" s="367" t="s">
         <v>330</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="370"/>
+      <c r="D61" s="370"/>
+      <c r="E61" s="370"/>
+      <c r="F61" s="370"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7403,22 +7403,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="368" t="s">
         <v>335</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="368"/>
+      <c r="D64" s="368"/>
+      <c r="E64" s="368"/>
+      <c r="F64" s="368"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="368" t="s">
         <v>350</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="368"/>
+      <c r="D65" s="368"/>
+      <c r="E65" s="368"/>
+      <c r="F65" s="368"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.006755425642</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3126792993517</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12056737215284274</v>
+        <v>0.12038865296639753</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7462,14 +7462,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5597668412732086E-2</v>
+        <v>4.5529957806060596E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>426</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41173207125409761</v>
+        <v>0.41384583689866911</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -7489,11 +7489,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.2003590889358437</v>
+        <v>0.20035937581782973</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114095520263008</v>
+        <v>0.19114156469642632</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -7503,11 +7503,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.768880167736374E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779844291915587E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -7553,22 +7553,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="368" t="s">
         <v>473</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="368"/>
+      <c r="D80" s="368"/>
+      <c r="E80" s="368"/>
+      <c r="F80" s="368"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7612,22 +7612,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="368" t="s">
         <v>351</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="368"/>
+      <c r="D89" s="368"/>
+      <c r="E89" s="368"/>
+      <c r="F89" s="368"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="368" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="368"/>
+      <c r="D90" s="368"/>
+      <c r="E90" s="368"/>
+      <c r="F90" s="368"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.12103981376579</v>
+        <v>12.18333168019943</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -7664,13 +7664,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="368" t="s">
         <v>353</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="368"/>
+      <c r="D97" s="368"/>
+      <c r="E97" s="368"/>
+      <c r="F97" s="368"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7683,13 +7683,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="368" t="s">
         <v>336</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="368"/>
+      <c r="D101" s="368"/>
+      <c r="E101" s="368"/>
+      <c r="F101" s="368"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0526348446966884</v>
+        <v>3.0683146879542789</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17132.75927384858</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1541273505972445</v>
+        <v>2.1648699400997713</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9915868009388996E-2</v>
+        <v>2.0018165763497582E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -7811,13 +7811,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="368" t="s">
         <v>354</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="368"/>
+      <c r="D116" s="368"/>
+      <c r="E116" s="368"/>
+      <c r="F116" s="368"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1793344671276307</v>
+        <v>-3.1956651023474385</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.85 HKD</v>
+        <v>12.92 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.02 HKD</v>
+        <v>14.09 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>12.99 HKD</v>
+        <v>13.06 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.07 HKD</v>
+        <v>12.13 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.24 HKD</v>
+        <v>11.3 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.917841027032001</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -8005,13 +8005,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="372" t="s">
         <v>476</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8024,22 +8024,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="373" t="s">
         <v>355</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="368" t="s">
         <v>478</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="368"/>
+      <c r="D139" s="368"/>
+      <c r="E139" s="368"/>
+      <c r="F139" s="368"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.5830543257629508</v>
+        <v>0.58604918132338757</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.250354530115124</v>
+        <v>5.2772069444640133</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8334088558780746</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842230650841528</v>
+        <v>0.5484213143271619</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67111013151206389</v>
+        <v>0.67455728526809577</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6139346058403845</v>
+        <v>6.6477609144246523</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2850447373524485</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604780999335013</v>
+        <v>0.43604666796787828</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89407744430634128</v>
+        <v>0.89866986852348141</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.398352669954194</v>
+        <v>10.45153400710732</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.292430114260537</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582682426344416</v>
+        <v>0.12582530281537296</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.82946844320445867</v>
+        <v>0.83372900361808255</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2589968114381982</v>
+        <v>9.3063510267411278</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.088465254642657</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261993883957398</v>
+        <v>0.22261862186231296</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -8372,13 +8372,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="374" t="s">
         <v>479</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="368"/>
+      <c r="D179" s="368"/>
+      <c r="E179" s="368"/>
+      <c r="F179" s="368"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8386,13 +8386,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="370"/>
+      <c r="D182" s="370"/>
+      <c r="E182" s="370"/>
+      <c r="F182" s="370"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8429,22 +8429,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="371" t="s">
         <v>365</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="371" t="s">
         <v>366</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8468,6 +8468,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8484,17 +8495,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9183,19 +9183,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.30896853055199996</v>
+        <v>0.31055554582799999</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27641687775599999</v>
+        <v>0.27783669163399999</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.226228543512</v>
+        <v>0.227390565268</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -10568,19 +10568,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.30896853055199996</v>
+        <v>0.31055554582799999</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27641687775599999</v>
+        <v>0.27783669163399999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.226228543512</v>
+        <v>0.227390565268</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -11918,11 +11918,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.1912808392909326</v>
+        <v>8.2333553114021711</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1793344671276307</v>
+        <v>-3.1956651023474385</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17132.75927384858</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -12180,11 +12180,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14496.662634605224</v>
+        <v>-14497.936892666634</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13979.62036307571</v>
+        <v>-13980.89462113712</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>343</v>
@@ -12196,11 +12196,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1105090279441381</v>
+        <v>3.1102356379278002</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2255525421206173</v>
+        <v>3.2252585561890528</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -12213,7 +12213,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27959.24072615142</v>
+        <v>27961.789242274241</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>344</v>
@@ -12328,11 +12328,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26432.159807159998</v>
+        <v>-26567.928460739997</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0526348446966884</v>
+        <v>-3.0683146879542789</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -12345,11 +12345,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18652.161582600937</v>
+        <v>18745.179534933755</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1541273505972445</v>
+        <v>2.1648699400997709</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>172.447551936</v>
+        <v>173.33332790399999</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9915868009388996E-2</v>
+        <v>2.0018165763497582E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -12379,11 +12379,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7607.5506726230615</v>
+        <v>-7649.4155979022416</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.87859162609005492</v>
+        <v>-0.88342658209101044</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -12963,48 +12963,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.40759273848585</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.99324457435773</v>
+        <v>-208.93910019296732</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.55753943600337</v>
+        <v>-420.50836865123335</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.378076293709</v>
+        <v>-366.32952720851665</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.99418202488022</v>
+        <v>-454.96428392701432</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.38389426882884</v>
+        <v>-503.36524328150233</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.10662736260338</v>
+        <v>-818.09114139130793</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.08560245243791</v>
+        <v>-947.06892960013079</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1697020930997</v>
+        <v>-1014.1577767648394</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.60296696915537</v>
+        <v>-468.58324213710398</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.48901881965605</v>
+        <v>-437.47630223738793</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -13018,48 +13018,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.899665615674</v>
+        <v>17798.925150776904</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.006755425642</v>
+        <v>16980.060899807031</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.442460563998</v>
+        <v>17261.491631348767</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.621923706291</v>
+        <v>16973.670472791484</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.005817975119</v>
+        <v>14670.035716072985</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.616105731171</v>
+        <v>11589.634756718498</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.893372637398</v>
+        <v>20402.908858608691</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.914397547564</v>
+        <v>19208.931070399871</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.830297906901</v>
+        <v>16944.842223235162</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.397033030844</v>
+        <v>17752.416757862895</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.510981180343</v>
+        <v>11857.523697762612</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7249164039185</v>
+        <v>-4449.731287694226</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -13185,50 +13185,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3126792993517</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.006755425642</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.442460563998</v>
+        <v>10350.491631348767</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.621923706291</v>
+        <v>10809.670472791484</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0058179751195</v>
+        <v>8651.0357160729855</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.616105731171</v>
+        <v>5607.6347567184985</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.893372637398</v>
+        <v>12308.908858608691</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.914397547564</v>
+        <v>11857.931070399871</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.830297906901</v>
+        <v>10224.842223235162</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.397033030844</v>
+        <v>11296.416757862895</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5109811803432</v>
+        <v>7067.5236977626118</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -13293,50 +13293,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3126792993517</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.006755425642</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.442460563998</v>
+        <v>10350.491631348767</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.621923706291</v>
+        <v>10809.670472791484</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0058179751195</v>
+        <v>8651.0357160729855</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.616105731171</v>
+        <v>5607.6347567184985</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.893372637398</v>
+        <v>12308.908858608691</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.914397547564</v>
+        <v>11857.931070399871</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.830297906901</v>
+        <v>10224.842223235162</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.397033030844</v>
+        <v>11296.416757862895</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5109811803432</v>
+        <v>7067.5236977626118</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -14154,43 +14154,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421665226961742</v>
+        <v>0.18421606485731437</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337897210074381</v>
+        <v>0.19337842124476803</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787975921309216</v>
+        <v>0.18787922182841446</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391267416500598</v>
+        <v>0.18391229934389186</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957520412226601</v>
+        <v>0.19957488294953873</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967756168660361</v>
+        <v>0.19967741012973447</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636716172162119</v>
+        <v>0.19636699128003474</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838214003454283</v>
+        <v>0.20838199338074748</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847888840666229</v>
+        <v>0.2084786567643391</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986064395282465</v>
+        <v>0.21986040816362973</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -14292,48 +14292,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.59240726151421</v>
+        <v>279.61789242274239</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.00675542564227</v>
+        <v>594.06089980703268</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.44246056399663</v>
+        <v>539.49163134876665</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.621923706291</v>
+        <v>532.67047279148335</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.00581797511978</v>
+        <v>328.03571607298568</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.61610573117113</v>
+        <v>204.6347567184977</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.89337263739665</v>
+        <v>169.90885860869201</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.91439754756209</v>
+        <v>182.93107039986916</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83029790690034</v>
+        <v>130.84222323516065</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.39703303084463</v>
+        <v>216.41675786289605</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.51098118034398</v>
+        <v>139.52369776261207</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -14404,48 +14404,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.40759273848585</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.99324457435773</v>
+        <v>-208.93910019296732</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.55753943600337</v>
+        <v>-420.50836865123335</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.378076293709</v>
+        <v>-366.32952720851665</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.99418202488022</v>
+        <v>-454.96428392701432</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.38389426882884</v>
+        <v>-503.36524328150233</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.10662736260338</v>
+        <v>-818.09114139130793</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.08560245243791</v>
+        <v>-947.06892960013079</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1697020930997</v>
+        <v>-1014.1577767648394</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.60296696915537</v>
+        <v>-468.58324213710398</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.48901881965605</v>
+        <v>-437.47630223738793</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -15490,50 +15490,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8727090710125459E-3</v>
+        <v>2.8725691963625553E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1173360808269502E-3</v>
+        <v>1.1170466098872327E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3712887188109847E-3</v>
+        <v>2.3710114722601877E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1307988431914404E-3</v>
+        <v>2.1305164891390026E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2840421086337505E-3</v>
+        <v>3.2838263111219608E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.607590724742372E-3</v>
+        <v>4.6074200078855326E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2198832204831169E-3</v>
+        <v>7.2197465550405335E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9796681753336292E-3</v>
+        <v>8.9795100938667941E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432932406974721E-2</v>
+        <v>1.14327979704286E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7229057298204171E-3</v>
+        <v>5.722664836436628E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0506208275969743E-2</v>
+        <v>1.0505902889877475E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -15547,50 +15547,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.768880167736374E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0779844291915587E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327618551394379E-2</v>
+        <v>9.7327895797945166E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8715988482914727E-2</v>
+        <v>9.8716270836967171E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588468763650688</v>
+        <v>0.10588490343401867</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608247160878317</v>
+        <v>0.10608264232564002</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005783425235761</v>
+        <v>0.18005797091780018</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212680759976832</v>
+        <v>0.18212696568123515</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102236937644468</v>
+        <v>0.1910225038129908</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680463390037913</v>
+        <v>0.21680487479376293</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475567304292265</v>
+        <v>0.28475597842901496</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422200419340935E-2</v>
+        <v>2.4422235388003435E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -15719,50 +15719,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683384628426736E-2</v>
+        <v>3.968348953441423E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093435601005325E-2</v>
+        <v>5.5093725071945036E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360355337708752E-2</v>
+        <v>5.8360632584259539E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867107451881371E-2</v>
+        <v>6.2867389805933815E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.244094652338282E-2</v>
+        <v>6.2441162320894611E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327824054069722E-2</v>
+        <v>5.1327994770926567E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862737172819886</v>
+        <v>0.10862750839364142</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242926327436772</v>
+        <v>0.11242942135583456</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526650167865647</v>
+        <v>0.1152666361152026</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795946646431259</v>
+        <v>0.13795970735769639</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972481403377304</v>
+        <v>0.16972511941986532</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -15826,50 +15826,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683384628426736E-2</v>
+        <v>3.968348953441423E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093435601005325E-2</v>
+        <v>5.5093725071945036E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360355337708752E-2</v>
+        <v>5.8360632584259539E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867107451881371E-2</v>
+        <v>6.2867389805933815E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.244094652338282E-2</v>
+        <v>6.2441162320894611E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327824054069722E-2</v>
+        <v>5.1327994770926567E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862737172819886</v>
+        <v>0.10862750839364142</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242926327436772</v>
+        <v>0.11242942135583456</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526650167865647</v>
+        <v>0.1152666361152026</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795946646431259</v>
+        <v>0.13795970735769639</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972481403377304</v>
+        <v>0.16972511941986532</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -15895,24 +15895,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.30896853055199996</v>
+        <v>0.31055554582799999</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27641687775599999</v>
+        <v>0.27783669163399999</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.226228543512</v>
+        <v>0.227390565268</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -15951,24 +15951,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2976.9516152626861</v>
+        <v>2992.2427119996059</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2976.9516152626861</v>
+        <v>2992.2427119996059</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2675.2972400619074</v>
+        <v>2689.0388906443586</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2393.4389332336796</v>
+        <v>2405.7328200655484</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1958.868098960058</v>
+        <v>1968.929814925644</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -16006,24 +16006,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41173207125409761</v>
+        <v>0.41384583689866911</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28888400424340382</v>
+        <v>0.29036632981525007</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25847177550669947</v>
+        <v>0.25979818026227913</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22141745105670102</v>
+        <v>0.22255376110871333</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.2264324103088578</v>
+        <v>0.22759469265252458</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -16082,24 +16082,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5597668412732086E-2</v>
+        <v>4.5529957806060596E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5597668412732086E-2</v>
+        <v>4.5529957806060596E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0977258693899198E-2</v>
+        <v>4.0916409199999997E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6660063362864717E-2</v>
+        <v>3.6605624721212121E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0003785611671087E-2</v>
+        <v>2.995923126060606E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -16219,46 +16219,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8226889540451401E-2</v>
+        <v>4.8225047943095456E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304298194159128E-2</v>
+        <v>-1.630396361752573E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956931063470959E-2</v>
+        <v>1.6956919189556219E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.1570289837859884</v>
+        <v>0.1570299351210549</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578876160709641</v>
+        <v>0.26578930432374337</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196212938728751</v>
+        <v>-0.43196164639884516</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157545730032071E-2</v>
+        <v>6.2157429990921775E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361503537278452</v>
+        <v>0.13361522151325422</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490574237459391E-2</v>
+        <v>-4.5490963041414756E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714362999170514</v>
+        <v>0.49714368786904362</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -16830,43 +16830,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143611641410434</v>
+        <v>1.214354783699952</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920177861860126</v>
+        <v>1.3920111733013887</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756262804519559</v>
+        <v>1.3756201021509935</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871219431001096</v>
+        <v>1.3871171491876846</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848690931059285</v>
+        <v>2.9848591654344512</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067787260028483</v>
+        <v>1.3067770819304068</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351596266810323</v>
+        <v>1.4351576087738316</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994836699363066</v>
+        <v>1.2994821543364572</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941613378097171</v>
+        <v>1.3941589034450128</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917551080715944</v>
+        <v>1.8917517042401404</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -16938,48 +16938,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.768880167736374E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0779844291915587E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327618551394379E-2</v>
+        <v>9.7327895797945166E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8715988482914727E-2</v>
+        <v>9.8716270836967171E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588468763650688</v>
+        <v>0.10588490343401867</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608247160878317</v>
+        <v>0.10608264232564002</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005783425235761</v>
+        <v>0.18005797091780018</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212680759976832</v>
+        <v>0.18212696568123515</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102236937644468</v>
+        <v>0.1910225038129908</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680463390037913</v>
+        <v>0.21680487479376293</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475567304292265</v>
+        <v>0.28475597842901496</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -17103,50 +17103,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.2003590889358437</v>
+        <v>0.20035937581782973</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114095520263008</v>
+        <v>0.19114156469642632</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122218225713717</v>
+        <v>0.20122275545677776</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032467502300178</v>
+        <v>0.21032527660766132</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338007431981016</v>
+        <v>0.19338046843665369</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.13711140943995612</v>
+        <v>0.1371116300911957</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.2576610895073233</v>
+        <v>0.25766128507430308</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404505945655211</v>
+        <v>0.2740452973207389</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820693787286708</v>
+        <v>0.25820711959215487</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774651272236316</v>
+        <v>0.26774681021768088</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1686125786528119</v>
+        <v>0.16861275948129531</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -17224,50 +17224,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.90907798603243428</v>
+        <v>0.91374987601495727</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2956638533896403</v>
+        <v>1.3023258667630979</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3013765522939902</v>
+        <v>1.3080672803663771</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3591098703531064</v>
+        <v>1.3660970667495278</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0877038511316208</v>
+        <v>1.0932946148376705</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70505392808753731</v>
+        <v>0.7086777910425589</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5476155034790997</v>
+        <v>1.5555667796680086</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4909132450012039</v>
+        <v>1.4985734203244503</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2855831479262336</v>
+        <v>1.2921880462773399</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4203128301230792</v>
+        <v>1.4276107524775969</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.88860868596019593</v>
+        <v>0.89317462701552608</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -17281,50 +17281,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12056737215284274</v>
+        <v>0.12038865296639753</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17183870734610615</v>
+        <v>0.17158443567366244</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17259635972068835</v>
+        <v>0.17234088015367288</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18025329845531915</v>
+        <v>0.17998643830692065</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14425780518987014</v>
+        <v>0.14404408627637294</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.3508478526198577E-2</v>
+        <v>9.3369932943683648E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20525404555425725</v>
+        <v>0.20494950983768229</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19773385212217559</v>
+        <v>0.19744050333655472</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17050174375679492</v>
+        <v>0.1702487544502424</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18837040187308743</v>
+        <v>0.18809100823156746</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11785261087005251</v>
+        <v>0.1176778164710838</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17338,43 +17338,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14561776260565532</v>
+        <v>0.14465848880719909</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14175790395659407</v>
+        <v>0.14082405742196566</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12564452578670354</v>
+        <v>0.12481682798837215</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.40340117952510191</v>
+        <v>0.40074372774957423</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14906406497088856</v>
+        <v>0.14808208825830035</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14659804416732167</v>
+        <v>0.14563231265106788</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1257976947807139</v>
+        <v>0.12496898796397665</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12175403333884023</v>
+        <v>0.12095196460801783</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2291894555139079E-2</v>
+        <v>5.1947415671376632E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5535206610404997E-2</v>
+        <v>3.530111434024423E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3126792993517</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.169057324689</v>
+        <v>96404.42390893698</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17132.75927384858</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89416.328331173267</v>
+        <v>89414.03466666273</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.08868404</v>
+        <v>1.0942760599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>12.977519952831315</v>
+        <v>13.043893660857972</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7204126969455</v>
+        <v>7373.7399056769073</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2748025087867</v>
+        <v>6859.292935513402</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9725290293345</v>
+        <v>7519.9924086376759</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2774723888242</v>
+        <v>6507.2946748622398</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1254444610322</v>
+        <v>7669.1457183662314</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3435854139398</v>
+        <v>6173.3599051082156</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2366941281143</v>
+        <v>7821.257370150749</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5461800695548</v>
+        <v>5856.5616622862572</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3649543321653</v>
+        <v>7976.3860404479283</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0058637150096</v>
+        <v>5556.0205514309673</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5700651744291</v>
+        <v>8134.5915695172034</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -18490,7 +18490,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.8883714921831</v>
+        <v>5270.9023054787804</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.913053638882</v>
+        <v>8295.9349845038814</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.40225050356</v>
+        <v>5000.4154694399194</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4561571331487</v>
+        <v>8460.4785229801164</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.796662831327</v>
+        <v>4743.8092034116735</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2628474963312</v>
+        <v>8628.285656952803</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3593012988977</v>
+        <v>4500.3711983344192</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.3978554830155</v>
+        <v>8799.4211173476469</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4144121892859</v>
+        <v>4269.4256987047656</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9271957328947</v>
+        <v>8973.9509189788569</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3209194316159</v>
+        <v>4050.3316267571049</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.918192235662</v>
+        <v>9151.9423860140996</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4706450487461</v>
+        <v>3842.4808029065289</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4395043009517</v>
+        <v>9333.4641779445192</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2866209261379</v>
+        <v>3645.2962575132447</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5611530434053</v>
+        <v>9518.5863160698609</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2214872156892</v>
+        <v>3458.2306292821604</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3545483930266</v>
+        <v>9707.3802105089053</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7559729286418</v>
+        <v>3280.7646458517879</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.8925166412773</v>
+        <v>9899.9186877456395</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.3974544998969</v>
+        <v>3112.4056823547412</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.249328533526</v>
+        <v>10096.276018721766</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6785883224652</v>
+        <v>2952.6863939485715</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.500727918687</v>
+        <v>10296.52794748644</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1560134561328</v>
+        <v>2801.1634185210096</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.723960967105</v>
+        <v>10500.75172041421</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4091209092103</v>
+        <v>2657.4161459684542</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10708.99780596796</v>
+        <v>10709.026116002509</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0388860770458</v>
+        <v>2521.0455506314011</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.272169292613</v>
+        <v>98316.532075692099</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.943136956572</v>
+        <v>23145.004322340275</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110203.98774818353</v>
+        <v>110204.27908064592</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19142,7 +19142,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110203.98774818353</v>
+        <v>110204.27908064592</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -19172,19 +19172,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.169057324703</v>
+        <v>96404.42390893698</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.789278716606</v>
+        <v>97922.048142271145</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.193779830588</v>
+        <v>99461.45671291578</v>
       </c>
       <c r="E56" s="123">
-        <v>101022.86068906962</v>
+        <v>101023.12775053777</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.27559868761</v>
+        <v>102607.54684867477</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19193,19 +19193,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.169057324732</v>
+        <v>96404.423908936995</v>
       </c>
       <c r="C57" s="123">
-        <v>99376.855842051198</v>
+        <v>99377.118552182757</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.62606144218</v>
+        <v>102492.89700834473</v>
       </c>
       <c r="E57" s="123">
-        <v>105759.86882495845</v>
+        <v>105760.14840906096</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.43600482987</v>
+        <v>109187.72464996192</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -19214,19 +19214,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.169057324718</v>
+        <v>96404.423908937009</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.34099541401</v>
+        <v>101173.60845468809</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.7743300822</v>
+        <v>106331.05542341602</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.47137276991</v>
+        <v>111913.76722437982</v>
       </c>
       <c r="F58" s="123">
-        <v>117961.96448964026</v>
+        <v>117962.2763308929</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -19245,19 +19245,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.169057324732</v>
+        <v>96404.423908937024</v>
       </c>
       <c r="C59" s="341">
-        <v>102997.88525430034</v>
+        <v>102998.15753689327</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.10651776266</v>
+        <v>110332.3981889166</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.42699472501</v>
+        <v>118504.74027001776</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.73681782281</v>
+        <v>127626.0742059785</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -19276,19 +19276,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.169057324732</v>
+        <v>96404.423908937024</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.41186206749</v>
+        <v>104688.68861369361</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.45125954597</v>
+        <v>114140.75299834332</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.39257370782</v>
+        <v>124956.72290525284</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.16404572231</v>
+        <v>137367.52718606754</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -19307,19 +19307,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.169057324718</v>
+        <v>96404.423908937024</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.16575541096</v>
+        <v>106173.44643209476</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.53404858407</v>
+        <v>117578.84487620974</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.30946734073</v>
+        <v>130953.6556521829</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.56082238597</v>
+        <v>146703.94864419254</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -19399,23 +19399,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -19426,23 +19426,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.242448187675739</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.433260839302132</v>
+        <v>11.491698364961856</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.62681246087565</v>
+        <v>11.6862446777454</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.823163168192794</v>
+        <v>11.883604461199756</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.022374015491149</v>
+        <v>12.083839083329538</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.242448187675743</v>
+        <v>11.299905098108422</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.616208526298642</v>
+        <v>11.675586247936419</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.007958958350255</v>
+        <v>12.069349945018397</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.418754259062512</v>
+        <v>12.482256385236559</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.849707387519791</v>
+        <v>12.915424247341239</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -19480,23 +19480,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.242448187675741</v>
+        <v>11.299905098108423</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.842083281318846</v>
+        <v>11.902621807663701</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.490535058847097</v>
+        <v>12.554406077464485</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.192455876009815</v>
+        <v>13.25993417242362</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.952941927596228</v>
+        <v>14.024328477450158</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -19507,23 +19507,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.242448187675743</v>
+        <v>11.299905098108425</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.071485949483423</v>
+        <v>12.133203411017368</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>12.993628516622119</v>
+        <v>13.060085009007176</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.021146546607026</v>
+        <v>14.092883610367592</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.16798242103606</v>
+        <v>15.245613248715305</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -19534,23 +19534,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.242448187675743</v>
+        <v>11.299905098108425</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.284038378692074</v>
+        <v>12.34684817947528</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.472457375281254</v>
+        <v>13.541374641970037</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.832361792011968</v>
+        <v>14.908267814252337</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.392786580719864</v>
+        <v>16.476711863189674</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -19560,23 +19560,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.242448187675741</v>
+        <v>11.299905098108425</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.470718697923482</v>
+        <v>12.53448787724929</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.904732646946877</v>
+        <v>13.975871441978022</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.586363088204315</v>
+        <v>15.66614403774093</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.566665658291317</v>
+        <v>17.656623683812288</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.849707387519791</v>
+        <v>12.915424247341239</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.021146546607026</v>
+        <v>14.092883610367592</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.993628516622119</v>
+        <v>13.060085009007176</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.071485949483423</v>
+        <v>12.133203411017368</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.242448187675743</v>
+        <v>11.299905098108422</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2976.9516152626861</v>
+        <v>2992.2427119996059</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39692.688203502483</v>
+        <v>39896.569493328083</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>4.9906208282751701</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.240276618657127</v>
+        <v>5.2671932726911681</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3035.9971783683327</v>
+        <v>3051.5915623379724</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -20032,7 +20032,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2824.1834217379837</v>
+        <v>2838.689825430672</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3096.2138651511627</v>
+        <v>3112.1175518242967</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2679.2548319317798</v>
+        <v>2693.0168106646161</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3157.6249039554427</v>
+        <v>3173.8440281151175</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2541.7635409856789</v>
+        <v>2554.8192964061977</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3220.2539838419193</v>
+        <v>3236.7948019499195</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2411.3278891153109</v>
+        <v>2423.7136624775162</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3284.125263725778</v>
+        <v>3300.9941563360335</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2287.5858021672925</v>
+        <v>2299.335974933153</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3349.2633816958473</v>
+        <v>3366.4668559157049</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2170.1937865436139</v>
+        <v>2181.34097582199</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3415.6934645186425</v>
+        <v>3433.2381565189557</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2058.8259757034816</v>
+        <v>2069.4011247914145</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3483.4411373309144</v>
+        <v>3501.3338149059218</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1953.1732255958182</v>
+        <v>1963.2056898735125</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3552.5325335244424</v>
+        <v>3570.7800987024148</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1852.9422565114385</v>
+        <v>1862.4598849293739</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3622.994304826886</v>
+        <v>3641.6037965325581</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1757.85483897279</v>
+        <v>1766.8840513571586</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3694.8536315825804</v>
+        <v>3713.8322283523848</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1667.6470214013802</v>
+        <v>1676.2128817924415</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3768.1382332372455</v>
+        <v>3787.4932559884073</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1582.0683974189885</v>
+        <v>1590.1946836459224</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3842.8763790306489</v>
+        <v>3862.6152938851974</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -20296,7 +20296,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1500.8814107487694</v>
+        <v>1508.5906804341548</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3919.0968989013531</v>
+        <v>3939.2273200661507</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1423.8606957867416</v>
+        <v>1431.1743489638866</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>3996.8291946077461</v>
+        <v>4017.358887311636</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1350.7924520131619</v>
+        <v>1357.7307905300986</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4076.1032510696546</v>
+        <v>4097.0401345588671</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -20362,7 +20362,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1281.4738505072237</v>
+        <v>1288.0561343822708</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4156.9496479349009</v>
+        <v>4178.3017985278711</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1215.7124709176337</v>
+        <v>1221.9569718029597</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4239.3995713752847</v>
+        <v>4261.1752255780602</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1153.3257673261644</v>
+        <v>1159.2498192277637</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4323.484826116518</v>
+        <v>4345.6923837999566</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1094.1405615214799</v>
+        <v>1099.7606089163503</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4409.2378477067741</v>
+        <v>4431.8858753467612</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1037.992562276625</v>
+        <v>1043.3242057607179</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40479.96237824444</v>
+        <v>40687.887497839634</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9529.5153768374403</v>
+        <v>9578.4636838022234</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45374.5161360208</v>
+        <v>45607.582105944399</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -20724,7 +20724,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45374.5161360208</v>
+        <v>45607.582105944399</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -20754,19 +20754,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39692.68820350249</v>
+        <v>39896.569493328083</v>
       </c>
       <c r="C51" s="123">
-        <v>40317.541120633279</v>
+        <v>40524.631964269967</v>
       </c>
       <c r="D51" s="123">
-        <v>40951.363324374819</v>
+        <v>41161.709792517373</v>
       </c>
       <c r="E51" s="123">
-        <v>41594.351675524784</v>
+        <v>41808.000850042459</v>
       </c>
       <c r="F51" s="123">
-        <v>42246.70610798768</v>
+        <v>42463.706097709197</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -20775,19 +20775,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39692.68820350249</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C52" s="123">
-        <v>40916.638690567604</v>
+        <v>41126.806795806318</v>
       </c>
       <c r="D52" s="123">
-        <v>42199.501216549295</v>
+        <v>42416.258738587509</v>
       </c>
       <c r="E52" s="123">
-        <v>43544.72984686181</v>
+        <v>43768.397128875265</v>
       </c>
       <c r="F52" s="123">
-        <v>44955.969181192835</v>
+        <v>45186.885286824923</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -20796,19 +20796,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39692.688203502483</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C53" s="123">
-        <v>41656.309243738913</v>
+        <v>41870.276662988646</v>
       </c>
       <c r="D53" s="123">
-        <v>43779.789952976775</v>
+        <v>44004.664620022348</v>
       </c>
       <c r="E53" s="123">
-        <v>46078.365369546715</v>
+        <v>46315.046657456289</v>
       </c>
       <c r="F53" s="123">
-        <v>48568.723968521888</v>
+        <v>48818.196970630423</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -20817,19 +20817,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39692.68820350249</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C54" s="123">
-        <v>42407.532630544956</v>
+        <v>42625.35870487654</v>
       </c>
       <c r="D54" s="123">
-        <v>45427.266742386142</v>
+        <v>45660.603665529372</v>
       </c>
       <c r="E54" s="123">
-        <v>48792.073179318133</v>
+        <v>49042.693413504894</v>
       </c>
       <c r="F54" s="123">
-        <v>52547.608965332533</v>
+        <v>52817.519489864797</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -20838,19 +20838,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39692.68820350249</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C55" s="123">
-        <v>43103.576652271084</v>
+        <v>43324.977953158173</v>
       </c>
       <c r="D55" s="123">
-        <v>46995.284410970235</v>
+        <v>47236.675448843649</v>
       </c>
       <c r="E55" s="123">
-        <v>51448.554330812854</v>
+        <v>51712.819566839426</v>
       </c>
       <c r="F55" s="123">
-        <v>56558.466974846648</v>
+        <v>56848.979251018784</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -20859,19 +20859,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39692.688203502497</v>
+        <v>39896.569493328097</v>
       </c>
       <c r="C56" s="123">
-        <v>43714.897448079981</v>
+        <v>43939.438795106253</v>
       </c>
       <c r="D56" s="123">
-        <v>48410.85335884396</v>
+        <v>48659.51545937379</v>
       </c>
       <c r="E56" s="123">
-        <v>53917.677344567026</v>
+        <v>54194.625218317735</v>
       </c>
       <c r="F56" s="123">
-        <v>60402.560957752452</v>
+        <v>60712.818402995217</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -20921,23 +20921,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>4.9906208282751701</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>4.9906208282751701</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>4.9906208282751701</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>4.9906208282751701</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>4.9906208282751701</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -20948,23 +20948,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.9906208282751718</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.0691845165507932</v>
+        <v>5.1213939404386917</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1488759265958475</v>
+        <v>5.2019061220681468</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2297198100117406</v>
+        <v>5.2835826468219551</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3117413047861781</v>
+        <v>5.366448911593344</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -20975,23 +20975,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>4.9906208282751718</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.144509946649011</v>
+        <v>5.1974951752638239</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3058061634523108</v>
+        <v>5.3604526420230272</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.4749437634760181</v>
+        <v>5.5313322533359637</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.652380987669166</v>
+        <v>5.7105969697462831</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -21002,23 +21002,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>4.990620828275171</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2375098273774929</v>
+        <v>5.2914528964849188</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5044982208476005</v>
+        <v>5.5611911030980092</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.7935015327543757</v>
+        <v>5.8531709680118977</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.106618029933899</v>
+        <v>6.1695123688961822</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -21029,23 +21029,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>4.9906208282751718</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3319622630921097</v>
+        <v>5.3868781330982518</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7116379322516968</v>
+        <v>5.7704642237243196</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1347000589883134</v>
+        <v>6.1978836252520964</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6068891689554832</v>
+        <v>6.674935987152006</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -21056,23 +21056,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>4.9906208282751718</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4194769150202786</v>
+        <v>5.4752941310997381</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9087871300036579</v>
+        <v>5.9696439346684889</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.4687033922117898</v>
+        <v>6.5353269835027321</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1111803225027295</v>
+        <v>7.1844210235639432</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -21082,23 +21082,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>4.9906208282751736</v>
+        <v>5.042021095406203</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.4963391895198024</v>
+        <v>5.5529480388604391</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.0867687229584728</v>
+        <v>6.1494586264975863</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.7791499076213393</v>
+        <v>6.848970903477972</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.5945039865130726</v>
+        <v>7.6727226184361417</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.652380987669166</v>
+        <v>5.7105969697462831</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1347000589883134</v>
+        <v>6.1978836252520964</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7116379322516968</v>
+        <v>5.7704642237243196</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3319622630921097</v>
+        <v>5.3868781330982518</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>4.9906208282751718</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.54</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.261647446864</v>
+        <v>13.329480415733649</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.006755425642</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3126792993517</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052136251482979E-2</v>
+        <v>6.0052771628752E-2</v>
       </c>
       <c r="E14" s="377"/>
       <c r="F14" s="377"/>
@@ -21564,7 +21564,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.242448187675736</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>12.993628516622119</v>
+        <v>13.060085009007176</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.071485949483423</v>
+        <v>12.133203411017368</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.021146546607026</v>
+        <v>14.092883610367592</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.014703609191359</v>
+        <v>13.081268409681297</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.242448187675743</v>
+        <v>11.299905098108422</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.849707387519791</v>
+        <v>12.915424247341239</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.917841027032001</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>12.977519952831315</v>
+        <v>13.043893660857972</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8013813163632031E-2</v>
+        <v>-6.8040113935075849E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34380641983199994</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.5830543257629508</v>
+        <v>0.58604918132338757</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.250354530115124</v>
+        <v>5.2772069444640133</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8334088558780746</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842230650841528</v>
+        <v>0.5484213143271619</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22175,7 +22175,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23523677184925385</v>
+        <v>0.23459463611465181</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67111013151206389</v>
+        <v>0.67455728526809577</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6139346058403845</v>
+        <v>6.6477609144246523</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.2850447373524485</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604780999335013</v>
+        <v>0.43604666796787828</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89407744430634128</v>
+        <v>0.89866986852348141</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.398352669954194</v>
+        <v>10.45153400710732</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -22285,7 +22285,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.292430114260537</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D99" t="s">
         <v>379</v>
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582682426344416</v>
+        <v>0.12582530281537296</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.82946844320445867</v>
+        <v>0.83372900361808255</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2589968114381982</v>
+        <v>9.3063510267411278</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.088465254642657</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D105" t="s">
         <v>379</v>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261993883957398</v>
+        <v>0.22261862186231296</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88BC6DA-21DB-402E-8E2A-DAA8C6CA1AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DAF8C6-5F29-4475-A9E8-419BB8E7EF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4737,15 +4737,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4755,7 +4746,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>65720.304963720002</v>
+        <v>65633.716946639994</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0942760599999999</v>
+        <v>1.0934214200000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5240,13 +5240,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="368" t="s">
+      <c r="B18" s="371" t="s">
         <v>491</v>
       </c>
-      <c r="C18" s="368"/>
-      <c r="D18" s="368"/>
-      <c r="E18" s="368"/>
-      <c r="F18" s="368"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5330,14 +5330,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.98390803598565</v>
+        <v>12.973811066999007</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>448</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23459463611465181</v>
+        <v>0.23482489268397044</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8632561257874007</v>
+        <v>5.8586945824552004</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3223181996927478</v>
+        <v>7.3166217159225635</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.3502038756308</v>
+        <v>11.341374344019066</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.14008003035921</v>
+        <v>10.13219177262668</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5459,22 +5459,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="368" t="s">
+      <c r="B36" s="371" t="s">
         <v>494</v>
       </c>
-      <c r="C36" s="368"/>
-      <c r="D36" s="368"/>
-      <c r="E36" s="368"/>
-      <c r="F36" s="368"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="374" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61789242274239</v>
+        <v>279.61399747276158</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38210757725756</v>
+        <v>-523.38600252723836</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.731287694226</v>
+        <v>-4449.7303139567312</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5664,10 +5664,10 @@
       <c r="B61" s="367" t="s">
         <v>501</v>
       </c>
-      <c r="C61" s="370"/>
-      <c r="D61" s="370"/>
-      <c r="E61" s="370"/>
-      <c r="F61" s="370"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5683,22 +5683,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="368" t="s">
+      <c r="B64" s="371" t="s">
         <v>502</v>
       </c>
-      <c r="C64" s="368"/>
-      <c r="D64" s="368"/>
-      <c r="E64" s="368"/>
-      <c r="F64" s="368"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="368" t="s">
+      <c r="B65" s="371" t="s">
         <v>503</v>
       </c>
-      <c r="C65" s="368"/>
-      <c r="D65" s="368"/>
-      <c r="E65" s="368"/>
-      <c r="F65" s="368"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060899807031</v>
+        <v>10305.052624809068</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3288719577904</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12038865296639753</v>
+        <v>0.12045327965610227</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5742,14 +5742,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5529957806060596E-2</v>
+        <v>4.5554417471767805E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>505</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41384583689866911</v>
+        <v>0.41352278644020923</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5769,11 +5769,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035937581782973</v>
+        <v>0.20035933197306158</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114156469642632</v>
+        <v>0.1911414715462269</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5783,11 +5783,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688920174681254E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0780089522411969E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5833,22 +5833,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="368" t="s">
+      <c r="B80" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C80" s="368"/>
-      <c r="D80" s="368"/>
-      <c r="E80" s="368"/>
-      <c r="F80" s="368"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="374" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5892,22 +5892,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="368" t="s">
+      <c r="B89" s="371" t="s">
         <v>509</v>
       </c>
-      <c r="C89" s="368"/>
-      <c r="D89" s="368"/>
-      <c r="E89" s="368"/>
-      <c r="F89" s="368"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="368" t="s">
+      <c r="B90" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C90" s="368"/>
-      <c r="D90" s="368"/>
-      <c r="E90" s="368"/>
-      <c r="F90" s="368"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.18333168019943</v>
+        <v>12.173811463910068</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5944,13 +5944,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="368" t="s">
+      <c r="B97" s="371" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="368"/>
-      <c r="D97" s="368"/>
-      <c r="E97" s="368"/>
-      <c r="F97" s="368"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5963,13 +5963,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="368" t="s">
+      <c r="B101" s="371" t="s">
         <v>513</v>
       </c>
-      <c r="C101" s="368"/>
-      <c r="D101" s="368"/>
-      <c r="E101" s="368"/>
-      <c r="F101" s="368"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0683146879542789</v>
+        <v>3.0659183050297427</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.210757725759</v>
+        <v>17130.600252723845</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1648699400997713</v>
+        <v>2.1632283409931699</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0018165763497582E-2</v>
+        <v>2.0002531385835957E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6091,13 +6091,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="368" t="s">
+      <c r="B116" s="371" t="s">
         <v>518</v>
       </c>
-      <c r="C116" s="368"/>
-      <c r="D116" s="368"/>
-      <c r="E116" s="368"/>
-      <c r="F116" s="368"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1956651023474385</v>
+        <v>-3.1931692575392558</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.92 HKD</v>
+        <v>12.91 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.09 HKD</v>
+        <v>14.08 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.06 HKD</v>
+        <v>13.05 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.13 HKD</v>
+        <v>12.12 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.3 HKD</v>
+        <v>11.29 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.98390803598565</v>
+        <v>12.973811066999007</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6285,13 +6285,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="369" t="s">
         <v>526</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6304,22 +6304,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="370" t="s">
         <v>528</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="368" t="s">
+      <c r="B139" s="371" t="s">
         <v>529</v>
       </c>
-      <c r="C139" s="368"/>
-      <c r="D139" s="368"/>
-      <c r="E139" s="368"/>
-      <c r="F139" s="368"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58604918132338757</v>
+        <v>0.5855914713444943</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2772069444640133</v>
+        <v>5.2731031111107063</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8632561257874007</v>
+        <v>5.8586945824552004</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5484213143271619</v>
+        <v>0.54842146596710195</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67455728526809577</v>
+        <v>0.67403044961907199</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6477609144246523</v>
+        <v>6.6425912663034916</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3223181996927478</v>
+        <v>7.3166217159225635</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604666796787828</v>
+        <v>0.43604684250924708</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89866986852348141</v>
+        <v>0.89796799881755474</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.45153400710732</v>
+        <v>10.443406345201511</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.3502038756308</v>
+        <v>11.341374344019066</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582530281537296</v>
+        <v>0.12582553534576346</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83372900361808255</v>
+        <v>0.83307785334467521</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.3063510267411278</v>
+        <v>9.2991139192820036</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.14008003035921</v>
+        <v>10.13219177262668</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261862186231296</v>
+        <v>0.22261882314240478</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6652,13 +6652,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="372" t="s">
         <v>536</v>
       </c>
-      <c r="C179" s="368"/>
-      <c r="D179" s="368"/>
-      <c r="E179" s="368"/>
-      <c r="F179" s="368"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6666,13 +6666,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="370" t="s">
+      <c r="B182" s="373" t="s">
         <v>538</v>
       </c>
-      <c r="C182" s="370"/>
-      <c r="D182" s="370"/>
-      <c r="E182" s="370"/>
-      <c r="F182" s="370"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6709,22 +6709,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="368" t="s">
         <v>545</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="368" t="s">
         <v>546</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6748,15 +6748,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6769,12 +6766,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -6915,7 +6915,7 @@
         <v>465</v>
       </c>
       <c r="C12" s="50">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>65720.304963720002</v>
+        <v>65633.716946639994</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -6963,7 +6963,7 @@
         <v>469</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0942760599999999</v>
+        <v>1.0934214200000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -6973,13 +6973,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="368" t="s">
+      <c r="B18" s="371" t="s">
         <v>470</v>
       </c>
-      <c r="C18" s="368"/>
-      <c r="D18" s="368"/>
-      <c r="E18" s="368"/>
-      <c r="F18" s="368"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.98390803598565</v>
+        <v>12.973811066999007</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23459463611465181</v>
+        <v>0.23482489268397044</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8632561257874007</v>
+        <v>5.8586945824552004</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3223181996927478</v>
+        <v>7.3166217159225635</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.3502038756308</v>
+        <v>11.341374344019066</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.14008003035921</v>
+        <v>10.13219177262668</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -7179,22 +7179,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="368" t="s">
+      <c r="B36" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C36" s="368"/>
-      <c r="D36" s="368"/>
-      <c r="E36" s="368"/>
-      <c r="F36" s="368"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="374" t="s">
         <v>331</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61789242274239</v>
+        <v>279.61399747276158</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38210757725756</v>
+        <v>-523.38600252723836</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.731287694226</v>
+        <v>-4449.7303139567312</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7384,10 +7384,10 @@
       <c r="B61" s="367" t="s">
         <v>330</v>
       </c>
-      <c r="C61" s="370"/>
-      <c r="D61" s="370"/>
-      <c r="E61" s="370"/>
-      <c r="F61" s="370"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7403,22 +7403,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="368" t="s">
+      <c r="B64" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C64" s="368"/>
-      <c r="D64" s="368"/>
-      <c r="E64" s="368"/>
-      <c r="F64" s="368"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="368" t="s">
+      <c r="B65" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C65" s="368"/>
-      <c r="D65" s="368"/>
-      <c r="E65" s="368"/>
-      <c r="F65" s="368"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060899807031</v>
+        <v>10305.052624809068</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3288719577904</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12038865296639753</v>
+        <v>0.12045327965610227</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7462,14 +7462,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5529957806060596E-2</v>
+        <v>4.5554417471767805E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>426</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41384583689866911</v>
+        <v>0.41352278644020923</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -7489,11 +7489,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035937581782973</v>
+        <v>0.20035933197306158</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114156469642632</v>
+        <v>0.1911414715462269</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -7503,11 +7503,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688920174681254E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0780089522411969E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -7553,22 +7553,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="368" t="s">
+      <c r="B80" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="C80" s="368"/>
-      <c r="D80" s="368"/>
-      <c r="E80" s="368"/>
-      <c r="F80" s="368"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="374" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7612,22 +7612,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="368" t="s">
+      <c r="B89" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C89" s="368"/>
-      <c r="D89" s="368"/>
-      <c r="E89" s="368"/>
-      <c r="F89" s="368"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="368" t="s">
+      <c r="B90" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="368"/>
-      <c r="D90" s="368"/>
-      <c r="E90" s="368"/>
-      <c r="F90" s="368"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.18333168019943</v>
+        <v>12.173811463910068</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -7664,13 +7664,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="368" t="s">
+      <c r="B97" s="371" t="s">
         <v>353</v>
       </c>
-      <c r="C97" s="368"/>
-      <c r="D97" s="368"/>
-      <c r="E97" s="368"/>
-      <c r="F97" s="368"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7683,13 +7683,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="368" t="s">
+      <c r="B101" s="371" t="s">
         <v>336</v>
       </c>
-      <c r="C101" s="368"/>
-      <c r="D101" s="368"/>
-      <c r="E101" s="368"/>
-      <c r="F101" s="368"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0683146879542789</v>
+        <v>3.0659183050297427</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.210757725759</v>
+        <v>17130.600252723845</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1648699400997713</v>
+        <v>2.1632283409931699</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0018165763497582E-2</v>
+        <v>2.0002531385835957E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -7811,13 +7811,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="368" t="s">
+      <c r="B116" s="371" t="s">
         <v>354</v>
       </c>
-      <c r="C116" s="368"/>
-      <c r="D116" s="368"/>
-      <c r="E116" s="368"/>
-      <c r="F116" s="368"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1956651023474385</v>
+        <v>-3.1931692575392558</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.92 HKD</v>
+        <v>12.91 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.09 HKD</v>
+        <v>14.08 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.06 HKD</v>
+        <v>13.05 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.13 HKD</v>
+        <v>12.12 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.3 HKD</v>
+        <v>11.29 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.98390803598565</v>
+        <v>12.973811066999007</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -8005,13 +8005,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="369" t="s">
         <v>476</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8024,22 +8024,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="370" t="s">
         <v>355</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="368" t="s">
+      <c r="B139" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C139" s="368"/>
-      <c r="D139" s="368"/>
-      <c r="E139" s="368"/>
-      <c r="F139" s="368"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58604918132338757</v>
+        <v>0.5855914713444943</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2772069444640133</v>
+        <v>5.2731031111107063</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8632561257874007</v>
+        <v>5.8586945824552004</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5484213143271619</v>
+        <v>0.54842146596710195</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67455728526809577</v>
+        <v>0.67403044961907199</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6477609144246523</v>
+        <v>6.6425912663034916</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3223181996927478</v>
+        <v>7.3166217159225635</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604666796787828</v>
+        <v>0.43604684250924708</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89866986852348141</v>
+        <v>0.89796799881755474</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.45153400710732</v>
+        <v>10.443406345201511</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.3502038756308</v>
+        <v>11.341374344019066</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582530281537296</v>
+        <v>0.12582553534576346</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83372900361808255</v>
+        <v>0.83307785334467521</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.3063510267411278</v>
+        <v>9.2991139192820036</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.14008003035921</v>
+        <v>10.13219177262668</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261862186231296</v>
+        <v>0.22261882314240478</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -8372,13 +8372,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="372" t="s">
         <v>479</v>
       </c>
-      <c r="C179" s="368"/>
-      <c r="D179" s="368"/>
-      <c r="E179" s="368"/>
-      <c r="F179" s="368"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8386,13 +8386,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="370" t="s">
+      <c r="B182" s="373" t="s">
         <v>364</v>
       </c>
-      <c r="C182" s="370"/>
-      <c r="D182" s="370"/>
-      <c r="E182" s="370"/>
-      <c r="F182" s="370"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8429,22 +8429,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="368" t="s">
         <v>365</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="368" t="s">
         <v>366</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8468,17 +8468,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8495,6 +8484,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9183,19 +9183,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.31055554582799999</v>
+        <v>0.31031299899600001</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27783669163399999</v>
+        <v>0.27761969853800006</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.227390565268</v>
+        <v>0.22721297107600003</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -10568,19 +10568,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.31055554582799999</v>
+        <v>0.31031299899600001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27783669163399999</v>
+        <v>0.27761969853800006</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.227390565268</v>
+        <v>0.22721297107600003</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -11918,11 +11918,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2333553114021711</v>
+        <v>8.2269249826756745</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1956651023474385</v>
+        <v>-3.1931692575392558</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17130.210757725759</v>
+        <v>17130.600252723845</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -12180,11 +12180,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.936892666634</v>
+        <v>-14497.742145167591</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.89462113712</v>
+        <v>-13980.699873638077</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>343</v>
@@ -12196,11 +12196,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1102356379278002</v>
+        <v>3.1102774175791321</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2252585561890528</v>
+        <v>3.2253034831986631</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -12213,7 +12213,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27961.789242274241</v>
+        <v>27961.399747276155</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>344</v>
@@ -12328,11 +12328,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26567.928460739997</v>
+        <v>-26547.178656180004</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0683146879542789</v>
+        <v>-3.0659183050297432</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -12345,11 +12345,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18745.179534933755</v>
+        <v>18730.965253785667</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1648699400997709</v>
+        <v>2.1632283409931699</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -12362,11 +12362,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>173.33332790399999</v>
+        <v>173.19795292800001</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.0018165763497582E-2</v>
+        <v>2.0002531385835957E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -12379,11 +12379,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7649.4155979022416</v>
+        <v>-7643.0154494663366</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88342658209101044</v>
+        <v>-0.88268743265073735</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -12963,48 +12963,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.38210757725756</v>
+        <v>-523.38600252723836</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.93910019296732</v>
+        <v>-208.94737519093053</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.50836865123335</v>
+        <v>-420.51588352412273</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.32952720851665</v>
+        <v>-366.33694706577171</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.96428392701432</v>
+        <v>-454.96885331524243</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.36524328150233</v>
+        <v>-503.36809375052928</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09114139130793</v>
+        <v>-818.09350814437892</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.06892960013079</v>
+        <v>-947.07147774668533</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1577767648394</v>
+        <v>-1014.1595993374597</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.58324213710398</v>
+        <v>-468.58625672404463</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.47630223738793</v>
+        <v>-437.47824573899726</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -13018,48 +13018,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.925150776904</v>
+        <v>17798.921255826925</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.060899807031</v>
+        <v>16980.052624809068</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.491631348767</v>
+        <v>17261.484116475876</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.670472791484</v>
+        <v>16973.663052934229</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.035716072985</v>
+        <v>14670.031146684758</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.634756718498</v>
+        <v>11589.631906249471</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.908858608691</v>
+        <v>20402.906491855621</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.931070399871</v>
+        <v>19208.928522253314</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.842223235162</v>
+        <v>16944.840400662539</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.416757862895</v>
+        <v>17752.413743275956</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.523697762612</v>
+        <v>11857.521754261003</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.731287694226</v>
+        <v>-4449.7303139567312</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -13185,50 +13185,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3288719577904</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.060899807031</v>
+        <v>10305.052624809068</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.491631348767</v>
+        <v>10350.484116475876</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.670472791484</v>
+        <v>10809.663052934229</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0357160729855</v>
+        <v>8651.0311466847579</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6347567184985</v>
+        <v>5607.6319062494713</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.908858608691</v>
+        <v>12308.906491855621</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.931070399871</v>
+        <v>11857.928522253314</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.842223235162</v>
+        <v>10224.840400662539</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.416757862895</v>
+        <v>11296.413743275956</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5236977626118</v>
+        <v>7067.5217542610026</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -13293,50 +13293,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3288719577904</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.060899807031</v>
+        <v>10305.052624809068</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.491631348767</v>
+        <v>10350.484116475876</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.670472791484</v>
+        <v>10809.663052934229</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0357160729855</v>
+        <v>8651.0311466847579</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6347567184985</v>
+        <v>5607.6319062494713</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.908858608691</v>
+        <v>12308.906491855621</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.931070399871</v>
+        <v>11857.928522253314</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.842223235162</v>
+        <v>10224.840400662539</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.416757862895</v>
+        <v>11296.413743275956</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5236977626118</v>
+        <v>7067.5217542610026</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -14154,43 +14154,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421606485731437</v>
+        <v>0.1842161546325109</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337842124476803</v>
+        <v>0.19337850543302471</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787922182841446</v>
+        <v>0.1878793039578289</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391229934389186</v>
+        <v>0.18391235662848024</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957488294953873</v>
+        <v>0.19957493203496499</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967741012973447</v>
+        <v>0.19967743329246981</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636699128003474</v>
+        <v>0.19636701732895631</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838199338074748</v>
+        <v>0.20838201579413748</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2084786567643391</v>
+        <v>0.20847869216668183</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986040816362973</v>
+        <v>0.21986044419974807</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -14292,48 +14292,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.61789242274239</v>
+        <v>279.61399747276158</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.06089980703268</v>
+        <v>594.05262480906947</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.49163134876665</v>
+        <v>539.48411647587727</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.67047279148335</v>
+        <v>532.66305293422829</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.03571607298568</v>
+        <v>328.03114668475757</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.6347567184977</v>
+        <v>204.63190624947069</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90885860869201</v>
+        <v>169.90649185562111</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.93107039986916</v>
+        <v>182.9285222533147</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.84222323516065</v>
+        <v>130.84040066254036</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.41675786289605</v>
+        <v>216.41374327595537</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.52369776261207</v>
+        <v>139.52175426100274</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -14404,48 +14404,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.38210757725756</v>
+        <v>-523.38600252723836</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.93910019296732</v>
+        <v>-208.94737519093053</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.50836865123335</v>
+        <v>-420.51588352412273</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.32952720851665</v>
+        <v>-366.33694706577171</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.96428392701432</v>
+        <v>-454.96885331524243</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.36524328150233</v>
+        <v>-503.36809375052928</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09114139130793</v>
+        <v>-818.09350814437892</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.06892960013079</v>
+        <v>-947.07147774668533</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1577767648394</v>
+        <v>-1014.1595993374597</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.58324213710398</v>
+        <v>-468.58625672404463</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.47630223738793</v>
+        <v>-437.47824573899726</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -15490,50 +15490,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8725691963625553E-3</v>
+        <v>2.8725905736950515E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1170466098872327E-3</v>
+        <v>1.1170908503305632E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3710114722601877E-3</v>
+        <v>2.3710538444248379E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1305164891390026E-3</v>
+        <v>2.1305596418937081E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2838263111219608E-3</v>
+        <v>3.2838592919026931E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074200078855326E-3</v>
+        <v>4.6074460988963879E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2197465550405335E-3</v>
+        <v>7.2197674419032139E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795100938667941E-3</v>
+        <v>8.9795342537848238E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.14327979704286E-2</v>
+        <v>1.1432818516644417E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.722664836436628E-3</v>
+        <v>5.7227016526714613E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0505902889877475E-2</v>
+        <v>1.0505949562666537E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -15547,50 +15547,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688920174681254E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0780089522411969E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327895797945166E-2</v>
+        <v>9.7327853425780514E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716270836967171E-2</v>
+        <v>9.8716227684212468E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588490343401867</v>
+        <v>0.10588487045323795</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608264232564002</v>
+        <v>0.10608261623462917</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005797091780018</v>
+        <v>0.1800579500309375</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212696568123515</v>
+        <v>0.18212694152131709</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1910225038129908</v>
+        <v>0.19102248326677496</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680487479376293</v>
+        <v>0.21680483797752811</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475597842901496</v>
+        <v>0.28475593175622588</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422235388003435E-2</v>
+        <v>2.4422230043670314E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -15719,50 +15719,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.968348953441423E-2</v>
+        <v>3.9683473501414879E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093725071945036E-2</v>
+        <v>5.5093680831501707E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360632584259539E-2</v>
+        <v>5.8360590212094887E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867389805933815E-2</v>
+        <v>6.2867346653179113E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2441162320894611E-2</v>
+        <v>6.2441129340113879E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327994770926567E-2</v>
+        <v>5.1327968679915709E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862750839364142</v>
+        <v>0.10862748750677875</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242942135583456</v>
+        <v>0.11242939719591651</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1152666361152026</v>
+        <v>0.11526661556898675</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795970735769639</v>
+        <v>0.13795967054146158</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972511941986532</v>
+        <v>0.16972507274707627</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -15826,50 +15826,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.968348953441423E-2</v>
+        <v>3.9683473501414879E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093725071945036E-2</v>
+        <v>5.5093680831501707E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360632584259539E-2</v>
+        <v>5.8360590212094887E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867389805933815E-2</v>
+        <v>6.2867346653179113E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2441162320894611E-2</v>
+        <v>6.2441129340113879E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327994770926567E-2</v>
+        <v>5.1327968679915709E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862750839364142</v>
+        <v>0.10862748750677875</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242942135583456</v>
+        <v>0.11242939719591651</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1152666361152026</v>
+        <v>0.11526661556898675</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795970735769639</v>
+        <v>0.13795967054146158</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972511941986532</v>
+        <v>0.16972507274707627</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -15895,24 +15895,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.31055554582799999</v>
+        <v>0.31031299899600001</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27783669163399999</v>
+        <v>0.27761969853800006</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.227390565268</v>
+        <v>0.22721297107600003</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -15951,24 +15951,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2992.2427119996059</v>
+        <v>2989.9057420110803</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2992.2427119996059</v>
+        <v>2989.9057420110803</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2689.0388906443586</v>
+        <v>2686.938725721167</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2405.7328200655484</v>
+        <v>2403.8539198752801</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1968.929814925644</v>
+        <v>1967.3920620326235</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -16006,24 +16006,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41384583689866911</v>
+        <v>0.41352278644020923</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.29036632981525007</v>
+        <v>0.29013978393598711</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25979818026227913</v>
+        <v>0.25959546389179078</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22255376110871333</v>
+        <v>0.22238009715046261</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22759469265252458</v>
+        <v>0.22741705915445309</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -16082,24 +16082,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5529957806060596E-2</v>
+        <v>4.5554417471767805E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5529957806060596E-2</v>
+        <v>4.5554417471767805E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0916409199999997E-2</v>
+        <v>4.0938390368865436E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6605624721212121E-2</v>
+        <v>3.6625290044591037E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.995923126060606E-2</v>
+        <v>2.9975325999472297E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -16219,46 +16219,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225047943095456E-2</v>
+        <v>4.8225329397473704E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.630396361752573E-2</v>
+        <v>-1.6304014751442164E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956919189556219E-2</v>
+        <v>1.6956921004266823E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.1570299351210549</v>
+        <v>0.15702978972679715</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578930432374337</v>
+        <v>0.26578922137934713</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196164639884516</v>
+        <v>-0.43196172021492185</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157429990921775E-2</v>
+        <v>6.2157447679556777E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361522151325422</v>
+        <v>0.13361519306503777</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490963041414756E-2</v>
+        <v>-4.549090361975705E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714368786904362</v>
+        <v>0.49714367902353818</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -16830,43 +16830,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.214354783699952</v>
+        <v>1.21435575883164</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920111733013887</v>
+        <v>1.3920121839581763</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756201021509935</v>
+        <v>1.3756210463899348</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871171491876846</v>
+        <v>1.3871178818491054</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848591654344512</v>
+        <v>2.9848606826967723</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067770819304068</v>
+        <v>1.3067773331971357</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351576087738316</v>
+        <v>1.4351579171744018</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994821543364572</v>
+        <v>1.2994823859684932</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941589034450128</v>
+        <v>1.3941592754934624</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917517042401404</v>
+        <v>1.8917522244539593</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -16938,48 +16938,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688920174681254E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0780089522411969E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327895797945166E-2</v>
+        <v>9.7327853425780514E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716270836967171E-2</v>
+        <v>9.8716227684212468E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588490343401867</v>
+        <v>0.10588487045323795</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608264232564002</v>
+        <v>0.10608261623462917</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005797091780018</v>
+        <v>0.1800579500309375</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212696568123515</v>
+        <v>0.18212694152131709</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1910225038129908</v>
+        <v>0.19102248326677496</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680487479376293</v>
+        <v>0.21680483797752811</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475597842901496</v>
+        <v>0.28475593175622588</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -17103,50 +17103,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035937581782973</v>
+        <v>0.20035933197306158</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114156469642632</v>
+        <v>0.1911414715462269</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122275545677776</v>
+        <v>0.20122266785348936</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032527660766132</v>
+        <v>0.21032518466623168</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338046843665369</v>
+        <v>0.19338040820296012</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371116300911957</v>
+        <v>0.1371115963686097</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766128507430308</v>
+        <v>0.25766125518539651</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.2740452973207389</v>
+        <v>0.27404526096746246</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820711959215487</v>
+        <v>0.25820709181961965</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774681021768088</v>
+        <v>0.26774676475085524</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861275948129531</v>
+        <v>0.16861273184490363</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -17224,50 +17224,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91374987601495727</v>
+        <v>0.91303585979325508</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.3023258667630979</v>
+        <v>1.3013076929320369</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3080672803663771</v>
+        <v>1.3070447184242757</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3660970667495278</v>
+        <v>1.36502919499134</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0932946148376705</v>
+        <v>1.0924401643396864</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.7086777910425589</v>
+        <v>0.70812394700107451</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5555667796680086</v>
+        <v>1.5543515683627656</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4985734203244503</v>
+        <v>1.4974026984682534</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2921880462773399</v>
+        <v>1.2911786049836864</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4276107524775969</v>
+        <v>1.4264953942377905</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89317462701552608</v>
+        <v>0.89247680372275329</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -17281,50 +17281,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12038865296639753</v>
+        <v>0.12045327965610227</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17158443567366244</v>
+        <v>0.1716764766401104</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17234088015367288</v>
+        <v>0.17243334016151396</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17998643830692065</v>
+        <v>0.1800830072547942</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14404408627637294</v>
+        <v>0.14412139371235969</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.3369932943683648E-2</v>
+        <v>9.3420045778505864E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20494950983768229</v>
+        <v>0.20505957366263397</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19744050333655472</v>
+        <v>0.19754653014093052</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.1702487544502424</v>
+        <v>0.17034018535404835</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18809100823156746</v>
+        <v>0.18819200451685891</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1176778164710838</v>
+        <v>0.11774100312965083</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17338,43 +17338,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14465848880719909</v>
+        <v>0.14484933114071782</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14082405742196566</v>
+        <v>0.14100984113888118</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12481682798837215</v>
+        <v>0.12498149398835681</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.40074372774957423</v>
+        <v>0.40127241340623593</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14808208825830035</v>
+        <v>0.14827744721378625</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14563231265106788</v>
+        <v>0.14582443971261283</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12496898796397665</v>
+        <v>0.1251338547027154</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12095196460801783</v>
+        <v>0.12111153184364847</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1947415671376632E-2</v>
+        <v>5.2015947882024891E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.530111434024423E-2</v>
+        <v>3.5347685731194421E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3288719577904</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.42390893698</v>
+        <v>96404.384959437215</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17130.210757725759</v>
+        <v>17130.600252723845</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89414.03466666273</v>
+        <v>89414.385212161054</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0942760599999999</v>
+        <v>1.0934214200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.043893660857972</v>
+        <v>13.033749818311779</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7399056769073</v>
+        <v>7373.7369265244051</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.292935513402</v>
+        <v>6859.290164208749</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9924086376759</v>
+        <v>7519.9893703959578</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2946748622398</v>
+        <v>6507.2920457725977</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1457183662314</v>
+        <v>7669.142619863308</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3599051082156</v>
+        <v>6173.3574109355377</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.257370150749</v>
+        <v>7821.2542101913841</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5616622862572</v>
+        <v>5856.5592961070115</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3860404479283</v>
+        <v>7976.3828178131816</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0205514309673</v>
+        <v>5556.0183066769159</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5915695172034</v>
+        <v>8134.5882829639568</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -18490,7 +18490,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.9023054787804</v>
+        <v>5270.9001759187486</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9349845038814</v>
+        <v>8295.931632764361</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4154694399194</v>
+        <v>5000.4134491624964</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4785229801164</v>
+        <v>8460.4751047613991</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8092034116735</v>
+        <v>4743.8072868088038</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.285656952803</v>
+        <v>8628.282170936327</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3711983344192</v>
+        <v>4500.3693800858391</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4211173476469</v>
+        <v>8799.4175621886934</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4256987047656</v>
+        <v>4269.4239737632279</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9509189788569</v>
+        <v>8973.9472933060406</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3316267571049</v>
+        <v>4050.3299903343732</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9423860140996</v>
+        <v>9151.9386884288306</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4808029065289</v>
+        <v>3842.479250460085</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4641779445192</v>
+        <v>9333.4604070204678</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2962575132447</v>
+        <v>3645.2947847336773</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5863160698609</v>
+        <v>9518.5824703524104</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2306292821604</v>
+        <v>3458.2292320812066</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3802105089053</v>
+        <v>9707.3762885145843</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7646458517879</v>
+        <v>3280.7633203509799</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9186877456395</v>
+        <v>9899.9146879615528</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4056823547412</v>
+        <v>3112.4044248746432</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.276018721766</v>
+        <v>10096.271939605016</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6863939485715</v>
+        <v>2952.6852009985664</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.52794748644</v>
+        <v>10296.523787463522</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1634185210096</v>
+        <v>2801.1622867896072</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.75172041421</v>
+        <v>10500.747477880412</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4161459684542</v>
+        <v>2657.4150723140992</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.026116002509</v>
+        <v>10709.021789321292</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0455506314011</v>
+        <v>2521.0445320737549</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.532075692099</v>
+        <v>98316.492353658745</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23145.004322340275</v>
+        <v>23144.994971251355</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.27908064592</v>
+        <v>110204.23455570228</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19142,7 +19142,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.27908064592</v>
+        <v>110204.23455570228</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -19172,19 +19172,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.42390893698</v>
+        <v>96404.384959437215</v>
       </c>
       <c r="C56" s="123">
-        <v>97922.048142271145</v>
+        <v>97922.008579617948</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.45671291578</v>
+        <v>99461.416528307775</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.12775053777</v>
+        <v>101023.08693498044</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.54684867477</v>
+        <v>102607.50539297739</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19193,19 +19193,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.423908936995</v>
+        <v>96404.384959437244</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.118552182757</v>
+        <v>99377.078401649196</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.89700834473</v>
+        <v>102492.85559896842</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.14840906096</v>
+        <v>105760.10567964349</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.72464996192</v>
+        <v>109187.68053572852</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -19214,19 +19214,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.423908937009</v>
+        <v>96404.384959437244</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.60845468809</v>
+        <v>101173.56757833326</v>
       </c>
       <c r="D58" s="123">
-        <v>106331.05542341602</v>
+        <v>106331.01246333958</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.76722437982</v>
+        <v>111913.72200876546</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.2763308929</v>
+        <v>117962.22867154832</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -19245,19 +19245,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.423908937024</v>
+        <v>96404.384959437259</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.15753689327</v>
+        <v>102998.11592338064</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.3981889166</v>
+        <v>110332.35361220999</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.74027001776</v>
+        <v>118504.69239150587</v>
       </c>
       <c r="F59" s="123">
-        <v>127626.0742059785</v>
+        <v>127626.02264224782</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -19276,19 +19276,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.423908937024</v>
+        <v>96404.384959437244</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.68861369361</v>
+        <v>104688.64631716938</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.75299834332</v>
+        <v>114140.70688297792</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.72290525284</v>
+        <v>124956.67241999859</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.52718606754</v>
+        <v>137367.47168657638</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -19307,19 +19307,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.423908937024</v>
+        <v>96404.38495943723</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.44643209476</v>
+        <v>106173.40353569583</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.84487620974</v>
+        <v>117578.79737177987</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.6556521829</v>
+        <v>130953.60274403641</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.94864419254</v>
+        <v>146703.88937258252</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -19399,23 +19399,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -19426,23 +19426,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.491698364961856</v>
+        <v>11.482767428320892</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.6862446777454</v>
+        <v>11.677161720046104</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.883604461199756</v>
+        <v>11.874367283958991</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.083839083329538</v>
+        <v>12.074445440110392</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108422</v>
+        <v>11.291124031259336</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.675586247936419</v>
+        <v>11.666511618874951</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.069349945018397</v>
+        <v>12.059967623803296</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.482256385236559</v>
+        <v>12.472551413475506</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.915424247341239</v>
+        <v>12.905380792491558</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -19480,23 +19480,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108423</v>
+        <v>11.291124031259336</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.902621807663701</v>
+        <v>11.893369770017234</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.554406077464485</v>
+        <v>12.544644726980984</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.25993417242362</v>
+        <v>13.249621512968277</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.024328477450158</v>
+        <v>14.013418510188934</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -19507,23 +19507,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108425</v>
+        <v>11.291124031259338</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.133203411017368</v>
+        <v>12.123771193860575</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.060085009007176</v>
+        <v>13.049928514327684</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.092883610367592</v>
+        <v>14.081920073220045</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.245613248715305</v>
+        <v>15.233748953403383</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -19534,23 +19534,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108425</v>
+        <v>11.291124031259336</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.34684817947528</v>
+        <v>12.337249017474644</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.541374641970037</v>
+        <v>13.530842061214594</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.908267814252337</v>
+        <v>14.896667125118482</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.476711863189674</v>
+        <v>16.46388557116035</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -19560,23 +19560,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108425</v>
+        <v>11.291124031259335</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.53448787724929</v>
+        <v>12.524742091110516</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.975871441978022</v>
+        <v>13.964999339684324</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.66614403774093</v>
+        <v>15.653951134116198</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.656623683812288</v>
+        <v>17.642875393102344</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.915424247341239</v>
+        <v>12.905380792491558</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.092883610367592</v>
+        <v>14.081920073220045</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.060085009007176</v>
+        <v>13.049928514327684</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.133203411017368</v>
+        <v>12.123771193860575</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.299905098108422</v>
+        <v>11.291124031259336</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2992.2427119996059</v>
+        <v>2989.9057420110803</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39896.569493328083</v>
+        <v>39865.409893481075</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2671932726911681</v>
+        <v>5.2630795446995569</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3051.5915623379724</v>
+        <v>3049.2082403334362</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -20032,7 +20032,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2838.689825430672</v>
+        <v>2836.4727817055218</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3112.1175518242967</v>
+        <v>3109.6869584468909</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2693.0168106646161</v>
+        <v>2690.9135389480939</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3173.8440281151175</v>
+        <v>3171.365225773241</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2554.8192964061977</v>
+        <v>2552.8239582613787</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3236.7948019499195</v>
+        <v>3234.2668344555591</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2423.7136624775162</v>
+        <v>2421.8207190784815</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3300.9941563360335</v>
+        <v>3298.4160485359143</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2299.335974933153</v>
+        <v>2297.5401716898509</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3366.4668559157049</v>
+        <v>3363.8376133151323</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -20142,7 +20142,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2181.34097582199</v>
+        <v>2179.6373277941098</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3433.2381565189557</v>
+        <v>3430.5567648981923</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2069.4011247914145</v>
+        <v>2067.7849028507726</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3501.3338149059218</v>
+        <v>3498.5992399289548</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1963.2056898735125</v>
+        <v>1961.6724075765455</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3570.7800987024148</v>
+        <v>3567.9912855179673</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1862.4598849293739</v>
+        <v>1861.0052860632932</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -20218,7 +20218,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3641.6037965325581</v>
+        <v>3638.7596693671817</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1766.8840513571586</v>
+        <v>1765.5040981252007</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3713.8322283523848</v>
+        <v>3710.9316900954873</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1676.2128817924415</v>
+        <v>1674.9037436054157</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3787.4932559884073</v>
+        <v>3784.5351877690437</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1590.1946836459224</v>
+        <v>1588.9527264889409</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3862.6152938851974</v>
+        <v>3859.5985546404731</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -20296,7 +20296,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1508.5906804341548</v>
+        <v>1507.4124567790329</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3939.2273200661507</v>
+        <v>3936.1507461010583</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1431.1743489638866</v>
+        <v>1430.0565881992054</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4017.358887311636</v>
+        <v>4014.2212918501668</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -20340,7 +20340,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1357.7307905300986</v>
+        <v>1356.6703898823698</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4097.0401345588671</v>
+        <v>4093.8403072862156</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -20362,7 +20362,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1288.0561343822708</v>
+        <v>1287.0501503029993</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4178.3017985278711</v>
+        <v>4175.0385051235617</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1221.9569718029597</v>
+        <v>1221.0026117976963</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -20394,7 +20394,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4261.1752255780602</v>
+        <v>4257.8472072398117</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1159.2498192277637</v>
+        <v>1158.3444341044665</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4345.6923837999566</v>
+        <v>4342.2983567581068</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1099.7606089163503</v>
+        <v>1098.9016854315364</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4431.8858753467612</v>
+        <v>4428.4245303690559</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1043.3242057607179</v>
+        <v>1042.5093596429924</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40687.887497839634</v>
+        <v>40656.109871112487</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9578.4636838022234</v>
+        <v>9570.9828126564917</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45607.582105944399</v>
+        <v>45571.962150984386</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -20724,7 +20724,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45607.582105944399</v>
+        <v>45571.962150984386</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -20754,19 +20754,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39896.569493328083</v>
+        <v>39865.409893481075</v>
       </c>
       <c r="C51" s="123">
-        <v>40524.631964269967</v>
+        <v>40492.981841665685</v>
       </c>
       <c r="D51" s="123">
-        <v>41161.709792517373</v>
+        <v>41129.562106076111</v>
       </c>
       <c r="E51" s="123">
-        <v>41808.000850042459</v>
+        <v>41775.348404144606</v>
       </c>
       <c r="F51" s="123">
-        <v>42463.706097709197</v>
+        <v>42430.541539782811</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -20775,19 +20775,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39896.56949332809</v>
+        <v>39865.409893481083</v>
       </c>
       <c r="C52" s="123">
-        <v>41126.806795806318</v>
+        <v>41094.686368937109</v>
       </c>
       <c r="D52" s="123">
-        <v>42416.258738587509</v>
+        <v>42383.131237499416</v>
       </c>
       <c r="E52" s="123">
-        <v>43768.397128875265</v>
+        <v>43734.213594857167</v>
       </c>
       <c r="F52" s="123">
-        <v>45186.885286824923</v>
+        <v>45151.59390007786</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -20796,19 +20796,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39896.56949332809</v>
+        <v>39865.409893481075</v>
       </c>
       <c r="C53" s="123">
-        <v>41870.276662988646</v>
+        <v>41837.575579089171</v>
       </c>
       <c r="D53" s="123">
-        <v>44004.664620022348</v>
+        <v>43970.2965588488</v>
       </c>
       <c r="E53" s="123">
-        <v>46315.046657456289</v>
+        <v>46278.874165959671</v>
       </c>
       <c r="F53" s="123">
-        <v>48818.196970630423</v>
+        <v>48780.069494955809</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -20817,19 +20817,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39896.56949332809</v>
+        <v>39865.409893481075</v>
       </c>
       <c r="C54" s="123">
-        <v>42625.35870487654</v>
+        <v>42592.067894728032</v>
       </c>
       <c r="D54" s="123">
-        <v>45660.603665529372</v>
+        <v>45624.942300227573</v>
       </c>
       <c r="E54" s="123">
-        <v>49042.693413504894</v>
+        <v>49004.390603975393</v>
       </c>
       <c r="F54" s="123">
-        <v>52817.519489864797</v>
+        <v>52776.268505303568</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -20838,19 +20838,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39896.56949332809</v>
+        <v>39865.409893481075</v>
       </c>
       <c r="C55" s="123">
-        <v>43324.977953158173</v>
+        <v>43291.140733729408</v>
       </c>
       <c r="D55" s="123">
-        <v>47236.675448843649</v>
+        <v>47199.783156504214</v>
       </c>
       <c r="E55" s="123">
-        <v>51712.819566839426</v>
+        <v>51672.431363414282</v>
       </c>
       <c r="F55" s="123">
-        <v>56848.979251018784</v>
+        <v>56804.57965807963</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -20859,19 +20859,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39896.569493328097</v>
+        <v>39865.409893481075</v>
       </c>
       <c r="C56" s="123">
-        <v>43939.438795106253</v>
+        <v>43905.121675921684</v>
       </c>
       <c r="D56" s="123">
-        <v>48659.51545937379</v>
+        <v>48621.511915467199</v>
       </c>
       <c r="E56" s="123">
-        <v>54194.625218317735</v>
+        <v>54152.298701098203</v>
       </c>
       <c r="F56" s="123">
-        <v>60712.818402995217</v>
+        <v>60665.401114966538</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -20921,23 +20921,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -20948,23 +20948,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0420210954062012</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1213939404386917</v>
+        <v>5.1133973497096168</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2019061220681468</v>
+        <v>5.193783818891899</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2835826468219551</v>
+        <v>5.2753328131826684</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.366448911593344</v>
+        <v>5.3580696898202156</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -20975,23 +20975,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1974951752638239</v>
+        <v>5.1893797593797331</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3604526420230272</v>
+        <v>5.352082782879334</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5313322533359637</v>
+        <v>5.5226955812246477</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.7105969697462831</v>
+        <v>5.7016803920885533</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -21002,23 +21002,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2914528964849188</v>
+        <v>5.283190774166763</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5611911030980092</v>
+        <v>5.5525078091091418</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8531709680118977</v>
+        <v>5.8440317740262699</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1695123688961822</v>
+        <v>6.1598792365916211</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -21029,23 +21029,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3868781330982518</v>
+        <v>5.3784670129542516</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7704642237243196</v>
+        <v>5.7614541687958125</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1978836252520964</v>
+        <v>6.1882061938117587</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.674935987152006</v>
+        <v>6.6645136818474784</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -21056,23 +21056,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4752941310997381</v>
+        <v>5.4667449574183342</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9696439346684889</v>
+        <v>5.9603228787413327</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5353269835027321</v>
+        <v>6.5251226649567462</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1844210235639432</v>
+        <v>7.1732032037244746</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -21082,23 +21082,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.042021095406203</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5529480388604391</v>
+        <v>5.5442776156664788</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1494586264975863</v>
+        <v>6.1398568062874359</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.848970903477972</v>
+        <v>6.8382768584840949</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6727226184361417</v>
+        <v>7.6607423600785731</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.7105969697462831</v>
+        <v>5.7016803920885533</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1978836252520964</v>
+        <v>6.1882061938117587</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7704642237243196</v>
+        <v>5.7614541687958125</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3868781330982518</v>
+        <v>5.3784670129542516</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0420210954062021</v>
+        <v>5.0341484381538546</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.59</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.329480415733649</v>
+        <v>13.319113551435006</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060899807031</v>
+        <v>10305.052624809068</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3288719577904</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052771628752E-2</v>
+        <v>6.00526745230614E-2</v>
       </c>
       <c r="E14" s="377"/>
       <c r="F14" s="377"/>
@@ -21564,7 +21564,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.29990509810842</v>
+        <v>11.291124031259333</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.060085009007176</v>
+        <v>13.049928514327684</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.133203411017368</v>
+        <v>12.123771193860575</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.092883610367592</v>
+        <v>14.081920073220045</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.081268409681297</v>
+        <v>13.071095362012736</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -21843,7 +21843,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.299905098108422</v>
+        <v>11.291124031259336</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.915424247341239</v>
+        <v>12.905380792491558</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.98390803598565</v>
+        <v>12.973811066999007</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -21989,7 +21989,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.043893660857972</v>
+        <v>13.033749818311779</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8040113935075849E-2</v>
+        <v>-6.8036094258840871E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34557237974799992</v>
+        <v>0.34530248443599998</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58604918132338757</v>
+        <v>0.5855914713444943</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2772069444640133</v>
+        <v>5.2731031111107063</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -22134,7 +22134,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8632561257874007</v>
+        <v>5.8586945824552004</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -22145,7 +22145,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.5484213143271619</v>
+        <v>0.54842146596710195</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22175,7 +22175,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23459463611465181</v>
+        <v>0.23482489268397044</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22201,7 +22201,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67455728526809577</v>
+        <v>0.67403044961907199</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -22213,7 +22213,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6477609144246523</v>
+        <v>6.6425912663034916</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3223181996927478</v>
+        <v>7.3166217159225635</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604666796787828</v>
+        <v>0.43604684250924708</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89866986852348141</v>
+        <v>0.89796799881755474</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.45153400710732</v>
+        <v>10.443406345201511</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -22285,7 +22285,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.3502038756308</v>
+        <v>11.341374344019066</v>
       </c>
       <c r="D99" t="s">
         <v>379</v>
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582530281537296</v>
+        <v>0.12582553534576346</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83372900361808255</v>
+        <v>0.83307785334467521</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.3063510267411278</v>
+        <v>9.2991139192820036</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.14008003035921</v>
+        <v>10.13219177262668</v>
       </c>
       <c r="D105" t="s">
         <v>379</v>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261862186231296</v>
+        <v>0.22261882314240478</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,33 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DAF8C6-5F29-4475-A9E8-419BB8E7EF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E224FD4C-4837-4485-B634-3CFFB56FFD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
-    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
-    <sheet name="Data" sheetId="4" r:id="rId3"/>
-    <sheet name="BS" sheetId="3" r:id="rId4"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
-    <sheet name="DCF" sheetId="8" r:id="rId6"/>
-    <sheet name="DDM" sheetId="10" r:id="rId7"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId9"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
+    <sheet name="Data" sheetId="4" r:id="rId2"/>
+    <sheet name="BS" sheetId="3" r:id="rId3"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,14 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -1518,10 +1531,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1726,10 +1735,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2110,6 +2115,9 @@
   </si>
   <si>
     <t>@ Entry Yield</t>
+  </si>
+  <si>
+    <t>CNY</t>
   </si>
   <si>
     <t>Company Information</t>
@@ -3265,26 +3273,32 @@
     <t>估计(净资产)可变现价值</t>
   </si>
   <si>
-    <t>0135.HK</t>
-  </si>
-  <si>
-    <t>昆仑能源</t>
-  </si>
-  <si>
-    <t>ENG_02</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>DCF</t>
-  </si>
-  <si>
     <t>昆仑能源是中国国内销售规模最大的
 天然气终端利用企业和 LPG 销售企业之一。</t>
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>昆仑能源</t>
+  </si>
+  <si>
+    <t>0135.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ENG_02</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3311,7 +3325,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3751,6 +3765,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3954,11 +3974,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="379">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4734,28 +4755,28 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4770,9 +4791,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{4ACDDE7F-B1E4-4BD6-B1C6-8E7DA039EDE8}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4857,6 +4884,91 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="投资主题"/>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="6">
+          <cell r="C6">
+            <v>8658801708</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>7.58</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1.0934214200000001</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>7.4999999999999997E-2</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="3">
+          <cell r="C3">
+            <v>1000000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="93">
+          <cell r="C93">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5056,1749 +5168,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
-  <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="B1" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="C1" s="33">
-        <f>Thesis!C1</f>
-        <v>45867</v>
-      </c>
-      <c r="D1" s="358" t="str">
-        <f>Thesis!D1</f>
-        <v>INT</v>
-      </c>
-      <c r="E1" s="292" t="s">
-        <v>345</v>
-      </c>
-      <c r="F1" s="307" t="str">
-        <f>Thesis!F1</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="222" t="s">
-        <v>440</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="45" t="s">
-        <v>441</v>
-      </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.4">
-      <c r="B5" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="C5" s="359" t="str">
-        <f>Thesis!C5</f>
-        <v>昆仑能源</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="C6" s="34">
-        <f>Common_Shares</f>
-        <v>8658801708</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C7" s="360">
-        <f>Thesis!C7</f>
-        <v>6</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C8" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="E9" s="34"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="45" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C11" s="365" t="str">
-        <f>Thesis!C11</f>
-        <v>0135.HK</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="C12" s="366">
-        <f>Market_Price</f>
-        <v>7.58</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="48"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="C13" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="C14" s="35">
-        <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>65633.716946639994</v>
-      </c>
-      <c r="D14" s="35" t="str">
-        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
-        <v/>
-      </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="C15" s="32" t="str">
-        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
-        <v>CNY/HKD</v>
-      </c>
-      <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
-        <v/>
-      </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="C16" s="366">
-        <f>Exchange_Rate</f>
-        <v>1.0934214200000001</v>
-      </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
-        <v>491</v>
-      </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="45" t="s">
-        <v>492</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C21" s="32" t="str">
-        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Low Growth </v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E21" s="363" t="str">
-        <f>valuation_method</f>
-        <v>DCF</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C22" s="32" t="str">
-        <f>Thesis!C22</f>
-        <v>ENG_02</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","终值贴现率","")</f>
-        <v/>
-      </c>
-      <c r="E22" s="364">
-        <f>Thesis!E22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C23" s="253" t="str">
-        <f>Thesis!C23</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C24" s="253" t="str">
-        <f>Thesis!C24</f>
-        <v>N</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="C25" s="32" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="D25" s="32" t="str">
-        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
-        <v/>
-      </c>
-      <c r="E25" s="299" t="str">
-        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="1" t="str">
-        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
-        <v>预期股权价值 (HKD) :</v>
-      </c>
-      <c r="C26" s="304">
-        <f>C132</f>
-        <v>12.973811066999007</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E26" s="301">
-        <f ca="1">Scenarios!C87</f>
-        <v>0.23482489268397044</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="45" t="s">
-        <v>450</v>
-      </c>
-      <c r="C28" s="309" t="str">
-        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
-        <v>0135.HK (HKD)</v>
-      </c>
-      <c r="D28" s="309" t="str">
-        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
-        <v/>
-      </c>
-      <c r="E28" s="305" t="s">
-        <v>455</v>
-      </c>
-      <c r="F28" s="361">
-        <f>Thesis!F28</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C29" s="310">
-        <f>C149</f>
-        <v>5.8586945824552004</v>
-      </c>
-      <c r="D29" s="310" t="str">
-        <f>D149</f>
-        <v/>
-      </c>
-      <c r="E29" s="306" t="s">
-        <v>457</v>
-      </c>
-      <c r="F29" s="362">
-        <f>Thesis!F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C30" s="311">
-        <f>C157</f>
-        <v>7.3166217159225635</v>
-      </c>
-      <c r="D30" s="311" t="str">
-        <f>D157</f>
-        <v/>
-      </c>
-      <c r="E30" s="307" t="s">
-        <v>456</v>
-      </c>
-      <c r="F30" s="224">
-        <f>Thesis!F30</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C31" s="311">
-        <f>C165</f>
-        <v>11.341374344019066</v>
-      </c>
-      <c r="D31" s="311" t="str">
-        <f>D165</f>
-        <v/>
-      </c>
-      <c r="E31" s="307" t="s">
-        <v>493</v>
-      </c>
-      <c r="F31" s="224">
-        <f>Thesis!F31</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C32" s="311">
-        <f>C173</f>
-        <v>10.13219177262668</v>
-      </c>
-      <c r="D32" s="311" t="str">
-        <f>D173</f>
-        <v/>
-      </c>
-      <c r="E32" s="307" t="s">
-        <v>458</v>
-      </c>
-      <c r="F32" s="224">
-        <f>Thesis!F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="222" t="s">
-        <v>459</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-    </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
-        <v>494</v>
-      </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
-        <v>331</v>
-      </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39" s="210" t="s">
-        <v>495</v>
-      </c>
-      <c r="C39" s="108">
-        <f>scaling_factor</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
-        <v>496</v>
-      </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="B41" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C41" s="349">
-        <f>Normalized_FCF!C8</f>
-        <v>17421.507258354162</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="B42" s="47"/>
-      <c r="C42" s="76"/>
-    </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
-        <v>497</v>
-      </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="B44" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="C44" s="349">
-        <f>Normalized_FCF!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="B45" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="C45" s="349">
-        <f>Normalized_FCF!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
-        <v>498</v>
-      </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="B48" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="C48" s="349">
-        <f>Normalized_FCF!C11</f>
-        <v>900.8</v>
-      </c>
-      <c r="D48" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
-        <v>499</v>
-      </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="47" t="s">
-        <v>332</v>
-      </c>
-      <c r="C51" s="350">
-        <f>Normalized_FCF!C48</f>
-        <v>279.61399747276158</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E51" s="286"/>
-      <c r="F51" s="286"/>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="47" t="s">
-        <v>333</v>
-      </c>
-      <c r="C52" s="350">
-        <f>Normalized_FCF!C47</f>
-        <v>-803</v>
-      </c>
-      <c r="D52" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E52" s="286"/>
-      <c r="F52" s="286"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C53" s="349">
-        <f>Normalized_FCF!C12</f>
-        <v>-523.38600252723836</v>
-      </c>
-      <c r="D53" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="349">
-        <f>Normalized_FCF!C15</f>
-        <v>-6118.862069912404</v>
-      </c>
-      <c r="D56" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
-        <v>237</v>
-      </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="C59" s="349">
-        <f>Normalized_FCF!C14</f>
-        <v>-4449.7303139567312</v>
-      </c>
-      <c r="D59" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
-        <v>501</v>
-      </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C62" s="349">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
-        <v>502</v>
-      </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
-        <v>503</v>
-      </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="47" t="s">
-        <v>504</v>
-      </c>
-      <c r="C67" s="349">
-        <f>Normalized_FCF!G19</f>
-        <v>10305.052624809068</v>
-      </c>
-      <c r="D67" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="C68" s="349">
-        <f>Normalized_FCF!C19</f>
-        <v>7230.3288719577904</v>
-      </c>
-      <c r="D68" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="227" t="s">
-        <v>373</v>
-      </c>
-      <c r="C69" s="92">
-        <f>Normalized_FCF!C126</f>
-        <v>0.12045327965610227</v>
-      </c>
-      <c r="F69" s="314"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="227" t="s">
-        <v>436</v>
-      </c>
-      <c r="C70" s="92">
-        <f>Normalized_FCF!C94</f>
-        <v>4.5554417471767805E-2</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>505</v>
-      </c>
-      <c r="F70" s="315">
-        <f>Normalized_FCF!C92</f>
-        <v>0.41352278644020923</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="210" t="s">
-        <v>515</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>431</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="47" t="s">
-        <v>430</v>
-      </c>
-      <c r="C73" s="92">
-        <f>Normalized_FCF!C121</f>
-        <v>0.20035933197306158</v>
-      </c>
-      <c r="D73" s="92">
-        <f>Normalized_FCF!G121</f>
-        <v>0.1911414715462269</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
-        <v>Pre-tax Profit/Sales</v>
-      </c>
-      <c r="C74" s="322">
-        <f>Normalized_FCF!C118</f>
-        <v>9.7688920174681254E-2</v>
-      </c>
-      <c r="D74" s="322">
-        <f>Normalized_FCF!G118</f>
-        <v>9.0780089522411969E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
-        <v>Sales/Total Assets</v>
-      </c>
-      <c r="C75" s="324">
-        <f>Normalized_FCF!C119</f>
-        <v>1.2706604365715879</v>
-      </c>
-      <c r="D75" s="324">
-        <f>Normalized_FCF!G119</f>
-        <v>1.3044563777111375</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B120</f>
-        <v>Total Assets/Equity</v>
-      </c>
-      <c r="C76" s="324">
-        <f>Normalized_FCF!C120</f>
-        <v>1.6141160578600777</v>
-      </c>
-      <c r="D76" s="324">
-        <f>Normalized_FCF!G120</f>
-        <v>1.6141160578600777</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="13.9">
-      <c r="A78" s="222" t="s">
-        <v>507</v>
-      </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="209"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
-        <v>508</v>
-      </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="B83" s="210" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="B84" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C84" s="92">
-        <f>F31</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="B85" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C85" s="92">
-        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="C86" s="236">
-        <f>F31+C85</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="C87" s="121"/>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="B88" s="293" t="s">
-        <v>514</v>
-      </c>
-      <c r="C88" s="121"/>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
-        <v>509</v>
-      </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
-        <v>510</v>
-      </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="C92" s="236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="C93" s="223">
-        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.173811463910068</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="13.9">
-      <c r="A95" s="222" t="s">
-        <v>511</v>
-      </c>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36"/>
-      <c r="D95" s="36"/>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="209"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
-        <v>512</v>
-      </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6">
-      <c r="B100" s="210" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
-        <v>513</v>
-      </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
-    </row>
-    <row r="102" spans="2:6">
-      <c r="B102" s="47" t="s">
-        <v>251</v>
-      </c>
-      <c r="C102" s="349">
-        <f>DCF!C7</f>
-        <v>24279</v>
-      </c>
-      <c r="D102" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="103" spans="2:6">
-      <c r="B103" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="C103" s="223">
-        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0659183050297427</v>
-      </c>
-      <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6">
-      <c r="B104" s="296" t="s">
-        <v>386</v>
-      </c>
-      <c r="C104" s="325">
-        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
-        <v>0.27330444081724548</v>
-      </c>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="B105" s="296" t="s">
-        <v>388</v>
-      </c>
-      <c r="C105" s="326">
-        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>1.3936222417470483</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="47" t="s">
-        <v>260</v>
-      </c>
-      <c r="C108" s="349">
-        <f>BS!C66</f>
-        <v>45092</v>
-      </c>
-      <c r="D108" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="B109" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="C109" s="349">
-        <f>DCF!C8</f>
-        <v>17130.600252723845</v>
-      </c>
-      <c r="D109" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="B110" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C110" s="223">
-        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1632283409931699</v>
-      </c>
-      <c r="D110" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="B112" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="C113" s="349">
-        <f>DCF!C9</f>
-        <v>158.4</v>
-      </c>
-      <c r="D113" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="C114" s="223">
-        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0002531385835957E-2</v>
-      </c>
-      <c r="D114" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
-        <v>518</v>
-      </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="47" t="s">
-        <v>519</v>
-      </c>
-      <c r="C118" s="223">
-        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.291124031259333</v>
-      </c>
-      <c r="D118" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="296" t="s">
-        <v>552</v>
-      </c>
-      <c r="C119" s="223">
-        <f>BS!D47</f>
-        <v>-3.1931692575392558</v>
-      </c>
-      <c r="D119" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="222" t="s">
-        <v>520</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
-        <v>521</v>
-      </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
-      <c r="B125" s="233" t="s">
-        <v>522</v>
-      </c>
-      <c r="C125" s="233" t="s">
-        <v>523</v>
-      </c>
-      <c r="D125" s="233" t="s">
-        <v>108</v>
-      </c>
-      <c r="E125" s="233" t="s">
-        <v>524</v>
-      </c>
-      <c r="F125" s="233" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="228" t="str">
-        <f>DCF!B74</f>
-        <v>Snowball Scenario</v>
-      </c>
-      <c r="C126" s="229">
-        <f>DCF!C74</f>
-        <v>0.04</v>
-      </c>
-      <c r="D126" s="230">
-        <f>DCF!D74</f>
-        <v>10</v>
-      </c>
-      <c r="E126" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.91 HKD</v>
-      </c>
-      <c r="F126" s="232">
-        <f>DCF!F74</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="218" t="str">
-        <f>DCF!B75</f>
-        <v>Optimistic</v>
-      </c>
-      <c r="C127" s="219">
-        <f>DCF!C75</f>
-        <v>0.03</v>
-      </c>
-      <c r="D127" s="220">
-        <f>DCF!D75</f>
-        <v>20</v>
-      </c>
-      <c r="E127" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.08 HKD</v>
-      </c>
-      <c r="F127" s="221">
-        <f>DCF!F75</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="218" t="str">
-        <f>DCF!B76</f>
-        <v>Base</v>
-      </c>
-      <c r="C128" s="219">
-        <f>DCF!C76</f>
-        <v>0.02</v>
-      </c>
-      <c r="D128" s="220">
-        <f>DCF!D76</f>
-        <v>20</v>
-      </c>
-      <c r="E128" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.05 HKD</v>
-      </c>
-      <c r="F128" s="221">
-        <f>DCF!F76</f>
-        <v>0.53999999999999992</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="B129" s="218" t="str">
-        <f>DCF!B77</f>
-        <v>Pessimistic</v>
-      </c>
-      <c r="C129" s="219">
-        <f>DCF!C77</f>
-        <v>0.01</v>
-      </c>
-      <c r="D129" s="220">
-        <f>DCF!D77</f>
-        <v>20</v>
-      </c>
-      <c r="E129" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
-      </c>
-      <c r="F129" s="221">
-        <f>DCF!F77</f>
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="B130" s="218" t="str">
-        <f>DCF!B78</f>
-        <v>Devil's advocate</v>
-      </c>
-      <c r="C130" s="219">
-        <f>DCF!C78</f>
-        <v>0</v>
-      </c>
-      <c r="D130" s="220">
-        <f>DCF!D78</f>
-        <v>10</v>
-      </c>
-      <c r="E130" s="231" t="str">
-        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.29 HKD</v>
-      </c>
-      <c r="F130" s="221">
-        <f>DCF!F78</f>
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="211" t="s">
-        <v>254</v>
-      </c>
-      <c r="C132" s="217">
-        <f>Scenarios!C60</f>
-        <v>12.973811066999007</v>
-      </c>
-      <c r="D132" s="212" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
-        <v>526</v>
-      </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
-      <c r="A136" s="222" t="s">
-        <v>527</v>
-      </c>
-      <c r="B136" s="36"/>
-      <c r="C136" s="36"/>
-      <c r="D136" s="36"/>
-      <c r="E136" s="36"/>
-      <c r="F136" s="36"/>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
-        <v>528</v>
-      </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
-        <v>529</v>
-      </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="210" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="B141" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C141" s="225">
-        <f>F28</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="B142" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C142" s="224">
-        <f>F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="B143" s="212" t="s">
-        <v>532</v>
-      </c>
-      <c r="C143" s="213">
-        <f>Scenarios!C77</f>
-        <v>0.34530248443599998</v>
-      </c>
-      <c r="D143" s="212" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="210" t="s">
-        <v>533</v>
-      </c>
-      <c r="C145" s="241" t="str">
-        <f>C11</f>
-        <v>0135.HK</v>
-      </c>
-      <c r="D145" s="241" t="str">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C146" s="297">
-        <f>F29</f>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C147" s="216">
-        <f>Scenarios!C81</f>
-        <v>0.5855914713444943</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C148" s="216">
-        <f>Scenarios!C82</f>
-        <v>5.2731031111107063</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C149" s="215">
-        <f>Scenarios!C83</f>
-        <v>5.8586945824552004</v>
-      </c>
-      <c r="D149" s="300" t="str">
-        <f>IF($D$11="","",C149*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" s="259" t="s">
-        <v>534</v>
-      </c>
-      <c r="C150" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D150" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="214" t="s">
-        <v>535</v>
-      </c>
-      <c r="C151" s="92">
-        <f>Scenarios!F83</f>
-        <v>0.54842146596710195</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="210" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C154" s="297">
-        <f>Scenarios!C90</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C155" s="216">
-        <f>Scenarios!C91</f>
-        <v>0.67403044961907199</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C156" s="216">
-        <f>Scenarios!C92</f>
-        <v>6.6425912663034916</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="80" t="s">
-        <v>256</v>
-      </c>
-      <c r="C157" s="215">
-        <f>Scenarios!C93</f>
-        <v>7.3166217159225635</v>
-      </c>
-      <c r="D157" s="300" t="str">
-        <f>IF($D$11="","",C157*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" s="259" t="s">
-        <v>534</v>
-      </c>
-      <c r="C158" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D158" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="214" t="s">
-        <v>535</v>
-      </c>
-      <c r="C159" s="92">
-        <f>Scenarios!F93</f>
-        <v>0.43604684250924708</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" s="210" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C162" s="92">
-        <f>Scenarios!C96</f>
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C163" s="216">
-        <f>Scenarios!C97</f>
-        <v>0.89796799881755474</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C164" s="216">
-        <f>Scenarios!C98</f>
-        <v>10.443406345201511</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4">
-      <c r="B165" s="80" t="s">
-        <v>384</v>
-      </c>
-      <c r="C165" s="215">
-        <f>Scenarios!C99</f>
-        <v>11.341374344019066</v>
-      </c>
-      <c r="D165" s="300" t="str">
-        <f>IF($D$11="","",C165*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="2:4">
-      <c r="B166" s="259" t="s">
-        <v>534</v>
-      </c>
-      <c r="C166" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D166" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" s="214" t="s">
-        <v>535</v>
-      </c>
-      <c r="C167" s="92">
-        <f>Scenarios!F99</f>
-        <v>0.12582553534576346</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" s="210" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C170" s="92">
-        <f>F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" s="212" t="str">
-        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
-        <v>PV(3 yrs of Dividends)</v>
-      </c>
-      <c r="C171" s="216">
-        <f>Scenarios!C103</f>
-        <v>0.83307785334467521</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" s="212" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
-        <v>+ PV(Equity Value realized at year 3)</v>
-      </c>
-      <c r="C172" s="216">
-        <f>Scenarios!C104</f>
-        <v>9.2991139192820036</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" s="80" t="s">
-        <v>384</v>
-      </c>
-      <c r="C173" s="215">
-        <f>Scenarios!C105</f>
-        <v>10.13219177262668</v>
-      </c>
-      <c r="D173" s="300" t="str">
-        <f>IF($D$11="","",C173*$E$25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
-      <c r="B174" s="259" t="s">
-        <v>534</v>
-      </c>
-      <c r="C174" s="298" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="D174" s="298" t="str">
-        <f>IF($D$11="","",D$13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" s="214" t="s">
-        <v>535</v>
-      </c>
-      <c r="C175" s="92">
-        <f>Scenarios!F105</f>
-        <v>0.22261882314240478</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="13.9">
-      <c r="A177" s="222" t="s">
-        <v>359</v>
-      </c>
-      <c r="B177" s="36"/>
-      <c r="C177" s="36"/>
-      <c r="D177" s="36"/>
-      <c r="E177" s="36"/>
-      <c r="F177" s="36"/>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
-        <v>536</v>
-      </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="B181" s="210" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
-        <v>538</v>
-      </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="B183" s="214" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="B184" s="214" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="B185" s="214" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="B187" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
-        <v>543</v>
-      </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="B190" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
-        <v>545</v>
-      </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
-        <v>546</v>
-      </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" s="214" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="214" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="214" t="s">
-        <v>550</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B116:F116"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
-  </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
-      <formula1>"INT,CN"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
-      <formula1>"DCF,DDM"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
-      <formula1>"Y, N"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6821,13 +5190,13 @@
         <v>45867</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -6846,7 +5215,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -6855,7 +5224,7 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C5" s="294" t="s">
         <v>554</v>
@@ -6863,7 +5232,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C6" s="51">
         <v>8658801708</v>
@@ -6872,7 +5241,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -6882,7 +5251,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -6895,24 +5264,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>553</v>
-      </c>
-      <c r="D11" s="49"/>
+        <v>555</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>556</v>
+      </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C12" s="50">
         <v>7.58</v>
@@ -6922,17 +5293,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -6946,7 +5317,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -6960,7 +5331,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C16" s="50">
         <v>1.0934214200000001</v>
@@ -6973,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
-        <v>470</v>
-      </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="B18" s="367" t="s">
+        <v>469</v>
+      </c>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367"/>
+      <c r="E18" s="367"/>
+      <c r="F18" s="367"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -6990,17 +5361,17 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -7008,7 +5379,7 @@
         <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
@@ -7018,26 +5389,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>312</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>312</v>
+        <v>553</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>556</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -7058,7 +5429,7 @@
         <v>12.973811066999007</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -7071,7 +5442,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -7082,7 +5453,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -7090,7 +5461,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -7101,7 +5472,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.35</v>
@@ -7109,7 +5480,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -7120,7 +5491,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.25</v>
@@ -7128,7 +5499,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -7139,7 +5510,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -7147,7 +5518,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -7158,7 +5529,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -7170,7 +5541,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -7179,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
-        <v>471</v>
-      </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="B36" s="367" t="s">
+        <v>470</v>
+      </c>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="367"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
-        <v>331</v>
-      </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="B37" s="369" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7206,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="368" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="368"/>
+      <c r="D40" s="368"/>
+      <c r="E40" s="368"/>
+      <c r="F40" s="368"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7232,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="368" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="368"/>
+      <c r="D43" s="368"/>
+      <c r="E43" s="368"/>
+      <c r="F43" s="368"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7267,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="368" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="368"/>
+      <c r="D47" s="368"/>
+      <c r="E47" s="368"/>
+      <c r="F47" s="368"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7289,17 +5660,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="368" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="368"/>
+      <c r="D50" s="368"/>
+      <c r="E50" s="368"/>
+      <c r="F50" s="368"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -7314,7 +5685,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -7359,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="368" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7381,13 +5752,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
-        <v>330</v>
-      </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="B61" s="368" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="371"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7403,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
-        <v>335</v>
-      </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="B64" s="367" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="367"/>
+      <c r="D64" s="367"/>
+      <c r="E64" s="367"/>
+      <c r="F64" s="367"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
-        <v>350</v>
-      </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="B65" s="367" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="367"/>
+      <c r="D65" s="367"/>
+      <c r="E65" s="367"/>
+      <c r="F65" s="367"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7448,7 +5819,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -7458,14 +5829,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>4.5554417471767805E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -7474,18 +5845,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C72" s="323" t="s">
+        <v>430</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>431</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -7540,7 +5911,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -7553,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
-        <v>473</v>
-      </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="B80" s="367" t="s">
+        <v>472</v>
+      </c>
+      <c r="C80" s="367"/>
+      <c r="D80" s="367"/>
+      <c r="E80" s="367"/>
+      <c r="F80" s="367"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7577,7 +5948,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -7586,7 +5957,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -7607,27 +5978,27 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
-        <v>351</v>
-      </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="B89" s="367" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="B90" s="367" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7652,7 +6023,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -7664,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
-        <v>353</v>
-      </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="B97" s="367" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="367"/>
+      <c r="D97" s="367"/>
+      <c r="E97" s="367"/>
+      <c r="F97" s="367"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7683,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
-        <v>336</v>
-      </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="B101" s="367" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="367"/>
+      <c r="D101" s="367"/>
+      <c r="E101" s="367"/>
+      <c r="F101" s="367"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7719,7 +6090,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -7728,7 +6099,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -7811,17 +6182,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
-        <v>354</v>
-      </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="B116" s="367" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="367"/>
+      <c r="D116" s="367"/>
+      <c r="E116" s="367"/>
+      <c r="F116" s="367"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -7834,7 +6205,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -7847,7 +6218,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -7856,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
-        <v>475</v>
-      </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="B123" s="368" t="s">
+        <v>474</v>
+      </c>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8005,17 +6376,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
-        <v>476</v>
-      </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="B134" s="372" t="s">
+        <v>475</v>
+      </c>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -8025,7 +6396,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="370" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C138" s="370"/>
       <c r="D138" s="370"/>
@@ -8033,13 +6404,13 @@
       <c r="F138" s="370"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
-        <v>478</v>
-      </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="B139" s="367" t="s">
+        <v>477</v>
+      </c>
+      <c r="C139" s="367"/>
+      <c r="D139" s="367"/>
+      <c r="E139" s="367"/>
+      <c r="F139" s="367"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8079,7 +6450,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -8092,7 +6463,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -8134,7 +6505,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -8156,12 +6527,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -8203,7 +6574,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -8225,12 +6596,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -8259,7 +6630,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -8272,7 +6643,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -8294,12 +6665,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -8328,7 +6699,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -8341,7 +6712,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -8363,7 +6734,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -8372,102 +6743,113 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
-        <v>479</v>
-      </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="B179" s="374" t="s">
+        <v>478</v>
+      </c>
+      <c r="C179" s="367"/>
+      <c r="D179" s="367"/>
+      <c r="E179" s="367"/>
+      <c r="F179" s="367"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
-        <v>364</v>
-      </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="B182" s="371" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="371"/>
+      <c r="D182" s="371"/>
+      <c r="E182" s="371"/>
+      <c r="F182" s="371"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
-        <v>480</v>
-      </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="B188" s="368" t="s">
+        <v>479</v>
+      </c>
+      <c r="C188" s="368"/>
+      <c r="D188" s="368"/>
+      <c r="E188" s="368"/>
+      <c r="F188" s="368"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
-        <v>365</v>
-      </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="B191" s="373" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="373"/>
+      <c r="D191" s="373"/>
+      <c r="E191" s="373"/>
+      <c r="F191" s="373"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
-        <v>366</v>
-      </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="B192" s="373" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="373"/>
+      <c r="D192" s="373"/>
+      <c r="E192" s="373"/>
+      <c r="F192" s="373"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8484,17 +6866,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -8519,7 +6890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9070,7 +7441,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>12514</v>
@@ -9106,7 +7477,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-3491</v>
@@ -9142,7 +7513,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-8586</v>
@@ -9210,7 +7581,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>215</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -10515,7 +8886,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -11126,7 +9497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -11393,7 +9764,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -11891,7 +10262,7 @@
         <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>57</v>
@@ -12187,12 +10558,12 @@
         <v>-13980.699873638077</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -12216,12 +10587,12 @@
         <v>27961.399747276155</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -12229,7 +10600,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -12397,7 +10768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -13246,7 +11617,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -13271,7 +11642,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -13599,7 +11970,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -13659,7 +12030,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -13783,7 +12154,7 @@
         <v>-5900</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -13841,7 +12212,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -14149,7 +12520,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -14288,7 +12659,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -14343,7 +12714,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -14475,7 +12846,7 @@
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -14502,7 +12873,7 @@
         <v>3.3073849829070391E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -14817,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -15378,7 +13749,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>346</v>
+        <v>560</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16057,7 +14428,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C93" s="356">
         <v>0</v>
@@ -16078,7 +14449,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -16772,7 +15143,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -16824,7 +15195,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -17333,7 +15704,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -18078,7 +16449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -18283,7 +16654,7 @@
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18342,7 +16713,7 @@
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -18364,7 +16735,7 @@
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -18386,7 +16757,7 @@
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -18418,7 +16789,7 @@
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -18450,7 +16821,7 @@
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -18482,7 +16853,7 @@
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
@@ -18504,7 +16875,7 @@
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
@@ -18526,7 +16897,7 @@
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
@@ -18548,7 +16919,7 @@
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
@@ -18570,7 +16941,7 @@
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
@@ -18592,7 +16963,7 @@
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E31" s="124">
         <f t="shared" si="0"/>
@@ -18614,7 +16985,7 @@
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E32" s="124">
         <f t="shared" si="0"/>
@@ -18636,7 +17007,7 @@
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E33" s="124">
         <f t="shared" si="0"/>
@@ -18668,7 +17039,7 @@
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E34" s="124">
         <f t="shared" si="0"/>
@@ -18700,7 +17071,7 @@
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E35" s="124">
         <f t="shared" si="0"/>
@@ -18732,7 +17103,7 @@
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E36" s="124">
         <f t="shared" si="0"/>
@@ -18754,7 +17125,7 @@
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E37" s="124">
         <f t="shared" si="0"/>
@@ -18776,7 +17147,7 @@
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E38" s="124">
         <f t="shared" si="0"/>
@@ -18798,7 +17169,7 @@
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E39" s="124">
         <f t="shared" si="0"/>
@@ -18820,7 +17191,7 @@
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E40" s="124">
         <f t="shared" si="0"/>
@@ -19838,7 +18209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -19855,7 +18226,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -19867,7 +18238,7 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -19880,7 +18251,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -19912,7 +18283,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -19928,7 +18299,7 @@
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -19965,7 +18336,7 @@
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="H11" s="120"/>
     </row>
@@ -20001,7 +18372,7 @@
         <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D15" s="128" t="s">
         <v>114</v>
@@ -20010,7 +18381,7 @@
         <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -20024,7 +18395,7 @@
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -20046,7 +18417,7 @@
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -20068,7 +18439,7 @@
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -20090,7 +18461,7 @@
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -20112,7 +18483,7 @@
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -20134,7 +18505,7 @@
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" si="0"/>
@@ -20156,7 +18527,7 @@
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -20178,7 +18549,7 @@
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -20200,7 +18571,7 @@
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -20222,7 +18593,7 @@
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -20244,7 +18615,7 @@
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
@@ -20266,7 +18637,7 @@
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
@@ -20288,7 +18659,7 @@
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
@@ -20310,7 +18681,7 @@
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
@@ -20332,7 +18703,7 @@
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
@@ -20354,7 +18725,7 @@
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E31" s="124">
         <f t="shared" si="0"/>
@@ -20376,7 +18747,7 @@
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E32" s="124">
         <f t="shared" si="0"/>
@@ -20398,7 +18769,7 @@
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E33" s="124">
         <f t="shared" si="0"/>
@@ -20420,7 +18791,7 @@
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E34" s="124">
         <f t="shared" si="0"/>
@@ -20442,7 +18813,7 @@
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="E35" s="124">
         <f t="shared" si="0"/>
@@ -21289,7 +19660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -21458,7 +19829,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E11" s="377"/>
       <c r="F11" s="377"/>
@@ -21532,7 +19903,7 @@
         <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -21543,7 +19914,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="377" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F18" s="378"/>
     </row>
@@ -21943,7 +20314,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -21968,7 +20339,7 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -21976,7 +20347,7 @@
         <v>130</v>
       </c>
       <c r="C65" s="151">
-        <v>1.9834236741680042E-2</v>
+        <v>1.983423674168E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
@@ -22001,7 +20372,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
         <v>306</v>
@@ -22048,7 +20419,7 @@
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -22081,7 +20452,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -22183,12 +20554,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -22239,14 +20610,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -22281,14 +20652,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>11.341374344019066</v>
       </c>
       <c r="D99" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
         <v>122</v>
@@ -22303,12 +20674,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -22337,14 +20708,14 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>10.13219177262668</v>
       </c>
       <c r="D105" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
         <v>122</v>
@@ -22359,32 +20730,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
+        <v>316</v>
+      </c>
+      <c r="F108" s="283" t="s">
         <v>317</v>
-      </c>
-      <c r="F108" s="283" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -22403,27 +20774,1771 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45867</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>INT</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>439</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>昆仑能源</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>8658801708</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>0135.HK</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>7.58</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>65633.716946639994</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1.0934214200000001</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="367" t="s">
+        <v>490</v>
+      </c>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367"/>
+      <c r="E18" s="367"/>
+      <c r="F18" s="367"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>491</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>ENG_02</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (HKD) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>12.973811066999007</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>0.23482489268397044</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>449</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0135.HK (HKD)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>454</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>5.8586945824552004</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>7.3166217159225635</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>455</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>11.341374344019066</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>492</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>10.13219177262668</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>457</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>458</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="367" t="s">
+        <v>493</v>
+      </c>
+      <c r="C36" s="367"/>
+      <c r="D36" s="367"/>
+      <c r="E36" s="367"/>
+      <c r="F36" s="367"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="369" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="369"/>
+      <c r="D37" s="369"/>
+      <c r="E37" s="369"/>
+      <c r="F37" s="369"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>494</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="368" t="s">
+        <v>495</v>
+      </c>
+      <c r="C40" s="368"/>
+      <c r="D40" s="368"/>
+      <c r="E40" s="368"/>
+      <c r="F40" s="368"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>17421.507258354162</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="368" t="s">
+        <v>496</v>
+      </c>
+      <c r="C43" s="368"/>
+      <c r="D43" s="368"/>
+      <c r="E43" s="368"/>
+      <c r="F43" s="368"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="368" t="s">
+        <v>497</v>
+      </c>
+      <c r="C47" s="368"/>
+      <c r="D47" s="368"/>
+      <c r="E47" s="368"/>
+      <c r="F47" s="368"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>900.8</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="368" t="s">
+        <v>498</v>
+      </c>
+      <c r="C50" s="368"/>
+      <c r="D50" s="368"/>
+      <c r="E50" s="368"/>
+      <c r="F50" s="368"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>279.61399747276158</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-803</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-523.38600252723836</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-6118.862069912404</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="368" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="368"/>
+      <c r="D58" s="368"/>
+      <c r="E58" s="368"/>
+      <c r="F58" s="368"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-4449.7303139567312</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="368" t="s">
+        <v>500</v>
+      </c>
+      <c r="C61" s="371"/>
+      <c r="D61" s="371"/>
+      <c r="E61" s="371"/>
+      <c r="F61" s="371"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="367" t="s">
+        <v>501</v>
+      </c>
+      <c r="C64" s="367"/>
+      <c r="D64" s="367"/>
+      <c r="E64" s="367"/>
+      <c r="F64" s="367"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="367" t="s">
+        <v>502</v>
+      </c>
+      <c r="C65" s="367"/>
+      <c r="D65" s="367"/>
+      <c r="E65" s="367"/>
+      <c r="F65" s="367"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>10305.052624809068</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>7230.3288719577904</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>0.12045327965610227</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>435</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>4.5554417471767805E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.41352278644020923</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>514</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>430</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>429</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.20035933197306158</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.1911414715462269</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>9.7688920174681254E-2</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>9.0780089522411969E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>1.2706604365715879</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>1.3044563777111375</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.6141160578600777</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.6141160578600777</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>506</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="367" t="s">
+        <v>507</v>
+      </c>
+      <c r="C80" s="367"/>
+      <c r="D80" s="367"/>
+      <c r="E80" s="367"/>
+      <c r="F80" s="367"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="369" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="369"/>
+      <c r="D81" s="369"/>
+      <c r="E81" s="369"/>
+      <c r="F81" s="369"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>513</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="367" t="s">
+        <v>508</v>
+      </c>
+      <c r="C89" s="367"/>
+      <c r="D89" s="367"/>
+      <c r="E89" s="367"/>
+      <c r="F89" s="367"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="367" t="s">
+        <v>509</v>
+      </c>
+      <c r="C90" s="367"/>
+      <c r="D90" s="367"/>
+      <c r="E90" s="367"/>
+      <c r="F90" s="367"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>12.173811463910068</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>510</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="367" t="s">
+        <v>511</v>
+      </c>
+      <c r="C97" s="367"/>
+      <c r="D97" s="367"/>
+      <c r="E97" s="367"/>
+      <c r="F97" s="367"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="367" t="s">
+        <v>512</v>
+      </c>
+      <c r="C101" s="367"/>
+      <c r="D101" s="367"/>
+      <c r="E101" s="367"/>
+      <c r="F101" s="367"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>24279</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>3.0659183050297427</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>0.27330444081724548</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>1.3936222417470483</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>45092</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>17130.600252723845</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.1632283409931699</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>158.4</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.0002531385835957E-2</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="367" t="s">
+        <v>517</v>
+      </c>
+      <c r="C116" s="367"/>
+      <c r="D116" s="367"/>
+      <c r="E116" s="367"/>
+      <c r="F116" s="367"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>518</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>11.291124031259333</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>551</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>-3.1931692575392558</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>519</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="368" t="s">
+        <v>520</v>
+      </c>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>523</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.04</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>12.91 HKD</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.03</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>20</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>14.08 HKD</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.02</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>20</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>13.05 HKD</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>20</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>12.12 HKD</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>11.29 HKD</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>12.973811066999007</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="372" t="s">
+        <v>525</v>
+      </c>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>526</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>527</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="367" t="s">
+        <v>528</v>
+      </c>
+      <c r="C139" s="367"/>
+      <c r="D139" s="367"/>
+      <c r="E139" s="367"/>
+      <c r="F139" s="367"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>531</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.34530248443599998</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>532</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>0135.HK</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.5855914713444943</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>5.2731031111107063</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>5.8586945824552004</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>533</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>534</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.54842146596710195</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.67403044961907199</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>6.6425912663034916</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>7.3166217159225635</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>533</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>534</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.43604684250924708</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.89796799881755474</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>10.443406345201511</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>11.341374344019066</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>533</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>534</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>0.12582553534576346</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.83307785334467521</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>9.2991139192820036</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>10.13219177262668</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>533</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>534</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.22261882314240478</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="374" t="s">
+        <v>535</v>
+      </c>
+      <c r="C179" s="367"/>
+      <c r="D179" s="367"/>
+      <c r="E179" s="367"/>
+      <c r="F179" s="367"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="371" t="s">
+        <v>537</v>
+      </c>
+      <c r="C182" s="371"/>
+      <c r="D182" s="371"/>
+      <c r="E182" s="371"/>
+      <c r="F182" s="371"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="368" t="s">
+        <v>542</v>
+      </c>
+      <c r="C188" s="368"/>
+      <c r="D188" s="368"/>
+      <c r="E188" s="368"/>
+      <c r="F188" s="368"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="373" t="s">
+        <v>544</v>
+      </c>
+      <c r="C191" s="373"/>
+      <c r="D191" s="373"/>
+      <c r="E191" s="373"/>
+      <c r="F191" s="373"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="373" t="s">
+        <v>545</v>
+      </c>
+      <c r="C192" s="373"/>
+      <c r="D192" s="373"/>
+      <c r="E192" s="373"/>
+      <c r="F192" s="373"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>549</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE636CB3-F248-4447-B9F2-29F264D6A054}">
   <dimension ref="B2:E4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
-        <v>438</v>
-      </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="B2" s="379" t="s">
+        <v>437</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" t="s">
-        <v>558</v>
+      <c r="B4" s="381" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E224FD4C-4837-4485-B634-3CFFB56FFD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18CBDAE-EC59-47B7-9B5F-B7815BC39D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4755,29 +4755,34 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4791,11 +4796,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>65633.716946639994</v>
+        <v>65720.304963720002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0934214200000001</v>
+        <v>1.09192109</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.973811066999007</v>
+        <v>12.956085561144668</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23482489268397044</v>
+        <v>0.23368025713785046</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8586945824552004</v>
+        <v>5.8506866755559459</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3166217159225635</v>
+        <v>7.306621391099414</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.341374344019066</v>
+        <v>11.325873870677544</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.13219177262668</v>
+        <v>10.118343730556358</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="367" t="s">
+      <c r="B36" s="372" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="367"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="368" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="368"/>
-      <c r="D40" s="368"/>
-      <c r="E40" s="368"/>
-      <c r="F40" s="368"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="368" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="368"/>
-      <c r="D43" s="368"/>
-      <c r="E43" s="368"/>
-      <c r="F43" s="368"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="368" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="368"/>
-      <c r="D47" s="368"/>
-      <c r="E47" s="368"/>
-      <c r="F47" s="368"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="368" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="368"/>
-      <c r="D50" s="368"/>
-      <c r="E50" s="368"/>
-      <c r="F50" s="368"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61399747276158</v>
+        <v>279.60715984486581</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38600252723836</v>
+        <v>-523.39284015513419</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="368" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="368"/>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7303139567312</v>
+        <v>-4449.7286045497567</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,13 +5752,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="368" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="371"/>
-      <c r="D61" s="371"/>
-      <c r="E61" s="371"/>
-      <c r="F61" s="371"/>
+      <c r="C61" s="374"/>
+      <c r="D61" s="374"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="374"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="367" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="367"/>
-      <c r="D64" s="367"/>
-      <c r="E64" s="367"/>
-      <c r="F64" s="367"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="367" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="367"/>
-      <c r="D65" s="367"/>
-      <c r="E65" s="367"/>
-      <c r="F65" s="367"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.052624809068</v>
+        <v>10305.038097958353</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3288719577904</v>
+        <v>7230.3237437368662</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12045327965610227</v>
+        <v>0.12012943317399906</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5554417471767805E-2</v>
+        <v>4.5431973678787874E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41352278644020923</v>
+        <v>0.4129556671456151</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035933197306158</v>
+        <v>0.20035925500308469</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.1911414715462269</v>
+        <v>0.19114130802001861</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688920174681254E-2</v>
+        <v>9.7688882646536926E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780089522411969E-2</v>
+        <v>9.0780011857822959E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="367" t="s">
+      <c r="B80" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="367"/>
-      <c r="D80" s="367"/>
-      <c r="E80" s="367"/>
-      <c r="F80" s="367"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="367" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="367"/>
-      <c r="D89" s="367"/>
-      <c r="E89" s="367"/>
-      <c r="F89" s="367"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="367" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="367"/>
-      <c r="D90" s="367"/>
-      <c r="E90" s="367"/>
-      <c r="F90" s="367"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.173811463910068</v>
+        <v>12.157098637208703</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="367" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="367"/>
-      <c r="D97" s="367"/>
-      <c r="E97" s="367"/>
-      <c r="F97" s="367"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="367" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="367"/>
-      <c r="D101" s="367"/>
-      <c r="E101" s="367"/>
-      <c r="F101" s="367"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0659183050297427</v>
+        <v>3.0617114282241049</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.600252723845</v>
+        <v>17131.284015513422</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1632283409931699</v>
+        <v>2.1603463095864894</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0002531385835957E-2</v>
+        <v>1.9975085062428365E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="367" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="367"/>
-      <c r="D116" s="367"/>
-      <c r="E116" s="367"/>
-      <c r="F116" s="367"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1931692575392558</v>
+        <v>-3.1887877742936066</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="368" t="s">
+      <c r="B123" s="373" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.91 HKD</v>
+        <v>12.89 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.08 HKD</v>
+        <v>14.06 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.05 HKD</v>
+        <v>13.03 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.29 HKD</v>
+        <v>11.28 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.973811066999007</v>
+        <v>12.956085561144668</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="376" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="367" t="s">
+      <c r="B139" s="372" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="367"/>
-      <c r="D139" s="367"/>
-      <c r="E139" s="367"/>
-      <c r="F139" s="367"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.5855914713444943</v>
+        <v>0.58478795639944925</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2731031111107063</v>
+        <v>5.265898719156497</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8586945824552004</v>
+        <v>5.8506866755559459</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842146596710195</v>
+        <v>0.54842173217023449</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67403044961907199</v>
+        <v>0.67310558379334395</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6425912663034916</v>
+        <v>6.63351580730607</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3166217159225635</v>
+        <v>7.306621391099414</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604684250924708</v>
+        <v>0.43604714891571961</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89796799881755474</v>
+        <v>0.89673585876338791</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.443406345201511</v>
+        <v>10.429138011914157</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.341374344019066</v>
+        <v>11.325873870677544</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582553534576346</v>
+        <v>0.12582594355166454</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83307785334467521</v>
+        <v>0.83193475181689591</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2991139192820036</v>
+        <v>9.2864089787394626</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.13219177262668</v>
+        <v>10.118343730556358</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261882314240478</v>
+        <v>0.22261917648858442</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="367"/>
-      <c r="D179" s="367"/>
-      <c r="E179" s="367"/>
-      <c r="F179" s="367"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6757,13 +6757,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="371" t="s">
+      <c r="B182" s="374" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="371"/>
-      <c r="D182" s="371"/>
-      <c r="E182" s="371"/>
-      <c r="F182" s="371"/>
+      <c r="C182" s="374"/>
+      <c r="D182" s="374"/>
+      <c r="E182" s="374"/>
+      <c r="F182" s="374"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="368" t="s">
+      <c r="B188" s="373" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="368"/>
-      <c r="D188" s="368"/>
-      <c r="E188" s="368"/>
-      <c r="F188" s="368"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="373" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="373"/>
-      <c r="D191" s="373"/>
-      <c r="E191" s="373"/>
-      <c r="F191" s="373"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="373" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="373"/>
-      <c r="D192" s="373"/>
-      <c r="E192" s="373"/>
-      <c r="F192" s="373"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,17 +6839,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6866,6 +6855,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.31031299899600001</v>
+        <v>0.30988720534199998</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27761969853800006</v>
+        <v>0.27723876475100001</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22721297107600003</v>
+        <v>0.22690120250200002</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.31031299899600001</v>
+        <v>0.30988720534199998</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27761969853800006</v>
+        <v>0.27723876475100001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22721297107600003</v>
+        <v>0.22690120250200002</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2269249826756745</v>
+        <v>8.2156364692685955</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1931692575392558</v>
+        <v>-3.1887877742936066</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17130.600252723845</v>
+        <v>17131.284015513422</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.742145167591</v>
+        <v>-14497.400263772803</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.699873638077</v>
+        <v>-13980.357992243289</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1102774175791321</v>
+        <v>3.1103507649353719</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2253034831986631</v>
+        <v>3.2253823560897623</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27961.399747276155</v>
+        <v>27960.715984486578</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26547.178656180004</v>
+        <v>-26510.75214411</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0659183050297432</v>
+        <v>-3.0617114282241049</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18730.965253785667</v>
+        <v>18706.010315318992</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1632283409931699</v>
+        <v>2.1603463095864894</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>173.19795292800001</v>
+        <v>172.96030065600002</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.0002531385835957E-2</v>
+        <v>1.9975085062428365E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7643.0154494663366</v>
+        <v>-7631.7815281350076</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88268743265073735</v>
+        <v>-0.88139003357518708</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.38600252723836</v>
+        <v>-523.39284015513419</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.94737519093053</v>
+        <v>-208.96190204164509</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.51588352412273</v>
+        <v>-420.52907596683838</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.33694706577171</v>
+        <v>-366.34997270748761</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.96885331524243</v>
+        <v>-454.97687492696269</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.36809375052928</v>
+        <v>-503.37309778052492</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09350814437892</v>
+        <v>-818.09766300564797</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.07147774668533</v>
+        <v>-947.07595104622681</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1595993374597</v>
+        <v>-1014.1627988839114</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.58625672404463</v>
+        <v>-468.59154886485817</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.47824573899726</v>
+        <v>-437.48165757763059</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.921255826925</v>
+        <v>17798.914418199027</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.052624809068</v>
+        <v>16980.038097958353</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.484116475876</v>
+        <v>17261.470924033161</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.663052934229</v>
+        <v>16973.650027292511</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.031146684758</v>
+        <v>14670.023125073038</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.631906249471</v>
+        <v>11589.626902219476</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.906491855621</v>
+        <v>20402.902336994353</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.928522253314</v>
+        <v>19208.924048953773</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.840400662539</v>
+        <v>16944.83720111609</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.413743275956</v>
+        <v>17752.408451135143</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.521754261003</v>
+        <v>11857.518342422369</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7303139567312</v>
+        <v>-4449.7286045497567</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3288719577904</v>
+        <v>7230.3237437368662</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.052624809068</v>
+        <v>10305.038097958353</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.484116475876</v>
+        <v>10350.470924033161</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.663052934229</v>
+        <v>10809.650027292511</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0311466847579</v>
+        <v>8651.0231250730376</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6319062494713</v>
+        <v>5607.6269022194756</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.906491855621</v>
+        <v>12308.902336994353</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.928522253314</v>
+        <v>11857.924048953773</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.840400662539</v>
+        <v>10224.83720111609</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.413743275956</v>
+        <v>11296.408451135143</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5217542610026</v>
+        <v>7067.5183424223687</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3288719577904</v>
+        <v>7230.3237437368662</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.052624809068</v>
+        <v>10305.038097958353</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.484116475876</v>
+        <v>10350.470924033161</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.663052934229</v>
+        <v>10809.650027292511</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0311466847579</v>
+        <v>8651.0231250730376</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6319062494713</v>
+        <v>5607.6269022194756</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.906491855621</v>
+        <v>12308.902336994353</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.928522253314</v>
+        <v>11857.924048953773</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.840400662539</v>
+        <v>10224.83720111609</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.413743275956</v>
+        <v>11296.408451135143</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5217542610026</v>
+        <v>7067.5183424223687</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.1842161546325109</v>
+        <v>0.18421631223407589</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337850543302471</v>
+        <v>0.19337865322662043</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1878793039578289</v>
+        <v>0.18787944813710061</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391235662848024</v>
+        <v>0.18391245719229685</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957493203496499</v>
+        <v>0.19957501820503368</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967743329246981</v>
+        <v>0.19967747395492164</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636701732895631</v>
+        <v>0.19636706305814378</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838201579413748</v>
+        <v>0.20838205514110381</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847869216668183</v>
+        <v>0.20847875431591631</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986044419974807</v>
+        <v>0.21986050746158212</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.61399747276158</v>
+        <v>279.60715984486581</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.05262480906947</v>
+        <v>594.03809795835491</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.48411647587727</v>
+        <v>539.47092403316162</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.66305293422829</v>
+        <v>532.65002729251239</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.03114668475757</v>
+        <v>328.02312507303731</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.63190624947069</v>
+        <v>204.62690221947508</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90649185562111</v>
+        <v>169.90233699435203</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.9285222533147</v>
+        <v>182.92404895377319</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.84040066254036</v>
+        <v>130.83720111608861</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.41374327595537</v>
+        <v>216.40845113514183</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.52175426100274</v>
+        <v>139.51834242236939</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.38600252723836</v>
+        <v>-523.39284015513419</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.94737519093053</v>
+        <v>-208.96190204164509</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.51588352412273</v>
+        <v>-420.52907596683838</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.33694706577171</v>
+        <v>-366.34997270748761</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.96885331524243</v>
+        <v>-454.97687492696269</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.36809375052928</v>
+        <v>-503.37309778052492</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09350814437892</v>
+        <v>-818.09766300564797</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.07147774668533</v>
+        <v>-947.07595104622681</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1595993374597</v>
+        <v>-1014.1627988839114</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.58625672404463</v>
+        <v>-468.59154886485817</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.47824573899726</v>
+        <v>-437.48165757763059</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8725905736950515E-3</v>
+        <v>2.8726281018393754E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1170908503305632E-3</v>
+        <v>1.1171685149195657E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3710538444248379E-3</v>
+        <v>2.3711282292298926E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1305596418937081E-3</v>
+        <v>2.1306353970332644E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2838592919026931E-3</v>
+        <v>3.2839171900291069E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074460988963879E-3</v>
+        <v>4.6074919019553585E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2197674419032139E-3</v>
+        <v>7.2198041090223361E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795342537848238E-3</v>
+        <v>8.9795766667889153E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432818516644417E-2</v>
+        <v>1.1432854585754193E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7227016526714613E-3</v>
+        <v>5.7227662839800953E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0505949562666537E-2</v>
+        <v>1.050603149726545E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688920174681254E-2</v>
+        <v>9.7688882646536926E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780089522411969E-2</v>
+        <v>9.0780011857822959E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327853425780514E-2</v>
+        <v>9.7327779040975462E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716227684212468E-2</v>
+        <v>9.8716151929072904E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588487045323795</v>
+        <v>0.10588481255511153</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608261623462917</v>
+        <v>0.1060825704315702</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1800579500309375</v>
+        <v>0.18005791336381838</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212694152131709</v>
+        <v>0.18212689910831301</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102248326677496</v>
+        <v>0.1910224471976652</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680483797752811</v>
+        <v>0.21680477334621948</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475593175622588</v>
+        <v>0.28475584982162699</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422230043670314E-2</v>
+        <v>2.4422220661634231E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683473501414879E-2</v>
+        <v>3.9683445355306622E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093680831501707E-2</v>
+        <v>5.5093603166912704E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360590212094887E-2</v>
+        <v>5.8360515827289836E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867346653179113E-2</v>
+        <v>6.2867270898039548E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2441129340113879E-2</v>
+        <v>6.2441071441987468E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327968679915709E-2</v>
+        <v>5.1327922876856738E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862748750677875</v>
+        <v>0.10862745083965965</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242939719591651</v>
+        <v>0.11242935478291242</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526661556898675</v>
+        <v>0.11526657949987701</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795967054146158</v>
+        <v>0.13795960591015294</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972507274707627</v>
+        <v>0.16972499081247733</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683473501414879E-2</v>
+        <v>3.9683445355306622E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093680831501707E-2</v>
+        <v>5.5093603166912704E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360590212094887E-2</v>
+        <v>5.8360515827289836E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867346653179113E-2</v>
+        <v>6.2867270898039548E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2441129340113879E-2</v>
+        <v>6.2441071441987468E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327968679915709E-2</v>
+        <v>5.1327922876856738E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862748750677875</v>
+        <v>0.10862745083965965</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242939719591651</v>
+        <v>0.11242935478291242</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526661556898675</v>
+        <v>0.11526657949987701</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795967054146158</v>
+        <v>0.13795960591015294</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972507274707627</v>
+        <v>0.16972499081247733</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.31031299899600001</v>
+        <v>0.30988720534199998</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27761969853800006</v>
+        <v>0.27723876475100001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22721297107600003</v>
+        <v>0.22690120250200002</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2989.9057420110803</v>
+        <v>2985.803165273639</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2989.9057420110803</v>
+        <v>2985.803165273639</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2686.938725721167</v>
+        <v>2683.2518629026563</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2403.8539198752801</v>
+        <v>2400.5554897497691</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1967.3920620326235</v>
+        <v>1964.6925197715716</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41352278644020923</v>
+        <v>0.4129556671456151</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.29013978393598711</v>
+        <v>0.28974207925201073</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25959546389179078</v>
+        <v>0.25923959234282851</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22238009715046261</v>
+        <v>0.22207522756877221</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22741705915445309</v>
+        <v>0.2271052211243493</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5554417471767805E-2</v>
+        <v>4.5431973678787874E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5554417471767805E-2</v>
+        <v>4.5431973678787874E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0938390368865436E-2</v>
+        <v>4.0828353800000002E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6625290044591037E-2</v>
+        <v>3.6526846475757581E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.9975325999472297E-2</v>
+        <v>2.9894756587878792E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225329397473704E-2</v>
+        <v>4.8225823494420395E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304014751442164E-2</v>
+        <v>-1.6304104517707585E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956921004266823E-2</v>
+        <v>1.6956924190015377E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702978972679715</v>
+        <v>0.15702953448534562</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578922137934713</v>
+        <v>0.26578907576944077</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196172021492185</v>
+        <v>-0.4319618497999046</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157447679556777E-2</v>
+        <v>6.2157478732163041E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361519306503777</v>
+        <v>0.13361514312386302</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.549090361975705E-2</v>
+        <v>-4.5490799304328422E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714367902353818</v>
+        <v>0.49714366349514827</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.21435575883164</v>
+        <v>1.2143574706899229</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920121839581763</v>
+        <v>1.3920139581809272</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756210463899348</v>
+        <v>1.3756227040150053</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871178818491054</v>
+        <v>1.3871191680462289</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848606826967723</v>
+        <v>2.9848633462713376</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067773331971357</v>
+        <v>1.3067777742988993</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351579171744018</v>
+        <v>1.4351584585753441</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994823859684932</v>
+        <v>1.2994827926013004</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941592754934624</v>
+        <v>1.3941599286291237</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917522244539593</v>
+        <v>1.8917531376957808</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688920174681254E-2</v>
+        <v>9.7688882646536926E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780089522411969E-2</v>
+        <v>9.0780011857822959E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327853425780514E-2</v>
+        <v>9.7327779040975462E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716227684212468E-2</v>
+        <v>9.8716151929072904E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588487045323795</v>
+        <v>0.10588481255511153</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608261623462917</v>
+        <v>0.1060825704315702</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1800579500309375</v>
+        <v>0.18005791336381838</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212694152131709</v>
+        <v>0.18212689910831301</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102248326677496</v>
+        <v>0.1910224471976652</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680483797752811</v>
+        <v>0.21680477334621948</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475593175622588</v>
+        <v>0.28475584982162699</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035933197306158</v>
+        <v>0.20035925500308469</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.1911414715462269</v>
+        <v>0.19114130802001861</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122266785348936</v>
+        <v>0.20122251406494482</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032518466623168</v>
+        <v>0.21032502326203206</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338040820296012</v>
+        <v>0.19338030246204291</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371115963686097</v>
+        <v>0.1371115371682359</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766125518539651</v>
+        <v>0.25766120271508941</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404526096746246</v>
+        <v>0.27404519714888254</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820709181961965</v>
+        <v>0.25820704306462611</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774676475085524</v>
+        <v>0.26774668493333853</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861273184490363</v>
+        <v>0.16861268332891144</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91303585979325508</v>
+        <v>0.91178239779065284</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.3013076929320369</v>
+        <v>1.2995202814285549</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3070447184242757</v>
+        <v>1.3052496031802647</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.36502919499134</v>
+        <v>1.3631545378172285</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0924401643396864</v>
+        <v>1.0909401691942475</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70812394700107451</v>
+        <v>0.7071516690037607</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5543515683627656</v>
+        <v>1.5522182525668278</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4974026984682534</v>
+        <v>1.4953474844802181</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2911786049836864</v>
+        <v>1.2894065204657565</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4264953942377905</v>
+        <v>1.4245373719151462</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89247680372275329</v>
+        <v>0.89125176811969409</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12045327965610227</v>
+        <v>0.12012943317399906</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.1716764766401104</v>
+        <v>0.17121479333709552</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17243334016151396</v>
+        <v>0.17196964468778192</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.1800830072547942</v>
+        <v>0.17959875333560324</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14412139371235969</v>
+        <v>0.14373388263428821</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.3420045778505864E-2</v>
+        <v>9.3168862846345291E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20505957366263397</v>
+        <v>0.20450833367151883</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19754653014093052</v>
+        <v>0.19701547885114865</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17034018535404835</v>
+        <v>0.16988228201129862</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18819200451685891</v>
+        <v>0.1876860832562775</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11774100312965083</v>
+        <v>0.11742447537808881</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14484933114071782</v>
+        <v>0.14465848880719909</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14100984113888118</v>
+        <v>0.14082405742196566</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12498149398835681</v>
+        <v>0.12481682798837215</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.40127241340623593</v>
+        <v>0.40074372774957423</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14827744721378625</v>
+        <v>0.14808208825830035</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14582443971261283</v>
+        <v>0.14563231265106788</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1251338547027154</v>
+        <v>0.12496898796397665</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12111153184364847</v>
+        <v>0.12095196460801783</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2015947882024891E-2</v>
+        <v>5.1947415671376632E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5347685731194421E-2</v>
+        <v>3.530111434024423E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3288719577904</v>
+        <v>7230.3237437368662</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,16 +16527,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.384959437215</v>
+        <v>96404.316583158216</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -16551,8 +16551,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -16561,14 +16561,14 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17130.600252723845</v>
+        <v>17131.284015513422</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -16583,8 +16583,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89414.385212161054</v>
+        <v>89415.000598671628</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0934214200000001</v>
+        <v>1.09192109</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.033749818311779</v>
+        <v>13.015942025495272</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7369265244051</v>
+        <v>7373.7316965891332</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.290164208749</v>
+        <v>6859.2852991526815</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9893703959578</v>
+        <v>7519.9840367289116</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2920457725977</v>
+        <v>6507.2874303765602</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.142619863308</v>
+        <v>7669.1371804070468</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3574109355377</v>
+        <v>6173.3530323877276</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2542101913841</v>
+        <v>7821.2486628476599</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5592961070115</v>
+        <v>5856.5551422530916</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3828178131816</v>
+        <v>7976.377160442129</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0183066769159</v>
+        <v>5556.0143659862724</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5882829639568</v>
+        <v>8134.5825133832668</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.9001759187486</v>
+        <v>5270.896437452483</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.931632764361</v>
+        <v>8295.925748748441</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4134491624964</v>
+        <v>5000.4099025430642</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4751047613991</v>
+        <v>8460.469104040516</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8072868088038</v>
+        <v>4743.8039221912031</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.282170936327</v>
+        <v>8628.276051195724</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3693800858391</v>
+        <v>4500.3661881302824</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4175621886934</v>
+        <v>8799.4113210677078</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4239737632279</v>
+        <v>4269.4209456092194</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9472933060406</v>
+        <v>8973.9409283971818</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3299903343732</v>
+        <v>4050.3271175761106</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9386884288306</v>
+        <v>9151.932197276863</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.479250460085</v>
+        <v>3842.476525123127</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4604070204678</v>
+        <v>9333.4537871214561</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2947847336773</v>
+        <v>3645.2921992528063</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5824703524104</v>
+        <v>9518.5757191527537</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2292320812066</v>
+        <v>3458.2267792794291</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3762885145843</v>
+        <v>9707.3694034100354</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7633203509799</v>
+        <v>3280.7609934196043</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9146879615528</v>
+        <v>9899.9076662962125</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4044248746432</v>
+        <v>3112.4022173543804</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.271939605016</v>
+        <v>10096.264778670302</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6852009985664</v>
+        <v>2952.6831067615967</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.523787463522</v>
+        <v>10296.516484497133</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1622867896072</v>
+        <v>2801.1603000225723</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.747477880412</v>
+        <v>10500.740030065259</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4150723140992</v>
+        <v>2657.4131875019671</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.021789321292</v>
+        <v>10709.014193784409</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0445320737549</v>
+        <v>2521.0427439845062</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.492353658745</v>
+        <v>98316.422621188452</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.994971251355</v>
+        <v>23144.978555311001</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.23455570228</v>
+        <v>110204.15639166971</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.23455570228</v>
+        <v>110204.15639166971</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.384959437215</v>
+        <v>96404.31658315823</v>
       </c>
       <c r="C56" s="123">
-        <v>97922.008579617948</v>
+        <v>97921.939126941274</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.416528307775</v>
+        <v>99461.34598378255</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.08693498044</v>
+        <v>101023.01528281669</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.50539297739</v>
+        <v>102607.43261704073</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.384959437244</v>
+        <v>96404.316583158245</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.078401649196</v>
+        <v>99377.007916942093</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.85559896842</v>
+        <v>102492.78290434886</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.10567964349</v>
+        <v>105760.03066767703</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.68053572852</v>
+        <v>109187.60309270237</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.384959437244</v>
+        <v>96404.316583158245</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.56757833326</v>
+        <v>101173.49581943882</v>
       </c>
       <c r="D58" s="123">
-        <v>106331.01246333958</v>
+        <v>106330.93704644879</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.72200876546</v>
+        <v>111913.64263225286</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.22867154832</v>
+        <v>117962.14500504021</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.384959437259</v>
+        <v>96404.316583158245</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.11592338064</v>
+        <v>102998.04287039749</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.35361220999</v>
+        <v>110332.27535730705</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.69239150587</v>
+        <v>118504.6083402471</v>
       </c>
       <c r="F59" s="123">
-        <v>127626.02264224782</v>
+        <v>127625.93212154656</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.384959437244</v>
+        <v>96404.316583158245</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.64631716938</v>
+        <v>104688.57206515179</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.70688297792</v>
+        <v>114140.62592694239</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.67241999859</v>
+        <v>124956.58379257467</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.47168657638</v>
+        <v>137367.37425660394</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.38495943723</v>
+        <v>96404.31658315823</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.40353569583</v>
+        <v>106173.32823059156</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.79737177987</v>
+        <v>117578.71397722626</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.60274403641</v>
+        <v>130953.50986319828</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.88937258252</v>
+        <v>146703.78532061359</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.482767428320892</v>
+        <v>11.467088902905772</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.677161720046104</v>
+        <v>11.661216320273764</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.874367283958991</v>
+        <v>11.858151150372185</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.074445440110392</v>
+        <v>12.057954629068597</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.291124031259336</v>
+        <v>11.275708603633518</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.666511618874951</v>
+        <v>11.650580840102432</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.059967623803296</v>
+        <v>12.043496688643071</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.472551413475506</v>
+        <v>12.455514062333151</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.905380792491558</v>
+        <v>12.887749231193725</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.291124031259336</v>
+        <v>11.275708603633518</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.893369770017234</v>
+        <v>11.877127548852405</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.544644726980984</v>
+        <v>12.527508402476139</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.249621512968277</v>
+        <v>13.23151736052494</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.013418510188934</v>
+        <v>13.994265778433569</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.291124031259338</v>
+        <v>11.275708603633518</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.123771193860575</v>
+        <v>12.107212665918709</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.049928514327684</v>
+        <v>13.032098510575551</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.081920073220045</v>
+        <v>14.06267329903967</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.233748953403383</v>
+        <v>15.212920890033404</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.291124031259336</v>
+        <v>11.275708603633518</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.337249017474644</v>
+        <v>12.320397416333705</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.530842061214594</v>
+        <v>13.512351834919071</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.896667125118482</v>
+        <v>14.8763018248032</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.46388557116035</v>
+        <v>16.441368713761278</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.291124031259335</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.524742091110516</v>
+        <v>12.507633089955073</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.964999339684324</v>
+        <v>13.945913080225502</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.653951134116198</v>
+        <v>15.632546195849921</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.642875393102344</v>
+        <v>17.618739958593284</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.905380792491558</v>
+        <v>12.887749231193725</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.081920073220045</v>
+        <v>14.06267329903967</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.049928514327684</v>
+        <v>13.032098510575551</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.123771193860575</v>
+        <v>12.107212665918709</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.291124031259336</v>
+        <v>11.275708603633518</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2989.9057420110803</v>
+        <v>2985.803165273639</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,14 +18287,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39865.409893481075</v>
+        <v>39810.708870315189</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2630795446995569</v>
+        <v>5.2558578495792085</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3049.2082403334362</v>
+        <v>3045.0242921177337</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2836.4727817055218</v>
+        <v>2832.5807368537057</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3109.6869584468909</v>
+        <v>3105.4200248117631</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2690.9135389480939</v>
+        <v>2687.2212221194272</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3171.365225773241</v>
+        <v>3167.0136607662334</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2552.8239582613787</v>
+        <v>2549.3211200150799</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3234.2668344555591</v>
+        <v>3229.8289594780053</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2421.8207190784815</v>
+        <v>2418.497635944208</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3298.4160485359143</v>
+        <v>3293.8901516954261</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2297.5401716898509</v>
+        <v>2294.3876191764825</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3363.8376133151323</v>
+        <v>3359.2219487652415</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2179.6373277941098</v>
+        <v>2176.646554783636</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3430.5567648981923</v>
+        <v>3425.8495521648988</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2067.7849028507726</v>
+        <v>2064.947607306211</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3498.5992399289548</v>
+        <v>3493.7986632239158</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1961.6724075765455</v>
+        <v>1958.980713496454</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3567.9912855179673</v>
+        <v>3563.0954930380635</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1861.0052860632932</v>
+        <v>1858.4517216189095</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3638.7596693671817</v>
+        <v>3633.7667725801934</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1765.5040981252007</v>
+        <v>1763.0815749195181</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3710.9316900954873</v>
+        <v>3705.8397630115992</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1674.9037436054157</v>
+        <v>1672.6055369966191</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3784.5351877690437</v>
+        <v>3779.3422661979025</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1588.9527264889409</v>
+        <v>1586.7724569235859</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3859.5985546404731</v>
+        <v>3854.3026354335088</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1507.4124567790329</v>
+        <v>1505.3440720831493</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3936.1507461010583</v>
+        <v>3930.7497863787785</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1430.0565881992054</v>
+        <v>1428.0943467781685</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4014.2212918501668</v>
+        <v>4008.7132082141229</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1356.6703898823698</v>
+        <v>1354.8088447829036</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4093.8403072862156</v>
+        <v>4088.2229750153415</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1287.0501503029993</v>
+        <v>1285.2841340930697</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4175.0385051235617</v>
+        <v>4169.3097573545701</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1221.0026117976963</v>
+        <v>1219.3272222223225</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4257.8472072398117</v>
+        <v>4252.0048341313368</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1158.3444341044665</v>
+        <v>1156.7550204776328</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4342.2983567581068</v>
+        <v>4336.3401046382651</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1098.9016854315364</v>
+        <v>1097.3938357264303</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4428.4245303690559</v>
+        <v>4422.348100866102</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1042.5093596429924</v>
+        <v>1041.0788882447339</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40656.109871112487</v>
+        <v>40600.323894903115</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9570.9828126564917</v>
+        <v>9557.8500603794091</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45571.962150984386</v>
+        <v>45509.430924941655</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45571.962150984386</v>
+        <v>45509.430924941655</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39865.409893481075</v>
+        <v>39810.708870315197</v>
       </c>
       <c r="C51" s="123">
-        <v>40492.981841665685</v>
+        <v>40437.419700358339</v>
       </c>
       <c r="D51" s="123">
-        <v>41129.562106076111</v>
+        <v>41073.126485933775</v>
       </c>
       <c r="E51" s="123">
-        <v>41775.348404144606</v>
+        <v>41718.026673177228</v>
       </c>
       <c r="F51" s="123">
-        <v>42430.541539782811</v>
+        <v>42372.320790468802</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39865.409893481083</v>
+        <v>39810.708870315204</v>
       </c>
       <c r="C52" s="123">
-        <v>41094.686368937109</v>
+        <v>41038.298603275893</v>
       </c>
       <c r="D52" s="123">
-        <v>42383.131237499416</v>
+        <v>42324.975541876076</v>
       </c>
       <c r="E52" s="123">
-        <v>43734.213594857167</v>
+        <v>43674.204021711266</v>
       </c>
       <c r="F52" s="123">
-        <v>45151.59390007786</v>
+        <v>45089.639479177524</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39865.409893481075</v>
+        <v>39810.708870315204</v>
       </c>
       <c r="C53" s="123">
-        <v>41837.575579089171</v>
+        <v>41780.168463570459</v>
       </c>
       <c r="D53" s="123">
-        <v>43970.2965588488</v>
+        <v>43909.963046234654</v>
       </c>
       <c r="E53" s="123">
-        <v>46278.874165959671</v>
+        <v>46215.372955897925</v>
       </c>
       <c r="F53" s="123">
-        <v>48780.069494955809</v>
+        <v>48713.136288484166</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39865.409893481075</v>
+        <v>39810.708870315204</v>
       </c>
       <c r="C54" s="123">
-        <v>42592.067894728032</v>
+        <v>42533.625508237645</v>
       </c>
       <c r="D54" s="123">
-        <v>45624.942300227573</v>
+        <v>45562.33837787043</v>
       </c>
       <c r="E54" s="123">
-        <v>49004.390603975393</v>
+        <v>48937.149596976567</v>
       </c>
       <c r="F54" s="123">
-        <v>52776.268505303568</v>
+        <v>52703.851944334252</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39865.409893481075</v>
+        <v>39810.708870315197</v>
       </c>
       <c r="C55" s="123">
-        <v>43291.140733729408</v>
+        <v>43231.739119686543</v>
       </c>
       <c r="D55" s="123">
-        <v>47199.783156504214</v>
+        <v>47135.018328078579</v>
       </c>
       <c r="E55" s="123">
-        <v>51672.431363414282</v>
+        <v>51601.529424299632</v>
       </c>
       <c r="F55" s="123">
-        <v>56804.57965807963</v>
+        <v>56726.635680177293</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39865.409893481075</v>
+        <v>39810.708870315204</v>
       </c>
       <c r="C56" s="123">
-        <v>43905.121675921684</v>
+        <v>43844.877592534292</v>
       </c>
       <c r="D56" s="123">
-        <v>48621.511915467199</v>
+        <v>48554.796272588937</v>
       </c>
       <c r="E56" s="123">
-        <v>54152.298701098203</v>
+        <v>54077.994030616945</v>
       </c>
       <c r="F56" s="123">
-        <v>60665.401114966538</v>
+        <v>60582.159539861103</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1133973497096168</v>
+        <v>5.0993743574480694</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.193783818891899</v>
+        <v>5.1795403745985258</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2753328131826684</v>
+        <v>5.2608657287460261</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3580696898202156</v>
+        <v>5.3433757075891171</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835712</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1893797593797331</v>
+        <v>5.1751483927889588</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.352082782879334</v>
+        <v>5.3374052191551433</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5226955812246477</v>
+        <v>5.5075501285829134</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.7016803920885533</v>
+        <v>5.6860440911035299</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835712</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.283190774166763</v>
+        <v>5.2687021400404488</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5525078091091418</v>
+        <v>5.537280599347369</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8440317740262699</v>
+        <v>5.8280050882949022</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1598792365916211</v>
+        <v>6.1429863700766232</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835712</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3784670129542516</v>
+        <v>5.3637170930588374</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7614541687958125</v>
+        <v>5.7456539440726395</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1882061938117587</v>
+        <v>6.1712356433862938</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6645136818474784</v>
+        <v>6.6462369047077479</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835695</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4667449574183342</v>
+        <v>5.4517529438917336</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9603228787413327</v>
+        <v>5.9439772760258176</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5251226649567462</v>
+        <v>6.507228154051675</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1732032037244746</v>
+        <v>7.1535313953088728</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835712</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5442776156664788</v>
+        <v>5.5290729764055042</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1398568062874359</v>
+        <v>6.1230188493298208</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8382768584840949</v>
+        <v>6.8195235528223908</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6607423600785731</v>
+        <v>7.6397335231965373</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.7016803920885533</v>
+        <v>5.6860440911035299</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1882061938117587</v>
+        <v>6.1712356433862938</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7614541687958125</v>
+        <v>5.7456539440726395</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3784670129542516</v>
+        <v>5.3637170930588374</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0341484381538546</v>
+        <v>5.0203427782835712</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.58</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.319113551435006</v>
+        <v>13.300914241366668</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19759,11 +19759,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 昆仑能源(0135.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -19778,14 +19778,14 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.052624809068</v>
+        <v>10305.038097958353</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -19800,14 +19800,14 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3288719577904</v>
+        <v>7230.3237437368662</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -19817,8 +19817,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19831,8 +19831,8 @@
       <c r="B11" s="159" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19850,8 +19850,8 @@
         <v>0.10522432036524854</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19868,8 +19868,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.2708395417024878E-2</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19884,10 +19884,10 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.00526745230614E-2</v>
-      </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+        <v>6.0052504052653388E-2</v>
+      </c>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19913,21 +19913,21 @@
       <c r="C18" s="150">
         <v>20</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19935,14 +19935,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19950,14 +19950,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19977,8 +19977,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19988,8 +19988,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19997,14 +19997,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.049928514327684</v>
+        <v>13.032098510575551</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -20014,8 +20014,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -20035,8 +20035,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -20046,8 +20046,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -20055,14 +20055,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.123771193860575</v>
+        <v>12.107212665918709</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -20072,8 +20072,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -20093,8 +20093,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -20104,8 +20104,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -20113,14 +20113,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.081920073220045</v>
+        <v>14.06267329903967</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -20131,8 +20131,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.071095362012736</v>
+        <v>13.053236299337007</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20194,8 +20194,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -20205,8 +20205,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -20214,14 +20214,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.291124031259336</v>
+        <v>11.275708603633518</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -20231,8 +20231,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -20252,8 +20252,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -20263,8 +20263,8 @@
         <v>0.04</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.905380792491558</v>
+        <v>12.887749231193725</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -20289,8 +20289,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.973811066999007</v>
+        <v>12.956085561144668</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.033749818311779</v>
+        <v>13.015942025495272</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8036094258840871E-2</v>
+        <v>-6.8029037737947481E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.5855914713444943</v>
+        <v>0.58478795639944925</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2731031111107063</v>
+        <v>5.265898719156497</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8586945824552004</v>
+        <v>5.8506866755559459</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842146596710195</v>
+        <v>0.54842173217023449</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23482489268397044</v>
+        <v>0.23368025713785046</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67403044961907199</v>
+        <v>0.67310558379334395</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6425912663034916</v>
+        <v>6.63351580730607</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3166217159225635</v>
+        <v>7.306621391099414</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604684250924708</v>
+        <v>0.43604714891571961</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89796799881755474</v>
+        <v>0.89673585876338791</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.443406345201511</v>
+        <v>10.429138011914157</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.341374344019066</v>
+        <v>11.325873870677544</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582553534576346</v>
+        <v>0.12582594355166454</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83307785334467521</v>
+        <v>0.83193475181689591</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2991139192820036</v>
+        <v>9.2864089787394626</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.13219177262668</v>
+        <v>10.118343730556358</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261882314240478</v>
+        <v>0.22261917648858442</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.58</v>
+        <v>7.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>65633.716946639994</v>
+        <v>65720.304963720002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0934214200000001</v>
+        <v>1.09192109</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="367" t="s">
+      <c r="B18" s="372" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367"/>
-      <c r="E18" s="367"/>
-      <c r="F18" s="367"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.973811066999007</v>
+        <v>12.956085561144668</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23482489268397044</v>
+        <v>0.23368025713785046</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8586945824552004</v>
+        <v>5.8506866755559459</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3166217159225635</v>
+        <v>7.306621391099414</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.341374344019066</v>
+        <v>11.325873870677544</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.13219177262668</v>
+        <v>10.118343730556358</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="367" t="s">
+      <c r="B36" s="372" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="367"/>
-      <c r="D36" s="367"/>
-      <c r="E36" s="367"/>
-      <c r="F36" s="367"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="369" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="369"/>
-      <c r="D37" s="369"/>
-      <c r="E37" s="369"/>
-      <c r="F37" s="369"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="368" t="s">
+      <c r="B40" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="368"/>
-      <c r="D40" s="368"/>
-      <c r="E40" s="368"/>
-      <c r="F40" s="368"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="368" t="s">
+      <c r="B43" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="368"/>
-      <c r="D43" s="368"/>
-      <c r="E43" s="368"/>
-      <c r="F43" s="368"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="368" t="s">
+      <c r="B47" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="368"/>
-      <c r="D47" s="368"/>
-      <c r="E47" s="368"/>
-      <c r="F47" s="368"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="368" t="s">
+      <c r="B50" s="373" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="368"/>
-      <c r="D50" s="368"/>
-      <c r="E50" s="368"/>
-      <c r="F50" s="368"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61399747276158</v>
+        <v>279.60715984486581</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38600252723836</v>
+        <v>-523.39284015513419</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="368" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="368"/>
-      <c r="D58" s="368"/>
-      <c r="E58" s="368"/>
-      <c r="F58" s="368"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7303139567312</v>
+        <v>-4449.7286045497567</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,13 +21380,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="368" t="s">
+      <c r="B61" s="373" t="s">
         <v>500</v>
       </c>
-      <c r="C61" s="371"/>
-      <c r="D61" s="371"/>
-      <c r="E61" s="371"/>
-      <c r="F61" s="371"/>
+      <c r="C61" s="374"/>
+      <c r="D61" s="374"/>
+      <c r="E61" s="374"/>
+      <c r="F61" s="374"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="367" t="s">
+      <c r="B64" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="367"/>
-      <c r="D64" s="367"/>
-      <c r="E64" s="367"/>
-      <c r="F64" s="367"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="367" t="s">
+      <c r="B65" s="372" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="367"/>
-      <c r="D65" s="367"/>
-      <c r="E65" s="367"/>
-      <c r="F65" s="367"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.052624809068</v>
+        <v>10305.038097958353</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3288719577904</v>
+        <v>7230.3237437368662</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12045327965610227</v>
+        <v>0.12012943317399906</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5554417471767805E-2</v>
+        <v>4.5431973678787874E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41352278644020923</v>
+        <v>0.4129556671456151</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035933197306158</v>
+        <v>0.20035925500308469</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.1911414715462269</v>
+        <v>0.19114130802001861</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688920174681254E-2</v>
+        <v>9.7688882646536926E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780089522411969E-2</v>
+        <v>9.0780011857822959E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="367" t="s">
+      <c r="B80" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="367"/>
-      <c r="D80" s="367"/>
-      <c r="E80" s="367"/>
-      <c r="F80" s="367"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="369" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="369"/>
-      <c r="D81" s="369"/>
-      <c r="E81" s="369"/>
-      <c r="F81" s="369"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="367" t="s">
+      <c r="B89" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="367"/>
-      <c r="D89" s="367"/>
-      <c r="E89" s="367"/>
-      <c r="F89" s="367"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="367" t="s">
+      <c r="B90" s="372" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="367"/>
-      <c r="D90" s="367"/>
-      <c r="E90" s="367"/>
-      <c r="F90" s="367"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.173811463910068</v>
+        <v>12.157098637208703</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="367" t="s">
+      <c r="B97" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="367"/>
-      <c r="D97" s="367"/>
-      <c r="E97" s="367"/>
-      <c r="F97" s="367"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="367" t="s">
+      <c r="B101" s="372" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="367"/>
-      <c r="D101" s="367"/>
-      <c r="E101" s="367"/>
-      <c r="F101" s="367"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0659183050297427</v>
+        <v>3.0617114282241049</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.600252723845</v>
+        <v>17131.284015513422</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1632283409931699</v>
+        <v>2.1603463095864894</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0002531385835957E-2</v>
+        <v>1.9975085062428365E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="367" t="s">
+      <c r="B116" s="372" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="367"/>
-      <c r="D116" s="367"/>
-      <c r="E116" s="367"/>
-      <c r="F116" s="367"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.291124031259333</v>
+        <v>11.275708603633516</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1931692575392558</v>
+        <v>-3.1887877742936066</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="368" t="s">
+      <c r="B123" s="373" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.91 HKD</v>
+        <v>12.89 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.08 HKD</v>
+        <v>14.06 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.05 HKD</v>
+        <v>13.03 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.29 HKD</v>
+        <v>11.28 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.973811066999007</v>
+        <v>12.956085561144668</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="376" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="377" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="367" t="s">
+      <c r="B139" s="372" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="367"/>
-      <c r="D139" s="367"/>
-      <c r="E139" s="367"/>
-      <c r="F139" s="367"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34530248443599998</v>
+        <v>0.34482868022199997</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.5855914713444943</v>
+        <v>0.58478795639944925</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2731031111107063</v>
+        <v>5.265898719156497</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8586945824552004</v>
+        <v>5.8506866755559459</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842146596710195</v>
+        <v>0.54842173217023449</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67403044961907199</v>
+        <v>0.67310558379334395</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6425912663034916</v>
+        <v>6.63351580730607</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3166217159225635</v>
+        <v>7.306621391099414</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604684250924708</v>
+        <v>0.43604714891571961</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89796799881755474</v>
+        <v>0.89673585876338791</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.443406345201511</v>
+        <v>10.429138011914157</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.341374344019066</v>
+        <v>11.325873870677544</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582553534576346</v>
+        <v>0.12582594355166454</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83307785334467521</v>
+        <v>0.83193475181689591</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2991139192820036</v>
+        <v>9.2864089787394626</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.13219177262668</v>
+        <v>10.118343730556358</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261882314240478</v>
+        <v>0.22261917648858442</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="374" t="s">
+      <c r="B179" s="371" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="367"/>
-      <c r="D179" s="367"/>
-      <c r="E179" s="367"/>
-      <c r="F179" s="367"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22385,13 +22385,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="371" t="s">
+      <c r="B182" s="374" t="s">
         <v>537</v>
       </c>
-      <c r="C182" s="371"/>
-      <c r="D182" s="371"/>
-      <c r="E182" s="371"/>
-      <c r="F182" s="371"/>
+      <c r="C182" s="374"/>
+      <c r="D182" s="374"/>
+      <c r="E182" s="374"/>
+      <c r="F182" s="374"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="368" t="s">
+      <c r="B188" s="373" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="368"/>
-      <c r="D188" s="368"/>
-      <c r="E188" s="368"/>
-      <c r="F188" s="368"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="373" t="s">
+      <c r="B191" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="373"/>
-      <c r="D191" s="373"/>
-      <c r="E191" s="373"/>
-      <c r="F191" s="373"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="373" t="s">
+      <c r="B192" s="370" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="373"/>
-      <c r="D192" s="373"/>
-      <c r="E192" s="373"/>
-      <c r="F192" s="373"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,15 +22467,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22488,12 +22485,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -22522,22 +22522,22 @@
   <dimension ref="B2:E4"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>437</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="381" t="s">
+      <c r="B4" s="369" t="s">
         <v>552</v>
       </c>
     </row>

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18CBDAE-EC59-47B7-9B5F-B7815BC39D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFBD65F-E0DD-4F6A-895F-F910D9AFEA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4760,29 +4760,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.59</v>
+        <v>7.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>65720.304963720002</v>
+        <v>66672.773151599991</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.09192109</v>
+        <v>1.0926782399999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.956085561144668</v>
+        <v>12.965030863934569</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23368025713785046</v>
+        <v>0.22786042821432195</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8506866755559459</v>
+        <v>5.8547279216240158</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.306621391099414</v>
+        <v>7.3116681248852835</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.325873870677544</v>
+        <v>11.333696293136333</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.118343730556358</v>
+        <v>10.125332241935542</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.60715984486581</v>
+        <v>279.61061049236417</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.39284015513419</v>
+        <v>-523.38938950763577</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7286045497567</v>
+        <v>-4449.7294672116313</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,7 +5752,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.038097958353</v>
+        <v>10305.045429015536</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3237437368662</v>
+        <v>7230.3263317224901</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12012943317399906</v>
+        <v>0.11849544990139041</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5431973678787874E-2</v>
+        <v>4.4813998466493497E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.4129556671456151</v>
+        <v>0.41324186719811112</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035925500308469</v>
+        <v>0.20035929384641779</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114130802001861</v>
+        <v>0.19114139054444235</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688882646536926E-2</v>
+        <v>9.7688901585326698E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780011857822959E-2</v>
+        <v>9.0780051051696037E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.157098637208703</v>
+        <v>12.16553285654275</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0617114282241049</v>
+        <v>3.0638344523410583</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17131.284015513422</v>
+        <v>17130.938950763582</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1603463095864894</v>
+        <v>2.1618007726142277</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9975085062428365E-2</v>
+        <v>1.9988936004399837E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1887877742936066</v>
+        <v>-3.1909989145357152</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.89 HKD</v>
+        <v>12.9 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.06 HKD</v>
+        <v>14.07 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.03 HKD</v>
+        <v>13.04 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.11 HKD</v>
+        <v>12.12 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.956085561144668</v>
+        <v>12.965030863934569</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58478795639944925</v>
+        <v>0.58519345475023921</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.265898719156497</v>
+        <v>5.2695344668737762</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8506866755559459</v>
+        <v>5.8547279216240158</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842173217023449</v>
+        <v>0.548421597829714</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67310558379334395</v>
+        <v>0.67357232255078392</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.63351580730607</v>
+        <v>6.6380958023344991</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.306621391099414</v>
+        <v>7.3116681248852835</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604714891571961</v>
+        <v>0.43604699428641613</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89673585876338791</v>
+        <v>0.8973576651939813</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.429138011914157</v>
+        <v>10.436338627942352</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.325873870677544</v>
+        <v>11.333696293136333</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582594355166454</v>
+        <v>0.12582573754885507</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83193475181689591</v>
+        <v>0.83251162445275484</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2864089787394626</v>
+        <v>9.2928206174827874</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.118343730556358</v>
+        <v>10.125332241935542</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261917648858442</v>
+        <v>0.22261899817095931</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,6 +6839,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6855,17 +6866,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.30988720534199998</v>
+        <v>0.310102084512</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27723876475100001</v>
+        <v>0.277431005136</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22690120250200002</v>
+        <v>0.22705853827199998</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.30988720534199998</v>
+        <v>0.310102084512</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27723876475100001</v>
+        <v>0.277431005136</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22690120250200002</v>
+        <v>0.22705853827199998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2156364692685955</v>
+        <v>8.2213332812540703</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1887877742936066</v>
+        <v>-3.1909989145357152</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17131.284015513422</v>
+        <v>17130.938950763582</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.400263772803</v>
+        <v>-14497.572796147722</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.357992243289</v>
+        <v>-13980.530524618209</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1103507649353719</v>
+        <v>3.1103137493458073</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2253823560897623</v>
+        <v>3.2253425519580849</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27960.715984486578</v>
+        <v>27961.061049236418</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26510.75214411</v>
+        <v>-26529.134988959999</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0617114282241049</v>
+        <v>-3.0638344523410583</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18706.010315318992</v>
+        <v>18718.604222267797</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1603463095864894</v>
+        <v>2.1618007726142277</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>172.96030065600002</v>
+        <v>173.08023321599998</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9975085062428365E-2</v>
+        <v>1.9988936004399837E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7631.7815281350076</v>
+        <v>-7637.4505334762016</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88139003357518708</v>
+        <v>-0.8820447437224308</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.39284015513419</v>
+        <v>-523.38938950763577</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.96190204164509</v>
+        <v>-208.95457098446536</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.52907596683838</v>
+        <v>-420.52241832618461</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.34997270748761</v>
+        <v>-366.34339924389951</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.97687492696269</v>
+        <v>-454.97282677534673</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.37309778052492</v>
+        <v>-503.37057246855278</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09766300564797</v>
+        <v>-818.095566231465</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.07595104622681</v>
+        <v>-947.07369357037294</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1627988839114</v>
+        <v>-1014.1611842147413</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.59154886485817</v>
+        <v>-468.58887815613616</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.48165757763059</v>
+        <v>-437.47993577401326</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.914418199027</v>
+        <v>17798.917868846525</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.038097958353</v>
+        <v>16980.045429015536</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.470924033161</v>
+        <v>17261.477581673815</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.650027292511</v>
+        <v>16973.656600756101</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.023125073038</v>
+        <v>14670.027173224653</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.626902219476</v>
+        <v>11589.629427531447</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.902336994353</v>
+        <v>20402.904433768534</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.924048953773</v>
+        <v>19208.926306429628</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.83720111609</v>
+        <v>16944.838815785261</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.408451135143</v>
+        <v>17752.411121843863</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.518342422369</v>
+        <v>11857.520064225986</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7286045497567</v>
+        <v>-4449.7294672116313</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3237437368662</v>
+        <v>7230.3263317224901</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.038097958353</v>
+        <v>10305.045429015536</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.470924033161</v>
+        <v>10350.477581673815</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.650027292511</v>
+        <v>10809.656600756101</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0231250730376</v>
+        <v>8651.0271732246529</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6269022194756</v>
+        <v>5607.6294275314467</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.902336994353</v>
+        <v>12308.904433768534</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.924048953773</v>
+        <v>11857.926306429628</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.83720111609</v>
+        <v>10224.838815785261</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.408451135143</v>
+        <v>11296.411121843863</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5183424223687</v>
+        <v>7067.5200642259861</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3237437368662</v>
+        <v>7230.3263317224901</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.038097958353</v>
+        <v>10305.045429015536</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.470924033161</v>
+        <v>10350.477581673815</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.650027292511</v>
+        <v>10809.656600756101</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0231250730376</v>
+        <v>8651.0271732246529</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6269022194756</v>
+        <v>5607.6294275314467</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.902336994353</v>
+        <v>12308.904433768534</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.924048953773</v>
+        <v>11857.926306429628</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.83720111609</v>
+        <v>10224.838815785261</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.408451135143</v>
+        <v>11296.411121843863</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5183424223687</v>
+        <v>7067.5200642259861</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421631223407589</v>
+        <v>0.18421623269952314</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337865322662043</v>
+        <v>0.1933785786417202</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787944813710061</v>
+        <v>0.18787937537618996</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391245719229685</v>
+        <v>0.18391240644218565</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957501820503368</v>
+        <v>0.19957497471881303</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967747395492164</v>
+        <v>0.19967745343438384</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636706305814378</v>
+        <v>0.19636703998064864</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838205514110381</v>
+        <v>0.20838203528443336</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847875431591631</v>
+        <v>0.20847872295194986</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986050746158212</v>
+        <v>0.21986047553613608</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.60715984486581</v>
+        <v>279.61061049236417</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.03809795835491</v>
+        <v>594.04542901553464</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.47092403316162</v>
+        <v>539.47758167381539</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.65002729251239</v>
+        <v>532.65660075610049</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.02312507303731</v>
+        <v>328.02717322465327</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.62690221947508</v>
+        <v>204.62942753144722</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90233699435203</v>
+        <v>169.90443376853494</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.92404895377319</v>
+        <v>182.92630642962706</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83720111608861</v>
+        <v>130.83881578525867</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.40845113514183</v>
+        <v>216.41112184386387</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.51834242236939</v>
+        <v>139.52006422598674</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.39284015513419</v>
+        <v>-523.38938950763577</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.96190204164509</v>
+        <v>-208.95457098446536</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.52907596683838</v>
+        <v>-420.52241832618461</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.34997270748761</v>
+        <v>-366.34339924389951</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.97687492696269</v>
+        <v>-454.97282677534673</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.37309778052492</v>
+        <v>-503.37057246855278</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09766300564797</v>
+        <v>-818.095566231465</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.07595104622681</v>
+        <v>-947.07369357037294</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1627988839114</v>
+        <v>-1014.1611842147413</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.59154886485817</v>
+        <v>-468.58887815613616</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.48165757763059</v>
+        <v>-437.47993577401326</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8726281018393754E-3</v>
+        <v>2.8726091630495924E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1171685149195657E-3</v>
+        <v>1.1171293210465092E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3711282292298926E-3</v>
+        <v>2.3710906905183115E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1306353970332644E-3</v>
+        <v>2.1305971667746446E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2839171900291069E-3</v>
+        <v>3.2838879714129263E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074919019553585E-3</v>
+        <v>4.6074687871832092E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2198041090223361E-3</v>
+        <v>7.2197856047537794E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795766667889153E-3</v>
+        <v>8.9795552628270884E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432854585754193E-2</v>
+        <v>1.1432836383274426E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7227662839800953E-3</v>
+        <v>5.7227336674255166E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.050603149726545E-2</v>
+        <v>1.05059901485078E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688882646536926E-2</v>
+        <v>9.7688901585326698E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780011857822959E-2</v>
+        <v>9.0780051051696037E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327779040975462E-2</v>
+        <v>9.7327816579687032E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716151929072904E-2</v>
+        <v>9.8716190159331529E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588481255511153</v>
+        <v>0.10588484177372771</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1060825704315702</v>
+        <v>0.10608259354634234</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005791336381838</v>
+        <v>0.18005793186808691</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212689910831301</v>
+        <v>0.18212692051227486</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1910224471976652</v>
+        <v>0.19102246540014498</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680477334621948</v>
+        <v>0.21680480596277402</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475584982162699</v>
+        <v>0.28475589117038463</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422220661634231E-2</v>
+        <v>2.4422225396331675E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683445355306622E-2</v>
+        <v>3.9683459559398955E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093603166912704E-2</v>
+        <v>5.5093642360785774E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360515827289836E-2</v>
+        <v>5.8360553366001412E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867270898039548E-2</v>
+        <v>6.2867309128298174E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2441071441987468E-2</v>
+        <v>6.2441100660603641E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327922876856738E-2</v>
+        <v>5.1327945991628876E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862745083965965</v>
+        <v>0.10862746934392818</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242935478291242</v>
+        <v>0.11242937618687426</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526657949987701</v>
+        <v>0.11526659770235678</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795960591015294</v>
+        <v>0.13795963852670751</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972499081247733</v>
+        <v>0.169725032161235</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683445355306622E-2</v>
+        <v>3.9683459559398955E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093603166912704E-2</v>
+        <v>5.5093642360785774E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360515827289836E-2</v>
+        <v>5.8360553366001412E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867270898039548E-2</v>
+        <v>6.2867309128298174E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2441071441987468E-2</v>
+        <v>6.2441100660603641E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327922876856738E-2</v>
+        <v>5.1327945991628876E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862745083965965</v>
+        <v>0.10862746934392818</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242935478291242</v>
+        <v>0.11242937618687426</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526657949987701</v>
+        <v>0.11526659770235678</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795960591015294</v>
+        <v>0.13795963852670751</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972499081247733</v>
+        <v>0.169725032161235</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.30988720534199998</v>
+        <v>0.310102084512</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27723876475100001</v>
+        <v>0.277431005136</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22690120250200002</v>
+        <v>0.22705853827199998</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2985.803165273639</v>
+        <v>2987.8735537726716</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2985.803165273639</v>
+        <v>2987.8735537726716</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2683.2518629026563</v>
+        <v>2685.112459026866</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2400.5554897497691</v>
+        <v>2402.2200611237536</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1964.6925197715716</v>
+        <v>1966.0548590055769</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.4129556671456151</v>
+        <v>0.41324186719811112</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28974207925201073</v>
+        <v>0.28994278330494561</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25923959234282851</v>
+        <v>0.25941918504137718</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22207522756877221</v>
+        <v>0.22222908181521009</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.2271052211243493</v>
+        <v>0.22726259201804516</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5431973678787874E-2</v>
+        <v>4.4813998466493497E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5431973678787874E-2</v>
+        <v>4.4813998466493497E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0828353800000002E-2</v>
+        <v>4.0272997988571424E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6526846475757581E-2</v>
+        <v>3.6030000667012986E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.9894756587878792E-2</v>
+        <v>2.948812185350649E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225823494420395E-2</v>
+        <v>4.8225574145502437E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304104517707585E-2</v>
+        <v>-1.6304059216638023E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956924190015377E-2</v>
+        <v>1.6956922582308742E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702953448534562</v>
+        <v>0.15702966329441925</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578907576944077</v>
+        <v>0.26578914925231745</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.4319618497999046</v>
+        <v>-0.43196178440410526</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157478732163041E-2</v>
+        <v>6.2157463061288221E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361514312386302</v>
+        <v>0.13361516832696085</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490799304328422E-2</v>
+        <v>-4.5490851947705635E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714366349514827</v>
+        <v>0.49714367133163884</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143574706899229</v>
+        <v>1.2143566067903779</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920139581809272</v>
+        <v>1.3920130628088399</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756227040150053</v>
+        <v>1.375621867484661</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871191680462289</v>
+        <v>1.3871185189592954</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848633462713376</v>
+        <v>2.9848620020828109</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067777742988993</v>
+        <v>1.3067775516943683</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351584585753441</v>
+        <v>1.4351581853542525</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994827926013004</v>
+        <v>1.2994825873917277</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941599286291237</v>
+        <v>1.3941595990204507</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917531376957808</v>
+        <v>1.8917526768230326</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688882646536926E-2</v>
+        <v>9.7688901585326698E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780011857822959E-2</v>
+        <v>9.0780051051696037E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327779040975462E-2</v>
+        <v>9.7327816579687032E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716151929072904E-2</v>
+        <v>9.8716190159331529E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588481255511153</v>
+        <v>0.10588484177372771</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1060825704315702</v>
+        <v>0.10608259354634234</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005791336381838</v>
+        <v>0.18005793186808691</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212689910831301</v>
+        <v>0.18212692051227486</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1910224471976652</v>
+        <v>0.19102246540014498</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680477334621948</v>
+        <v>0.21680480596277402</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475584982162699</v>
+        <v>0.28475589117038463</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035925500308469</v>
+        <v>0.20035929384641779</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114130802001861</v>
+        <v>0.19114139054444235</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122251406494482</v>
+        <v>0.20122259167520154</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032502326203206</v>
+        <v>0.21032510471557211</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338030246204291</v>
+        <v>0.1933803558247934</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371115371682359</v>
+        <v>0.13711156704403854</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766120271508941</v>
+        <v>0.25766122919452589</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404519714888254</v>
+        <v>0.27404522935528902</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820704306462611</v>
+        <v>0.25820706766910873</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774668493333853</v>
+        <v>0.26774672521369869</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861268332891144</v>
+        <v>0.16861270781278065</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91178239779065284</v>
+        <v>0.91241496424070634</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2995202814285549</v>
+        <v>1.3004223080999024</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3052496031802647</v>
+        <v>1.3061555176455371</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3631545378172285</v>
+        <v>1.3641005935735606</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0909401691942475</v>
+        <v>1.091697149860553</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.7071516690037607</v>
+        <v>0.70764233436436463</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5522182525668278</v>
+        <v>1.5532948422403574</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4953474844802181</v>
+        <v>1.4963846596219137</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2894065204657565</v>
+        <v>1.2903008127779987</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4245373719151462</v>
+        <v>1.4255254986990373</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89125176811969409</v>
+        <v>0.89186998910116833</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12012943317399906</v>
+        <v>0.11849544990139041</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17121479333709552</v>
+        <v>0.16888601403894837</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17196964468778192</v>
+        <v>0.16963058670721259</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17959875333560324</v>
+        <v>0.17715592124331955</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14373388263428821</v>
+        <v>0.14177885063124065</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.3168862846345291E-2</v>
+        <v>9.1901601865501892E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20450833367151883</v>
+        <v>0.20172660288835811</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19701547885114865</v>
+        <v>0.19433567008076802</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.16988228201129862</v>
+        <v>0.16757153412701281</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.1876860832562775</v>
+        <v>0.18513318164922563</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11742447537808881</v>
+        <v>0.11582727131184004</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14465848880719909</v>
+        <v>0.14259193896709624</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14082405742196566</v>
+        <v>0.13881228517308045</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12481682798837215</v>
+        <v>0.12303373044568112</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.40074372774957423</v>
+        <v>0.39501881735315175</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14808208825830035</v>
+        <v>0.14596662985461034</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14563231265106788</v>
+        <v>0.14355185104176693</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12496898796397665</v>
+        <v>0.12318371670734841</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12095196460801783</v>
+        <v>0.11922407939933187</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1947415671376632E-2</v>
+        <v>5.1205309733214112E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.530111434024423E-2</v>
+        <v>3.4796812706812168E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3237437368662</v>
+        <v>7230.3263317224901</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.316583158216</v>
+        <v>96404.351089633201</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17131.284015513422</v>
+        <v>17130.938950763582</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89415.000598671628</v>
+        <v>89414.690040396774</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.09192109</v>
+        <v>1.0926782399999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.015942025495272</v>
+        <v>13.024928854850346</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7316965891332</v>
+        <v>7373.7343359054767</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2852991526815</v>
+        <v>6859.2877543306759</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9840367289116</v>
+        <v>7519.9867283940803</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2874303765602</v>
+        <v>6507.2897595622117</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1371804070468</v>
+        <v>7669.1399254593398</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3530323877276</v>
+        <v>6173.3552420465849</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2486628476599</v>
+        <v>7821.2514623459701</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5551422530916</v>
+        <v>5856.5572385189098</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.377160442129</v>
+        <v>7976.3800154663504</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0143659862724</v>
+        <v>5556.0163546780395</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5825133832668</v>
+        <v>8134.5854250347156</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.896437452483</v>
+        <v>5270.8983240905773</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.925748748441</v>
+        <v>8295.9287181502732</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4099025430642</v>
+        <v>5000.4116923645715</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.469104040516</v>
+        <v>8460.4721323381673</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8039221912031</v>
+        <v>4743.8056201644595</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.276051195724</v>
+        <v>8628.2791395573477</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3661881302824</v>
+        <v>4500.3677989686639</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4113210677078</v>
+        <v>8799.4144706846273</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4209456092194</v>
+        <v>4269.4224737842251</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9409283971818</v>
+        <v>8973.9441404843492</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3271175761106</v>
+        <v>4050.3285673297764</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.932197276863</v>
+        <v>9151.9354730733285</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.476525123127</v>
+        <v>3842.4779004798002</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4537871214561</v>
+        <v>9333.4571278908443</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2921992528063</v>
+        <v>3645.2935040303159</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5757191527537</v>
+        <v>9518.5791261837512</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2267792794291</v>
+        <v>3458.2280170996851</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3694034100354</v>
+        <v>9707.3728780168931</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7609934196043</v>
+        <v>3280.7621677186521</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9076662962125</v>
+        <v>9899.9112098192436</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4022173543804</v>
+        <v>3112.4033313919363</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.264778670302</v>
+        <v>10096.268392476408</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6831067615967</v>
+        <v>2952.6841636300992</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.516484497133</v>
+        <v>10296.520169980326</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1603000225723</v>
+        <v>2801.1613026557661</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.740030065259</v>
+        <v>10500.743788647198</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4131875019671</v>
+        <v>2657.4141386830438</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.014193784409</v>
+        <v>10709.018026914953</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0427439845062</v>
+        <v>2521.0436463538344</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.422621188452</v>
+        <v>98316.457812073029</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.978555311001</v>
+        <v>23144.986839707923</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.15639166971</v>
+        <v>110204.19583758974</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.15639166971</v>
+        <v>110204.19583758974</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.31658315823</v>
+        <v>96404.351089633201</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.939126941274</v>
+        <v>97921.97417662642</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.34598378255</v>
+        <v>99461.381584475239</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.01528281669</v>
+        <v>101023.05144248539</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.43261704073</v>
+        <v>102607.46934382778</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.316583158245</v>
+        <v>96404.351089633215</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.007916942093</v>
+        <v>99377.043487447227</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.78290434886</v>
+        <v>102492.81959009878</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.03066767703</v>
+        <v>105760.06852288912</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.60309270237</v>
+        <v>109187.64217476246</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.316583158245</v>
+        <v>96404.351089633215</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.49581943882</v>
+        <v>101173.53203296979</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.93704644879</v>
+        <v>106330.97510600825</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.64263225286</v>
+        <v>111913.6826900578</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.14500504021</v>
+        <v>117962.18722781559</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.316583158245</v>
+        <v>96404.351089633215</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.04287039749</v>
+        <v>102998.07973699761</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.27535730705</v>
+        <v>110332.31484908535</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.6083402471</v>
+        <v>118504.65075718908</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.93212154656</v>
+        <v>127625.97780332917</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.316583158245</v>
+        <v>96404.35108963323</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.57206515179</v>
+        <v>104688.60953685141</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.62592694239</v>
+        <v>114140.66678186248</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.58379257467</v>
+        <v>124956.62851890422</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.37425660394</v>
+        <v>137367.42342518925</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.31658315823</v>
+        <v>96404.351089633245</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.32823059156</v>
+        <v>106173.36623373732</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.71397722626</v>
+        <v>117578.75606275827</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.50986319828</v>
+        <v>130953.55673603732</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.78532061359</v>
+        <v>146703.83783102679</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.467088902905772</v>
+        <v>11.475001185829832</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.661216320273764</v>
+        <v>11.669263282800722</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.858151150372185</v>
+        <v>11.866334740198232</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.057954629068597</v>
+        <v>12.066276836373474</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.275708603633518</v>
+        <v>11.283488112820319</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.650580840102432</v>
+        <v>11.658620424061924</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.043496688643071</v>
+        <v>12.051808865475689</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.455514062333151</v>
+        <v>12.464112084086734</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.887749231193725</v>
+        <v>12.89664712434976</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.275708603633518</v>
+        <v>11.283488112820319</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.877127548852405</v>
+        <v>11.885324303917276</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.527508402476139</v>
+        <v>12.536156371678015</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.23151736052494</v>
+        <v>13.240653749385364</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.994265778433569</v>
+        <v>14.003931338574523</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.275708603633518</v>
+        <v>11.283488112820319</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.107212665918709</v>
+        <v>12.115569046927295</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.032098510575551</v>
+        <v>13.041096548800677</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.06267329903967</v>
+        <v>14.072386318204368</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.212920890033404</v>
+        <v>15.223431915429719</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.275708603633518</v>
+        <v>11.283488112820322</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.320397416333705</v>
+        <v>12.328901698333913</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.512351834919071</v>
+        <v>13.521683058058978</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.8763018248032</v>
+        <v>14.886579314294865</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.441368713761278</v>
+        <v>16.452731998293999</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.275708603633516</v>
+        <v>11.283488112820324</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.507633089955073</v>
+        <v>12.516267270279346</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.945913080225502</v>
+        <v>13.955545094758719</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.632546195849921</v>
+        <v>15.643348344315402</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.618739958593284</v>
+        <v>17.630920066910438</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.887749231193725</v>
+        <v>12.89664712434976</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.06267329903967</v>
+        <v>14.072386318204368</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.032098510575551</v>
+        <v>13.041096548800677</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.107212665918709</v>
+        <v>12.115569046927295</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.275708603633518</v>
+        <v>11.283488112820319</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2985.803165273639</v>
+        <v>2987.8735537726716</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39810.708870315189</v>
+        <v>39838.314050302288</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2558578495792085</v>
+        <v>5.2595023187695666</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3045.0242921177337</v>
+        <v>3047.1357451924032</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2832.5807368537057</v>
+        <v>2834.5448792487473</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3105.4200248117631</v>
+        <v>3107.5733569465847</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2687.2212221194272</v>
+        <v>2689.0845706406358</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3167.0136607662334</v>
+        <v>3169.2097026004003</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2549.3211200150799</v>
+        <v>2551.0888471005778</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3229.8289594780053</v>
+        <v>3232.0685581258058</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2418.497635944208</v>
+        <v>2420.1746485981676</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3293.8901516954261</v>
+        <v>3296.1741710730134</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2294.3876191764825</v>
+        <v>2295.9785725903962</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3359.2219487652415</v>
+        <v>3361.5512699238861</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2176.646554783636</v>
+        <v>2178.155865258585</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3425.8495521648988</v>
+        <v>3428.2250736308515</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2064.947607306211</v>
+        <v>2066.3794645120024</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3493.7986632239158</v>
+        <v>3496.2213013450091</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1958.980713496454</v>
+        <v>1960.3390921016548</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3563.0954930380635</v>
+        <v>3565.5661823371902</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1858.4517216189095</v>
+        <v>1859.7403923240643</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3633.7667725801934</v>
+        <v>3636.2864661157942</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1763.0815749195181</v>
+        <v>1764.3041149241719</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3705.8397630115992</v>
+        <v>3708.4094327453013</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1672.6055369966191</v>
+        <v>1673.7653399292074</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3779.3422661979025</v>
+        <v>3781.9629033694509</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1586.7724569235859</v>
+        <v>1587.8727422617505</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3854.3026354335088</v>
+        <v>3856.9752509431319</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1505.3440720831493</v>
+        <v>1506.3878940906332</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3930.7497863787785</v>
+        <v>3933.475411177139</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1428.0943467781685</v>
+        <v>1429.0846029830955</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4008.7132082141229</v>
+        <v>4011.4928937000027</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1354.8088447829036</v>
+        <v>1355.7482840209784</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4088.2229750153415</v>
+        <v>4091.0577934412158</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1285.2841340930697</v>
+        <v>1286.1753641380253</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4169.3097573545701</v>
+        <v>4172.2008022402233</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1219.3272222223225</v>
+        <v>1220.1727170247955</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4252.0048341313368</v>
+        <v>4254.9532206856829</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1156.7550204776328</v>
+        <v>1157.5571270325622</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4336.3401046382651</v>
+        <v>4339.3469701895356</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1097.3938357264303</v>
+        <v>1098.1547805880414</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4422.348100866102</v>
+        <v>4425.414605300567</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1041.0788882447339</v>
+        <v>1041.800783707193</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40600.323894903115</v>
+        <v>40628.476602565381</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9557.8500603794091</v>
+        <v>9564.4775779166121</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45509.430924941655</v>
+        <v>45540.987660991887</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45509.430924941655</v>
+        <v>45540.987660991887</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39810.708870315197</v>
+        <v>39838.314050302288</v>
       </c>
       <c r="C51" s="123">
-        <v>40437.419700358339</v>
+        <v>40465.459448474328</v>
       </c>
       <c r="D51" s="123">
-        <v>41073.126485933775</v>
+        <v>41101.607040072369</v>
       </c>
       <c r="E51" s="123">
-        <v>41718.026673177228</v>
+        <v>41746.954408143501</v>
       </c>
       <c r="F51" s="123">
-        <v>42372.320790468802</v>
+        <v>42401.702220116342</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39810.708870315204</v>
+        <v>39838.314050302302</v>
       </c>
       <c r="C52" s="123">
-        <v>41038.298603275893</v>
+        <v>41066.755007380583</v>
       </c>
       <c r="D52" s="123">
-        <v>42324.975541876076</v>
+        <v>42354.324141811565</v>
       </c>
       <c r="E52" s="123">
-        <v>43674.204021711266</v>
+        <v>43704.488191398879</v>
       </c>
       <c r="F52" s="123">
-        <v>45089.639479177524</v>
+        <v>45120.905127258069</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39810.708870315204</v>
+        <v>39838.314050302295</v>
       </c>
       <c r="C53" s="123">
-        <v>41780.168463570459</v>
+        <v>41809.139288332342</v>
       </c>
       <c r="D53" s="123">
-        <v>43909.963046234654</v>
+        <v>43940.410693802725</v>
       </c>
       <c r="E53" s="123">
-        <v>46215.372955897925</v>
+        <v>46247.41919985642</v>
       </c>
       <c r="F53" s="123">
-        <v>48713.136288484166</v>
+        <v>48746.914508795693</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39810.708870315204</v>
+        <v>39838.314050302295</v>
       </c>
       <c r="C54" s="123">
-        <v>42533.625508237645</v>
+        <v>42563.118788336826</v>
       </c>
       <c r="D54" s="123">
-        <v>45562.33837787043</v>
+        <v>45593.931800525919</v>
       </c>
       <c r="E54" s="123">
-        <v>48937.149596976567</v>
+        <v>48971.08315056088</v>
       </c>
       <c r="F54" s="123">
-        <v>52703.851944334252</v>
+        <v>52740.397370432445</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39810.708870315197</v>
+        <v>39838.314050302288</v>
       </c>
       <c r="C55" s="123">
-        <v>43231.739119686543</v>
+        <v>43261.716479382449</v>
       </c>
       <c r="D55" s="123">
-        <v>47135.018328078579</v>
+        <v>47167.702264174281</v>
       </c>
       <c r="E55" s="123">
-        <v>51601.529424299632</v>
+        <v>51637.310487932729</v>
       </c>
       <c r="F55" s="123">
-        <v>56726.635680177293</v>
+        <v>56765.97054841878</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39810.708870315204</v>
+        <v>39838.314050302295</v>
       </c>
       <c r="C56" s="123">
-        <v>43844.877592534292</v>
+        <v>43875.28010913849</v>
       </c>
       <c r="D56" s="123">
-        <v>48554.796272588937</v>
+        <v>48588.464698205469</v>
       </c>
       <c r="E56" s="123">
-        <v>54077.994030616945</v>
+        <v>54115.492301833852</v>
       </c>
       <c r="F56" s="123">
-        <v>60582.159539861103</v>
+        <v>60624.167870422418</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.0993743574480694</v>
+        <v>5.1064487329809971</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1795403745985258</v>
+        <v>5.1867259646590673</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2608657287460261</v>
+        <v>5.2681641416854674</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3433757075891171</v>
+        <v>5.3507885868404284</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0203427782835712</v>
+        <v>5.027307513097699</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1751483927889588</v>
+        <v>5.1823278898415213</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3374052191551433</v>
+        <v>5.3448098155320602</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5075501285829134</v>
+        <v>5.5151907674426797</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6860440911035299</v>
+        <v>5.6939323551095828</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0203427782835712</v>
+        <v>5.0273075130976981</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2687021400404488</v>
+        <v>5.2760114244540031</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.537280599347369</v>
+        <v>5.5449624833678586</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8280050882949022</v>
+        <v>5.8360902951678169</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1429863700766232</v>
+        <v>6.1515085513148167</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0203427782835712</v>
+        <v>5.0273075130976981</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3637170930588374</v>
+        <v>5.3711581919680116</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7456539440726395</v>
+        <v>5.753624904985374</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1712356433862938</v>
+        <v>6.1797970149160646</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6462369047077479</v>
+        <v>6.6554572467436328</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0203427782835695</v>
+        <v>5.0273075130976963</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4517529438917336</v>
+        <v>5.4593161751696062</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9439772760258176</v>
+        <v>5.9522233714214954</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.507228154051675</v>
+        <v>6.5162556488801249</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1535313953088728</v>
+        <v>7.1634555083332616</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0203427782835712</v>
+        <v>5.0273075130976981</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5290729764055042</v>
+        <v>5.5367434739689783</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1230188493298208</v>
+        <v>6.1315133295736732</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8195235528223908</v>
+        <v>6.8289842958835152</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6397335231965373</v>
+        <v>7.6503321457188536</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6860440911035299</v>
+        <v>5.6939323551095828</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1712356433862938</v>
+        <v>6.1797970149160646</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7456539440726395</v>
+        <v>5.753624904985374</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3637170930588374</v>
+        <v>5.3711581919680116</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0203427782835712</v>
+        <v>5.027307513097699</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.59</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.300914241366668</v>
+        <v>13.31009865212657</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.038097958353</v>
+        <v>10305.045429015536</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3237437368662</v>
+        <v>7230.3263317224901</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052504052653388E-2</v>
+        <v>6.005259008155317E-2</v>
       </c>
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.59</v>
+        <v>7.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.032098510575551</v>
+        <v>13.041096548800677</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.107212665918709</v>
+        <v>12.115569046927295</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.06267329903967</v>
+        <v>14.072386318204368</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.053236299337007</v>
+        <v>13.062249002306739</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.275708603633518</v>
+        <v>11.283488112820319</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.887749231193725</v>
+        <v>12.89664712434976</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.956085561144668</v>
+        <v>12.965030863934569</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.015942025495272</v>
+        <v>13.024928854850346</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8029037737947481E-2</v>
+        <v>-6.8032598840628747E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58478795639944925</v>
+        <v>0.58519345475023921</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.265898719156497</v>
+        <v>5.2695344668737762</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8506866755559459</v>
+        <v>5.8547279216240158</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842173217023449</v>
+        <v>0.548421597829714</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.59</v>
+        <v>7.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23368025713785046</v>
+        <v>0.22786042821432195</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67310558379334395</v>
+        <v>0.67357232255078392</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.63351580730607</v>
+        <v>6.6380958023344991</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.306621391099414</v>
+        <v>7.3116681248852835</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604714891571961</v>
+        <v>0.43604699428641613</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89673585876338791</v>
+        <v>0.8973576651939813</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.429138011914157</v>
+        <v>10.436338627942352</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.325873870677544</v>
+        <v>11.333696293136333</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582594355166454</v>
+        <v>0.12582573754885507</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83193475181689591</v>
+        <v>0.83251162445275484</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2864089787394626</v>
+        <v>9.2928206174827874</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.118343730556358</v>
+        <v>10.125332241935542</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261917648858442</v>
+        <v>0.22261899817095931</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.59</v>
+        <v>7.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>65720.304963720002</v>
+        <v>66672.773151599991</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.09192109</v>
+        <v>1.0926782399999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.956085561144668</v>
+        <v>12.965030863934569</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23368025713785046</v>
+        <v>0.22786042821432195</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8506866755559459</v>
+        <v>5.8547279216240158</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.306621391099414</v>
+        <v>7.3116681248852835</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.325873870677544</v>
+        <v>11.333696293136333</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.118343730556358</v>
+        <v>10.125332241935542</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.60715984486581</v>
+        <v>279.61061049236417</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.39284015513419</v>
+        <v>-523.38938950763577</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7286045497567</v>
+        <v>-4449.7294672116313</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,7 +21380,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>500</v>
       </c>
       <c r="C61" s="374"/>
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.038097958353</v>
+        <v>10305.045429015536</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3237437368662</v>
+        <v>7230.3263317224901</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12012943317399906</v>
+        <v>0.11849544990139041</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5431973678787874E-2</v>
+        <v>4.4813998466493497E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.4129556671456151</v>
+        <v>0.41324186719811112</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035925500308469</v>
+        <v>0.20035929384641779</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114130802001861</v>
+        <v>0.19114139054444235</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688882646536926E-2</v>
+        <v>9.7688901585326698E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780011857822959E-2</v>
+        <v>9.0780051051696037E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.157098637208703</v>
+        <v>12.16553285654275</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0617114282241049</v>
+        <v>3.0638344523410583</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17131.284015513422</v>
+        <v>17130.938950763582</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1603463095864894</v>
+        <v>2.1618007726142277</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9975085062428365E-2</v>
+        <v>1.9988936004399837E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.275708603633516</v>
+        <v>11.283488112820317</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1887877742936066</v>
+        <v>-3.1909989145357152</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.89 HKD</v>
+        <v>12.9 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.06 HKD</v>
+        <v>14.07 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.03 HKD</v>
+        <v>13.04 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.11 HKD</v>
+        <v>12.12 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.956085561144668</v>
+        <v>12.965030863934569</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34482868022199997</v>
+        <v>0.34506778819199996</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58478795639944925</v>
+        <v>0.58519345475023921</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.265898719156497</v>
+        <v>5.2695344668737762</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8506866755559459</v>
+        <v>5.8547279216240158</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842173217023449</v>
+        <v>0.548421597829714</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67310558379334395</v>
+        <v>0.67357232255078392</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.63351580730607</v>
+        <v>6.6380958023344991</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.306621391099414</v>
+        <v>7.3116681248852835</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604714891571961</v>
+        <v>0.43604699428641613</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89673585876338791</v>
+        <v>0.8973576651939813</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.429138011914157</v>
+        <v>10.436338627942352</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.325873870677544</v>
+        <v>11.333696293136333</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582594355166454</v>
+        <v>0.12582573754885507</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83193475181689591</v>
+        <v>0.83251162445275484</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2864089787394626</v>
+        <v>9.2928206174827874</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.118343730556358</v>
+        <v>10.125332241935542</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261917648858442</v>
+        <v>0.22261899817095931</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,12 +22467,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22485,15 +22488,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFBD65F-E0DD-4F6A-895F-F910D9AFEA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE669085-2A37-4ADB-8E15-9C2B0C908826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4760,29 +4760,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>66672.773151599991</v>
+        <v>66759.36116868</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0926782399999999</v>
+        <v>1.0942760599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.965030863934569</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22786042821432195</v>
+        <v>0.22792724483207127</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8547279216240158</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3116681248852835</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.333696293136333</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.125332241935542</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61061049236417</v>
+        <v>279.61789242274239</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38938950763577</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7294672116313</v>
+        <v>-4449.731287694226</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,7 +5752,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.045429015536</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3263317224901</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11849544990139041</v>
+        <v>0.11851489961283493</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4813998466493497E-2</v>
+        <v>4.4821320330479884E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41324186719811112</v>
+        <v>0.41384583689866911</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035929384641779</v>
+        <v>0.20035937581782973</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114139054444235</v>
+        <v>0.19114156469642632</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688901585326698E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780051051696037E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.16553285654275</v>
+        <v>12.18333168019943</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0638344523410583</v>
+        <v>3.0683146879542789</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.938950763582</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1618007726142277</v>
+        <v>2.1648699400997713</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9988936004399837E-2</v>
+        <v>2.0018165763497582E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1909989145357152</v>
+        <v>-3.1956651023474385</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.9 HKD</v>
+        <v>12.92 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.07 HKD</v>
+        <v>14.09 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.04 HKD</v>
+        <v>13.06 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
+        <v>12.13 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.28 HKD</v>
+        <v>11.3 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.965030863934569</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58519345475023921</v>
+        <v>0.58604918132338757</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2695344668737762</v>
+        <v>5.2772069444640133</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8547279216240158</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.548421597829714</v>
+        <v>0.5484213143271619</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67357232255078392</v>
+        <v>0.67455728526809577</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6380958023344991</v>
+        <v>6.6477609144246523</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3116681248852835</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604699428641613</v>
+        <v>0.43604666796787828</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.8973576651939813</v>
+        <v>0.89866986852348141</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.436338627942352</v>
+        <v>10.45153400710732</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.333696293136333</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582573754885507</v>
+        <v>0.12582530281537296</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83251162445275484</v>
+        <v>0.83372900361808255</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2928206174827874</v>
+        <v>9.3063510267411278</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.125332241935542</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261899817095931</v>
+        <v>0.22261862186231296</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,17 +6839,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6866,6 +6855,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.310102084512</v>
+        <v>0.31055554582799999</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.277431005136</v>
+        <v>0.27783669163399999</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22705853827199998</v>
+        <v>0.227390565268</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.310102084512</v>
+        <v>0.31055554582799999</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.277431005136</v>
+        <v>0.27783669163399999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22705853827199998</v>
+        <v>0.227390565268</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2213332812540703</v>
+        <v>8.2333553114021711</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1909989145357152</v>
+        <v>-3.1956651023474385</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17130.938950763582</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.572796147722</v>
+        <v>-14497.936892666634</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.530524618209</v>
+        <v>-13980.89462113712</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1103137493458073</v>
+        <v>3.1102356379278002</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2253425519580849</v>
+        <v>3.2252585561890528</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27961.061049236418</v>
+        <v>27961.789242274241</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26529.134988959999</v>
+        <v>-26567.928460739997</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0638344523410583</v>
+        <v>-3.0683146879542789</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18718.604222267797</v>
+        <v>18745.179534933755</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1618007726142277</v>
+        <v>2.1648699400997709</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>173.08023321599998</v>
+        <v>173.33332790399999</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9988936004399837E-2</v>
+        <v>2.0018165763497582E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7637.4505334762016</v>
+        <v>-7649.4155979022416</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.8820447437224308</v>
+        <v>-0.88342658209101044</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.38938950763577</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.95457098446536</v>
+        <v>-208.93910019296732</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.52241832618461</v>
+        <v>-420.50836865123335</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.34339924389951</v>
+        <v>-366.32952720851665</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.97282677534673</v>
+        <v>-454.96428392701432</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.37057246855278</v>
+        <v>-503.36524328150233</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.095566231465</v>
+        <v>-818.09114139130793</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.07369357037294</v>
+        <v>-947.06892960013079</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1611842147413</v>
+        <v>-1014.1577767648394</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.58887815613616</v>
+        <v>-468.58324213710398</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.47993577401326</v>
+        <v>-437.47630223738793</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.917868846525</v>
+        <v>17798.925150776904</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.045429015536</v>
+        <v>16980.060899807031</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.477581673815</v>
+        <v>17261.491631348767</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.656600756101</v>
+        <v>16973.670472791484</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.027173224653</v>
+        <v>14670.035716072985</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.629427531447</v>
+        <v>11589.634756718498</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.904433768534</v>
+        <v>20402.908858608691</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.926306429628</v>
+        <v>19208.931070399871</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.838815785261</v>
+        <v>16944.842223235162</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.411121843863</v>
+        <v>17752.416757862895</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.520064225986</v>
+        <v>11857.523697762612</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7294672116313</v>
+        <v>-4449.731287694226</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3263317224901</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.045429015536</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.477581673815</v>
+        <v>10350.491631348767</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.656600756101</v>
+        <v>10809.670472791484</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0271732246529</v>
+        <v>8651.0357160729855</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6294275314467</v>
+        <v>5607.6347567184985</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.904433768534</v>
+        <v>12308.908858608691</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.926306429628</v>
+        <v>11857.931070399871</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.838815785261</v>
+        <v>10224.842223235162</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.411121843863</v>
+        <v>11296.416757862895</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5200642259861</v>
+        <v>7067.5236977626118</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3263317224901</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.045429015536</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.477581673815</v>
+        <v>10350.491631348767</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.656600756101</v>
+        <v>10809.670472791484</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0271732246529</v>
+        <v>8651.0357160729855</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6294275314467</v>
+        <v>5607.6347567184985</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.904433768534</v>
+        <v>12308.908858608691</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.926306429628</v>
+        <v>11857.931070399871</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.838815785261</v>
+        <v>10224.842223235162</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.411121843863</v>
+        <v>11296.416757862895</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5200642259861</v>
+        <v>7067.5236977626118</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421623269952314</v>
+        <v>0.18421606485731437</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1933785786417202</v>
+        <v>0.19337842124476803</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787937537618996</v>
+        <v>0.18787922182841446</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391240644218565</v>
+        <v>0.18391229934389186</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957497471881303</v>
+        <v>0.19957488294953873</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967745343438384</v>
+        <v>0.19967741012973447</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636703998064864</v>
+        <v>0.19636699128003474</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838203528443336</v>
+        <v>0.20838199338074748</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847872295194986</v>
+        <v>0.2084786567643391</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986047553613608</v>
+        <v>0.21986040816362973</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.61061049236417</v>
+        <v>279.61789242274239</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.04542901553464</v>
+        <v>594.06089980703268</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.47758167381539</v>
+        <v>539.49163134876665</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.65660075610049</v>
+        <v>532.67047279148335</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.02717322465327</v>
+        <v>328.03571607298568</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.62942753144722</v>
+        <v>204.6347567184977</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90443376853494</v>
+        <v>169.90885860869201</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.92630642962706</v>
+        <v>182.93107039986916</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83881578525867</v>
+        <v>130.84222323516065</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.41112184386387</v>
+        <v>216.41675786289605</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.52006422598674</v>
+        <v>139.52369776261207</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.38938950763577</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.95457098446536</v>
+        <v>-208.93910019296732</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.52241832618461</v>
+        <v>-420.50836865123335</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.34339924389951</v>
+        <v>-366.32952720851665</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.97282677534673</v>
+        <v>-454.96428392701432</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.37057246855278</v>
+        <v>-503.36524328150233</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.095566231465</v>
+        <v>-818.09114139130793</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.07369357037294</v>
+        <v>-947.06892960013079</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1611842147413</v>
+        <v>-1014.1577767648394</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.58887815613616</v>
+        <v>-468.58324213710398</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.47993577401326</v>
+        <v>-437.47630223738793</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8726091630495924E-3</v>
+        <v>2.8725691963625553E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1171293210465092E-3</v>
+        <v>1.1170466098872327E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3710906905183115E-3</v>
+        <v>2.3710114722601877E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1305971667746446E-3</v>
+        <v>2.1305164891390026E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2838879714129263E-3</v>
+        <v>3.2838263111219608E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074687871832092E-3</v>
+        <v>4.6074200078855326E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2197856047537794E-3</v>
+        <v>7.2197465550405335E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795552628270884E-3</v>
+        <v>8.9795100938667941E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432836383274426E-2</v>
+        <v>1.14327979704286E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7227336674255166E-3</v>
+        <v>5.722664836436628E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.05059901485078E-2</v>
+        <v>1.0505902889877475E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688901585326698E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780051051696037E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327816579687032E-2</v>
+        <v>9.7327895797945166E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716190159331529E-2</v>
+        <v>9.8716270836967171E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588484177372771</v>
+        <v>0.10588490343401867</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608259354634234</v>
+        <v>0.10608264232564002</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005793186808691</v>
+        <v>0.18005797091780018</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212692051227486</v>
+        <v>0.18212696568123515</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102246540014498</v>
+        <v>0.1910225038129908</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680480596277402</v>
+        <v>0.21680487479376293</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475589117038463</v>
+        <v>0.28475597842901496</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422225396331675E-2</v>
+        <v>2.4422235388003435E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683459559398955E-2</v>
+        <v>3.968348953441423E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093642360785774E-2</v>
+        <v>5.5093725071945036E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360553366001412E-2</v>
+        <v>5.8360632584259539E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867309128298174E-2</v>
+        <v>6.2867389805933815E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2441100660603641E-2</v>
+        <v>6.2441162320894611E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327945991628876E-2</v>
+        <v>5.1327994770926567E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862746934392818</v>
+        <v>0.10862750839364142</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242937618687426</v>
+        <v>0.11242942135583456</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526659770235678</v>
+        <v>0.1152666361152026</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795963852670751</v>
+        <v>0.13795970735769639</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.169725032161235</v>
+        <v>0.16972511941986532</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683459559398955E-2</v>
+        <v>3.968348953441423E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093642360785774E-2</v>
+        <v>5.5093725071945036E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360553366001412E-2</v>
+        <v>5.8360632584259539E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867309128298174E-2</v>
+        <v>6.2867389805933815E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2441100660603641E-2</v>
+        <v>6.2441162320894611E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327945991628876E-2</v>
+        <v>5.1327994770926567E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862746934392818</v>
+        <v>0.10862750839364142</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242937618687426</v>
+        <v>0.11242942135583456</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526659770235678</v>
+        <v>0.1152666361152026</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795963852670751</v>
+        <v>0.13795970735769639</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.169725032161235</v>
+        <v>0.16972511941986532</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.310102084512</v>
+        <v>0.31055554582799999</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.277431005136</v>
+        <v>0.27783669163399999</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22705853827199998</v>
+        <v>0.227390565268</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2987.8735537726716</v>
+        <v>2992.2427119996059</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2987.8735537726716</v>
+        <v>2992.2427119996059</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2685.112459026866</v>
+        <v>2689.0388906443586</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2402.2200611237536</v>
+        <v>2405.7328200655484</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1966.0548590055769</v>
+        <v>1968.929814925644</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41324186719811112</v>
+        <v>0.41384583689866911</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28994278330494561</v>
+        <v>0.29036632981525007</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25941918504137718</v>
+        <v>0.25979818026227913</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22222908181521009</v>
+        <v>0.22255376110871333</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22726259201804516</v>
+        <v>0.22759469265252458</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4813998466493497E-2</v>
+        <v>4.4821320330479884E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4813998466493497E-2</v>
+        <v>4.4821320330479884E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.0272997988571424E-2</v>
+        <v>4.027957792840467E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6030000667012986E-2</v>
+        <v>3.6035887371465625E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.948812185350649E-2</v>
+        <v>2.9492939723476004E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225574145502437E-2</v>
+        <v>4.8225047943095456E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304059216638023E-2</v>
+        <v>-1.630396361752573E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956922582308742E-2</v>
+        <v>1.6956919189556219E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702966329441925</v>
+        <v>0.1570299351210549</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578914925231745</v>
+        <v>0.26578930432374337</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196178440410526</v>
+        <v>-0.43196164639884516</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157463061288221E-2</v>
+        <v>6.2157429990921775E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361516832696085</v>
+        <v>0.13361522151325422</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490851947705635E-2</v>
+        <v>-4.5490963041414756E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714367133163884</v>
+        <v>0.49714368786904362</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143566067903779</v>
+        <v>1.214354783699952</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920130628088399</v>
+        <v>1.3920111733013887</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.375621867484661</v>
+        <v>1.3756201021509935</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871185189592954</v>
+        <v>1.3871171491876846</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848620020828109</v>
+        <v>2.9848591654344512</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067775516943683</v>
+        <v>1.3067770819304068</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351581853542525</v>
+        <v>1.4351576087738316</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994825873917277</v>
+        <v>1.2994821543364572</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941595990204507</v>
+        <v>1.3941589034450128</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917526768230326</v>
+        <v>1.8917517042401404</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688901585326698E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780051051696037E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327816579687032E-2</v>
+        <v>9.7327895797945166E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716190159331529E-2</v>
+        <v>9.8716270836967171E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588484177372771</v>
+        <v>0.10588490343401867</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608259354634234</v>
+        <v>0.10608264232564002</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005793186808691</v>
+        <v>0.18005797091780018</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212692051227486</v>
+        <v>0.18212696568123515</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102246540014498</v>
+        <v>0.1910225038129908</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680480596277402</v>
+        <v>0.21680487479376293</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475589117038463</v>
+        <v>0.28475597842901496</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035929384641779</v>
+        <v>0.20035937581782973</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114139054444235</v>
+        <v>0.19114156469642632</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122259167520154</v>
+        <v>0.20122275545677776</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032510471557211</v>
+        <v>0.21032527660766132</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1933803558247934</v>
+        <v>0.19338046843665369</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.13711156704403854</v>
+        <v>0.1371116300911957</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766122919452589</v>
+        <v>0.25766128507430308</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404522935528902</v>
+        <v>0.2740452973207389</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820706766910873</v>
+        <v>0.25820711959215487</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774672521369869</v>
+        <v>0.26774681021768088</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861270781278065</v>
+        <v>0.16861275948129531</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91241496424070634</v>
+        <v>0.91374987601495727</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.3004223080999024</v>
+        <v>1.3023258667630979</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3061555176455371</v>
+        <v>1.3080672803663771</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3641005935735606</v>
+        <v>1.3660970667495278</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.091697149860553</v>
+        <v>1.0932946148376705</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70764233436436463</v>
+        <v>0.7086777910425589</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5532948422403574</v>
+        <v>1.5555667796680086</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4963846596219137</v>
+        <v>1.4985734203244503</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2903008127779987</v>
+        <v>1.2921880462773399</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4255254986990373</v>
+        <v>1.4276107524775969</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89186998910116833</v>
+        <v>0.89317462701552608</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11849544990139041</v>
+        <v>0.11851489961283493</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.16888601403894837</v>
+        <v>0.16891386079936418</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16963058670721259</v>
+        <v>0.16965853182443283</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17715592124331955</v>
+        <v>0.17718509296362228</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14177885063124065</v>
+        <v>0.14180215497246051</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.1901601865501892E-2</v>
+        <v>9.191670441537729E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20172660288835811</v>
+        <v>0.20175963419818529</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19433567008076802</v>
+        <v>0.19436749939357331</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.16757153412701281</v>
+        <v>0.16759896838876004</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18513318164922563</v>
+        <v>0.18516352172212672</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11582727131184004</v>
+        <v>0.11584625512523036</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14259193896709624</v>
+        <v>0.14240699481798197</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13881228517308045</v>
+        <v>0.13863224329866658</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12303373044568112</v>
+        <v>0.12287415362279437</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.39501881735315175</v>
+        <v>0.39450647128654587</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14596662985461034</v>
+        <v>0.14577730867451358</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14355185104176693</v>
+        <v>0.14336566187050653</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12318371670734841</v>
+        <v>0.12302394534975133</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11922407939933187</v>
+        <v>0.11906944375808759</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1205309733214112E-2</v>
+        <v>5.1138895583106178E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4796812706812168E-2</v>
+        <v>3.4751680654014745E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3263317224901</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.351089633201</v>
+        <v>96404.42390893698</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17130.938950763582</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89414.690040396774</v>
+        <v>89414.03466666273</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0926782399999999</v>
+        <v>1.0942760599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.024928854850346</v>
+        <v>13.043893660857972</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7343359054767</v>
+        <v>7373.7399056769073</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2877543306759</v>
+        <v>6859.292935513402</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9867283940803</v>
+        <v>7519.9924086376759</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2897595622117</v>
+        <v>6507.2946748622398</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1399254593398</v>
+        <v>7669.1457183662314</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3552420465849</v>
+        <v>6173.3599051082156</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2514623459701</v>
+        <v>7821.257370150749</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5572385189098</v>
+        <v>5856.5616622862572</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3800154663504</v>
+        <v>7976.3860404479283</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0163546780395</v>
+        <v>5556.0205514309673</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5854250347156</v>
+        <v>8134.5915695172034</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.8983240905773</v>
+        <v>5270.9023054787804</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9287181502732</v>
+        <v>8295.9349845038814</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4116923645715</v>
+        <v>5000.4154694399194</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4721323381673</v>
+        <v>8460.4785229801164</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8056201644595</v>
+        <v>4743.8092034116735</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2791395573477</v>
+        <v>8628.285656952803</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3677989686639</v>
+        <v>4500.3711983344192</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4144706846273</v>
+        <v>8799.4211173476469</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4224737842251</v>
+        <v>4269.4256987047656</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9441404843492</v>
+        <v>8973.9509189788569</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3285673297764</v>
+        <v>4050.3316267571049</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9354730733285</v>
+        <v>9151.9423860140996</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4779004798002</v>
+        <v>3842.4808029065289</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4571278908443</v>
+        <v>9333.4641779445192</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2935040303159</v>
+        <v>3645.2962575132447</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5791261837512</v>
+        <v>9518.5863160698609</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2280170996851</v>
+        <v>3458.2306292821604</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3728780168931</v>
+        <v>9707.3802105089053</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7621677186521</v>
+        <v>3280.7646458517879</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9112098192436</v>
+        <v>9899.9186877456395</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4033313919363</v>
+        <v>3112.4056823547412</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.268392476408</v>
+        <v>10096.276018721766</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6841636300992</v>
+        <v>2952.6863939485715</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.520169980326</v>
+        <v>10296.52794748644</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1613026557661</v>
+        <v>2801.1634185210096</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.743788647198</v>
+        <v>10500.75172041421</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4141386830438</v>
+        <v>2657.4161459684542</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.018026914953</v>
+        <v>10709.026116002509</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0436463538344</v>
+        <v>2521.0455506314011</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.457812073029</v>
+        <v>98316.532075692099</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.986839707923</v>
+        <v>23145.004322340275</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.19583758974</v>
+        <v>110204.27908064592</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.19583758974</v>
+        <v>110204.27908064592</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.351089633201</v>
+        <v>96404.42390893698</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.97417662642</v>
+        <v>97922.048142271145</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.381584475239</v>
+        <v>99461.45671291578</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.05144248539</v>
+        <v>101023.12775053777</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.46934382778</v>
+        <v>102607.54684867477</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.351089633215</v>
+        <v>96404.423908936995</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.043487447227</v>
+        <v>99377.118552182757</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.81959009878</v>
+        <v>102492.89700834473</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.06852288912</v>
+        <v>105760.14840906096</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.64217476246</v>
+        <v>109187.72464996192</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.351089633215</v>
+        <v>96404.423908937009</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.53203296979</v>
+        <v>101173.60845468809</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.97510600825</v>
+        <v>106331.05542341602</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.6826900578</v>
+        <v>111913.76722437982</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.18722781559</v>
+        <v>117962.2763308929</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.351089633215</v>
+        <v>96404.423908937024</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.07973699761</v>
+        <v>102998.15753689327</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.31484908535</v>
+        <v>110332.3981889166</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.65075718908</v>
+        <v>118504.74027001776</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.97780332917</v>
+        <v>127626.0742059785</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.35108963323</v>
+        <v>96404.423908937024</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.60953685141</v>
+        <v>104688.68861369361</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.66678186248</v>
+        <v>114140.75299834332</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.62851890422</v>
+        <v>124956.72290525284</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.42342518925</v>
+        <v>137367.52718606754</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.351089633245</v>
+        <v>96404.423908937024</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.36623373732</v>
+        <v>106173.44643209476</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.75606275827</v>
+        <v>117578.84487620974</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.55673603732</v>
+        <v>130953.6556521829</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.83783102679</v>
+        <v>146703.94864419254</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.475001185829832</v>
+        <v>11.491698364961856</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.669263282800722</v>
+        <v>11.6862446777454</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.866334740198232</v>
+        <v>11.883604461199756</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.066276836373474</v>
+        <v>12.083839083329538</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.283488112820319</v>
+        <v>11.299905098108422</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.658620424061924</v>
+        <v>11.675586247936419</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.051808865475689</v>
+        <v>12.069349945018397</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.464112084086734</v>
+        <v>12.482256385236559</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.89664712434976</v>
+        <v>12.915424247341239</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.283488112820319</v>
+        <v>11.299905098108423</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.885324303917276</v>
+        <v>11.902621807663701</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.536156371678015</v>
+        <v>12.554406077464485</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.240653749385364</v>
+        <v>13.25993417242362</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.003931338574523</v>
+        <v>14.024328477450158</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.283488112820319</v>
+        <v>11.299905098108425</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.115569046927295</v>
+        <v>12.133203411017368</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.041096548800677</v>
+        <v>13.060085009007176</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.072386318204368</v>
+        <v>14.092883610367592</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.223431915429719</v>
+        <v>15.245613248715305</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.283488112820322</v>
+        <v>11.299905098108425</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.328901698333913</v>
+        <v>12.34684817947528</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.521683058058978</v>
+        <v>13.541374641970037</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.886579314294865</v>
+        <v>14.908267814252337</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.452731998293999</v>
+        <v>16.476711863189674</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.283488112820324</v>
+        <v>11.299905098108425</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.516267270279346</v>
+        <v>12.53448787724929</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.955545094758719</v>
+        <v>13.975871441978022</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.643348344315402</v>
+        <v>15.66614403774093</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.630920066910438</v>
+        <v>17.656623683812288</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.89664712434976</v>
+        <v>12.915424247341239</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.072386318204368</v>
+        <v>14.092883610367592</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.041096548800677</v>
+        <v>13.060085009007176</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.115569046927295</v>
+        <v>12.133203411017368</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.283488112820319</v>
+        <v>11.299905098108422</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2987.8735537726716</v>
+        <v>2992.2427119996059</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39838.314050302288</v>
+        <v>39896.569493328083</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2595023187695666</v>
+        <v>5.2671932726911681</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3047.1357451924032</v>
+        <v>3051.5915623379724</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2834.5448792487473</v>
+        <v>2838.689825430672</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3107.5733569465847</v>
+        <v>3112.1175518242967</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2689.0845706406358</v>
+        <v>2693.0168106646161</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3169.2097026004003</v>
+        <v>3173.8440281151175</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2551.0888471005778</v>
+        <v>2554.8192964061977</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3232.0685581258058</v>
+        <v>3236.7948019499195</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2420.1746485981676</v>
+        <v>2423.7136624775162</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3296.1741710730134</v>
+        <v>3300.9941563360335</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2295.9785725903962</v>
+        <v>2299.335974933153</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3361.5512699238861</v>
+        <v>3366.4668559157049</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2178.155865258585</v>
+        <v>2181.34097582199</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3428.2250736308515</v>
+        <v>3433.2381565189557</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2066.3794645120024</v>
+        <v>2069.4011247914145</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3496.2213013450091</v>
+        <v>3501.3338149059218</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1960.3390921016548</v>
+        <v>1963.2056898735125</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3565.5661823371902</v>
+        <v>3570.7800987024148</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1859.7403923240643</v>
+        <v>1862.4598849293739</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3636.2864661157942</v>
+        <v>3641.6037965325581</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1764.3041149241719</v>
+        <v>1766.8840513571586</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3708.4094327453013</v>
+        <v>3713.8322283523848</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1673.7653399292074</v>
+        <v>1676.2128817924415</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3781.9629033694509</v>
+        <v>3787.4932559884073</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1587.8727422617505</v>
+        <v>1590.1946836459224</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3856.9752509431319</v>
+        <v>3862.6152938851974</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1506.3878940906332</v>
+        <v>1508.5906804341548</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3933.475411177139</v>
+        <v>3939.2273200661507</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1429.0846029830955</v>
+        <v>1431.1743489638866</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4011.4928937000027</v>
+        <v>4017.358887311636</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1355.7482840209784</v>
+        <v>1357.7307905300986</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4091.0577934412158</v>
+        <v>4097.0401345588671</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1286.1753641380253</v>
+        <v>1288.0561343822708</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4172.2008022402233</v>
+        <v>4178.3017985278711</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1220.1727170247955</v>
+        <v>1221.9569718029597</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4254.9532206856829</v>
+        <v>4261.1752255780602</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1157.5571270325622</v>
+        <v>1159.2498192277637</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4339.3469701895356</v>
+        <v>4345.6923837999566</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1098.1547805880414</v>
+        <v>1099.7606089163503</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4425.414605300567</v>
+        <v>4431.8858753467612</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1041.800783707193</v>
+        <v>1043.3242057607179</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40628.476602565381</v>
+        <v>40687.887497839634</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9564.4775779166121</v>
+        <v>9578.4636838022234</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45540.987660991887</v>
+        <v>45607.582105944399</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45540.987660991887</v>
+        <v>45607.582105944399</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39838.314050302288</v>
+        <v>39896.569493328083</v>
       </c>
       <c r="C51" s="123">
-        <v>40465.459448474328</v>
+        <v>40524.631964269967</v>
       </c>
       <c r="D51" s="123">
-        <v>41101.607040072369</v>
+        <v>41161.709792517373</v>
       </c>
       <c r="E51" s="123">
-        <v>41746.954408143501</v>
+        <v>41808.000850042459</v>
       </c>
       <c r="F51" s="123">
-        <v>42401.702220116342</v>
+        <v>42463.706097709197</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39838.314050302302</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C52" s="123">
-        <v>41066.755007380583</v>
+        <v>41126.806795806318</v>
       </c>
       <c r="D52" s="123">
-        <v>42354.324141811565</v>
+        <v>42416.258738587509</v>
       </c>
       <c r="E52" s="123">
-        <v>43704.488191398879</v>
+        <v>43768.397128875265</v>
       </c>
       <c r="F52" s="123">
-        <v>45120.905127258069</v>
+        <v>45186.885286824923</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39838.314050302295</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C53" s="123">
-        <v>41809.139288332342</v>
+        <v>41870.276662988646</v>
       </c>
       <c r="D53" s="123">
-        <v>43940.410693802725</v>
+        <v>44004.664620022348</v>
       </c>
       <c r="E53" s="123">
-        <v>46247.41919985642</v>
+        <v>46315.046657456289</v>
       </c>
       <c r="F53" s="123">
-        <v>48746.914508795693</v>
+        <v>48818.196970630423</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39838.314050302295</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C54" s="123">
-        <v>42563.118788336826</v>
+        <v>42625.35870487654</v>
       </c>
       <c r="D54" s="123">
-        <v>45593.931800525919</v>
+        <v>45660.603665529372</v>
       </c>
       <c r="E54" s="123">
-        <v>48971.08315056088</v>
+        <v>49042.693413504894</v>
       </c>
       <c r="F54" s="123">
-        <v>52740.397370432445</v>
+        <v>52817.519489864797</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39838.314050302288</v>
+        <v>39896.56949332809</v>
       </c>
       <c r="C55" s="123">
-        <v>43261.716479382449</v>
+        <v>43324.977953158173</v>
       </c>
       <c r="D55" s="123">
-        <v>47167.702264174281</v>
+        <v>47236.675448843649</v>
       </c>
       <c r="E55" s="123">
-        <v>51637.310487932729</v>
+        <v>51712.819566839426</v>
       </c>
       <c r="F55" s="123">
-        <v>56765.97054841878</v>
+        <v>56848.979251018784</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39838.314050302295</v>
+        <v>39896.569493328097</v>
       </c>
       <c r="C56" s="123">
-        <v>43875.28010913849</v>
+        <v>43939.438795106253</v>
       </c>
       <c r="D56" s="123">
-        <v>48588.464698205469</v>
+        <v>48659.51545937379</v>
       </c>
       <c r="E56" s="123">
-        <v>54115.492301833852</v>
+        <v>54194.625218317735</v>
       </c>
       <c r="F56" s="123">
-        <v>60624.167870422418</v>
+        <v>60712.818402995217</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062012</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1064487329809971</v>
+        <v>5.1213939404386917</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1867259646590673</v>
+        <v>5.2019061220681468</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2681641416854674</v>
+        <v>5.2835826468219551</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3507885868404284</v>
+        <v>5.366448911593344</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.027307513097699</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1823278898415213</v>
+        <v>5.1974951752638239</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3448098155320602</v>
+        <v>5.3604526420230272</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5151907674426797</v>
+        <v>5.5313322533359637</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6939323551095828</v>
+        <v>5.7105969697462831</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0273075130976981</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2760114244540031</v>
+        <v>5.2914528964849188</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5449624833678586</v>
+        <v>5.5611911030980092</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8360902951678169</v>
+        <v>5.8531709680118977</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1515085513148167</v>
+        <v>6.1695123688961822</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0273075130976981</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3711581919680116</v>
+        <v>5.3868781330982518</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.753624904985374</v>
+        <v>5.7704642237243196</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1797970149160646</v>
+        <v>6.1978836252520964</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6554572467436328</v>
+        <v>6.674935987152006</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0273075130976963</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4593161751696062</v>
+        <v>5.4752941310997381</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9522233714214954</v>
+        <v>5.9696439346684889</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5162556488801249</v>
+        <v>6.5353269835027321</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1634555083332616</v>
+        <v>7.1844210235639432</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0273075130976981</v>
+        <v>5.042021095406203</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5367434739689783</v>
+        <v>5.5529480388604391</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1315133295736732</v>
+        <v>6.1494586264975863</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8289842958835152</v>
+        <v>6.848970903477972</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6503321457188536</v>
+        <v>7.6727226184361417</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6939323551095828</v>
+        <v>5.7105969697462831</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1797970149160646</v>
+        <v>6.1978836252520964</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.753624904985374</v>
+        <v>5.7704642237243196</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3711581919680116</v>
+        <v>5.3868781330982518</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.027307513097699</v>
+        <v>5.0420210954062021</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.7</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.31009865212657</v>
+        <v>13.329480415733649</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.045429015536</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3263317224901</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.005259008155317E-2</v>
+        <v>6.0052771628752E-2</v>
       </c>
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.041096548800677</v>
+        <v>13.060085009007176</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.115569046927295</v>
+        <v>12.133203411017368</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.072386318204368</v>
+        <v>14.092883610367592</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.062249002306739</v>
+        <v>13.081268409681297</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.283488112820319</v>
+        <v>11.299905098108422</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.89664712434976</v>
+        <v>12.915424247341239</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.965030863934569</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.024928854850346</v>
+        <v>13.043893660857972</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8032598840628747E-2</v>
+        <v>-6.8040113935075849E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58519345475023921</v>
+        <v>0.58604918132338757</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2695344668737762</v>
+        <v>5.2772069444640133</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8547279216240158</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.548421597829714</v>
+        <v>0.5484213143271619</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22786042821432195</v>
+        <v>0.22792724483207127</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67357232255078392</v>
+        <v>0.67455728526809577</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6380958023344991</v>
+        <v>6.6477609144246523</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3116681248852835</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604699428641613</v>
+        <v>0.43604666796787828</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.8973576651939813</v>
+        <v>0.89866986852348141</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.436338627942352</v>
+        <v>10.45153400710732</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.333696293136333</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582573754885507</v>
+        <v>0.12582530281537296</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83251162445275484</v>
+        <v>0.83372900361808255</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2928206174827874</v>
+        <v>9.3063510267411278</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.125332241935542</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261899817095931</v>
+        <v>0.22261862186231296</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>66672.773151599991</v>
+        <v>66759.36116868</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0926782399999999</v>
+        <v>1.0942760599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.965030863934569</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22786042821432195</v>
+        <v>0.22792724483207127</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8547279216240158</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3116681248852835</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.333696293136333</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.125332241935542</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61061049236417</v>
+        <v>279.61789242274239</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38938950763577</v>
+        <v>-523.38210757725756</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7294672116313</v>
+        <v>-4449.731287694226</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,7 +21380,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>500</v>
       </c>
       <c r="C61" s="374"/>
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.045429015536</v>
+        <v>10305.060899807031</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3263317224901</v>
+        <v>7230.3317931702732</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11849544990139041</v>
+        <v>0.11851489961283493</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4813998466493497E-2</v>
+        <v>4.4821320330479884E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41324186719811112</v>
+        <v>0.41384583689866911</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035929384641779</v>
+        <v>0.20035937581782973</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114139054444235</v>
+        <v>0.19114156469642632</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688901585326698E-2</v>
+        <v>9.7688941552013742E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780051051696037E-2</v>
+        <v>9.0780133762855292E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.16553285654275</v>
+        <v>12.18333168019943</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0638344523410583</v>
+        <v>3.0683146879542789</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.938950763582</v>
+        <v>17130.210757725759</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1618007726142277</v>
+        <v>2.1648699400997713</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9988936004399837E-2</v>
+        <v>2.0018165763497582E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.283488112820317</v>
+        <v>11.29990509810842</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1909989145357152</v>
+        <v>-3.1956651023474385</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.9 HKD</v>
+        <v>12.92 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.07 HKD</v>
+        <v>14.09 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.04 HKD</v>
+        <v>13.06 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
+        <v>12.13 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.28 HKD</v>
+        <v>11.3 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.965030863934569</v>
+        <v>12.98390803598565</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34506778819199996</v>
+        <v>0.34557237974799992</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58519345475023921</v>
+        <v>0.58604918132338757</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2695344668737762</v>
+        <v>5.2772069444640133</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8547279216240158</v>
+        <v>5.8632561257874007</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.548421597829714</v>
+        <v>0.5484213143271619</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67357232255078392</v>
+        <v>0.67455728526809577</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6380958023344991</v>
+        <v>6.6477609144246523</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3116681248852835</v>
+        <v>7.3223181996927478</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604699428641613</v>
+        <v>0.43604666796787828</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.8973576651939813</v>
+        <v>0.89866986852348141</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.436338627942352</v>
+        <v>10.45153400710732</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.333696293136333</v>
+        <v>11.3502038756308</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582573754885507</v>
+        <v>0.12582530281537296</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83251162445275484</v>
+        <v>0.83372900361808255</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2928206174827874</v>
+        <v>9.3063510267411278</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.125332241935542</v>
+        <v>10.14008003035921</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261899817095931</v>
+        <v>0.22261862186231296</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,15 +22467,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22488,12 +22485,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE669085-2A37-4ADB-8E15-9C2B0C908826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98923B54-5D11-4593-842C-B054CC1CD378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4760,29 +4760,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>66759.36116868</v>
+        <v>64508.072724599995</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0942760599999999</v>
+        <v>1.0862193599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.98390803598565</v>
+        <v>12.888721099904831</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22792724483207127</v>
+        <v>0.23940266373813213</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8632561257874007</v>
+        <v>5.8202533102484413</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3223181996927478</v>
+        <v>7.2686160033806493</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.3502038756308</v>
+        <v>11.266965612474275</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.14008003035921</v>
+        <v>10.065715404372868</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61789242274239</v>
+        <v>279.58117468953202</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38210757725756</v>
+        <v>-523.41882531046804</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.731287694226</v>
+        <v>-4449.7221082609231</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,7 +5752,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060899807031</v>
+        <v>10304.982891316802</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3042548703652</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11851489961283493</v>
+        <v>0.12174749808229159</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4821320330479884E-2</v>
+        <v>4.6044036763489921E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41384583689866911</v>
+        <v>0.41080042656194116</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035937581782973</v>
+        <v>0.20035896249275276</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114156469642632</v>
+        <v>0.19114068656854621</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688740027682172E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0779716707744637E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.18333168019943</v>
+        <v>12.093584809507629</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0683146879542789</v>
+        <v>3.0457239616740734</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.210757725759</v>
+        <v>17133.882531046798</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1648699400997713</v>
+        <v>2.1493915145318203</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0018165763497582E-2</v>
+        <v>1.9870780325761905E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1956651023474385</v>
+        <v>-3.1721367478752747</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.92 HKD</v>
+        <v>12.82 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.09 HKD</v>
+        <v>13.99 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.06 HKD</v>
+        <v>12.96 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.13 HKD</v>
+        <v>12.04 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.3 HKD</v>
+        <v>11.22 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.98390803598565</v>
+        <v>12.888721099904831</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58604918132338757</v>
+        <v>0.58173434468228624</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2772069444640133</v>
+        <v>5.238518965566155</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8632561257874007</v>
+        <v>5.8202533102484413</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5484213143271619</v>
+        <v>0.54842274379795386</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67455728526809577</v>
+        <v>0.66959080022937589</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6477609144246523</v>
+        <v>6.5990252031512737</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3223181996927478</v>
+        <v>7.2686160033806493</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604666796787828</v>
+        <v>0.43604831332456095</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89866986852348141</v>
+        <v>0.89205333564444422</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.45153400710732</v>
+        <v>10.37491227682983</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.3502038756308</v>
+        <v>11.266965612474275</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582530281537296</v>
+        <v>0.12582749481967859</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83372900361808255</v>
+        <v>0.8275906033469026</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.3063510267411278</v>
+        <v>9.2381248010259664</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.14008003035921</v>
+        <v>10.065715404372868</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261862186231296</v>
+        <v>0.22262051927835047</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,6 +6839,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6855,17 +6866,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.31055554582799999</v>
+        <v>0.30826905436799995</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27783669163399999</v>
+        <v>0.27579109550399999</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.227390565268</v>
+        <v>0.22571638300799998</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.31055554582799999</v>
+        <v>0.30826905436799995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27783669163399999</v>
+        <v>0.27579109550399999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.227390565268</v>
+        <v>0.22571638300799998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.2333553114021711</v>
+        <v>8.1727365368880207</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1956651023474385</v>
+        <v>-3.1721367478752747</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17130.210757725759</v>
+        <v>17133.882531046798</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.936892666634</v>
+        <v>-14496.101006006114</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.89462113712</v>
+        <v>-13979.058734476601</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1102356379278002</v>
+        <v>3.1106295397167281</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2252585561890528</v>
+        <v>3.2256821332890921</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27961.789242274241</v>
+        <v>27958.117468953202</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26567.928460739997</v>
+        <v>-26372.319841439996</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0683146879542789</v>
+        <v>-3.0457239616740734</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18745.179534933755</v>
+        <v>18611.154917188829</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1648699400997709</v>
+        <v>2.1493915145318199</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>173.33332790399999</v>
+        <v>172.05714662399998</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.0018165763497582E-2</v>
+        <v>1.9870780325761905E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7649.4155979022416</v>
+        <v>-7589.1077776271668</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88342658209101044</v>
+        <v>-0.87646166681649162</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.38210757725756</v>
+        <v>-523.41882531046804</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.93910019296732</v>
+        <v>-209.01710868319958</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.50836865123335</v>
+        <v>-420.57921143463841</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.32952720851665</v>
+        <v>-366.39947427856828</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.96428392701432</v>
+        <v>-455.00735959646403</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.36524328150233</v>
+        <v>-503.39211468210419</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09114139130793</v>
+        <v>-818.11345279665625</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.06892960013079</v>
+        <v>-947.09295100369923</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1577767648394</v>
+        <v>-1014.1749581755273</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.58324213710398</v>
+        <v>-468.61166067895266</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.47630223738793</v>
+        <v>-437.49462364688924</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.925150776904</v>
+        <v>17798.888433043692</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.060899807031</v>
+        <v>16979.982891316802</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.491631348767</v>
+        <v>17261.420788565363</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.670472791484</v>
+        <v>16973.600525721431</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.035716072985</v>
+        <v>14669.992640403536</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.634756718498</v>
+        <v>11589.607885317895</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.908858608691</v>
+        <v>20402.886547203343</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.931070399871</v>
+        <v>19208.907048996301</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.842223235162</v>
+        <v>16944.825041824472</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.416757862895</v>
+        <v>17752.388339321049</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.523697762612</v>
+        <v>11857.50537635311</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.731287694226</v>
+        <v>-4449.7221082609231</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3042548703652</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.060899807031</v>
+        <v>10304.982891316802</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.491631348767</v>
+        <v>10350.420788565363</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.670472791484</v>
+        <v>10809.600525721431</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0357160729855</v>
+        <v>8650.9926404035359</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6347567184985</v>
+        <v>5607.6078853178951</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.908858608691</v>
+        <v>12308.886547203343</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.931070399871</v>
+        <v>11857.907048996301</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.842223235162</v>
+        <v>10224.825041824472</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.416757862895</v>
+        <v>11296.388339321049</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5236977626118</v>
+        <v>7067.5053763531105</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3042548703652</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.060899807031</v>
+        <v>10304.982891316802</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.491631348767</v>
+        <v>10350.420788565363</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.670472791484</v>
+        <v>10809.600525721431</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0357160729855</v>
+        <v>8650.9926404035359</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6347567184985</v>
+        <v>5607.6078853178951</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.908858608691</v>
+        <v>12308.886547203343</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.931070399871</v>
+        <v>11857.907048996301</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.842223235162</v>
+        <v>10224.825041824472</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.416757862895</v>
+        <v>11296.388339321049</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5236977626118</v>
+        <v>7067.5053763531105</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421606485731437</v>
+        <v>0.18421691117248368</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337842124476803</v>
+        <v>0.19337921489123427</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787922182841446</v>
+        <v>0.18787999606609437</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391229934389186</v>
+        <v>0.18391283936770841</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957488294953873</v>
+        <v>0.19957534567931209</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967741012973447</v>
+        <v>0.19967762848529047</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636699128003474</v>
+        <v>0.19636723684375856</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838199338074748</v>
+        <v>0.20838220467219487</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2084786567643391</v>
+        <v>0.20847899050306304</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986040816362973</v>
+        <v>0.2198607478769542</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.61789242274239</v>
+        <v>279.58117468953202</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.06089980703268</v>
+        <v>593.98289131680042</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.49163134876665</v>
+        <v>539.42078856536159</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.67047279148335</v>
+        <v>532.60052572143172</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.03571607298568</v>
+        <v>327.99264040353597</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.6347567184977</v>
+        <v>204.60788531789578</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90885860869201</v>
+        <v>169.88654720334378</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.93107039986916</v>
+        <v>182.90704899630077</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.84222323516065</v>
+        <v>130.82504182447275</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.41675786289605</v>
+        <v>216.38833932104734</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.52369776261207</v>
+        <v>139.50537635311076</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.38210757725756</v>
+        <v>-523.41882531046804</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.93910019296732</v>
+        <v>-209.01710868319958</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.50836865123335</v>
+        <v>-420.57921143463841</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.32952720851665</v>
+        <v>-366.39947427856828</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.96428392701432</v>
+        <v>-455.00735959646403</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.36524328150233</v>
+        <v>-503.39211468210419</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09114139130793</v>
+        <v>-818.11345279665625</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.06892960013079</v>
+        <v>-947.09295100369923</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1577767648394</v>
+        <v>-1014.1749581755273</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.58324213710398</v>
+        <v>-468.61166067895266</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.47630223738793</v>
+        <v>-437.49462364688924</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8725691963625553E-3</v>
+        <v>2.8727707206941165E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1170466098872327E-3</v>
+        <v>1.1174636649979126E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3710114722601877E-3</v>
+        <v>2.3714109150886837E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1305164891390026E-3</v>
+        <v>2.1309232905979171E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2838263111219608E-3</v>
+        <v>3.2841372212784399E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074200078855326E-3</v>
+        <v>4.6076659681110856E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2197465550405335E-3</v>
+        <v>7.2199434557081383E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9795100938667941E-3</v>
+        <v>8.9797378496605604E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.14327979704286E-2</v>
+        <v>1.1432991659814751E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.722664836436628E-3</v>
+        <v>5.7230119034580576E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0505902889877475E-2</v>
+        <v>1.0506342874736179E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688740027682172E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0779716707744637E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327895797945166E-2</v>
+        <v>9.7327496355116672E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716270836967171E-2</v>
+        <v>9.871586403550825E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588490343401867</v>
+        <v>0.1058845925238622</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608264232564002</v>
+        <v>0.10608239636541446</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005797091780018</v>
+        <v>0.18005777401713258</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212696568123515</v>
+        <v>0.18212673792544137</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1910225038129908</v>
+        <v>0.19102231012360463</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680487479376293</v>
+        <v>0.21680452772674152</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475597842901496</v>
+        <v>0.28475553844415624</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422235388003435E-2</v>
+        <v>2.4422185006920543E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.968348953441423E-2</v>
+        <v>3.9683338391165564E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093725071945036E-2</v>
+        <v>5.5093308016834375E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360632584259539E-2</v>
+        <v>5.8360233141431052E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867389805933815E-2</v>
+        <v>6.2866983004474894E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2441162320894611E-2</v>
+        <v>6.244085141073813E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327994770926567E-2</v>
+        <v>5.1327748810700999E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862750839364142</v>
+        <v>0.10862731149297382</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242942135583456</v>
+        <v>0.11242919360004078</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1152666361152026</v>
+        <v>0.11526644242581642</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795970735769639</v>
+        <v>0.13795936029067499</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972511941986532</v>
+        <v>0.1697246794350066</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.968348953441423E-2</v>
+        <v>3.9683338391165564E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093725071945036E-2</v>
+        <v>5.5093308016834375E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360632584259539E-2</v>
+        <v>5.8360233141431052E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867389805933815E-2</v>
+        <v>6.2866983004474894E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2441162320894611E-2</v>
+        <v>6.244085141073813E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327994770926567E-2</v>
+        <v>5.1327748810700999E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862750839364142</v>
+        <v>0.10862731149297382</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242942135583456</v>
+        <v>0.11242919360004078</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1152666361152026</v>
+        <v>0.11526644242581642</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795970735769639</v>
+        <v>0.13795936029067499</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972511941986532</v>
+        <v>0.1697246794350066</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.31055554582799999</v>
+        <v>0.30826905436799995</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27783669163399999</v>
+        <v>0.27579109550399999</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.227390565268</v>
+        <v>0.22571638300799998</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2992.2427119996059</v>
+        <v>2970.2120720733642</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2992.2427119996059</v>
+        <v>2970.2120720733642</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2689.0388906443586</v>
+        <v>2669.240614485183</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2405.7328200655484</v>
+        <v>2388.020408801226</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1968.929814925644</v>
+        <v>1954.4334027132522</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41384583689866911</v>
+        <v>0.41080042656194116</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.29036632981525007</v>
+        <v>0.28823066504808348</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25979818026227913</v>
+        <v>0.25788715927704398</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22255376110871333</v>
+        <v>0.22091661973251783</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22759469265252458</v>
+        <v>0.225920132400215</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4821320330479884E-2</v>
+        <v>4.6044036763489921E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4821320330479884E-2</v>
+        <v>4.6044036763489921E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.027957792840467E-2</v>
+        <v>4.1378396559463078E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.6035887371465625E-2</v>
+        <v>3.7018938993825502E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.9492939723476004E-2</v>
+        <v>3.0297501074899327E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225047943095456E-2</v>
+        <v>4.8227701227288033E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.630396361752573E-2</v>
+        <v>-1.6304445659247047E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956919189556219E-2</v>
+        <v>1.6956936296914416E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.1570299351210549</v>
+        <v>0.15702856448430569</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578930432374337</v>
+        <v>0.26578852240445294</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196164639884516</v>
+        <v>-0.43196234226443309</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157429990921775E-2</v>
+        <v>6.2157596742050458E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361522151325422</v>
+        <v>0.13361495333138329</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490963041414756E-2</v>
+        <v>-4.549040287203765E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714368786904362</v>
+        <v>0.49714360448225792</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.214354783699952</v>
+        <v>1.2143639763385305</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920111733013887</v>
+        <v>1.3920207008315306</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756201021509935</v>
+        <v>1.3756290035526155</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871171491876846</v>
+        <v>1.3871240560251183</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848591654344512</v>
+        <v>2.9848734687431024</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067770819304068</v>
+        <v>1.3067794506282628</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351576087738316</v>
+        <v>1.435160516074417</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994821543364572</v>
+        <v>1.2994843379373</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941589034450128</v>
+        <v>1.394162410757434</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917517042401404</v>
+        <v>1.891756608312483</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688740027682172E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0779716707744637E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327895797945166E-2</v>
+        <v>9.7327496355116672E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716270836967171E-2</v>
+        <v>9.871586403550825E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588490343401867</v>
+        <v>0.1058845925238622</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608264232564002</v>
+        <v>0.10608239636541446</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005797091780018</v>
+        <v>0.18005777401713258</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212696568123515</v>
+        <v>0.18212673792544137</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1910225038129908</v>
+        <v>0.19102231012360463</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680487479376293</v>
+        <v>0.21680452772674152</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475597842901496</v>
+        <v>0.28475553844415624</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035937581782973</v>
+        <v>0.20035896249275276</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114156469642632</v>
+        <v>0.19114068656854621</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122275545677776</v>
+        <v>0.20122192961968413</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032527660766132</v>
+        <v>0.21032440987486595</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338046843665369</v>
+        <v>0.1933799006130098</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371116300911957</v>
+        <v>0.13711131218803335</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766128507430308</v>
+        <v>0.25766100331127539</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.2740452973207389</v>
+        <v>0.27404495461803152</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820711959215487</v>
+        <v>0.25820685778018243</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774681021768088</v>
+        <v>0.26774638160145164</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861275948129531</v>
+        <v>0.16861249895274885</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91374987601495727</v>
+        <v>0.90701886071307225</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.3023258667630979</v>
+        <v>1.2927275965536045</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3080672803663771</v>
+        <v>1.298427637429177</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3660970667495278</v>
+        <v>1.3560302869687562</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0932946148376705</v>
+        <v>1.0852397371037981</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.7086777910425589</v>
+        <v>0.70345671996314485</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5555667796680086</v>
+        <v>1.5441109888522953</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4985734203244503</v>
+        <v>1.4875370334211435</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2921880462773399</v>
+        <v>1.2826720471934556</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4276107524775969</v>
+        <v>1.4170962826082505</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89317462701552608</v>
+        <v>0.88659625495362293</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11851489961283493</v>
+        <v>0.12174749808229159</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.16891386079936418</v>
+        <v>0.17352048275887308</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.16965853182443283</v>
+        <v>0.17428558891666804</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.17718509296362228</v>
+        <v>0.18201748818372565</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14180215497246051</v>
+        <v>0.14566976336963733</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.191670441537729E-2</v>
+        <v>9.442372080042212E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20175963419818529</v>
+        <v>0.20726321998017386</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19436749939357331</v>
+        <v>0.19966940045921389</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.16759896838876004</v>
+        <v>0.17217074458972559</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.18516352172212672</v>
+        <v>0.19021426612191281</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11584625512523036</v>
+        <v>0.11900620871860711</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14240699481798197</v>
+        <v>0.14737690336196524</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13863224329866658</v>
+        <v>0.14347041554801601</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12287415362279437</v>
+        <v>0.12716237911835498</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.39450647128654587</v>
+        <v>0.40827448236500247</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14577730867451358</v>
+        <v>0.15086483891013419</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14336566187050653</v>
+        <v>0.1483690272512222</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12302394534975133</v>
+        <v>0.12731739847605139</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11906944375808759</v>
+        <v>0.12322488743286648</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1138895583106178E-2</v>
+        <v>5.2923608717550155E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4751680654014745E-2</v>
+        <v>3.5964490985564257E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3042548703652</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.42390893698</v>
+        <v>96404.056731604869</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17130.210757725759</v>
+        <v>17133.882531046798</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89414.03466666273</v>
+        <v>89417.339262651658</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0942760599999999</v>
+        <v>1.0862193599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.043893660857972</v>
+        <v>12.948264848756697</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7399056769073</v>
+        <v>7373.7118211758398</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.292935513402</v>
+        <v>6859.2668103961296</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9924086376759</v>
+        <v>7519.9637671019655</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2946748622398</v>
+        <v>6507.2698904073259</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1457183662314</v>
+        <v>7669.116508747521</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3599051082156</v>
+        <v>6173.3363925169033</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.257370150749</v>
+        <v>7821.2275811815452</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5616622862572</v>
+        <v>5856.5393562903364</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3860404479283</v>
+        <v>7976.3556606372576</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0205514309673</v>
+        <v>5555.9993901115959</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5915695172034</v>
+        <v>8134.5605871461757</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.9023054787804</v>
+        <v>5270.882230094604</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9349845038814</v>
+        <v>8295.9033876211724</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4154694399194</v>
+        <v>5000.3964242640131</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4785229801164</v>
+        <v>8460.4462993973557</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8092034116735</v>
+        <v>4743.791135576851</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.285656952803</v>
+        <v>8628.2527942398719</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3711983344192</v>
+        <v>4500.3540576864789</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4211173476469</v>
+        <v>8799.3876028278883</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4256987047656</v>
+        <v>4269.4094376632693</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9509189788569</v>
+        <v>8973.9167397241799</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3316267571049</v>
+        <v>4050.316200183297</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9423860140996</v>
+        <v>9151.9075288399945</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4808029065289</v>
+        <v>3842.4661679780415</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4641779445192</v>
+        <v>9333.4286294049689</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2962575132447</v>
+        <v>3645.2823736052214</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5863160698609</v>
+        <v>9518.5500624521628</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2306292821604</v>
+        <v>3458.2174578544946</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3802105089053</v>
+        <v>9707.3432378283705</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7646458517879</v>
+        <v>3280.7521503421312</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9186877456395</v>
+        <v>9899.8809817402052</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4056823547412</v>
+        <v>3112.3938280770167</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.276018721766</v>
+        <v>10096.237564846493</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6863939485715</v>
+        <v>2952.6751479966879</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.52794748644</v>
+        <v>10296.4887309079</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1634185210096</v>
+        <v>2801.1527496775157</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.75172041421</v>
+        <v>10500.711726004767</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4161459684542</v>
+        <v>2657.4060246178851</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.026116002509</v>
+        <v>10708.985328334482</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0455506314011</v>
+        <v>2521.0359486780685</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.532075692099</v>
+        <v>98316.157615677861</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23145.004322340275</v>
+        <v>23144.916169529501</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.27908064592</v>
+        <v>110203.85934354737</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.27908064592</v>
+        <v>110203.85934354737</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.42390893698</v>
+        <v>96404.056731604884</v>
       </c>
       <c r="C56" s="123">
-        <v>97922.048142271145</v>
+        <v>97921.675184735243</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.45671291578</v>
+        <v>99461.077892205663</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.12775053777</v>
+        <v>101022.74298186196</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.54684867477</v>
+        <v>102607.15604539233</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.423908936995</v>
+        <v>96404.056731604898</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.118552182757</v>
+        <v>99376.74005269297</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.89700834473</v>
+        <v>102492.50664173128</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.14840906096</v>
+        <v>105759.74559840598</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.72464996192</v>
+        <v>109187.30878463322</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.423908937009</v>
+        <v>96404.056731604884</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.60845468809</v>
+        <v>101173.22311287362</v>
       </c>
       <c r="D58" s="123">
-        <v>106331.05542341602</v>
+        <v>106330.65043833683</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.76722437982</v>
+        <v>111913.34097632176</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.2763308929</v>
+        <v>117961.82704576512</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.423908937024</v>
+        <v>96404.056731604898</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.15753689327</v>
+        <v>102997.7652458846</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.3981889166</v>
+        <v>110331.97796384839</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.74027001776</v>
+        <v>118504.28891879744</v>
       </c>
       <c r="F59" s="123">
-        <v>127626.0742059785</v>
+        <v>127625.58811416305</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.423908937024</v>
+        <v>96404.056731604884</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.68861369361</v>
+        <v>104688.2898839276</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.75299834332</v>
+        <v>114140.31826832294</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.72290525284</v>
+        <v>124956.24698024562</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.52718606754</v>
+        <v>137367.00399179797</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.423908937024</v>
+        <v>96404.056731604898</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.44643209476</v>
+        <v>106173.0420473039</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.84487620974</v>
+        <v>117578.39705146453</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.6556521829</v>
+        <v>130953.1568865458</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.94864419254</v>
+        <v>146703.38989012002</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691138</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.491698364961856</v>
+        <v>11.407503590295153</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.6862446777454</v>
+        <v>11.600616803887501</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.883604461199756</v>
+        <v>11.79652276309818</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.083839083329538</v>
+        <v>11.995282383872672</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108422</v>
+        <v>11.21712314269114</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.675586247936419</v>
+        <v>11.590036887965114</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.069349945018397</v>
+        <v>11.980899977845977</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.482256385236559</v>
+        <v>12.390764798425867</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.915424247341239</v>
+        <v>12.820741787858886</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108423</v>
+        <v>11.217123142691138</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.902621807663701</v>
+        <v>11.815400020842652</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.554406077464485</v>
+        <v>12.46238300967069</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.25993417242362</v>
+        <v>13.162713927012915</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.024328477450158</v>
+        <v>13.921477424420363</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108425</v>
+        <v>11.21712314269114</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.133203411017368</v>
+        <v>12.044283075894155</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.060085009007176</v>
+        <v>12.96433692552211</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.092883610367592</v>
+        <v>13.989527555191364</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.245613248715305</v>
+        <v>15.133765766028858</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108425</v>
+        <v>11.217123142691138</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.34684817947528</v>
+        <v>12.256354058961334</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.541374641970037</v>
+        <v>13.442081203274375</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.908267814252337</v>
+        <v>14.798905341239758</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.476711863189674</v>
+        <v>16.355795658493332</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.299905098108425</v>
+        <v>11.21712314269114</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.53448787724929</v>
+        <v>12.442611534192711</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.975871441978022</v>
+        <v>13.873377341168753</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.66614403774093</v>
+        <v>15.55119877167837</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.656623683812288</v>
+        <v>17.527015817723754</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.915424247341239</v>
+        <v>12.820741787858886</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.092883610367592</v>
+        <v>13.989527555191364</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.060085009007176</v>
+        <v>12.96433692552211</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.133203411017368</v>
+        <v>12.044283075894155</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.299905098108422</v>
+        <v>11.21712314269114</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2992.2427119996059</v>
+        <v>2970.2120720733642</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39896.569493328083</v>
+        <v>39602.82762764486</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2671932726911681</v>
+        <v>5.2284131169413559</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3051.5915623379724</v>
+        <v>3029.1239614838632</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2838.689825430672</v>
+        <v>2817.789731612896</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3112.1175518242967</v>
+        <v>3089.2043232558294</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2693.0168106646161</v>
+        <v>2673.1892467330058</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3173.8440281151175</v>
+        <v>3150.476333146707</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2554.8192964061977</v>
+        <v>2536.0092233562991</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3236.7948019499195</v>
+        <v>3212.9636265873987</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2423.7136624775162</v>
+        <v>2405.868865740867</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3300.9941563360335</v>
+        <v>3276.6903077995398</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2299.335974933153</v>
+        <v>2282.4069194357285</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3366.4668559157049</v>
+        <v>3341.6809590936041</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2181.34097582199</v>
+        <v>2165.2806684806192</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3433.2381565189557</v>
+        <v>3407.960650351431</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2069.4011247914145</v>
+        <v>2054.1649840664622</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3501.3338149059218</v>
+        <v>3475.5549486968307</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1963.2056898735125</v>
+        <v>1948.7514220157261</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3570.7800987024148</v>
+        <v>3544.4899283580007</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1862.4598849293739</v>
+        <v>1848.7473665773687</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3641.6037965325581</v>
+        <v>3614.7921807255534</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1766.8840513571586</v>
+        <v>1753.8752181596483</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3713.8322283523848</v>
+        <v>3686.4888246100377</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1676.2128817924415</v>
+        <v>1663.8716227460393</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3787.4932559884073</v>
+        <v>3759.6075167029107</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1590.1946836459224</v>
+        <v>1578.486740855207</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3862.6152938851974</v>
+        <v>3834.1764622449955</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1508.5906804341548</v>
+        <v>1497.4835540157505</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3939.2273200661507</v>
+        <v>3910.2244259065401</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1431.1743489638866</v>
+        <v>1420.6372068305782</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4017.358887311636</v>
+        <v>3987.7807428830702</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1357.7307905300986</v>
+        <v>1347.7343828045534</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4097.0401345588671</v>
+        <v>4066.8753302113255</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1288.0561343822708</v>
+        <v>1278.5727122027915</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4178.3017985278711</v>
+        <v>4147.5386983096341</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1221.9569718029597</v>
+        <v>1212.9602102958822</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4261.1752255780602</v>
+        <v>4229.8019627471867</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1159.2498192277637</v>
+        <v>1150.7147444326781</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4345.6923837999566</v>
+        <v>4313.6968562467364</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1099.7606089163503</v>
+        <v>1091.6635284612996</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4431.8858753467612</v>
+        <v>4399.255740925375</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1043.3242057607179</v>
+        <v>1035.6426430949386</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40687.887497839634</v>
+        <v>40388.31948645151</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9578.4636838022234</v>
+        <v>9507.9414351830892</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45607.582105944399</v>
+        <v>45271.79242710142</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45607.582105944399</v>
+        <v>45271.79242710142</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39896.569493328083</v>
+        <v>39602.82762764486</v>
       </c>
       <c r="C51" s="123">
-        <v>40524.631964269967</v>
+        <v>40226.26593554909</v>
       </c>
       <c r="D51" s="123">
-        <v>41161.709792517373</v>
+        <v>40858.653224428548</v>
       </c>
       <c r="E51" s="123">
-        <v>41808.000850042459</v>
+        <v>41500.185909406246</v>
       </c>
       <c r="F51" s="123">
-        <v>42463.706097709197</v>
+        <v>42151.063471754831</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39896.56949332809</v>
+        <v>39602.82762764486</v>
       </c>
       <c r="C52" s="123">
-        <v>41126.806795806318</v>
+        <v>40824.007203981411</v>
       </c>
       <c r="D52" s="123">
-        <v>42416.258738587509</v>
+        <v>42103.965447825802</v>
       </c>
       <c r="E52" s="123">
-        <v>43768.397128875265</v>
+        <v>43446.148604907561</v>
       </c>
       <c r="F52" s="123">
-        <v>45186.885286824923</v>
+        <v>44854.193023877713</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39896.56949332809</v>
+        <v>39602.827627644867</v>
       </c>
       <c r="C53" s="123">
-        <v>41870.276662988646</v>
+        <v>41562.003211414922</v>
       </c>
       <c r="D53" s="123">
-        <v>44004.664620022348</v>
+        <v>43680.676556677427</v>
       </c>
       <c r="E53" s="123">
-        <v>46315.046657456289</v>
+        <v>45974.048211044959</v>
       </c>
       <c r="F53" s="123">
-        <v>48818.196970630423</v>
+        <v>48458.768868426239</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39896.56949332809</v>
+        <v>39602.827627644867</v>
       </c>
       <c r="C54" s="123">
-        <v>42625.35870487654</v>
+        <v>42311.525897936073</v>
       </c>
       <c r="D54" s="123">
-        <v>45660.603665529372</v>
+        <v>45324.423610971615</v>
       </c>
       <c r="E54" s="123">
-        <v>49042.693413504894</v>
+        <v>48681.612437261509</v>
       </c>
       <c r="F54" s="123">
-        <v>52817.519489864797</v>
+        <v>52428.646037516781</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39896.56949332809</v>
+        <v>39602.827627644867</v>
       </c>
       <c r="C55" s="123">
-        <v>43324.977953158173</v>
+        <v>43005.994140357609</v>
       </c>
       <c r="D55" s="123">
-        <v>47236.675448843649</v>
+        <v>46888.89143254279</v>
       </c>
       <c r="E55" s="123">
-        <v>51712.819566839426</v>
+        <v>51332.079561064173</v>
       </c>
       <c r="F55" s="123">
-        <v>56848.979251018784</v>
+        <v>56430.423835366477</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39896.569493328097</v>
+        <v>39602.827627644874</v>
       </c>
       <c r="C56" s="123">
-        <v>43939.438795106253</v>
+        <v>43615.930962411352</v>
       </c>
       <c r="D56" s="123">
-        <v>48659.51545937379</v>
+        <v>48301.255663210919</v>
       </c>
       <c r="E56" s="123">
-        <v>54194.625218317735</v>
+        <v>53795.61270862582</v>
       </c>
       <c r="F56" s="123">
-        <v>60712.818402995217</v>
+        <v>60265.815144944034</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0420210954062012</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1213939404386917</v>
+        <v>5.046258167493531</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2019061220681468</v>
+        <v>5.1255891580120139</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2835826468219551</v>
+        <v>5.2060674096217872</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.366448911593344</v>
+        <v>5.287717946619237</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1974951752638239</v>
+        <v>5.1212429240381061</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3604526420230272</v>
+        <v>5.2818096480884851</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5313322533359637</v>
+        <v>5.4501822912154365</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.7105969697462831</v>
+        <v>5.6268170218863389</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>4.9680497984087477</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2914528964849188</v>
+        <v>5.2138221951555348</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5611911030980092</v>
+        <v>5.4796030829444131</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8531709680118977</v>
+        <v>5.7672993225231162</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1695123688961822</v>
+        <v>6.0789996909177244</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>4.9680497984087477</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3868781330982518</v>
+        <v>5.3078474518034939</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7704642237243196</v>
+        <v>5.6858059656906121</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1978836252520964</v>
+        <v>6.106954713666048</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.674935987152006</v>
+        <v>6.5770082587665613</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0420210954062021</v>
+        <v>4.9680497984087477</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4752941310997381</v>
+        <v>5.3949663021088998</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9696439346684889</v>
+        <v>5.8820635187787706</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5353269835027321</v>
+        <v>6.4394474534244868</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1844210235639432</v>
+        <v>7.0790186598624105</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.042021095406203</v>
+        <v>4.9680497984087486</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5529480388604391</v>
+        <v>5.4714809523842991</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1494586264975863</v>
+        <v>6.059240156200298</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.848970903477972</v>
+        <v>6.7484899155484159</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6727226184361417</v>
+        <v>7.5601564008722075</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.7105969697462831</v>
+        <v>5.6268170218863389</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1978836252520964</v>
+        <v>6.106954713666048</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7704642237243196</v>
+        <v>5.6858059656906121</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3868781330982518</v>
+        <v>5.3078474518034939</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0420210954062021</v>
+        <v>4.9680497984087468</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.71</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.329480415733649</v>
+        <v>13.231749173792831</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060899807031</v>
+        <v>10304.982891316802</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3042548703652</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052771628752E-2</v>
+        <v>6.0051856207635534E-2</v>
       </c>
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.060085009007176</v>
+        <v>12.96433692552211</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.133203411017368</v>
+        <v>12.044283075894155</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.092883610367592</v>
+        <v>13.989527555191364</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.081268409681297</v>
+        <v>12.985364281530369</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.299905098108422</v>
+        <v>11.21712314269114</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.915424247341239</v>
+        <v>12.820741787858886</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.98390803598565</v>
+        <v>12.888721099904831</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.043893660857972</v>
+        <v>12.948264848756697</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8040113935075849E-2</v>
+        <v>-6.8002221478976943E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58604918132338757</v>
+        <v>0.58173434468228624</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2772069444640133</v>
+        <v>5.238518965566155</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8632561257874007</v>
+        <v>5.8202533102484413</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.5484213143271619</v>
+        <v>0.54842274379795386</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22792724483207127</v>
+        <v>0.23940266373813213</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67455728526809577</v>
+        <v>0.66959080022937589</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6477609144246523</v>
+        <v>6.5990252031512737</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3223181996927478</v>
+        <v>7.2686160033806493</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604666796787828</v>
+        <v>0.43604831332456095</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89866986852348141</v>
+        <v>0.89205333564444422</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.45153400710732</v>
+        <v>10.37491227682983</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.3502038756308</v>
+        <v>11.266965612474275</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582530281537296</v>
+        <v>0.12582749481967859</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83372900361808255</v>
+        <v>0.8275906033469026</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.3063510267411278</v>
+        <v>9.2381248010259664</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.14008003035921</v>
+        <v>10.065715404372868</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261862186231296</v>
+        <v>0.22262051927835047</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>66759.36116868</v>
+        <v>64508.072724599995</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0942760599999999</v>
+        <v>1.0862193599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.98390803598565</v>
+        <v>12.888721099904831</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22792724483207127</v>
+        <v>0.23940266373813213</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8632561257874007</v>
+        <v>5.8202533102484413</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3223181996927478</v>
+        <v>7.2686160033806493</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.3502038756308</v>
+        <v>11.266965612474275</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.14008003035921</v>
+        <v>10.065715404372868</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.61789242274239</v>
+        <v>279.58117468953202</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.38210757725756</v>
+        <v>-523.41882531046804</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.731287694226</v>
+        <v>-4449.7221082609231</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,7 +21380,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>500</v>
       </c>
       <c r="C61" s="374"/>
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.060899807031</v>
+        <v>10304.982891316802</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3317931702732</v>
+        <v>7230.3042548703652</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.11851489961283493</v>
+        <v>0.12174749808229159</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4821320330479884E-2</v>
+        <v>4.6044036763489921E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41384583689866911</v>
+        <v>0.41080042656194116</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035937581782973</v>
+        <v>0.20035896249275276</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114156469642632</v>
+        <v>0.19114068656854621</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688941552013742E-2</v>
+        <v>9.7688740027682172E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780133762855292E-2</v>
+        <v>9.0779716707744637E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.18333168019943</v>
+        <v>12.093584809507629</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0683146879542789</v>
+        <v>3.0457239616740734</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.210757725759</v>
+        <v>17133.882531046798</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1648699400997713</v>
+        <v>2.1493915145318203</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0018165763497582E-2</v>
+        <v>1.9870780325761905E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.29990509810842</v>
+        <v>11.217123142691136</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1956651023474385</v>
+        <v>-3.1721367478752747</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.92 HKD</v>
+        <v>12.82 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.09 HKD</v>
+        <v>13.99 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.06 HKD</v>
+        <v>12.96 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.13 HKD</v>
+        <v>12.04 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.3 HKD</v>
+        <v>11.22 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.98390803598565</v>
+        <v>12.888721099904831</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34557237974799992</v>
+        <v>0.34302807388799994</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58604918132338757</v>
+        <v>0.58173434468228624</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2772069444640133</v>
+        <v>5.238518965566155</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8632561257874007</v>
+        <v>5.8202533102484413</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5484213143271619</v>
+        <v>0.54842274379795386</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67455728526809577</v>
+        <v>0.66959080022937589</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6477609144246523</v>
+        <v>6.5990252031512737</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3223181996927478</v>
+        <v>7.2686160033806493</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604666796787828</v>
+        <v>0.43604831332456095</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89866986852348141</v>
+        <v>0.89205333564444422</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.45153400710732</v>
+        <v>10.37491227682983</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.3502038756308</v>
+        <v>11.266965612474275</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582530281537296</v>
+        <v>0.12582749481967859</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83372900361808255</v>
+        <v>0.8275906033469026</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.3063510267411278</v>
+        <v>9.2381248010259664</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.14008003035921</v>
+        <v>10.065715404372868</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261862186231296</v>
+        <v>0.22262051927835047</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,12 +22467,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22485,15 +22488,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98923B54-5D11-4593-842C-B054CC1CD378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A8216D-0322-4665-A811-1C5251798377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4760,29 +4760,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.45</v>
+        <v>7.3</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>64508.072724599995</v>
+        <v>63209.252468400002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0862193599999999</v>
+        <v>1.0897717599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.888721099904831</v>
+        <v>12.930692140739255</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23940266373813213</v>
+        <v>0.24954400255547804</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8202533102484413</v>
+        <v>5.8392146276413683</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2686160033806493</v>
+        <v>7.2922950234277151</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.266965612474275</v>
+        <v>11.303668039799444</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.065715404372868</v>
+        <v>10.098505157895211</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.58117468953202</v>
+        <v>279.59736445400836</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.41882531046804</v>
+        <v>-523.40263554599164</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7221082609231</v>
+        <v>-4449.7261557020429</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,7 +5752,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10304.982891316802</v>
+        <v>10305.017287206025</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3042548703652</v>
+        <v>7230.3163971937247</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12174749808229159</v>
+        <v>0.12465571601983087</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.6044036763489921E-2</v>
+        <v>4.7143824905205467E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41080042656194116</v>
+        <v>0.41214322680481363</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035896249275276</v>
+        <v>0.20035914473808938</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114068656854621</v>
+        <v>0.19114107375703299</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688740027682172E-2</v>
+        <v>9.7688828884786888E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779716707744637E-2</v>
+        <v>9.0779900597746141E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.093584809507629</v>
+        <v>12.133156359263538</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0457239616740734</v>
+        <v>3.0556847764043975</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17133.882531046798</v>
+        <v>17132.263554599165</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1493915145318203</v>
+        <v>2.156217180655569</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9870780325761905E-2</v>
+        <v>1.9935766241709157E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1721367478752747</v>
+        <v>-3.1825109862640586</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.82 HKD</v>
+        <v>12.86 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>13.99 HKD</v>
+        <v>14.04 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>12.96 HKD</v>
+        <v>13.01 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.04 HKD</v>
+        <v>12.08 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.22 HKD</v>
+        <v>11.25 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.888721099904831</v>
+        <v>12.930692140739255</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58173434468228624</v>
+        <v>0.58363686378860125</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.238518965566155</v>
+        <v>5.2555777638527674</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8202533102484413</v>
+        <v>5.8392146276413683</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842274379795386</v>
+        <v>0.54842211351978432</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.66959080022937589</v>
+        <v>0.67178064736921583</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.5990252031512737</v>
+        <v>6.620514376058499</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2686160033806493</v>
+        <v>7.2922950234277151</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604831332456095</v>
+        <v>0.43604758785860243</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89205333564444422</v>
+        <v>0.89497073003662608</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.37491227682983</v>
+        <v>10.408697309762818</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.266965612474275</v>
+        <v>11.303668039799444</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582749481967859</v>
+        <v>0.12582652832741514</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.8275906033469026</v>
+        <v>0.83029717714552231</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2381248010259664</v>
+        <v>9.268207980749688</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.065715404372868</v>
+        <v>10.098505157895211</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22262051927835047</v>
+        <v>0.2226196826750263</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,17 +6839,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6866,6 +6855,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.30826905436799995</v>
+        <v>0.30927722548799996</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27579109550399999</v>
+        <v>0.27669304986400001</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22571638300799998</v>
+        <v>0.22645457172799999</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.30826905436799995</v>
+        <v>0.30927722548799996</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27579109550399999</v>
+        <v>0.27669304986400001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22571638300799998</v>
+        <v>0.22645457172799999</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.1727365368880207</v>
+        <v>8.1994648666736722</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1721367478752747</v>
+        <v>-3.1825109862640586</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17133.882531046798</v>
+        <v>17132.263554599165</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14496.101006006114</v>
+        <v>-14496.910494229931</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13979.058734476601</v>
+        <v>-13979.868222700417</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1106295397167281</v>
+        <v>3.110455846295495</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2256821332890921</v>
+        <v>3.2254953538674926</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27958.117468953202</v>
+        <v>27959.736445400835</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26372.319841439996</v>
+        <v>-26458.568561039996</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0457239616740734</v>
+        <v>-3.0556847764043975</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18611.154917188829</v>
+        <v>18670.257006679385</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1493915145318199</v>
+        <v>2.156217180655569</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>172.05714662399998</v>
+        <v>172.61984678399998</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9870780325761905E-2</v>
+        <v>1.9935766241709157E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7589.1077776271668</v>
+        <v>-7615.6917075766105</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.87646166681649162</v>
+        <v>-0.87953182950711939</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.41882531046804</v>
+        <v>-523.40263554599164</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-209.01710868319958</v>
+        <v>-208.98271279397682</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.57921143463841</v>
+        <v>-420.54797508430045</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.39947427856828</v>
+        <v>-366.36863287059089</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-455.00735959646403</v>
+        <v>-454.98836645930453</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.39211468210419</v>
+        <v>-503.38026641128636</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.11345279665625</v>
+        <v>-818.10361514149236</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.09295100369923</v>
+        <v>-947.08235936766505</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1749581755273</v>
+        <v>-1014.167382462974</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.61166067895266</v>
+        <v>-468.59913023496648</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.49462364688924</v>
+        <v>-437.48654528042255</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.888433043692</v>
+        <v>17798.904622808172</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16979.982891316802</v>
+        <v>16980.017287206025</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.420788565363</v>
+        <v>17261.452024915699</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.600525721431</v>
+        <v>16973.631367129408</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14669.992640403536</v>
+        <v>14670.011633540695</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.607885317895</v>
+        <v>11589.619733588714</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.886547203343</v>
+        <v>20402.896384858508</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.907048996301</v>
+        <v>19208.917640632335</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.825041824472</v>
+        <v>16944.832617537028</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.388339321049</v>
+        <v>17752.400869765035</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.50537635311</v>
+        <v>11857.513454719578</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7221082609231</v>
+        <v>-4449.7261557020429</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3042548703652</v>
+        <v>7230.3163971937247</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10304.982891316802</v>
+        <v>10305.017287206025</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.420788565363</v>
+        <v>10350.452024915699</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.600525721431</v>
+        <v>10809.631367129408</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8650.9926404035359</v>
+        <v>8651.0116335406947</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6078853178951</v>
+        <v>5607.6197335887136</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.886547203343</v>
+        <v>12308.896384858508</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.907048996301</v>
+        <v>11857.917640632335</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.825041824472</v>
+        <v>10224.832617537028</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.388339321049</v>
+        <v>11296.400869765035</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5053763531105</v>
+        <v>7067.5134547195776</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3042548703652</v>
+        <v>7230.3163971937247</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10304.982891316802</v>
+        <v>10305.017287206025</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.420788565363</v>
+        <v>10350.452024915699</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.600525721431</v>
+        <v>10809.631367129408</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8650.9926404035359</v>
+        <v>8651.0116335406947</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6078853178951</v>
+        <v>5607.6197335887136</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.886547203343</v>
+        <v>12308.896384858508</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.907048996301</v>
+        <v>11857.917640632335</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.825041824472</v>
+        <v>10224.832617537028</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.388339321049</v>
+        <v>11296.400869765035</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5053763531105</v>
+        <v>7067.5134547195776</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421691117248368</v>
+        <v>0.18421653801005619</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337921489123427</v>
+        <v>0.19337886495190731</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787999606609437</v>
+        <v>0.18787965468460188</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391283936770841</v>
+        <v>0.18391260125734621</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957534567931209</v>
+        <v>0.199575141649948</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967762848529047</v>
+        <v>0.19967753220682019</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19636723684375856</v>
+        <v>0.1963671285685116</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838220467219487</v>
+        <v>0.20838211150847233</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20847899050306304</v>
+        <v>0.208478843349203</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2198607478769542</v>
+        <v>0.21986059808874608</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.58117468953202</v>
+        <v>279.59736445400836</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>593.98289131680042</v>
+        <v>594.01728720602318</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.42078856536159</v>
+        <v>539.45202491569955</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.60052572143172</v>
+        <v>532.63136712940911</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>327.99264040353597</v>
+        <v>328.01163354069547</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.60788531789578</v>
+        <v>204.61973358871364</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.88654720334378</v>
+        <v>169.89638485850767</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.90704899630077</v>
+        <v>182.91764063233492</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.82504182447275</v>
+        <v>130.83261753702598</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.38833932104734</v>
+        <v>216.40086976503352</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.50537635311076</v>
+        <v>139.51345471957748</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.41882531046804</v>
+        <v>-523.40263554599164</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-209.01710868319958</v>
+        <v>-208.98271279397682</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.57921143463841</v>
+        <v>-420.54797508430045</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.39947427856828</v>
+        <v>-366.36863287059089</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-455.00735959646403</v>
+        <v>-454.98836645930453</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.39211468210419</v>
+        <v>-503.38026641128636</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.11345279665625</v>
+        <v>-818.10361514149236</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.09295100369923</v>
+        <v>-947.08235936766505</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1749581755273</v>
+        <v>-1014.167382462974</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.61166067895266</v>
+        <v>-468.59913023496648</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.49462364688924</v>
+        <v>-437.48654528042255</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8727707206941165E-3</v>
+        <v>2.8726818635894163E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1174636649979126E-3</v>
+        <v>1.1172797749964009E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3714109150886837E-3</v>
+        <v>2.371234790781716E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1309232905979171E-3</v>
+        <v>2.1307439216872405E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2841372212784399E-3</v>
+        <v>3.2840001332349639E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6076659681110856E-3</v>
+        <v>4.6075575181122952E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2199434557081383E-3</v>
+        <v>7.2198566372922114E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9797378496605604E-3</v>
+        <v>8.9796374264498446E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432991659814751E-2</v>
+        <v>1.143290625733292E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7230119034580576E-3</v>
+        <v>5.7228588729509111E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0506342874736179E-2</v>
+        <v>1.0506148874436794E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688740027682172E-2</v>
+        <v>9.7688828884786888E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0779716707744637E-2</v>
+        <v>9.0779900597746141E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327496355116672E-2</v>
+        <v>9.732767247942363E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.871586403550825E-2</v>
+        <v>9.8716043404418932E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1058845925238622</v>
+        <v>0.10588472961190566</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608239636541446</v>
+        <v>0.10608250481541326</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005777401713258</v>
+        <v>0.18005786083554851</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212673792544137</v>
+        <v>0.18212683834865209</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102231012360463</v>
+        <v>0.19102239552608649</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680452772674152</v>
+        <v>0.21680468075724865</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475553844415624</v>
+        <v>0.28475573244445562</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422185006920543E-2</v>
+        <v>2.4422207221196722E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683338391165564E-2</v>
+        <v>3.9683405033994097E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093308016834375E-2</v>
+        <v>5.5093491906835886E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360233141431052E-2</v>
+        <v>5.836040926573801E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2866983004474894E-2</v>
+        <v>6.2867162373385563E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.244085141073813E-2</v>
+        <v>6.2440988498781602E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327748810700999E-2</v>
+        <v>5.13278572606998E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862731149297382</v>
+        <v>0.10862739831138976</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11242919360004078</v>
+        <v>0.1124292940232515</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526644242581642</v>
+        <v>0.11526652782829828</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795936029067499</v>
+        <v>0.13795951332118214</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1697246794350066</v>
+        <v>0.16972487343530601</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683338391165564E-2</v>
+        <v>3.9683405033994097E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093308016834375E-2</v>
+        <v>5.5093491906835886E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360233141431052E-2</v>
+        <v>5.836040926573801E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2866983004474894E-2</v>
+        <v>6.2867162373385563E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.244085141073813E-2</v>
+        <v>6.2440988498781602E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327748810700999E-2</v>
+        <v>5.13278572606998E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862731149297382</v>
+        <v>0.10862739831138976</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11242919360004078</v>
+        <v>0.1124292940232515</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526644242581642</v>
+        <v>0.11526652782829828</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795936029067499</v>
+        <v>0.13795951332118214</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1697246794350066</v>
+        <v>0.16972487343530601</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.30826905436799995</v>
+        <v>0.30927722548799996</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27579109550399999</v>
+        <v>0.27669304986400001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22571638300799998</v>
+        <v>0.22645457172799999</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2970.2120720733642</v>
+        <v>2979.9259307591765</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2970.2120720733642</v>
+        <v>2979.9259307591765</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2669.240614485183</v>
+        <v>2677.9701683009953</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2388.020408801226</v>
+        <v>2395.8302527541323</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1954.4334027132522</v>
+        <v>1960.8252324628147</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41080042656194116</v>
+        <v>0.41214322680481363</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28823066504808348</v>
+        <v>0.28917233690222333</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25788715927704398</v>
+        <v>0.25872977932312152</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22091661973251783</v>
+        <v>0.22163847881432114</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.225920132400215</v>
+        <v>0.22665848984187367</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.6044036763489921E-2</v>
+        <v>4.7143824905205467E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.6044036763489921E-2</v>
+        <v>4.7143824905205467E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.1378396559463078E-2</v>
+        <v>4.2366743217534246E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.7018938993825502E-2</v>
+        <v>3.7903157515616438E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>3.0297501074899327E-2</v>
+        <v>3.1021174209315067E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8227701227288033E-2</v>
+        <v>4.8226531325098021E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304445659247047E-2</v>
+        <v>-1.630423311453999E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956936296914416E-2</v>
+        <v>1.6956928753836031E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702856448430569</v>
+        <v>0.15702916883323015</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578852240445294</v>
+        <v>0.26578886717261963</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196234226443309</v>
+        <v>-0.43196203543974987</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157596742050458E-2</v>
+        <v>6.2157523217266863E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361495333138329</v>
+        <v>0.13361507157952657</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.549040287203765E-2</v>
+        <v>-4.5490649864910138E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714360448225792</v>
+        <v>0.49714364124960353</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143639763385305</v>
+        <v>1.2143599230577218</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920207008315306</v>
+        <v>1.3920164998897571</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756290035526155</v>
+        <v>1.375625078688401</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871240560251183</v>
+        <v>1.3871210106197289</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848734687431024</v>
+        <v>2.9848671620406342</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067794506282628</v>
+        <v>1.3067784062092338</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.435160516074417</v>
+        <v>1.4351592341716162</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994843379373</v>
+        <v>1.2994833751323152</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.394162410757434</v>
+        <v>1.3941608642937242</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.891756608312483</v>
+        <v>1.8917544459815239</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688740027682172E-2</v>
+        <v>9.7688828884786888E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0779716707744637E-2</v>
+        <v>9.0779900597746141E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327496355116672E-2</v>
+        <v>9.732767247942363E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.871586403550825E-2</v>
+        <v>9.8716043404418932E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1058845925238622</v>
+        <v>0.10588472961190566</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608239636541446</v>
+        <v>0.10608250481541326</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005777401713258</v>
+        <v>0.18005786083554851</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212673792544137</v>
+        <v>0.18212683834865209</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102231012360463</v>
+        <v>0.19102239552608649</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680452772674152</v>
+        <v>0.21680468075724865</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475553844415624</v>
+        <v>0.28475573244445562</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035896249275276</v>
+        <v>0.20035914473808938</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114068656854621</v>
+        <v>0.19114107375703299</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122192961968413</v>
+        <v>0.20122229375185877</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032440987486595</v>
+        <v>0.21032479203897558</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1933799006130098</v>
+        <v>0.19338015098061842</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.13711131218803335</v>
+        <v>0.13711145235946756</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766100331127539</v>
+        <v>0.25766112754762277</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404495461803152</v>
+        <v>0.27404510572420371</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820685778018243</v>
+        <v>0.25820697321961184</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774638160145164</v>
+        <v>0.26774657058903872</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861249895274885</v>
+        <v>0.16861261382628373</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.90701886071307225</v>
+        <v>0.90998672694476523</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2927275965536045</v>
+        <v>1.2969596954198934</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.298427637429177</v>
+        <v>1.3026779802067208</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3560302869687562</v>
+        <v>1.3604689652407755</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0852397371037981</v>
+        <v>1.0887913237409961</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70345671996314485</v>
+        <v>0.70575881427537857</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5441109888522953</v>
+        <v>1.549162127663877</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4875370334211435</v>
+        <v>1.4924032461937222</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2826720471934556</v>
+        <v>1.2868678846200841</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4170962826082505</v>
+        <v>1.421732368133054</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.88659625495362293</v>
+        <v>0.88949681908727152</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12174749808229159</v>
+        <v>0.12465571601983087</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17352048275887308</v>
+        <v>0.17766571170135526</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17428558891666804</v>
+        <v>0.17844903838448231</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18201748818372565</v>
+        <v>0.18636561167681856</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14566976336963733</v>
+        <v>0.14914949640287617</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.442372080042212E-2</v>
+        <v>9.6679289626764184E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.20726321998017386</v>
+        <v>0.21221399009094205</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.19966940045921389</v>
+        <v>0.20443880084845512</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17217074458972559</v>
+        <v>0.17628327186576495</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.19021426612191281</v>
+        <v>0.19475785864836356</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.11900620871860711</v>
+        <v>0.1218488793270235</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14737690336196524</v>
+        <v>0.15040519589680013</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14347041554801601</v>
+        <v>0.14641843778530403</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12716237911835498</v>
+        <v>0.12977530471667734</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.40827448236500247</v>
+        <v>0.41666368405743404</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15086483891013419</v>
+        <v>0.15396480135349311</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1483690272512222</v>
+        <v>0.15141770589337059</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12731739847605139</v>
+        <v>0.12993350940364148</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12322488743286648</v>
+        <v>0.12575690566778841</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2923608717550155E-2</v>
+        <v>5.4011080129554613E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5964490985564257E-2</v>
+        <v>3.6703487375678585E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3042548703652</v>
+        <v>7230.3163971937247</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.056731604869</v>
+        <v>96404.218629249663</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17133.882531046798</v>
+        <v>17132.263554599165</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89417.339262651658</v>
+        <v>89415.882183848822</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0862193599999999</v>
+        <v>1.0897717599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>12.948264848756697</v>
+        <v>12.990430723336237</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7118211758398</v>
+        <v>7373.7242043329152</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2668103961296</v>
+        <v>6859.2783296120142</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9637671019655</v>
+        <v>7519.9763958695094</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2698904073259</v>
+        <v>6507.280818491734</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.116508747521</v>
+        <v>7669.1293879970308</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3363925169033</v>
+        <v>6173.3467598049237</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2275811815452</v>
+        <v>7821.2407158811393</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5393562903364</v>
+        <v>5856.5491915603507</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3556606372576</v>
+        <v>7976.3690558535927</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5555.9993901115959</v>
+        <v>5556.008720665166</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5605871461757</v>
+        <v>8134.5742480464032</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.882230094604</v>
+        <v>5270.8910818322584</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9033876211724</v>
+        <v>8295.9173194749292</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.3964242640131</v>
+        <v>5000.4048217571435</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4462993973557</v>
+        <v>8460.4605075787968</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.791135576851</v>
+        <v>4743.7991021359176</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2527942398719</v>
+        <v>8628.2672842297488</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3540576864789</v>
+        <v>4500.3616154257215</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.3876028278883</v>
+        <v>8799.4023802156535</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4094376632693</v>
+        <v>4269.4166075620888</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9167397241799</v>
+        <v>8973.9318102101515</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.316200183297</v>
+        <v>4050.3230021444974</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9075288399945</v>
+        <v>9151.9228982375535</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4661679780415</v>
+        <v>3842.472620883073</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4286294049689</v>
+        <v>9333.4443036427983</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2823736052214</v>
+        <v>3645.2884953665966</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5500624521628</v>
+        <v>9518.5660475765362</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2174578544946</v>
+        <v>3458.2232654655077</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3432378283705</v>
+        <v>9707.3595400054855</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7521503421312</v>
+        <v>3280.7576599240338</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.8809817402052</v>
+        <v>9899.8976072585592</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.3938280770167</v>
+        <v>3112.3990549237647</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.237564846493</v>
+        <v>10096.254520119315</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6751479966879</v>
+        <v>2952.6801066173985</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.4887309079</v>
+        <v>10296.506022475618</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1527496775157</v>
+        <v>2801.1574538367418</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.711726004767</v>
+        <v>10500.729360537533</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4060246178851</v>
+        <v>2657.4104873738233</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10708.985328334482</v>
+        <v>10709.003312634744</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0359486780685</v>
+        <v>2521.0401824188089</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.157615677861</v>
+        <v>98316.322724438869</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.916169529501</v>
+        <v>23144.955038302702</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110203.85934354737</v>
+        <v>110204.04441610427</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110203.85934354737</v>
+        <v>110204.04441610427</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.056731604884</v>
+        <v>96404.218629249663</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.675184735243</v>
+        <v>97921.83963101609</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.077892205663</v>
+        <v>99461.244923706254</v>
       </c>
       <c r="E56" s="123">
-        <v>101022.74298186196</v>
+        <v>101022.912635969</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.15604539233</v>
+        <v>102607.32836030795</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.056731604898</v>
+        <v>96404.218629249692</v>
       </c>
       <c r="C57" s="123">
-        <v>99376.74005269297</v>
+        <v>99376.906942559493</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.50664173128</v>
+        <v>102492.67876410868</v>
       </c>
       <c r="E57" s="123">
-        <v>105759.74559840598</v>
+        <v>105759.92320767169</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.30878463322</v>
+        <v>109187.49215003022</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.056731604884</v>
+        <v>96404.218629249706</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.22311287362</v>
+        <v>101173.39301969178</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.65043833683</v>
+        <v>106330.82900636042</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.34097632176</v>
+        <v>111913.52891972312</v>
       </c>
       <c r="F58" s="123">
-        <v>117961.82704576512</v>
+        <v>117962.02514678516</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.056731604898</v>
+        <v>96404.218629249706</v>
       </c>
       <c r="C59" s="341">
-        <v>102997.7652458846</v>
+        <v>102997.93821677584</v>
       </c>
       <c r="D59" s="123">
-        <v>110331.97796384839</v>
+        <v>110332.16325156328</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.28891879744</v>
+        <v>118504.48793080922</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.58811416305</v>
+        <v>127625.80244416979</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.056731604884</v>
+        <v>96404.218629249706</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.2898839276</v>
+        <v>104688.46569382757</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.31826832294</v>
+        <v>114140.50995163305</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.24698024562</v>
+        <v>124956.45682745303</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.00399179797</v>
+        <v>137367.23468120224</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.056731604898</v>
+        <v>96404.218629249721</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.0420473039</v>
+        <v>106173.2203506454</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.39705146453</v>
+        <v>117578.59450856545</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.1568865458</v>
+        <v>130953.37680475667</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.38989012002</v>
+        <v>146703.63625872839</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.217123142691138</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.407503590295153</v>
+        <v>11.444627923283715</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.600616803887501</v>
+        <v>11.638373024712509</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.79652276309818</v>
+        <v>11.834920009932805</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>11.995282383872672</v>
+        <v>12.034329994213799</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.21712314269114</v>
+        <v>11.253624529756422</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.590036887965114</v>
+        <v>11.627758490132715</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>11.980899977845977</v>
+        <v>12.019900527360676</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.390764798425867</v>
+        <v>12.431106471056353</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.820741787858886</v>
+        <v>12.862490392850557</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.217123142691138</v>
+        <v>11.253624529756424</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.815400020842652</v>
+        <v>11.853859036156667</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.46238300967069</v>
+        <v>12.502959025025385</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.162713927012915</v>
+        <v>13.205581502742611</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.921477424420363</v>
+        <v>13.966827758402768</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.21712314269114</v>
+        <v>11.253624529756424</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.044283075894155</v>
+        <v>12.083491021930033</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>12.96433692552211</v>
+        <v>13.006555389717997</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>13.989527555191364</v>
+        <v>14.035100556743236</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.133765766028858</v>
+        <v>15.183082841815621</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.217123142691138</v>
+        <v>11.253624529756424</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.256354058961334</v>
+        <v>12.296255924756355</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.442081203274375</v>
+        <v>13.48586289969259</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.798905341239758</v>
+        <v>14.847126716606047</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.355795658493332</v>
+        <v>16.409111351518455</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.21712314269114</v>
+        <v>11.253624529756424</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.442611534192711</v>
+        <v>12.483122855088485</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.873377341168753</v>
+        <v>13.91857028634811</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.55119877167837</v>
+        <v>15.601881734521205</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.527015817723754</v>
+        <v>17.584163872909148</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.820741787858886</v>
+        <v>12.862490392850557</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>13.989527555191364</v>
+        <v>14.035100556743236</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.96433692552211</v>
+        <v>13.006555389717997</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.044283075894155</v>
+        <v>12.083491021930033</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.21712314269114</v>
+        <v>11.253624529756422</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2970.2120720733642</v>
+        <v>2979.9259307591765</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39602.82762764486</v>
+        <v>39732.345743455691</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2284131169413559</v>
+        <v>5.2455122549613451</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3029.1239614838632</v>
+        <v>3039.0304871425251</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2817.789731612896</v>
+        <v>2827.0051043186281</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3089.2043232558294</v>
+        <v>3099.3073372896929</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2673.1892467330058</v>
+        <v>2681.9317142582527</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3150.476333146707</v>
+        <v>3160.7797327527223</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2536.0092233562991</v>
+        <v>2544.3030537710424</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3212.9636265873987</v>
+        <v>3223.471386260444</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2405.868865740867</v>
+        <v>2413.7370817508063</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3276.6903077995398</v>
+        <v>3287.4064808655648</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2282.4069194357285</v>
+        <v>2289.8713622906262</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3341.6809590936041</v>
+        <v>3352.6096792731855</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2165.2806684806192</v>
+        <v>2172.3620586030625</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3407.960650351431</v>
+        <v>3419.1061333543375</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2054.1649840664622</v>
+        <v>2060.8829785693383</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3475.5549486968307</v>
+        <v>3486.9214938482173</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1948.7514220157261</v>
+        <v>1955.1246692680752</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3544.4899283580007</v>
+        <v>3556.081920256855</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1848.7473665773687</v>
+        <v>1854.7935579700809</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3614.7921807255534</v>
+        <v>3626.6140909360374</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1753.8752181596483</v>
+        <v>1759.6111372147002</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3686.4888246100377</v>
+        <v>3698.5452133863751</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1663.8716227460393</v>
+        <v>1669.3131917055935</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3759.6075167029107</v>
+        <v>3771.9030347484877</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1578.486740855207</v>
+        <v>1583.6490648798992</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3834.1764622449955</v>
+        <v>3846.7158525063505</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1497.4835540157505</v>
+        <v>1502.3809631148533</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3910.2244259065401</v>
+        <v>3923.0125254029354</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1420.6372068305782</v>
+        <v>1425.2832956404343</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>3987.7807428830702</v>
+        <v>4000.8224845723526</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1347.7343828045534</v>
+        <v>1352.1420483257007</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4066.8753302113255</v>
+        <v>4080.175744892797</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1278.5727122027915</v>
+        <v>1282.754189600533</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4147.5386983096341</v>
+        <v>4161.1029165646605</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1212.9602102958822</v>
+        <v>1216.927106863676</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4229.8019627471867</v>
+        <v>4243.6352169182983</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1150.7147444326781</v>
+        <v>1154.4780718126306</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4313.6968562467364</v>
+        <v>4327.8044824559865</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1091.6635284612996</v>
+        <v>1095.2337332112002</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4399.255740925375</v>
+        <v>4413.6431811327229</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1035.6426430949386</v>
+        <v>1039.0296356866841</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40388.31948645151</v>
+        <v>40520.40649523367</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9507.9414351830892</v>
+        <v>9539.0364537384066</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45271.79242710142</v>
+        <v>45419.850472594226</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45271.79242710142</v>
+        <v>45419.850472594226</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39602.82762764486</v>
+        <v>39732.345743455691</v>
       </c>
       <c r="C51" s="123">
-        <v>40226.26593554909</v>
+        <v>40357.822960190453</v>
       </c>
       <c r="D51" s="123">
-        <v>40858.653224428548</v>
+        <v>40992.278424880191</v>
       </c>
       <c r="E51" s="123">
-        <v>41500.185909406246</v>
+        <v>41635.909195009044</v>
       </c>
       <c r="F51" s="123">
-        <v>42151.063471754831</v>
+        <v>42288.915404238396</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39602.82762764486</v>
+        <v>39732.345743455699</v>
       </c>
       <c r="C52" s="123">
-        <v>40824.007203981411</v>
+        <v>40957.51909718816</v>
       </c>
       <c r="D52" s="123">
-        <v>42103.965447825802</v>
+        <v>42241.66334970895</v>
       </c>
       <c r="E52" s="123">
-        <v>43446.148604907561</v>
+        <v>43588.236017439107</v>
       </c>
       <c r="F52" s="123">
-        <v>44854.193023877713</v>
+        <v>45000.885341438712</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39602.827627644867</v>
+        <v>39732.345743455699</v>
       </c>
       <c r="C53" s="123">
-        <v>41562.003211414922</v>
+        <v>41697.928665927386</v>
       </c>
       <c r="D53" s="123">
-        <v>43680.676556677427</v>
+        <v>43823.530975512258</v>
       </c>
       <c r="E53" s="123">
-        <v>45974.048211044959</v>
+        <v>46124.402932088517</v>
       </c>
       <c r="F53" s="123">
-        <v>48458.768868426239</v>
+        <v>48617.249684426606</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39602.827627644867</v>
+        <v>39732.345743455706</v>
       </c>
       <c r="C54" s="123">
-        <v>42311.525897936073</v>
+        <v>42449.902610904828</v>
       </c>
       <c r="D54" s="123">
-        <v>45324.423610971615</v>
+        <v>45472.653782854781</v>
       </c>
       <c r="E54" s="123">
-        <v>48681.612437261509</v>
+        <v>48840.822046655812</v>
       </c>
       <c r="F54" s="123">
-        <v>52428.646037516781</v>
+        <v>52600.110042893808</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39602.827627644867</v>
+        <v>39732.345743455706</v>
       </c>
       <c r="C55" s="123">
-        <v>43005.994140357609</v>
+        <v>43146.642060299127</v>
       </c>
       <c r="D55" s="123">
-        <v>46888.89143254279</v>
+        <v>47042.238080613002</v>
       </c>
       <c r="E55" s="123">
-        <v>51332.079561064173</v>
+        <v>51499.957326962882</v>
       </c>
       <c r="F55" s="123">
-        <v>56430.423835366477</v>
+        <v>56614.975358764801</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39602.827627644874</v>
+        <v>39732.345743455713</v>
       </c>
       <c r="C56" s="123">
-        <v>43615.930962411352</v>
+        <v>43758.573635573499</v>
       </c>
       <c r="D56" s="123">
-        <v>48301.255663210919</v>
+        <v>48459.221343934929</v>
       </c>
       <c r="E56" s="123">
-        <v>53795.61270862582</v>
+        <v>53971.547277299054</v>
       </c>
       <c r="F56" s="123">
-        <v>60265.815144944034</v>
+        <v>60462.910031671985</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342197</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.046258167493531</v>
+        <v>5.0793189681732285</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1255891580120139</v>
+        <v>5.1591696994537184</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2060674096217872</v>
+        <v>5.240175208161169</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.287717946619237</v>
+        <v>5.3223606825398369</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342206</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1212429240381061</v>
+        <v>5.1547949909209709</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.2818096480884851</v>
+        <v>5.3164136755099145</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.4501822912154365</v>
+        <v>5.4858894200259707</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6268170218863389</v>
+        <v>5.6636813815459481</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>4.9680497984087477</v>
+        <v>5.0005982132342206</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2138221951555348</v>
+        <v>5.2479807995416143</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.4796030829444131</v>
+        <v>5.515502963472934</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.7672993225231162</v>
+        <v>5.8050840586649057</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.0789996909177244</v>
+        <v>6.1188265468657645</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>4.9680497984087477</v>
+        <v>5.0005982132342215</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3078474518034939</v>
+        <v>5.3426220671358449</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.6858059656906121</v>
+        <v>5.7230567942245232</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.106954713666048</v>
+        <v>6.1469647182768004</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.5770082587665613</v>
+        <v>6.6200978415612939</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>4.9680497984087477</v>
+        <v>5.0005982132342215</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.3949663021088998</v>
+        <v>5.430311680737498</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.8820635187787706</v>
+        <v>5.9206001380172326</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.4394474534244868</v>
+        <v>6.4816358000525804</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.0790186598624105</v>
+        <v>7.1253971877049187</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>4.9680497984087486</v>
+        <v>5.0005982132342224</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.4714809523842991</v>
+        <v>5.5073276203876924</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.059240156200298</v>
+        <v>6.0989375566157182</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.7484899155484159</v>
+        <v>6.7927029685832583</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.5601564008722075</v>
+        <v>7.609687125536011</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6268170218863389</v>
+        <v>5.6636813815459481</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.106954713666048</v>
+        <v>6.1469647182768004</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.6858059656906121</v>
+        <v>5.7230567942245232</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3078474518034939</v>
+        <v>5.3426220671358449</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>4.9680497984087468</v>
+        <v>5.0005982132342206</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.45</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.231749173792831</v>
+        <v>13.274842062547256</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10304.982891316802</v>
+        <v>10305.017287206025</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3042548703652</v>
+        <v>7230.3163971937247</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0051856207635534E-2</v>
+        <v>6.0052259840958966E-2</v>
       </c>
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.45</v>
+        <v>7.3</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>12.96433692552211</v>
+        <v>13.006555389717997</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.044283075894155</v>
+        <v>12.083491021930033</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>13.989527555191364</v>
+        <v>14.035100556743236</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>12.985364281530369</v>
+        <v>13.027651549565453</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.21712314269114</v>
+        <v>11.253624529756422</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.820741787858886</v>
+        <v>12.862490392850557</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.888721099904831</v>
+        <v>12.930692140739255</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>12.948264848756697</v>
+        <v>12.990430723336237</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8002221478976943E-2</v>
+        <v>-6.8018928912248935E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58173434468228624</v>
+        <v>0.58363686378860125</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.238518965566155</v>
+        <v>5.2555777638527674</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8202533102484413</v>
+        <v>5.8392146276413683</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842274379795386</v>
+        <v>0.54842211351978432</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.45</v>
+        <v>7.3</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23940266373813213</v>
+        <v>0.24954400255547804</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.66959080022937589</v>
+        <v>0.67178064736921583</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.5990252031512737</v>
+        <v>6.620514376058499</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.2686160033806493</v>
+        <v>7.2922950234277151</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604831332456095</v>
+        <v>0.43604758785860243</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89205333564444422</v>
+        <v>0.89497073003662608</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.37491227682983</v>
+        <v>10.408697309762818</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.266965612474275</v>
+        <v>11.303668039799444</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582749481967859</v>
+        <v>0.12582652832741514</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.8275906033469026</v>
+        <v>0.83029717714552231</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2381248010259664</v>
+        <v>9.268207980749688</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.065715404372868</v>
+        <v>10.098505157895211</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22262051927835047</v>
+        <v>0.2226196826750263</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.45</v>
+        <v>7.3</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>64508.072724599995</v>
+        <v>63209.252468400002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0862193599999999</v>
+        <v>1.0897717599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.888721099904831</v>
+        <v>12.930692140739255</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23940266373813213</v>
+        <v>0.24954400255547804</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8202533102484413</v>
+        <v>5.8392146276413683</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2686160033806493</v>
+        <v>7.2922950234277151</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.266965612474275</v>
+        <v>11.303668039799444</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.065715404372868</v>
+        <v>10.098505157895211</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.58117468953202</v>
+        <v>279.59736445400836</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.41882531046804</v>
+        <v>-523.40263554599164</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7221082609231</v>
+        <v>-4449.7261557020429</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,7 +21380,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>500</v>
       </c>
       <c r="C61" s="374"/>
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10304.982891316802</v>
+        <v>10305.017287206025</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3042548703652</v>
+        <v>7230.3163971937247</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12174749808229159</v>
+        <v>0.12465571601983087</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.6044036763489921E-2</v>
+        <v>4.7143824905205467E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41080042656194116</v>
+        <v>0.41214322680481363</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035896249275276</v>
+        <v>0.20035914473808938</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114068656854621</v>
+        <v>0.19114107375703299</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688740027682172E-2</v>
+        <v>9.7688828884786888E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779716707744637E-2</v>
+        <v>9.0779900597746141E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.093584809507629</v>
+        <v>12.133156359263538</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0457239616740734</v>
+        <v>3.0556847764043975</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17133.882531046798</v>
+        <v>17132.263554599165</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1493915145318203</v>
+        <v>2.156217180655569</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9870780325761905E-2</v>
+        <v>1.9935766241709157E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.217123142691136</v>
+        <v>11.253624529756417</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1721367478752747</v>
+        <v>-3.1825109862640586</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.82 HKD</v>
+        <v>12.86 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>13.99 HKD</v>
+        <v>14.04 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>12.96 HKD</v>
+        <v>13.01 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.04 HKD</v>
+        <v>12.08 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.22 HKD</v>
+        <v>11.25 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.888721099904831</v>
+        <v>12.930692140739255</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34302807388799994</v>
+        <v>0.34414992180799991</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58173434468228624</v>
+        <v>0.58363686378860125</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.238518965566155</v>
+        <v>5.2555777638527674</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8202533102484413</v>
+        <v>5.8392146276413683</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842274379795386</v>
+        <v>0.54842211351978432</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.66959080022937589</v>
+        <v>0.67178064736921583</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.5990252031512737</v>
+        <v>6.620514376058499</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2686160033806493</v>
+        <v>7.2922950234277151</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604831332456095</v>
+        <v>0.43604758785860243</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89205333564444422</v>
+        <v>0.89497073003662608</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.37491227682983</v>
+        <v>10.408697309762818</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.266965612474275</v>
+        <v>11.303668039799444</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582749481967859</v>
+        <v>0.12582652832741514</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.8275906033469026</v>
+        <v>0.83029717714552231</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2381248010259664</v>
+        <v>9.268207980749688</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.065715404372868</v>
+        <v>10.098505157895211</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22262051927835047</v>
+        <v>0.2226196826750263</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,15 +22467,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22488,12 +22485,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A8216D-0322-4665-A811-1C5251798377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52BA23D-32F5-4B68-8E37-485482886CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4760,29 +4760,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>63209.252468400002</v>
+        <v>62689.724365919996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0897717599999999</v>
+        <v>1.0927748799999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.930692140739255</v>
+        <v>12.966172607509471</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24954400255547804</v>
+        <v>0.25430003593741213</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8392146276413683</v>
+        <v>5.8552437306918286</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2922950234277151</v>
+        <v>7.3123122705118568</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.303668039799444</v>
+        <v>11.334694716910828</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.098505157895211</v>
+        <v>10.126224228531502</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.59736445400836</v>
+        <v>279.6110509210431</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.40263554599164</v>
+        <v>-523.3889490789569</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7261557020429</v>
+        <v>-4449.7295773188016</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,7 +5752,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.017287206025</v>
+        <v>10305.046364726248</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3163971937247</v>
+        <v>7230.3266620440008</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12465571601983087</v>
+        <v>0.12603531807473087</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.7143824905205467E-2</v>
+        <v>4.766551203093921E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41214322680481363</v>
+        <v>0.4132783967654487</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035914473808938</v>
+        <v>0.20035929880424613</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114107375703299</v>
+        <v>0.19114140107757358</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688828884786888E-2</v>
+        <v>9.7688904002608157E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779900597746141E-2</v>
+        <v>9.0780056054266048E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.133156359263538</v>
+        <v>12.166609371480687</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0556847764043975</v>
+        <v>3.0641054277761266</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17132.263554599165</v>
+        <v>17130.89490789569</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.156217180655569</v>
+        <v>2.1619864108878288</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9935766241709157E-2</v>
+        <v>1.9990703890594277E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1825109862640586</v>
+        <v>-3.1912811368073881</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.86 HKD</v>
+        <v>12.9 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.04 HKD</v>
+        <v>14.07 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.01 HKD</v>
+        <v>13.04 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.08 HKD</v>
+        <v>12.12 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.25 HKD</v>
+        <v>11.28 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.930692140739255</v>
+        <v>12.966172607509471</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58363686378860125</v>
+        <v>0.58524521115335659</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2555777638527674</v>
+        <v>5.269998519538472</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8392146276413683</v>
+        <v>5.8552437306918286</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842211351978432</v>
+        <v>0.54842158068289837</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67178064736921583</v>
+        <v>0.67363189546700775</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.620514376058499</v>
+        <v>6.6386803750448493</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2922950234277151</v>
+        <v>7.3123122705118568</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604758785860243</v>
+        <v>0.43604697455000185</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89497073003662608</v>
+        <v>0.89743703041019007</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.408697309762818</v>
+        <v>10.437257686500638</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.303668039799444</v>
+        <v>11.334694716910828</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582652832741514</v>
+        <v>0.12582571125528264</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83029717714552231</v>
+        <v>0.83258525447524612</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.268207980749688</v>
+        <v>9.2936389740562557</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.098505157895211</v>
+        <v>10.126224228531502</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.2226196826750263</v>
+        <v>0.22261897541104037</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,6 +6839,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6855,17 +6866,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.30927722548799996</v>
+        <v>0.31012951094399999</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27669304986400001</v>
+        <v>0.27745554203200001</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22645457172799999</v>
+        <v>0.22707862006399998</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.30927722548799996</v>
+        <v>0.31012951094399999</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27669304986400001</v>
+        <v>0.27745554203200001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22645457172799999</v>
+        <v>0.22707862006399998</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.1994648666736722</v>
+        <v>8.222060402577819</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1825109862640586</v>
+        <v>-3.1912811368073881</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17132.263554599165</v>
+        <v>17130.89490789569</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14496.910494229931</v>
+        <v>-14497.594817581668</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13979.868222700417</v>
+        <v>-13980.552546052155</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.110455846295495</v>
+        <v>3.1103090248677372</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2254953538674926</v>
+        <v>3.2253374715674692</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27959.736445400835</v>
+        <v>27961.10509210431</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26458.568561039996</v>
+        <v>-26531.481311519998</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0556847764043975</v>
+        <v>-3.0641054277761266</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18670.257006679385</v>
+        <v>18720.211627268323</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.156217180655569</v>
+        <v>2.1619864108878288</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>172.61984678399998</v>
+        <v>173.095540992</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9935766241709157E-2</v>
+        <v>1.9990703890594277E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7615.6917075766105</v>
+        <v>-7638.1741432596746</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.87953182950711939</v>
+        <v>-0.88212831299770345</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.40263554599164</v>
+        <v>-523.3889490789569</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.98271279397682</v>
+        <v>-208.95363527375309</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.54797508430045</v>
+        <v>-420.52156856802208</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.36863287059089</v>
+        <v>-366.34256022980571</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.98836645930453</v>
+        <v>-454.9723100833146</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.38026641128636</v>
+        <v>-503.37025014649112</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.10361514149236</v>
+        <v>-818.09529860648058</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.08235936766505</v>
+        <v>-947.07340543398448</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.167382462974</v>
+        <v>-1014.1609781239686</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.59913023496648</v>
+        <v>-468.58853727613757</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.48654528042255</v>
+        <v>-437.4797160089712</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.904622808172</v>
+        <v>17798.918309275206</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.017287206025</v>
+        <v>16980.046364726248</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.452024915699</v>
+        <v>17261.478431431977</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.631367129408</v>
+        <v>16973.657439770195</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.011633540695</v>
+        <v>14670.027689916686</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.619733588714</v>
+        <v>11589.62974985351</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.896384858508</v>
+        <v>20402.90470139352</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.917640632335</v>
+        <v>19208.926594566015</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.832617537028</v>
+        <v>16944.839021876032</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.400869765035</v>
+        <v>17752.411462723863</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.513454719578</v>
+        <v>11857.520283991029</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7261557020429</v>
+        <v>-4449.7295773188016</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3163971937247</v>
+        <v>7230.3266620440008</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.017287206025</v>
+        <v>10305.046364726248</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.452024915699</v>
+        <v>10350.478431431977</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.631367129408</v>
+        <v>10809.657439770195</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0116335406947</v>
+        <v>8651.0276899166856</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6197335887136</v>
+        <v>5607.6297498535096</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.896384858508</v>
+        <v>12308.90470139352</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.917640632335</v>
+        <v>11857.926594566015</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.832617537028</v>
+        <v>10224.839021876032</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.400869765035</v>
+        <v>11296.411462723863</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5134547195776</v>
+        <v>7067.5202839910289</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3163971937247</v>
+        <v>7230.3266620440008</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.017287206025</v>
+        <v>10305.046364726248</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.452024915699</v>
+        <v>10350.478431431977</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.631367129408</v>
+        <v>10809.657439770195</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0116335406947</v>
+        <v>8651.0276899166856</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6197335887136</v>
+        <v>5607.6297498535096</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.896384858508</v>
+        <v>12308.90470139352</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.917640632335</v>
+        <v>11857.926594566015</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.832617537028</v>
+        <v>10224.839021876032</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.400869765035</v>
+        <v>11296.411462723863</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5134547195776</v>
+        <v>7067.5202839910289</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421653801005619</v>
+        <v>0.18421622254801362</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337886495190731</v>
+        <v>0.19337856912196635</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787965468460188</v>
+        <v>0.18787936608924374</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391260125734621</v>
+        <v>0.18391239996461947</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.199575141649948</v>
+        <v>0.19957496916838399</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967753220682019</v>
+        <v>0.19967745081521385</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1963671285685116</v>
+        <v>0.1963670370351176</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838211150847233</v>
+        <v>0.20838203274999709</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.208478843349203</v>
+        <v>0.2084787189487626</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986059808874608</v>
+        <v>0.21986047146128351</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.59736445400836</v>
+        <v>279.6110509210431</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.01728720602318</v>
+        <v>594.04636472624691</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.45202491569955</v>
+        <v>539.47843143197792</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.63136712940911</v>
+        <v>532.65743977019429</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.01163354069547</v>
+        <v>328.0276899166854</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.61973358871364</v>
+        <v>204.62974985350886</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.89638485850767</v>
+        <v>169.90470139351947</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.91764063233492</v>
+        <v>182.9265945660155</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83261753702598</v>
+        <v>130.83902187603144</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.40086976503352</v>
+        <v>216.4114627238624</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.51345471957748</v>
+        <v>139.52028399102878</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.40263554599164</v>
+        <v>-523.3889490789569</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.98271279397682</v>
+        <v>-208.95363527375309</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.54797508430045</v>
+        <v>-420.52156856802208</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.36863287059089</v>
+        <v>-366.34256022980571</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.98836645930453</v>
+        <v>-454.9723100833146</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.38026641128636</v>
+        <v>-503.37025014649112</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.10361514149236</v>
+        <v>-818.09529860648058</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.08235936766505</v>
+        <v>-947.07340543398448</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.167382462974</v>
+        <v>-1014.1609781239686</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.59913023496648</v>
+        <v>-468.58853727613757</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.48654528042255</v>
+        <v>-437.4797160089712</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8726818635894163E-3</v>
+        <v>2.8726067457681497E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1172797749964009E-3</v>
+        <v>1.1171243184764875E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.371234790781716E-3</v>
+        <v>2.3710858992073598E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1307439216872405E-3</v>
+        <v>2.1305922871970276E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2840001332349639E-3</v>
+        <v>3.2838842420500956E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6075575181122952E-3</v>
+        <v>4.6074658368938605E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2198566372922114E-3</v>
+        <v>7.2197832429331194E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.9796374264498446E-3</v>
+        <v>8.979552530899635E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.143290625733292E-2</v>
+        <v>1.1432834059973042E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7228588729509111E-3</v>
+        <v>5.7227295043616126E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.0506148874436794E-2</v>
+        <v>1.050598487089578E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688828884786888E-2</v>
+        <v>9.7688904002608157E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0779900597746141E-2</v>
+        <v>9.0780056054266048E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.732767247942363E-2</v>
+        <v>9.7327821370997991E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716043404418932E-2</v>
+        <v>9.8716195038909146E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588472961190566</v>
+        <v>0.10588484550309055</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10608250481541326</v>
+        <v>0.1060825964966317</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18005786083554851</v>
+        <v>0.1800579342299076</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212683834865209</v>
+        <v>0.18212692324420229</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102239552608649</v>
+        <v>0.19102246772344636</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680468075724865</v>
+        <v>0.21680481012583797</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475573244445562</v>
+        <v>0.28475589644799665</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422207221196722E-2</v>
+        <v>2.4422226000652039E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683405033994097E-2</v>
+        <v>3.9683461372360049E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093491906835886E-2</v>
+        <v>5.5093647363355792E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.836040926573801E-2</v>
+        <v>5.8360558157312364E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867162373385563E-2</v>
+        <v>6.2867314007875791E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2440988498781602E-2</v>
+        <v>6.244110438996648E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.13278572606998E-2</v>
+        <v>5.1327948941918236E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862739831138976</v>
+        <v>0.10862747170574885</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1124292940232515</v>
+        <v>0.1124293789188017</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526652782829828</v>
+        <v>0.11526660002565815</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795951332118214</v>
+        <v>0.13795964268977143</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972487343530601</v>
+        <v>0.16972503743884704</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683405033994097E-2</v>
+        <v>3.9683461372360049E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093491906835886E-2</v>
+        <v>5.5093647363355792E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.836040926573801E-2</v>
+        <v>5.8360558157312364E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867162373385563E-2</v>
+        <v>6.2867314007875791E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2440988498781602E-2</v>
+        <v>6.244110438996648E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.13278572606998E-2</v>
+        <v>5.1327948941918236E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862739831138976</v>
+        <v>0.10862747170574885</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1124292940232515</v>
+        <v>0.1124293789188017</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526652782829828</v>
+        <v>0.11526660002565815</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795951332118214</v>
+        <v>0.13795964268977143</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972487343530601</v>
+        <v>0.16972503743884704</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.30927722548799996</v>
+        <v>0.31012951094399999</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27669304986400001</v>
+        <v>0.27745554203200001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22645457172799999</v>
+        <v>0.22707862006399998</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2979.9259307591765</v>
+        <v>2988.137810980023</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2979.9259307591765</v>
+        <v>2988.137810980023</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2677.9701683009953</v>
+        <v>2685.3499390631118</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2395.8302527541323</v>
+        <v>2402.4325212407475</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1960.8252324628147</v>
+        <v>1966.228743260446</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.41214322680481363</v>
+        <v>0.4132783967654487</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28917233690222333</v>
+        <v>0.28996840045361622</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.25872977932312152</v>
+        <v>0.259442107613918</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22163847881432114</v>
+        <v>0.2222487192241516</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22665848984187367</v>
+        <v>0.22728267828251306</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.7143824905205467E-2</v>
+        <v>4.766551203093921E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.7143824905205467E-2</v>
+        <v>4.766551203093921E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.2366743217534246E-2</v>
+        <v>4.2835567809944748E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.7903157515616438E-2</v>
+        <v>3.8322588678453041E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>3.1021174209315067E-2</v>
+        <v>3.1364450285082869E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8226531325098021E-2</v>
+        <v>4.8225542319487058E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.630423311453999E-2</v>
+        <v>-1.6304053434569088E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956928753836031E-2</v>
+        <v>1.6956922377106665E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702916883323015</v>
+        <v>0.15702967973515758</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.26578886717261963</v>
+        <v>0.2657891586314145</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.43196203543974987</v>
+        <v>-0.4319617760572132</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157523217266863E-2</v>
+        <v>6.2157461061112418E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361507157952657</v>
+        <v>0.13361517154379654</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490649864910138E-2</v>
+        <v>-4.5490858666922818E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714364124960353</v>
+        <v>0.49714367233186119</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143599230577218</v>
+        <v>1.2143564965253248</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.3920164998897571</v>
+        <v>1.392012948526735</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.375625078688401</v>
+        <v>1.3756217607129024</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.3871210106197289</v>
+        <v>1.387118436112134</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848671620406342</v>
+        <v>2.9848618305153356</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067784062092338</v>
+        <v>1.3067775232819034</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351592341716162</v>
+        <v>1.4351581504812678</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994833751323152</v>
+        <v>1.2994825611994945</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941608642937242</v>
+        <v>1.3941595569503538</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917544459815239</v>
+        <v>1.8917526179988493</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688828884786888E-2</v>
+        <v>9.7688904002608157E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0779900597746141E-2</v>
+        <v>9.0780056054266048E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.732767247942363E-2</v>
+        <v>9.7327821370997991E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716043404418932E-2</v>
+        <v>9.8716195038909146E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588472961190566</v>
+        <v>0.10588484550309055</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10608250481541326</v>
+        <v>0.1060825964966317</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18005786083554851</v>
+        <v>0.1800579342299076</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212683834865209</v>
+        <v>0.18212692324420229</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102239552608649</v>
+        <v>0.19102246772344636</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680468075724865</v>
+        <v>0.21680481012583797</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475573244445562</v>
+        <v>0.28475589644799665</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035914473808938</v>
+        <v>0.20035929880424613</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114107375703299</v>
+        <v>0.19114140107757358</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122229375185877</v>
+        <v>0.20122260158110555</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032479203897558</v>
+        <v>0.21032511511201946</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338015098061842</v>
+        <v>0.19338036263582981</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.13711145235946756</v>
+        <v>0.1371115708572824</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766112754762277</v>
+        <v>0.25766123257426937</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404510572420371</v>
+        <v>0.27404523346600301</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820697321961184</v>
+        <v>0.25820707080953953</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774657058903872</v>
+        <v>0.26774673035494417</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.16861261382628373</v>
+        <v>0.1686127109378168</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.90998672694476523</v>
+        <v>0.91249570286105153</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.2969596954198934</v>
+        <v>1.3005374397480267</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3026779802067208</v>
+        <v>1.3062711455097182</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3604689652407755</v>
+        <v>1.3642213449318525</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0887913237409961</v>
+        <v>1.0917937682983354</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70575881427537857</v>
+        <v>0.70770496122101501</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.549162127663877</v>
+        <v>1.5534322544387731</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4924032461937222</v>
+        <v>1.4965170410882085</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2868678846200841</v>
+        <v>1.2904149571674077</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.421732368133054</v>
+        <v>1.4256516198082561</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.88949681908727152</v>
+        <v>0.89194889670475652</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12465571601983087</v>
+        <v>0.12603531807473087</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17766571170135526</v>
+        <v>0.17963224305911971</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.17844903838448231</v>
+        <v>0.1804241913687456</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18636561167681856</v>
+        <v>0.18842836255964815</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.14914949640287617</v>
+        <v>0.15080024424010158</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.6679289626764184E-2</v>
+        <v>9.7749304036051796E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.21221399009094205</v>
+        <v>0.21456246608270346</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.20443880084845512</v>
+        <v>0.20670124876908957</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17628327186576495</v>
+        <v>0.17823411010599555</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.19475785864836356</v>
+        <v>0.19691320715583646</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1218488793270235</v>
+        <v>0.12319736142330891</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15040519589680013</v>
+        <v>0.1516516477964974</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14641843778530403</v>
+        <v>0.14763185025313805</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12977530471667734</v>
+        <v>0.13085079066736804</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.41666368405743404</v>
+        <v>0.4201166980137111</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15396480135349311</v>
+        <v>0.15524075274592539</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15141770589337059</v>
+        <v>0.15267254875989023</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12993350940364148</v>
+        <v>0.13101030644289818</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12575690566778841</v>
+        <v>0.12679908996890268</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4011080129554613E-2</v>
+        <v>5.4458685765987384E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6703487375678585E-2</v>
+        <v>3.7007659922990842E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3163971937247</v>
+        <v>7230.3266620440008</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.218629249663</v>
+        <v>96404.355493920011</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17132.263554599165</v>
+        <v>17130.89490789569</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89415.882183848822</v>
+        <v>89414.650401815699</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0897717599999999</v>
+        <v>1.0927748799999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>12.990430723336237</v>
+        <v>13.026075898734144</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7242043329152</v>
+        <v>7373.7346727786617</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2783296120142</v>
+        <v>6859.2880677010808</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9763958695094</v>
+        <v>7519.9870719488872</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.280818491734</v>
+        <v>6507.2900568513905</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1293879970308</v>
+        <v>7669.1402758282948</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3467598049237</v>
+        <v>6173.3555240797787</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2407158811393</v>
+        <v>7821.2518196642259</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5491915603507</v>
+        <v>5856.5575060790088</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3690558535927</v>
+        <v>7976.3803798717408</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.008720665166</v>
+        <v>5556.0166085077599</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5742480464032</v>
+        <v>8134.5857966678086</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.8910818322584</v>
+        <v>5270.8985648945209</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9173194749292</v>
+        <v>8295.9290971544251</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4048217571435</v>
+        <v>5000.4119208111815</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4605075787968</v>
+        <v>8460.4725188595785</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.7991021359176</v>
+        <v>4743.8058368878783</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2672842297488</v>
+        <v>8628.2795337451153</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3616154257215</v>
+        <v>4500.3680045704887</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4023802156535</v>
+        <v>8799.4148726908079</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4166075620888</v>
+        <v>4269.4226688351837</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9318102101515</v>
+        <v>8973.9445504640171</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.3230021444974</v>
+        <v>4050.328752371307</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9228982375535</v>
+        <v>9151.9358911846284</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.472620883073</v>
+        <v>3842.4780760255558</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4443036427983</v>
+        <v>9333.4575542950624</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2884953665966</v>
+        <v>3645.2936705675925</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5660475765362</v>
+        <v>9518.5795610453733</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2232654655077</v>
+        <v>3458.2281750907705</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3595400054855</v>
+        <v>9707.3733215036627</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7576599240338</v>
+        <v>3280.7623176021102</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.8976072585592</v>
+        <v>9899.9116621022349</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.3990549237647</v>
+        <v>3112.4034735838263</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.254520119315</v>
+        <v>10096.268853730087</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6801066173985</v>
+        <v>2952.6842985251301</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.506022475618</v>
+        <v>10296.52064038262</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.1574538367418</v>
+        <v>2801.16143062839</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.729360537533</v>
+        <v>10500.744268379562</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4104873738233</v>
+        <v>2657.4142600884979</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.003312634744</v>
+        <v>10709.018516162441</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0401824188089</v>
+        <v>2521.0437615291257</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.322724438869</v>
+        <v>98316.462303715496</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.955038302702</v>
+        <v>23144.987897099618</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.04441610427</v>
+        <v>110204.2008723302</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.04441610427</v>
+        <v>110204.2008723302</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.218629249663</v>
+        <v>96404.355493920011</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.83963101609</v>
+        <v>97921.978650246689</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.244923706254</v>
+        <v>99461.386128424172</v>
       </c>
       <c r="E56" s="123">
-        <v>101022.912635969</v>
+        <v>101023.05605778014</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.32836030795</v>
+        <v>102607.47403150753</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.218629249692</v>
+        <v>96404.35549392004</v>
       </c>
       <c r="C57" s="123">
-        <v>99376.906942559493</v>
+        <v>99377.048027543147</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.67876410868</v>
+        <v>102492.82427254066</v>
       </c>
       <c r="E57" s="123">
-        <v>105759.92320767169</v>
+        <v>105760.07335459715</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.49215003022</v>
+        <v>109187.64716306108</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.218629249706</v>
+        <v>96404.35549392004</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.39301969178</v>
+        <v>101173.53665513928</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.82900636042</v>
+        <v>106330.97996379843</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.52891972312</v>
+        <v>111913.68780289716</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.02514678516</v>
+        <v>117962.19261698422</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.218629249706</v>
+        <v>96404.35549392004</v>
       </c>
       <c r="C59" s="341">
-        <v>102997.93821677584</v>
+        <v>102998.08444252261</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.16325156328</v>
+        <v>110332.31988967897</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.48793080922</v>
+        <v>118504.65617114049</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.80244416979</v>
+        <v>127625.98363399351</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.218629249706</v>
+        <v>96404.355493920011</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.46569382757</v>
+        <v>104688.61431960919</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.50995163305</v>
+        <v>114140.67199644279</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.45682745303</v>
+        <v>124956.63422761786</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.23468120224</v>
+        <v>137367.42970089699</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.218629249721</v>
+        <v>96404.355493920011</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.2203506454</v>
+        <v>106173.37108432705</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.59450856545</v>
+        <v>117578.76143440964</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.37680475667</v>
+        <v>130953.562718724</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.63625872839</v>
+        <v>146703.84453327383</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.444627923283715</v>
+        <v>11.476011078278662</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.638373024712509</v>
+        <v>11.670290365293893</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.834920009932805</v>
+        <v>11.867379261333037</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.034329994213799</v>
+        <v>12.067339050169652</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.253624529756422</v>
+        <v>11.284481058482985</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.627758490132715</v>
+        <v>11.659646564779955</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.019900527360676</v>
+        <v>12.052869799016653</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.431106471056353</v>
+        <v>12.46520950189675</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.862490392850557</v>
+        <v>12.897782816720985</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.253624529756424</v>
+        <v>11.284481058482985</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.853859036156667</v>
+        <v>11.886370505418178</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.502959025025385</v>
+        <v>12.537260164609668</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.205581502742611</v>
+        <v>13.241819882533417</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.966827758402768</v>
+        <v>14.005165013336752</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.253624529756424</v>
+        <v>11.284481058482985</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.083491021930033</v>
+        <v>12.116635622538247</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.006555389717997</v>
+        <v>13.042245023346348</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.035100556743236</v>
+        <v>14.073626050474237</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.183082841815621</v>
+        <v>15.224773502488382</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.253624529756424</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.296255924756355</v>
+        <v>12.32998715152209</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.48586289969259</v>
+        <v>13.52287405918875</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.847126716606047</v>
+        <v>14.887891093628598</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.409111351518455</v>
+        <v>16.45418236479685</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.253624529756424</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.483122855088485</v>
+        <v>12.517369303245774</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.91857028634811</v>
+        <v>13.956774487874199</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.601881734521205</v>
+        <v>15.644727089327914</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.584163872909148</v>
+        <v>17.63247469001022</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.862490392850557</v>
+        <v>12.897782816720985</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.035100556743236</v>
+        <v>14.073626050474237</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.006555389717997</v>
+        <v>13.042245023346348</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.083491021930033</v>
+        <v>12.116635622538247</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.253624529756422</v>
+        <v>11.284481058482985</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2979.9259307591765</v>
+        <v>2988.137810980023</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39732.345743455691</v>
+        <v>39841.837479733644</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170213</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2455122549613451</v>
+        <v>5.2599674861770263</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3039.0304871425251</v>
+        <v>3047.4052437397659</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2827.0051043186281</v>
+        <v>2834.7955755718754</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3099.3073372896929</v>
+        <v>3107.8482007919374</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2681.9317142582527</v>
+        <v>2689.3224019832883</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3160.7797327527223</v>
+        <v>3169.4899977636487</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2544.3030537710424</v>
+        <v>2551.314473654817</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3223.471386260444</v>
+        <v>3232.3544127296796</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2413.7370817508063</v>
+        <v>2420.3886966769874</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3287.4064808655648</v>
+        <v>3296.4656953847739</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2289.8713622906262</v>
+        <v>2296.1816363662929</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3352.6096792731855</v>
+        <v>3361.8485763978624</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2172.3620586030625</v>
+        <v>2178.348508412912</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3419.1061333543375</v>
+        <v>3428.5282769518176</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2060.8829785693383</v>
+        <v>2066.5622217996829</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3486.9214938482173</v>
+        <v>3496.5305184724239</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1955.1246692680752</v>
+        <v>1960.5124708355997</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3556.081920256855</v>
+        <v>3565.8815325503147</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1854.7935579700809</v>
+        <v>1859.904873783413</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3626.6140909360374</v>
+        <v>3636.6080710597021</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1759.6111372147002</v>
+        <v>1764.4601556902678</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3698.5452133863751</v>
+        <v>3708.7374164778039</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1669.3131917055935</v>
+        <v>1673.9133731530137</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3771.9030347484877</v>
+        <v>3782.2973924089515</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1583.6490648798992</v>
+        <v>1588.0131788662277</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3846.7158525063505</v>
+        <v>3857.3163743174296</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1502.3809631148533</v>
+        <v>1506.5211239114124</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3923.0125254029354</v>
+        <v>3933.8233004732006</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1425.2832956404343</v>
+        <v>1429.2109958506171</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4000.8224845723526</v>
+        <v>4011.8476831147223</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1352.1420483257007</v>
+        <v>1355.8681907870978</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4080.175744892797</v>
+        <v>4091.4196198331801</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1282.754189600533</v>
+        <v>1286.2891176499375</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4161.1029165646605</v>
+        <v>4172.5698051825057</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1216.927106863676</v>
+        <v>1220.2806330489796</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4243.6352169182983</v>
+        <v>4255.3295425196802</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1154.4780718126306</v>
+        <v>1157.6595051313116</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4327.8044824559865</v>
+        <v>4339.7307560798799</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1095.2337332112002</v>
+        <v>1098.2519049510156</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4413.6431811327229</v>
+        <v>4425.8060032911189</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1039.0296356866841</v>
+        <v>1041.8929239402935</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40520.40649523367</v>
+        <v>40632.069916530214</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9539.0364537384066</v>
+        <v>9565.3234912690441</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45419.850472594226</v>
+        <v>45545.015453334097</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45419.850472594226</v>
+        <v>45545.015453334097</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39732.345743455691</v>
+        <v>39841.837479733644</v>
       </c>
       <c r="C51" s="123">
-        <v>40357.822960190453</v>
+        <v>40469.038344674453</v>
       </c>
       <c r="D51" s="123">
-        <v>40992.278424880191</v>
+        <v>41105.242199224391</v>
       </c>
       <c r="E51" s="123">
-        <v>41635.909195009044</v>
+        <v>41750.64664390542</v>
       </c>
       <c r="F51" s="123">
-        <v>42288.915404238396</v>
+        <v>42405.452363893848</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39732.345743455699</v>
+        <v>39841.837479733658</v>
       </c>
       <c r="C52" s="123">
-        <v>40957.51909718816</v>
+        <v>41070.387084106027</v>
       </c>
       <c r="D52" s="123">
-        <v>42241.66334970895</v>
+        <v>42358.070095318471</v>
       </c>
       <c r="E52" s="123">
-        <v>43588.236017439107</v>
+        <v>43708.353557784154</v>
       </c>
       <c r="F52" s="123">
-        <v>45000.885341438712</v>
+        <v>45124.895766141388</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39732.345743455699</v>
+        <v>39841.837479733651</v>
       </c>
       <c r="C53" s="123">
-        <v>41697.928665927386</v>
+        <v>41812.837023926324</v>
       </c>
       <c r="D53" s="123">
-        <v>43823.530975512258</v>
+        <v>43944.29692593767</v>
       </c>
       <c r="E53" s="123">
-        <v>46124.402932088517</v>
+        <v>46251.509471290279</v>
       </c>
       <c r="F53" s="123">
-        <v>48617.249684426606</v>
+        <v>48751.225843684297</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39732.345743455706</v>
+        <v>39841.837479733658</v>
       </c>
       <c r="C54" s="123">
-        <v>42449.902610904828</v>
+        <v>42566.883208318053</v>
       </c>
       <c r="D54" s="123">
-        <v>45472.653782854781</v>
+        <v>45597.964275419166</v>
       </c>
       <c r="E54" s="123">
-        <v>48840.822046655812</v>
+        <v>48975.414311649671</v>
       </c>
       <c r="F54" s="123">
-        <v>52600.110042893808</v>
+        <v>52745.061901870235</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39732.345743455706</v>
+        <v>39841.837479733658</v>
       </c>
       <c r="C55" s="123">
-        <v>43146.642060299127</v>
+        <v>43265.54268560448</v>
       </c>
       <c r="D55" s="123">
-        <v>47042.238080613002</v>
+        <v>47171.87392842085</v>
       </c>
       <c r="E55" s="123">
-        <v>51499.957326962882</v>
+        <v>51641.87745879648</v>
       </c>
       <c r="F55" s="123">
-        <v>56614.975358764801</v>
+        <v>56770.991114577191</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39732.345743455713</v>
+        <v>39841.837479733666</v>
       </c>
       <c r="C56" s="123">
-        <v>43758.573635573499</v>
+        <v>43879.16058091374</v>
       </c>
       <c r="D56" s="123">
-        <v>48459.221343934929</v>
+        <v>48592.76201928001</v>
       </c>
       <c r="E56" s="123">
-        <v>53971.547277299054</v>
+        <v>54120.278451117876</v>
       </c>
       <c r="F56" s="123">
-        <v>60462.910031671985</v>
+        <v>60629.52966803906</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170213</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170213</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170213</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170213</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170213</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0005982132342197</v>
+        <v>5.0281968151170222</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.0793189681732285</v>
+        <v>5.1073520346306349</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1591696994537184</v>
+        <v>5.1876434668930251</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.240175208161169</v>
+        <v>5.2690960498683523</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3223606825398369</v>
+        <v>5.3517351108163078</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0005982132342206</v>
+        <v>5.0281968151170249</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1547949909209709</v>
+        <v>5.1832446140811328</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3164136755099145</v>
+        <v>5.3457552818973992</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.4858894200259707</v>
+        <v>5.5161663732264259</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6636813815459481</v>
+        <v>5.6949395792605042</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0005982132342206</v>
+        <v>5.0281968151170231</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2479807995416143</v>
+        <v>5.2769447207764424</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.515502963472934</v>
+        <v>5.5459433555983102</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8050840586649057</v>
+        <v>5.8371226662473523</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1188265468657645</v>
+        <v>6.1525967180844701</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0005982132342215</v>
+        <v>5.0281968151170249</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3426220671358449</v>
+        <v>5.3721083192108328</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7230567942245232</v>
+        <v>5.7546426884078334</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1469647182768004</v>
+        <v>6.1808901857535465</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6200978415612939</v>
+        <v>6.6566345591625842</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0005982132342215</v>
+        <v>5.0281968151170249</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.430311680737498</v>
+        <v>5.4602818970567322</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9206001380172326</v>
+        <v>5.9532762857797064</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.4816358000525804</v>
+        <v>6.5174083373305285</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1253971877049187</v>
+        <v>7.1647226827466639</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0005982132342224</v>
+        <v>5.0281968151170258</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5073276203876924</v>
+        <v>5.5377228923035569</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.0989375566157182</v>
+        <v>6.1325979593026689</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.7927029685832583</v>
+        <v>6.8301923042475234</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.609687125536011</v>
+        <v>7.6516854458318795</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6636813815459481</v>
+        <v>5.6949395792605042</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1469647182768004</v>
+        <v>6.1808901857535465</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7230567942245232</v>
+        <v>5.7546426884078334</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3426220671358449</v>
+        <v>5.3721083192108328</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0005982132342206</v>
+        <v>5.0281968151170249</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.3</v>
+        <v>-7.24</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.274842062547256</v>
+        <v>13.31127091461347</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.017287206025</v>
+        <v>10305.046364726248</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3163971937247</v>
+        <v>7230.3266620440008</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052259840958966E-2</v>
+        <v>6.0052601061976629E-2</v>
       </c>
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.006555389717997</v>
+        <v>13.042245023346348</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.083491021930033</v>
+        <v>12.116635622538247</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.035100556743236</v>
+        <v>14.073626050474237</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.027651549565453</v>
+        <v>13.063399348610305</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.253624529756422</v>
+        <v>11.284481058482985</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.862490392850557</v>
+        <v>12.897782816720985</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.930692140739255</v>
+        <v>12.966172607509471</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>12.990430723336237</v>
+        <v>13.026075898734144</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8018928912248935E-2</v>
+        <v>-6.8033053368949548E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58363686378860125</v>
+        <v>0.58524521115335659</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2555777638527674</v>
+        <v>5.269998519538472</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8392146276413683</v>
+        <v>5.8552437306918286</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842211351978432</v>
+        <v>0.54842158068289837</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24954400255547804</v>
+        <v>0.25430003593741213</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67178064736921583</v>
+        <v>0.67363189546700775</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.620514376058499</v>
+        <v>6.6386803750448493</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.2922950234277151</v>
+        <v>7.3123122705118568</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604758785860243</v>
+        <v>0.43604697455000185</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89497073003662608</v>
+        <v>0.89743703041019007</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.408697309762818</v>
+        <v>10.437257686500638</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.303668039799444</v>
+        <v>11.334694716910828</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582652832741514</v>
+        <v>0.12582571125528264</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83029717714552231</v>
+        <v>0.83258525447524612</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.268207980749688</v>
+        <v>9.2936389740562557</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.098505157895211</v>
+        <v>10.126224228531502</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.2226196826750263</v>
+        <v>0.22261897541104037</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>63209.252468400002</v>
+        <v>62689.724365919996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0897717599999999</v>
+        <v>1.0927748799999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="372" t="s">
+      <c r="B18" s="370" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="372"/>
-      <c r="D18" s="372"/>
-      <c r="E18" s="372"/>
-      <c r="F18" s="372"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
+      <c r="F18" s="370"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.930692140739255</v>
+        <v>12.966172607509471</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24954400255547804</v>
+        <v>0.25430003593741213</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8392146276413683</v>
+        <v>5.8552437306918286</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.2922950234277151</v>
+        <v>7.3123122705118568</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.303668039799444</v>
+        <v>11.334694716910828</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.098505157895211</v>
+        <v>10.126224228531502</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="372" t="s">
+      <c r="B36" s="370" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="372"/>
-      <c r="D36" s="372"/>
-      <c r="E36" s="372"/>
-      <c r="F36" s="372"/>
+      <c r="C36" s="370"/>
+      <c r="D36" s="370"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="375" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="375"/>
-      <c r="D37" s="375"/>
-      <c r="E37" s="375"/>
-      <c r="F37" s="375"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="373" t="s">
+      <c r="B40" s="371" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="373"/>
-      <c r="D40" s="373"/>
-      <c r="E40" s="373"/>
-      <c r="F40" s="373"/>
+      <c r="C40" s="371"/>
+      <c r="D40" s="371"/>
+      <c r="E40" s="371"/>
+      <c r="F40" s="371"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="373" t="s">
+      <c r="B43" s="371" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
+      <c r="C43" s="371"/>
+      <c r="D43" s="371"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="373" t="s">
+      <c r="B47" s="371" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="373"/>
-      <c r="D47" s="373"/>
-      <c r="E47" s="373"/>
-      <c r="F47" s="373"/>
+      <c r="C47" s="371"/>
+      <c r="D47" s="371"/>
+      <c r="E47" s="371"/>
+      <c r="F47" s="371"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="373" t="s">
+      <c r="B50" s="371" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="373"/>
-      <c r="D50" s="373"/>
-      <c r="E50" s="373"/>
-      <c r="F50" s="373"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.59736445400836</v>
+        <v>279.6110509210431</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.40263554599164</v>
+        <v>-523.3889490789569</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="373" t="s">
+      <c r="B58" s="371" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="373"/>
-      <c r="D58" s="373"/>
-      <c r="E58" s="373"/>
-      <c r="F58" s="373"/>
+      <c r="C58" s="371"/>
+      <c r="D58" s="371"/>
+      <c r="E58" s="371"/>
+      <c r="F58" s="371"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7261557020429</v>
+        <v>-4449.7295773188016</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,7 +21380,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="373" t="s">
+      <c r="B61" s="371" t="s">
         <v>500</v>
       </c>
       <c r="C61" s="374"/>
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="372" t="s">
+      <c r="B64" s="370" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="372"/>
-      <c r="D64" s="372"/>
-      <c r="E64" s="372"/>
-      <c r="F64" s="372"/>
+      <c r="C64" s="370"/>
+      <c r="D64" s="370"/>
+      <c r="E64" s="370"/>
+      <c r="F64" s="370"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="372" t="s">
+      <c r="B65" s="370" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="372"/>
-      <c r="D65" s="372"/>
-      <c r="E65" s="372"/>
-      <c r="F65" s="372"/>
+      <c r="C65" s="370"/>
+      <c r="D65" s="370"/>
+      <c r="E65" s="370"/>
+      <c r="F65" s="370"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.017287206025</v>
+        <v>10305.046364726248</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3163971937247</v>
+        <v>7230.3266620440008</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12465571601983087</v>
+        <v>0.12603531807473087</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.7143824905205467E-2</v>
+        <v>4.766551203093921E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.41214322680481363</v>
+        <v>0.4132783967654487</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035914473808938</v>
+        <v>0.20035929880424613</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114107375703299</v>
+        <v>0.19114140107757358</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688828884786888E-2</v>
+        <v>9.7688904002608157E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0779900597746141E-2</v>
+        <v>9.0780056054266048E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="372" t="s">
+      <c r="B80" s="370" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="372"/>
-      <c r="D80" s="372"/>
-      <c r="E80" s="372"/>
-      <c r="F80" s="372"/>
+      <c r="C80" s="370"/>
+      <c r="D80" s="370"/>
+      <c r="E80" s="370"/>
+      <c r="F80" s="370"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="375" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="375"/>
-      <c r="D81" s="375"/>
-      <c r="E81" s="375"/>
-      <c r="F81" s="375"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="372" t="s">
+      <c r="B89" s="370" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="372"/>
-      <c r="D89" s="372"/>
-      <c r="E89" s="372"/>
-      <c r="F89" s="372"/>
+      <c r="C89" s="370"/>
+      <c r="D89" s="370"/>
+      <c r="E89" s="370"/>
+      <c r="F89" s="370"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="372" t="s">
+      <c r="B90" s="370" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="372"/>
-      <c r="D90" s="372"/>
-      <c r="E90" s="372"/>
-      <c r="F90" s="372"/>
+      <c r="C90" s="370"/>
+      <c r="D90" s="370"/>
+      <c r="E90" s="370"/>
+      <c r="F90" s="370"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.133156359263538</v>
+        <v>12.166609371480687</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="372" t="s">
+      <c r="B97" s="370" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="372"/>
-      <c r="D97" s="372"/>
-      <c r="E97" s="372"/>
-      <c r="F97" s="372"/>
+      <c r="C97" s="370"/>
+      <c r="D97" s="370"/>
+      <c r="E97" s="370"/>
+      <c r="F97" s="370"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="372" t="s">
+      <c r="B101" s="370" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="372"/>
-      <c r="D101" s="372"/>
-      <c r="E101" s="372"/>
-      <c r="F101" s="372"/>
+      <c r="C101" s="370"/>
+      <c r="D101" s="370"/>
+      <c r="E101" s="370"/>
+      <c r="F101" s="370"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0556847764043975</v>
+        <v>3.0641054277761266</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17132.263554599165</v>
+        <v>17130.89490789569</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.156217180655569</v>
+        <v>2.1619864108878288</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9935766241709157E-2</v>
+        <v>1.9990703890594277E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="372" t="s">
+      <c r="B116" s="370" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="372"/>
-      <c r="D116" s="372"/>
-      <c r="E116" s="372"/>
-      <c r="F116" s="372"/>
+      <c r="C116" s="370"/>
+      <c r="D116" s="370"/>
+      <c r="E116" s="370"/>
+      <c r="F116" s="370"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.253624529756417</v>
+        <v>11.284481058482982</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1825109862640586</v>
+        <v>-3.1912811368073881</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="373" t="s">
+      <c r="B123" s="371" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="373"/>
-      <c r="D123" s="373"/>
-      <c r="E123" s="373"/>
-      <c r="F123" s="373"/>
+      <c r="C123" s="371"/>
+      <c r="D123" s="371"/>
+      <c r="E123" s="371"/>
+      <c r="F123" s="371"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.86 HKD</v>
+        <v>12.9 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>14.04 HKD</v>
+        <v>14.07 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>13.01 HKD</v>
+        <v>13.04 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.08 HKD</v>
+        <v>12.12 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21983,7 +21983,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>11.25 HKD</v>
+        <v>11.28 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.930692140739255</v>
+        <v>12.966172607509471</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="376" t="s">
+      <c r="B134" s="375" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="376"/>
-      <c r="D134" s="376"/>
-      <c r="E134" s="376"/>
-      <c r="F134" s="376"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
+      <c r="B138" s="373" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="377"/>
-      <c r="D138" s="377"/>
-      <c r="E138" s="377"/>
-      <c r="F138" s="377"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="372" t="s">
+      <c r="B139" s="370" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="372"/>
-      <c r="D139" s="372"/>
-      <c r="E139" s="372"/>
-      <c r="F139" s="372"/>
+      <c r="C139" s="370"/>
+      <c r="D139" s="370"/>
+      <c r="E139" s="370"/>
+      <c r="F139" s="370"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34414992180799991</v>
+        <v>0.34509830710399991</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58363686378860125</v>
+        <v>0.58524521115335659</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2555777638527674</v>
+        <v>5.269998519538472</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8392146276413683</v>
+        <v>5.8552437306918286</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842211351978432</v>
+        <v>0.54842158068289837</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67178064736921583</v>
+        <v>0.67363189546700775</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.620514376058499</v>
+        <v>6.6386803750448493</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.2922950234277151</v>
+        <v>7.3123122705118568</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604758785860243</v>
+        <v>0.43604697455000185</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89497073003662608</v>
+        <v>0.89743703041019007</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.408697309762818</v>
+        <v>10.437257686500638</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.303668039799444</v>
+        <v>11.334694716910828</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582652832741514</v>
+        <v>0.12582571125528264</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83029717714552231</v>
+        <v>0.83258525447524612</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.268207980749688</v>
+        <v>9.2936389740562557</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.098505157895211</v>
+        <v>10.126224228531502</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.2226196826750263</v>
+        <v>0.22261897541104037</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="371" t="s">
+      <c r="B179" s="377" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="372"/>
-      <c r="D179" s="372"/>
-      <c r="E179" s="372"/>
-      <c r="F179" s="372"/>
+      <c r="C179" s="370"/>
+      <c r="D179" s="370"/>
+      <c r="E179" s="370"/>
+      <c r="F179" s="370"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="373" t="s">
+      <c r="B188" s="371" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="373"/>
-      <c r="D188" s="373"/>
-      <c r="E188" s="373"/>
-      <c r="F188" s="373"/>
+      <c r="C188" s="371"/>
+      <c r="D188" s="371"/>
+      <c r="E188" s="371"/>
+      <c r="F188" s="371"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="370" t="s">
+      <c r="B191" s="376" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="370"/>
-      <c r="D191" s="370"/>
-      <c r="E191" s="370"/>
-      <c r="F191" s="370"/>
+      <c r="C191" s="376"/>
+      <c r="D191" s="376"/>
+      <c r="E191" s="376"/>
+      <c r="F191" s="376"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="370" t="s">
+      <c r="B192" s="376" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="370"/>
-      <c r="D192" s="370"/>
-      <c r="E192" s="370"/>
-      <c r="F192" s="370"/>
+      <c r="C192" s="376"/>
+      <c r="D192" s="376"/>
+      <c r="E192" s="376"/>
+      <c r="F192" s="376"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,12 +22467,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22485,15 +22488,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52BA23D-32F5-4B68-8E37-485482886CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8008D97B-62A9-47A5-BE7B-A4C37D95C092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4760,29 +4760,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -5286,7 +5286,7 @@
         <v>464</v>
       </c>
       <c r="C12" s="50">
-        <v>7.24</v>
+        <v>7.41</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>62689.724365919996</v>
+        <v>64161.720656279998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -5334,7 +5334,7 @@
         <v>468</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0927748799999999</v>
+        <v>1.0923594000000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -5344,13 +5344,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>469</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.966172607509471</v>
+        <v>12.961263954595363</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25430003593741213</v>
+        <v>0.24411958340948536</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8552437306918286</v>
+        <v>5.8530261334837421</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3123122705118568</v>
+        <v>7.3095429210638656</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.334694716910828</v>
+        <v>11.330402233565579</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.126224228531502</v>
+        <v>10.122389346299705</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -5550,22 +5550,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>470</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5577,13 +5577,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5603,13 +5603,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5660,13 +5660,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.6110509210431</v>
+        <v>279.60915740585773</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.3889490789569</v>
+        <v>-523.39084259414221</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5730,13 +5730,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7295773188016</v>
+        <v>-4449.7291039400052</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5752,7 +5752,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="374"/>
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.046364726248</v>
+        <v>10305.04234186732</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3266620440008</v>
+        <v>7230.3252419076125</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12603531807473087</v>
+        <v>0.12309697530348271</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.766551203093921E-2</v>
+        <v>4.6554264307692307E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.4132783967654487</v>
+        <v>0.41312134681796203</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035929880424613</v>
+        <v>0.20035927748927812</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114140107757358</v>
+        <v>0.19114135579295682</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688904002608157E-2</v>
+        <v>9.7688893610098901E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780056054266048E-2</v>
+        <v>9.0780034546942029E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5924,22 +5924,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>472</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5983,22 +5983,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.166609371480687</v>
+        <v>12.161981159984091</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -6035,13 +6035,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6054,13 +6054,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0641054277761266</v>
+        <v>3.062940435291003</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.89490789569</v>
+        <v>17131.08425941423</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1619864108878288</v>
+        <v>2.1611882976455816</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9990703890594277E-2</v>
+        <v>1.9983103297091926E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -6182,13 +6182,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1912811368073881</v>
+        <v>-3.1900677913041315</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -6227,13 +6227,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>474</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.9 HKD</v>
+        <v>12.89 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.966172607509471</v>
+        <v>12.961263954595363</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -6376,13 +6376,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>475</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6395,22 +6395,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>477</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58524521115335659</v>
+        <v>0.58502269718018607</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.269998519538472</v>
+        <v>5.2680034363035562</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8552437306918286</v>
+        <v>5.8530261334837421</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842158068289837</v>
+        <v>0.54842165440133828</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67363189546700775</v>
+        <v>0.67337577631103995</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6386803750448493</v>
+        <v>6.6361671447528261</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3123122705118568</v>
+        <v>7.3095429210638656</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604697455000185</v>
+        <v>0.43604705940177257</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89743703041019007</v>
+        <v>0.89709581911020631</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.437257686500638</v>
+        <v>10.433306414455373</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.334694716910828</v>
+        <v>11.330402233565579</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582571125528264</v>
+        <v>0.12582582429791267</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83258525447524612</v>
+        <v>0.83226870023533794</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2936389740562557</v>
+        <v>9.2901206460643682</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.126224228531502</v>
+        <v>10.122389346299705</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261897541104037</v>
+        <v>0.2226190732616139</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -6743,13 +6743,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>478</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6786,13 +6786,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>479</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6800,22 +6800,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6839,17 +6839,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6866,6 +6855,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -7554,19 +7554,19 @@
       </c>
       <c r="C25" s="39">
         <f>(0.1517+0.1641)*Exchange_Rate</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="D25" s="39">
         <f>(0.2838)*Exchange_Rate</f>
-        <v>0.31012951094399999</v>
+        <v>0.31001159772000003</v>
       </c>
       <c r="E25" s="39">
         <f>0.2539*Exchange_Rate</f>
-        <v>0.27745554203200001</v>
+        <v>0.27735005166000004</v>
       </c>
       <c r="F25" s="39">
         <f>0.2078*Exchange_Rate</f>
-        <v>0.22707862006399998</v>
+        <v>0.22699228332000004</v>
       </c>
       <c r="G25" s="39"/>
       <c r="H25" s="39"/>
@@ -8939,19 +8939,19 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0.31012951094399999</v>
+        <v>0.31001159772000003</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.27745554203200001</v>
+        <v>0.27735005166000004</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
-        <v>0.22707862006399998</v>
+        <v>0.22699228332000004</v>
       </c>
       <c r="G65" s="73">
         <f t="shared" si="33"/>
@@ -10289,11 +10289,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>8.222060402577819</v>
+        <v>8.2189343226151639</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-3.1912811368073881</v>
+        <v>-3.1900677913041315</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>17130.89490789569</v>
+        <v>17131.08425941423</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>222</v>
@@ -10551,11 +10551,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-14497.594817581668</v>
+        <v>-14497.500141822398</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-13980.552546052155</v>
+        <v>-13980.457870292885</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>342</v>
@@ -10567,11 +10567,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.1103090248677372</v>
+        <v>3.110329336705338</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.2253374715674692</v>
+        <v>3.2253593135755674</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>310</v>
@@ -10584,7 +10584,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>27961.10509210431</v>
+        <v>27960.91574058577</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>343</v>
@@ -10699,11 +10699,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-26531.481311519998</v>
+        <v>-26521.393872600001</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0641054277761266</v>
+        <v>-3.062940435291003</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -10716,11 +10716,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>18720.211627268323</v>
+        <v>18713.300922963175</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>2.1619864108878288</v>
+        <v>2.1611882976455821</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -10733,11 +10733,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>173.095540992</v>
+        <v>173.02972896000003</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.9990703890594277E-2</v>
+        <v>1.998310329709193E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -10750,11 +10750,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-7638.1741432596746</v>
+        <v>-7635.0632206768259</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-0.88212831299770345</v>
+        <v>-0.88176903434832898</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -11334,48 +11334,48 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>-523.3889490789569</v>
+        <v>-523.39084259414221</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>-208.95363527375309</v>
+        <v>-208.95765813268054</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-420.52156856802208</v>
+        <v>-420.52522189502304</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>-366.34256022980571</v>
+        <v>-366.34616736531586</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>-454.9723100833146</v>
+        <v>-454.97453147410022</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>-503.37025014649112</v>
+        <v>-503.37163589121565</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>-818.09529860648058</v>
+        <v>-818.09644919452444</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
-        <v>-947.07340543398448</v>
+        <v>-947.07464420578367</v>
       </c>
       <c r="N12" s="328">
         <f t="shared" si="6"/>
-        <v>-1014.1609781239686</v>
+        <v>-1014.161864160747</v>
       </c>
       <c r="O12" s="328">
         <f t="shared" si="6"/>
-        <v>-468.58853727613757</v>
+        <v>-468.59000280616442</v>
       </c>
       <c r="P12" s="328">
         <f t="shared" si="6"/>
-        <v>-437.4797160089712</v>
+        <v>-437.48066083491972</v>
       </c>
       <c r="Q12" s="328" t="str">
         <f t="shared" si="6"/>
@@ -11389,48 +11389,48 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>17798.918309275206</v>
+        <v>17798.916415760021</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>16980.046364726248</v>
+        <v>16980.04234186732</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>17261.478431431977</v>
+        <v>17261.474778104977</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>16973.657439770195</v>
+        <v>16973.653832634685</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>14670.027689916686</v>
+        <v>14670.025468525901</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>11589.62974985351</v>
+        <v>11589.628364108785</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>20402.90470139352</v>
+        <v>20402.903550805477</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
-        <v>19208.926594566015</v>
+        <v>19208.925355794217</v>
       </c>
       <c r="N13" s="329">
         <f t="shared" si="7"/>
-        <v>16944.839021876032</v>
+        <v>16944.838135839254</v>
       </c>
       <c r="O13" s="329">
         <f t="shared" si="7"/>
-        <v>17752.411462723863</v>
+        <v>17752.409997193834</v>
       </c>
       <c r="P13" s="329">
         <f t="shared" si="7"/>
-        <v>11857.520283991029</v>
+        <v>11857.519339165081</v>
       </c>
       <c r="Q13" s="329" t="str">
         <f t="shared" si="7"/>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-4449.7295773188016</v>
+        <v>-4449.7291039400052</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -11556,50 +11556,50 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>7230.3266620440008</v>
+        <v>7230.3252419076125</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>10305.046364726248</v>
+        <v>10305.04234186732</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>10350.478431431977</v>
+        <v>10350.474778104977</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>10809.657439770195</v>
+        <v>10809.653832634685</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>8651.0276899166856</v>
+        <v>8651.0254685259006</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>5607.6297498535096</v>
+        <v>5607.6283641087848</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>12308.90470139352</v>
+        <v>12308.903550805477</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
-        <v>11857.926594566015</v>
+        <v>11857.925355794217</v>
       </c>
       <c r="N16" s="329">
         <f t="shared" si="8"/>
-        <v>10224.839021876032</v>
+        <v>10224.838135839254</v>
       </c>
       <c r="O16" s="329">
         <f t="shared" si="8"/>
-        <v>11296.411462723863</v>
+        <v>11296.409997193834</v>
       </c>
       <c r="P16" s="329">
         <f t="shared" si="8"/>
-        <v>7067.5202839910289</v>
+        <v>7067.519339165081</v>
       </c>
       <c r="Q16" s="329" t="str">
         <f t="shared" si="8"/>
@@ -11664,50 +11664,50 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>7230.3266620440008</v>
+        <v>7230.3252419076125</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>10305.046364726248</v>
+        <v>10305.04234186732</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>10350.478431431977</v>
+        <v>10350.474778104977</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>10809.657439770195</v>
+        <v>10809.653832634685</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>8651.0276899166856</v>
+        <v>8651.0254685259006</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>5607.6297498535096</v>
+        <v>5607.6283641087848</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>12308.90470139352</v>
+        <v>12308.903550805477</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
-        <v>11857.926594566015</v>
+        <v>11857.925355794217</v>
       </c>
       <c r="N19" s="334">
         <f t="shared" si="9"/>
-        <v>10224.839021876032</v>
+        <v>10224.838135839254</v>
       </c>
       <c r="O19" s="334">
         <f t="shared" si="9"/>
-        <v>11296.411462723863</v>
+        <v>11296.409997193834</v>
       </c>
       <c r="P19" s="334">
         <f t="shared" si="9"/>
-        <v>7067.5202839910289</v>
+        <v>7067.519339165081</v>
       </c>
       <c r="Q19" s="334" t="str">
         <f t="shared" si="9"/>
@@ -12525,43 +12525,43 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.18421622254801362</v>
+        <v>0.18421626619194928</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19337856912196635</v>
+        <v>0.19337861004982199</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18787936608924374</v>
+        <v>0.18787940601619993</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18391239996461947</v>
+        <v>0.1839124278133312</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19957496916838399</v>
+        <v>0.19957499303109572</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19967745081521385</v>
+        <v>0.19967746207569384</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1963670370351176</v>
+        <v>0.19636704969870719</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20838203274999709</v>
+        <v>0.20838204364618526</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2084787189487626</v>
+        <v>0.20847873615948628</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21986047146128351</v>
+        <v>0.21986048898011459</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -12663,48 +12663,48 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>279.6110509210431</v>
+        <v>279.60915740585773</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>594.04636472624691</v>
+        <v>594.04234186731946</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>539.47843143197792</v>
+        <v>539.47477810497696</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>532.65743977019429</v>
+        <v>532.65383263468414</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>328.0276899166854</v>
+        <v>328.02546852589978</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>204.62974985350886</v>
+        <v>204.62836410878435</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>169.90470139351947</v>
+        <v>169.9035508054755</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
-        <v>182.9265945660155</v>
+        <v>182.92535579421633</v>
       </c>
       <c r="N48" s="337">
         <f t="shared" si="19"/>
-        <v>130.83902187603144</v>
+        <v>130.83813583925303</v>
       </c>
       <c r="O48" s="337">
         <f t="shared" si="19"/>
-        <v>216.4114627238624</v>
+        <v>216.40999719383558</v>
       </c>
       <c r="P48" s="337">
         <f t="shared" si="19"/>
-        <v>139.52028399102878</v>
+        <v>139.51933916508025</v>
       </c>
       <c r="Q48" s="337" t="str">
         <f t="shared" si="19"/>
@@ -12775,48 +12775,48 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>-523.3889490789569</v>
+        <v>-523.39084259414221</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-208.95363527375309</v>
+        <v>-208.95765813268054</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-420.52156856802208</v>
+        <v>-420.52522189502304</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>-366.34256022980571</v>
+        <v>-366.34616736531586</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>-454.9723100833146</v>
+        <v>-454.97453147410022</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>-503.37025014649112</v>
+        <v>-503.37163589121565</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>-818.09529860648058</v>
+        <v>-818.09644919452444</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
-        <v>-947.07340543398448</v>
+        <v>-947.07464420578367</v>
       </c>
       <c r="N50" s="329">
         <f t="shared" si="20"/>
-        <v>-1014.1609781239686</v>
+        <v>-1014.161864160747</v>
       </c>
       <c r="O50" s="329">
         <f t="shared" si="20"/>
-        <v>-468.58853727613757</v>
+        <v>-468.59000280616442</v>
       </c>
       <c r="P50" s="329">
         <f t="shared" si="20"/>
-        <v>-437.4797160089712</v>
+        <v>-437.48066083491972</v>
       </c>
       <c r="Q50" s="329" t="str">
         <f t="shared" si="20"/>
@@ -13861,50 +13861,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8726067457681497E-3</v>
+        <v>2.8726171382773996E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>1.1171243184764875E-3</v>
+        <v>1.1171458258005011E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3710858992073598E-3</v>
+        <v>2.3711064982747669E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1305922871970276E-3</v>
+        <v>2.130613265745335E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2838842420500956E-3</v>
+        <v>3.2839002755317708E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>4.6074658368938605E-3</v>
+        <v>4.6074785209399977E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.2197832429331194E-3</v>
+        <v>7.2197933970023246E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>8.979552530899635E-3</v>
+        <v>8.9795642761523048E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1432834059973042E-2</v>
+        <v>1.1432844048438065E-2</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>5.7227295043616126E-3</v>
+        <v>5.7227474024347767E-3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>1.050598487089578E-2</v>
+        <v>1.0506007560695462E-2</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -13918,50 +13918,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>9.7688904002608157E-2</v>
+        <v>9.7688893610098901E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>9.0780056054266048E-2</v>
+        <v>9.0780034546942029E-2</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>9.7327821370997991E-2</v>
+        <v>9.7327800771930581E-2</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>9.8716195038909146E-2</v>
+        <v>9.8716174060360845E-2</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10588484550309055</v>
+        <v>0.10588482946960888</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1060825964966317</v>
+        <v>0.10608258381258556</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1800579342299076</v>
+        <v>0.1800579240758384</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18212692324420229</v>
+        <v>0.18212691149894963</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19102246772344636</v>
+        <v>0.19102245773498133</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21680481012583797</v>
+        <v>0.21680479222776475</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>0.28475589644799665</v>
+        <v>0.284755873758197</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>2.4422226000652039E-2</v>
+        <v>2.4422223402524725E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -14090,50 +14090,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>3.9683461372360049E-2</v>
+        <v>3.9683453577978117E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>5.5093647363355792E-2</v>
+        <v>5.509362585603178E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>5.8360558157312364E-2</v>
+        <v>5.8360537558244961E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>6.2867314007875791E-2</v>
+        <v>6.286729302932749E-2</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>6.244110438996648E-2</v>
+        <v>6.2441088356484806E-2</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>5.1327948941918236E-2</v>
+        <v>5.1327936257872103E-2</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10862747170574885</v>
+        <v>0.10862746155167965</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1124293789188017</v>
+        <v>0.11242936717354904</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11526660002565815</v>
+        <v>0.11526659003719314</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13795964268977143</v>
+        <v>0.13795962479169824</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>0.16972503743884704</v>
+        <v>0.16972501474904736</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>3.9683461372360049E-2</v>
+        <v>3.9683453577978117E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>5.5093647363355792E-2</v>
+        <v>5.509362585603178E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>5.8360558157312364E-2</v>
+        <v>5.8360537558244961E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>6.2867314007875791E-2</v>
+        <v>6.286729302932749E-2</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>6.244110438996648E-2</v>
+        <v>6.2441088356484806E-2</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>5.1327948941918236E-2</v>
+        <v>5.1327936257872103E-2</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10862747170574885</v>
+        <v>0.10862746155167965</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1124293789188017</v>
+        <v>0.11242936717354904</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11526660002565815</v>
+        <v>0.11526659003719314</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13795964268977143</v>
+        <v>0.13795962479169824</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>0.16972503743884704</v>
+        <v>0.16972501474904736</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -14266,24 +14266,24 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>0.31012951094399999</v>
+        <v>0.31001159772000003</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.27745554203200001</v>
+        <v>0.27735005166000004</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
-        <v>0.22707862006399998</v>
+        <v>0.22699228332000004</v>
       </c>
       <c r="K90" s="112">
         <f>Data!G65</f>
@@ -14322,24 +14322,24 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>2988.137810980023</v>
+        <v>2987.0017018687804</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>2988.137810980023</v>
+        <v>2987.0017018687804</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>2685.3499390631118</v>
+        <v>2684.3289518377451</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2402.4325212407475</v>
+        <v>2401.5191010274966</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
-        <v>1966.228743260446</v>
+        <v>1965.4811705140362</v>
       </c>
       <c r="K91" s="74">
         <f t="shared" si="37"/>
@@ -14377,24 +14377,24 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.4132783967654487</v>
+        <v>0.41312134681796203</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.28996840045361622</v>
+        <v>0.28985826576696261</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.259442107613918</v>
+        <v>0.25934355760337469</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.2222487192241516</v>
+        <v>0.22216429297460338</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
-        <v>0.22728267828251306</v>
+        <v>0.22719632229321671</v>
       </c>
       <c r="K92" s="170">
         <f t="shared" si="38"/>
@@ -14453,24 +14453,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.766551203093921E-2</v>
+        <v>4.6554264307692307E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.766551203093921E-2</v>
+        <v>4.6554264307692307E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>4.2835567809944748E-2</v>
+        <v>4.1836922769230775E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>3.8322588678453041E-2</v>
+        <v>3.7429156769230774E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>3.1364450285082869E-2</v>
+        <v>3.0633236615384619E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14590,46 +14590,46 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>4.8225542319487058E-2</v>
+        <v>4.82256791476674E-2</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-1.6304053434569088E-2</v>
+        <v>-1.6304078293161606E-2</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>1.6956922377106665E-2</v>
+        <v>1.6956923259322521E-2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.15702967973515758</v>
+        <v>0.15702960905222363</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.2657891586314145</v>
+        <v>0.26578911830828078</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>-0.4319617760572132</v>
+        <v>-0.43196181194263195</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>6.2157461061112418E-2</v>
+        <v>6.2157469660378828E-2</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
-        <v>0.13361517154379654</v>
+        <v>0.13361515771379939</v>
       </c>
       <c r="N98" s="6">
         <f t="shared" si="41"/>
-        <v>-4.5490858666922818E-2</v>
+        <v>-4.5490829779293862E-2</v>
       </c>
       <c r="O98" s="6">
         <f t="shared" si="41"/>
-        <v>0.49714367233186119</v>
+        <v>0.49714366803164989</v>
       </c>
       <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
@@ -15201,43 +15201,43 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.2143564965253248</v>
+        <v>1.2143569705830444</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.392012948526735</v>
+        <v>1.3920134398547752</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3756217607129024</v>
+        <v>1.3756222197520334</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.387118436112134</v>
+        <v>1.3871187922932737</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.9848618305153356</v>
+        <v>2.9848625681277925</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.3067775232819034</v>
+        <v>1.3067776454343427</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.4351581504812678</v>
+        <v>1.4351583004091335</v>
       </c>
       <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.2994825611994945</v>
+        <v>1.2994826738065917</v>
       </c>
       <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>1.3941595569503538</v>
+        <v>1.3941597378204442</v>
       </c>
       <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>1.8917526179988493</v>
+        <v>1.8917528708990361</v>
       </c>
       <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -15309,48 +15309,48 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>9.7688904002608157E-2</v>
+        <v>9.7688893610098901E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>9.0780056054266048E-2</v>
+        <v>9.0780034546942029E-2</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>9.7327821370997991E-2</v>
+        <v>9.7327800771930581E-2</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>9.8716195038909146E-2</v>
+        <v>9.8716174060360845E-2</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.10588484550309055</v>
+        <v>0.10588482946960888</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1060825964966317</v>
+        <v>0.10608258381258556</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.1800579342299076</v>
+        <v>0.1800579240758384</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18212692324420229</v>
+        <v>0.18212691149894963</v>
       </c>
       <c r="N118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19102246772344636</v>
+        <v>0.19102245773498133</v>
       </c>
       <c r="O118" s="23">
         <f t="shared" si="45"/>
-        <v>0.21680481012583797</v>
+        <v>0.21680479222776475</v>
       </c>
       <c r="P118" s="23">
         <f t="shared" si="45"/>
-        <v>0.28475589644799665</v>
+        <v>0.284755873758197</v>
       </c>
       <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.20035929880424613</v>
+        <v>0.20035927748927812</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.19114140107757358</v>
+        <v>0.19114135579295682</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.20122260158110555</v>
+        <v>0.2012225589930986</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.21032511511201946</v>
+        <v>0.21032507041504159</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19338036263582981</v>
+        <v>0.19338033335344776</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1371115708572824</v>
+        <v>0.13711155446317491</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25766123257426937</v>
+        <v>0.25766121804389058</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
-        <v>0.27404523346600301</v>
+        <v>0.27404521579299534</v>
       </c>
       <c r="N121" s="102">
         <f t="shared" si="48"/>
-        <v>0.25820707080953953</v>
+        <v>0.25820705730802673</v>
       </c>
       <c r="O121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26774673035494417</v>
+        <v>0.267746708251419</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="48"/>
-        <v>0.1686127109378168</v>
+        <v>0.16861269750248964</v>
       </c>
       <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
@@ -15595,50 +15595,50 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.91249570286105153</v>
+        <v>0.91214858699880685</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.3005374397480267</v>
+        <v>1.300042459586116</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3062711455097182</v>
+        <v>1.305774031974851</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3642213449318525</v>
+        <v>1.3637022041877813</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.0917937682983354</v>
+        <v>1.0913783810816045</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.70770496122101501</v>
+        <v>0.70743571244752823</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>1.5534322544387731</v>
+        <v>1.5528414844045926</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4965170410882085</v>
+        <v>1.4959478994573321</v>
       </c>
       <c r="N125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2904149571674077</v>
+        <v>1.2899242213669235</v>
       </c>
       <c r="O125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4256516198082561</v>
+        <v>1.4251093930569845</v>
       </c>
       <c r="P125" s="177">
         <f t="shared" si="49"/>
-        <v>0.89194889670475652</v>
+        <v>0.89160965283289584</v>
       </c>
       <c r="Q125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -15652,50 +15652,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12603531807473087</v>
+        <v>0.12309697530348271</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.17963224305911971</v>
+        <v>0.17544432652984021</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1804241913687456</v>
+        <v>0.17621781808027678</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.18842836255964815</v>
+        <v>0.18403538518053728</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.15080024424010158</v>
+        <v>0.14728453185986565</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>9.7749304036051796E-2</v>
+        <v>9.5470406538127967E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.21456246608270346</v>
+        <v>0.20956025430561304</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.20670124876908957</v>
+        <v>0.20188230761907316</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17823411010599555</v>
+        <v>0.17407884228973328</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.19691320715583646</v>
+        <v>0.19232245520337171</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.12319736142330891</v>
+        <v>0.12032518931618028</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -15709,43 +15709,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1516516477964974</v>
+        <v>0.1481724601952282</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14763185025313805</v>
+        <v>0.1442448847277624</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13085079066736804</v>
+        <v>0.12784881571278606</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.4201166980137111</v>
+        <v>0.4104783932009809</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15524075274592539</v>
+        <v>0.15167922400546555</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15267254875989023</v>
+        <v>0.14916993967902906</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13101030644289818</v>
+        <v>0.12800467188212994</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12679908996890268</v>
+        <v>0.12389006901145147</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4458685765987384E-2</v>
+        <v>5.3209296214001167E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7007659922990842E-2</v>
+        <v>3.6158631287780525E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16495,7 +16495,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3266620440008</v>
+        <v>7230.3252419076125</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>96404.355493920011</v>
+        <v>96404.336558768176</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>17130.89490789569</v>
+        <v>17131.08425941423</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>89414.650401815699</v>
+        <v>89414.820818182401</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>1.0927748799999999</v>
+        <v>1.0923594000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>13.026075898734144</v>
+        <v>13.021144458444139</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>7373.7346727786617</v>
+        <v>7373.7332244749523</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>6859.2880677010808</v>
+        <v>6859.2867204418162</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>7519.9870719488872</v>
+        <v>7519.9855949191797</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>6507.2900568513905</v>
+        <v>6507.2887787294148</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>7669.1402758282948</v>
+        <v>7669.1387695028297</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>6173.3555240797787</v>
+        <v>6173.3543115471739</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>7821.2518196642259</v>
+        <v>7821.2502834619445</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>5856.5575060790088</v>
+        <v>5856.5563557699261</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>7976.3803798717408</v>
+        <v>7976.3788132000609</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>5556.0166085077599</v>
+        <v>5556.015517229077</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>8134.5857966678086</v>
+        <v>8134.5841989223909</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>5270.8985648945209</v>
+        <v>5270.8975296169738</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16871,7 +16871,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>8295.9290971544251</v>
+        <v>8295.9274677189478</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>5000.4119208111815</v>
+        <v>5000.4109386609616</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>8460.4725188595785</v>
+        <v>8460.4708571054907</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>4743.8058368878783</v>
+        <v>4743.8049051386497</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>8628.2795337451153</v>
+        <v>8628.2778390314033</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>4500.3680045704887</v>
+        <v>4500.3671206358249</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>8799.4148726908079</v>
+        <v>8799.4131443637434</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>4269.4226688351837</v>
+        <v>4269.4218302613854</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>8973.9445504640171</v>
+        <v>8973.942787856904</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>4050.328752371307</v>
+        <v>4050.3279568305916</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>9151.9358911846284</v>
+        <v>9151.9340936175504</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>3842.4780760255558</v>
+        <v>3842.477321309595</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="C33" s="341">
         <f t="shared" si="2"/>
-        <v>9333.4575542950624</v>
+        <v>9333.4557210746116</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>3645.2936705675925</v>
+        <v>3645.2929545813818</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C34" s="341">
         <f t="shared" si="2"/>
-        <v>9518.5795610453733</v>
+        <v>9518.5776914643939</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
@@ -17047,7 +17047,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>3458.2281750907705</v>
+        <v>3458.2274958468161</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="C35" s="341">
         <f t="shared" si="2"/>
-        <v>9707.3733215036627</v>
+        <v>9707.3714148409726</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
@@ -17079,7 +17079,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>3280.7623176021102</v>
+        <v>3280.7616732149108</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="C36" s="123">
         <f t="shared" si="2"/>
-        <v>9899.9116621022349</v>
+        <v>9899.9097176223459</v>
       </c>
       <c r="D36" s="138">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>3112.4034735838263</v>
+        <v>3112.4028622646383</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C37" s="123">
         <f t="shared" si="2"/>
-        <v>10096.268853730087</v>
+        <v>10096.266870682923</v>
       </c>
       <c r="D37" s="138">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>2952.6842985251301</v>
+        <v>2952.6837185770014</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="C38" s="123">
         <f t="shared" si="2"/>
-        <v>10296.52064038262</v>
+        <v>10296.518618003229</v>
       </c>
       <c r="D38" s="138">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>2801.16143062839</v>
+        <v>2801.1608804414532</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C39" s="123">
         <f t="shared" si="2"/>
-        <v>10500.744268379562</v>
+        <v>10500.74220588782</v>
       </c>
       <c r="D39" s="138">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>2657.4142600884979</v>
+        <v>2657.4137381354985</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C40" s="123">
         <f t="shared" si="2"/>
-        <v>10709.018516162441</v>
+        <v>10709.01641276275</v>
       </c>
       <c r="D40" s="138">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>2521.0437615291257</v>
+        <v>2521.0432663611828</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>98316.462303715496</v>
+        <v>98316.442992999364</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>23144.987897099618</v>
+        <v>23144.983351103143</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -17492,7 +17492,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>110204.2008723302</v>
+        <v>110204.17922669744</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -17513,7 +17513,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>110204.2008723302</v>
+        <v>110204.17922669744</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>96404.355493920011</v>
+        <v>96404.336558768176</v>
       </c>
       <c r="C56" s="123">
-        <v>97921.978650246689</v>
+        <v>97921.959417012607</v>
       </c>
       <c r="D56" s="123">
-        <v>99461.386128424172</v>
+        <v>99461.366592829145</v>
       </c>
       <c r="E56" s="123">
-        <v>101023.05605778014</v>
+        <v>101023.03621545146</v>
       </c>
       <c r="F56" s="123">
-        <v>102607.47403150753</v>
+        <v>102607.45387797721</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -17564,19 +17564,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>96404.35549392004</v>
+        <v>96404.336558768206</v>
       </c>
       <c r="C57" s="123">
-        <v>99377.048027543147</v>
+        <v>99377.028508513278</v>
       </c>
       <c r="D57" s="123">
-        <v>102492.82427254066</v>
+        <v>102492.80414152917</v>
       </c>
       <c r="E57" s="123">
-        <v>105760.07335459715</v>
+        <v>105760.05258185259</v>
       </c>
       <c r="F57" s="123">
-        <v>109187.64716306108</v>
+        <v>109187.62571709356</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -17585,19 +17585,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>96404.35549392004</v>
+        <v>96404.336558768191</v>
       </c>
       <c r="C58" s="341">
-        <v>101173.53665513928</v>
+        <v>101173.51678325413</v>
       </c>
       <c r="D58" s="123">
-        <v>106330.97996379843</v>
+        <v>106330.95907891993</v>
       </c>
       <c r="E58" s="123">
-        <v>111913.68780289716</v>
+        <v>111913.66582149742</v>
       </c>
       <c r="F58" s="123">
-        <v>117962.19261698422</v>
+        <v>117962.16944757433</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -17616,19 +17616,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>96404.35549392004</v>
+        <v>96404.336558768191</v>
       </c>
       <c r="C59" s="341">
-        <v>102998.08444252261</v>
+        <v>102998.06421227098</v>
       </c>
       <c r="D59" s="123">
-        <v>110332.31988967897</v>
+        <v>110332.29821888186</v>
       </c>
       <c r="E59" s="123">
-        <v>118504.65617114049</v>
+        <v>118504.6328951832</v>
       </c>
       <c r="F59" s="123">
-        <v>127625.98363399351</v>
+        <v>127625.9585664811</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -17647,19 +17647,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>96404.355493920011</v>
+        <v>96404.336558768206</v>
       </c>
       <c r="C60" s="341">
-        <v>104688.61431960919</v>
+        <v>104688.59375731405</v>
       </c>
       <c r="D60" s="123">
-        <v>114140.67199644279</v>
+        <v>114140.64957763256</v>
       </c>
       <c r="E60" s="123">
-        <v>124956.63422761786</v>
+        <v>124956.60968440263</v>
       </c>
       <c r="F60" s="123">
-        <v>137367.42970089699</v>
+        <v>137367.40272002955</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -17678,19 +17678,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>96404.355493920011</v>
+        <v>96404.336558768191</v>
       </c>
       <c r="C61" s="341">
-        <v>106173.37108432705</v>
+        <v>106173.35023040512</v>
       </c>
       <c r="D61" s="123">
-        <v>117578.76143440964</v>
+        <v>117578.73834031097</v>
       </c>
       <c r="E61" s="123">
-        <v>130953.562718724</v>
+        <v>130953.53699762885</v>
       </c>
       <c r="F61" s="123">
-        <v>146703.84453327383</v>
+        <v>146703.81571860512</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -17770,23 +17770,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -17797,23 +17797,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>11.284481058482982</v>
+        <v>11.28021212563576</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>11.476011078278662</v>
+        <v>11.471669286887822</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>11.670290365293893</v>
+        <v>11.665874669530666</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.867379261333037</v>
+        <v>11.862888592414457</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>12.067339050169652</v>
+        <v>12.062772316000244</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -17824,23 +17824,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>11.284481058482985</v>
+        <v>11.280212125635764</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>11.659646564779955</v>
+        <v>11.655234917947567</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>12.052869799016653</v>
+        <v>12.048308568989983</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>12.46520950189675</v>
+        <v>12.460491416718806</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>12.897782816720985</v>
+        <v>12.892900179470431</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17851,23 +17851,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>11.284481058482985</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>11.886370505418178</v>
+        <v>11.881872612178382</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>12.537260164609668</v>
+        <v>12.532514671162476</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.241819882533417</v>
+        <v>13.236806372641627</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.005165013336752</v>
+        <v>13.999861124868458</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17878,23 +17878,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>11.284481058482985</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.116635622538247</v>
+        <v>12.112050135817821</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.042245023346348</v>
+        <v>13.037307432277098</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.073626050474237</v>
+        <v>14.068296119240078</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.224773502488382</v>
+        <v>15.219005671613578</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17905,23 +17905,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>11.284481058482982</v>
+        <v>11.280212125635764</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.32998715152209</v>
+        <v>12.325320505296238</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.52287405918875</v>
+        <v>13.517753635519117</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.887891093628598</v>
+        <v>14.882251413743939</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.45418236479685</v>
+        <v>16.447946863426779</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17931,23 +17931,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.517369303245774</v>
+        <v>12.512631376336675</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.956774487874199</v>
+        <v>13.951489007294201</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>15.644727089327914</v>
+        <v>15.638799506959542</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.63247469001022</v>
+        <v>17.625790963015461</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>12.897782816720985</v>
+        <v>12.892900179470431</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>14.073626050474237</v>
+        <v>14.068296119240078</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>13.042245023346348</v>
+        <v>13.037307432277098</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.116635622538247</v>
+        <v>12.112050135817821</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>11.284481058482985</v>
+        <v>11.280212125635764</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>2988.137810980023</v>
+        <v>2987.0017018687804</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>39841.837479733644</v>
+        <v>39826.689358250405</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>5.0281968151170213</v>
+        <v>5.0243740367873082</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -18356,7 +18356,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>5.2599674861770263</v>
+        <v>5.2579676128900807</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3047.4052437397659</v>
+        <v>3046.2466007714465</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>2834.7955755718754</v>
+        <v>2833.7177681594853</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3107.8482007919374</v>
+        <v>3106.666577024685</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -18425,7 +18425,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>2689.3224019832883</v>
+        <v>2688.2999044021071</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>3169.4899977636487</v>
+        <v>3168.2849373908575</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>2551.314473654817</v>
+        <v>2550.3444475708416</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>3232.3544127296796</v>
+        <v>3231.1254509041664</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>2420.3886966769874</v>
+        <v>2419.4684494109679</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>3296.4656953847739</v>
+        <v>3295.2123580394668</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2296.1816363662929</v>
+        <v>2295.3086134191722</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="C21" s="123">
         <f t="shared" si="2"/>
-        <v>3361.8485763978624</v>
+        <v>3360.5703800629312</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>2178.348508412912</v>
+        <v>2177.5202863748332</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" si="2"/>
-        <v>3428.5282769518176</v>
+        <v>3427.2247285681769</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2066.5622217996829</v>
+        <v>2065.7765016228859</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>3496.5305184724239</v>
+        <v>3495.201115201538</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>1960.5124708355997</v>
+        <v>1959.7670714525336</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>3565.8815325503147</v>
+        <v>3564.5257615802288</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>1859.904873783413</v>
+        <v>1859.1977260523461</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>3636.6080710597021</v>
+        <v>3635.2254094072282</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>1764.4601556902678</v>
+        <v>1763.7892966515922</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>3708.7374164778039</v>
+        <v>3707.3273307867817</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>1673.9133731530137</v>
+        <v>1673.2769405802985</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3782.2973924089515</v>
+        <v>3780.8593387445071</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>1588.0131788662277</v>
+        <v>1587.4094060968951</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3857.3163743174296</v>
+        <v>3855.8497979561571</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -18667,7 +18667,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>1506.5211239114124</v>
+        <v>1505.9483349426887</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3933.8233004732006</v>
+        <v>3932.3276356891788</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1429.2109958506171</v>
+        <v>1428.6676006871451</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>4011.8476831147223</v>
+        <v>4010.3223529612883</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1355.8681907870978</v>
+        <v>1355.3526810272947</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="C31" s="123">
         <f t="shared" si="2"/>
-        <v>4091.4196198331801</v>
+        <v>4089.8640359203741</v>
       </c>
       <c r="D31" s="138">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>1286.2891176499375</v>
+        <v>1285.8000622988475</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C32" s="123">
         <f t="shared" si="2"/>
-        <v>4172.5698051825057</v>
+        <v>4170.9833674501006</v>
       </c>
       <c r="D32" s="138">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>1220.2806330489796</v>
+        <v>1219.8166745459994</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="C33" s="123">
         <f t="shared" si="2"/>
-        <v>4255.3295425196802</v>
+        <v>4253.7116390057154</v>
       </c>
       <c r="D33" s="138">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>1157.6595051313116</v>
+        <v>1157.2193555817616</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -18787,7 +18787,7 @@
       </c>
       <c r="C34" s="123">
         <f t="shared" si="2"/>
-        <v>4339.7307560798799</v>
+        <v>4338.0807626845935</v>
       </c>
       <c r="D34" s="138">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -18799,7 +18799,7 @@
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>1098.2519049510156</v>
+        <v>1097.8343425510923</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C35" s="123">
         <f t="shared" si="2"/>
-        <v>4425.8060032911189</v>
+        <v>4424.123283536208</v>
       </c>
       <c r="D35" s="138">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>1041.8929239402935</v>
+        <v>1041.4967895854861</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>40632.069916530214</v>
+        <v>40616.621343619292</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>9565.3234912690441</v>
+        <v>9561.6866940870405</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>45545.015453334097</v>
+        <v>45527.698947101315</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -19095,7 +19095,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>45545.015453334097</v>
+        <v>45527.698947101315</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19125,19 +19125,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>39841.837479733644</v>
+        <v>39826.689358250413</v>
       </c>
       <c r="C51" s="123">
-        <v>40469.038344674453</v>
+        <v>40453.65175741008</v>
       </c>
       <c r="D51" s="123">
-        <v>41105.242199224391</v>
+        <v>41089.613723184637</v>
       </c>
       <c r="E51" s="123">
-        <v>41750.64664390542</v>
+        <v>41734.772780967069</v>
       </c>
       <c r="F51" s="123">
-        <v>42405.452363893848</v>
+        <v>42389.329539631872</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -19146,19 +19146,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>39841.837479733658</v>
+        <v>39826.689358250413</v>
       </c>
       <c r="C52" s="123">
-        <v>41070.387084106027</v>
+        <v>41054.771860204026</v>
       </c>
       <c r="D52" s="123">
-        <v>42358.070095318471</v>
+        <v>42341.96528609813</v>
       </c>
       <c r="E52" s="123">
-        <v>43708.353557784154</v>
+        <v>43691.735362153442</v>
       </c>
       <c r="F52" s="123">
-        <v>45124.895766141388</v>
+        <v>45107.738992101236</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -19167,19 +19167,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>39841.837479733651</v>
+        <v>39826.689358250413</v>
       </c>
       <c r="C53" s="123">
-        <v>41812.837023926324</v>
+        <v>41796.939515807651</v>
       </c>
       <c r="D53" s="123">
-        <v>43944.29692593767</v>
+        <v>43927.58902312901</v>
       </c>
       <c r="E53" s="123">
-        <v>46251.509471290279</v>
+        <v>46233.924351512345</v>
       </c>
       <c r="F53" s="123">
-        <v>48751.225843684297</v>
+        <v>48732.690315750559</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -19188,19 +19188,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>39841.837479733658</v>
+        <v>39826.68935825042</v>
       </c>
       <c r="C54" s="123">
-        <v>42566.883208318053</v>
+        <v>42550.699007016345</v>
       </c>
       <c r="D54" s="123">
-        <v>45597.964275419166</v>
+        <v>45580.627637705504</v>
       </c>
       <c r="E54" s="123">
-        <v>48975.414311649671</v>
+        <v>48956.793545826265</v>
       </c>
       <c r="F54" s="123">
-        <v>52745.061901870235</v>
+        <v>52725.007891918096</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -19209,19 +19209,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>39841.837479733658</v>
+        <v>39826.68935825042</v>
       </c>
       <c r="C55" s="123">
-        <v>43265.54268560448</v>
+        <v>43249.092849500099</v>
       </c>
       <c r="D55" s="123">
-        <v>47171.87392842085</v>
+        <v>47153.938880188609</v>
       </c>
       <c r="E55" s="123">
-        <v>51641.87745879648</v>
+        <v>51622.242886626816</v>
       </c>
       <c r="F55" s="123">
-        <v>56770.991114577191</v>
+        <v>56749.40642058399</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -19230,19 +19230,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>39841.837479733666</v>
+        <v>39826.689358250413</v>
       </c>
       <c r="C56" s="123">
-        <v>43879.16058091374</v>
+        <v>43862.477443360163</v>
       </c>
       <c r="D56" s="123">
-        <v>48592.76201928001</v>
+        <v>48574.286740306015</v>
       </c>
       <c r="E56" s="123">
-        <v>54120.278451117876</v>
+        <v>54099.701575036263</v>
       </c>
       <c r="F56" s="123">
-        <v>60629.52966803906</v>
+        <v>60606.477933004258</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -19292,23 +19292,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>5.0281968151170213</v>
+        <v>5.0243740367873082</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>5.0281968151170213</v>
+        <v>5.0243740367873082</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>5.0281968151170213</v>
+        <v>5.0243740367873082</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>5.0281968151170213</v>
+        <v>5.0243740367873082</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>5.0281968151170213</v>
+        <v>5.0243740367873082</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -19319,23 +19319,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.0281968151170222</v>
+        <v>5.02437403678731</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1073520346306349</v>
+        <v>5.1034690771017051</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>5.1876434668930251</v>
+        <v>5.1836994663384131</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>5.2690960498683523</v>
+        <v>5.2650901235020546</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>5.3517351108163078</v>
+        <v>5.3476663565968048</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -19346,23 +19346,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.0281968151170249</v>
+        <v>5.02437403678731</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.1832446140811328</v>
+        <v>5.1793039578345965</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>5.3457552818973992</v>
+        <v>5.3416910739518908</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>5.5161663732264259</v>
+        <v>5.5119726071408861</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>5.6949395792605042</v>
+        <v>5.690609897584725</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -19373,23 +19373,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.0281968151170231</v>
+        <v>5.02437403678731</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.2769447207764424</v>
+        <v>5.2729328273149481</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>5.5459433555983102</v>
+        <v>5.5417269510188669</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>5.8371226662473523</v>
+        <v>5.832684887286649</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>6.1525967180844701</v>
+        <v>6.1479190942224413</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -19400,23 +19400,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.0281968151170249</v>
+        <v>5.0243740367873109</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.3721083192108328</v>
+        <v>5.3680240758880968</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>5.7546426884078334</v>
+        <v>5.7502676163544963</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>6.1808901857535465</v>
+        <v>6.176191051266728</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6566345591625842</v>
+        <v>6.6515737313395604</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -19427,23 +19427,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.0281968151170249</v>
+        <v>5.0243740367873109</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.4602818970567322</v>
+        <v>5.4561306181633853</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9532762857797064</v>
+        <v>5.9487501989114158</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>6.5174083373305285</v>
+        <v>6.5124533587817712</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>7.1647226827466639</v>
+        <v>7.1592755716615013</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -19453,23 +19453,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.0281968151170258</v>
+        <v>5.02437403678731</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.5377228923035569</v>
+        <v>5.5335127374812556</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>6.1325979593026689</v>
+        <v>6.1279355398617286</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>6.8301923042475234</v>
+        <v>6.8249995259835643</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>7.6516854458318795</v>
+        <v>7.645868112425168</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>5.6949395792605042</v>
+        <v>5.690609897584725</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.1808901857535465</v>
+        <v>6.176191051266728</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>5.7546426884078334</v>
+        <v>5.7502676163544963</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>5.3721083192108328</v>
+        <v>5.3680240758880968</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.0281968151170249</v>
+        <v>5.02437403678731</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-7.24</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.31127091461347</v>
+        <v>13.306231053115363</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>10305.046364726248</v>
+        <v>10305.04234186732</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3266620440008</v>
+        <v>7230.3252419076125</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0052601061976629E-2</v>
+        <v>6.0052553854325064E-2</v>
       </c>
       <c r="E14" s="380"/>
       <c r="F14" s="380"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>7.24</v>
+        <v>7.41</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>13.042245023346348</v>
+        <v>13.037307432277098</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.116635622538247</v>
+        <v>12.112050135817821</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>14.073626050474237</v>
+        <v>14.068296119240078</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>13.063399348610305</v>
+        <v>13.058453710377838</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -20214,7 +20214,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>11.284481058482985</v>
+        <v>11.280212125635764</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -20272,7 +20272,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>12.897782816720985</v>
+        <v>12.892900179470431</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.966172607509471</v>
+        <v>12.961263954595363</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>13.026075898734144</v>
+        <v>13.021144458444139</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.8033053368949548E-2</v>
+        <v>-6.8031099238257647E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.58524521115335659</v>
+        <v>0.58502269718018607</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.269998519538472</v>
+        <v>5.2680034363035562</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8552437306918286</v>
+        <v>5.8530261334837421</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54842158068289837</v>
+        <v>0.54842165440133828</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>7.24</v>
+        <v>7.41</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -20546,7 +20546,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.25430003593741213</v>
+        <v>0.24411958340948536</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.67363189546700775</v>
+        <v>0.67337577631103995</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -20584,7 +20584,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6386803750448493</v>
+        <v>6.6361671447528261</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3123122705118568</v>
+        <v>7.3095429210638656</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43604697455000185</v>
+        <v>0.43604705940177257</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.89743703041019007</v>
+        <v>0.89709581911020631</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.437257686500638</v>
+        <v>10.433306414455373</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.334694716910828</v>
+        <v>11.330402233565579</v>
       </c>
       <c r="D99" t="s">
         <v>377</v>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.12582571125528264</v>
+        <v>0.12582582429791267</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>0.83258525447524612</v>
+        <v>0.83226870023533794</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>9.2936389740562557</v>
+        <v>9.2901206460643682</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.126224228531502</v>
+        <v>10.122389346299705</v>
       </c>
       <c r="D105" t="s">
         <v>377</v>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.22261897541104037</v>
+        <v>0.2226190732616139</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>7.24</v>
+        <v>7.41</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>62689.724365919996</v>
+        <v>64161.720656279998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="C16" s="366">
         <f>Exchange_Rate</f>
-        <v>1.0927748799999999</v>
+        <v>1.0923594000000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -20959,13 +20959,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="372" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
+      <c r="C18" s="372"/>
+      <c r="D18" s="372"/>
+      <c r="E18" s="372"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -21049,14 +21049,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.966172607509471</v>
+        <v>12.961263954595363</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>447</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.25430003593741213</v>
+        <v>0.24411958340948536</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8552437306918286</v>
+        <v>5.8530261334837421</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -21109,7 +21109,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3123122705118568</v>
+        <v>7.3095429210638656</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.334694716910828</v>
+        <v>11.330402233565579</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.126224228531502</v>
+        <v>10.122389346299705</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -21178,22 +21178,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="370" t="s">
+      <c r="B36" s="372" t="s">
         <v>493</v>
       </c>
-      <c r="C36" s="370"/>
-      <c r="D36" s="370"/>
-      <c r="E36" s="370"/>
-      <c r="F36" s="370"/>
+      <c r="C36" s="372"/>
+      <c r="D36" s="372"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="375" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="375"/>
+      <c r="D37" s="375"/>
+      <c r="E37" s="375"/>
+      <c r="F37" s="375"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -21205,13 +21205,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="371" t="s">
+      <c r="B40" s="373" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="371"/>
-      <c r="D40" s="371"/>
-      <c r="E40" s="371"/>
-      <c r="F40" s="371"/>
+      <c r="C40" s="373"/>
+      <c r="D40" s="373"/>
+      <c r="E40" s="373"/>
+      <c r="F40" s="373"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -21231,13 +21231,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="371" t="s">
+      <c r="B43" s="373" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="371"/>
-      <c r="D43" s="371"/>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
+      <c r="C43" s="373"/>
+      <c r="D43" s="373"/>
+      <c r="E43" s="373"/>
+      <c r="F43" s="373"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -21266,13 +21266,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="371" t="s">
+      <c r="B47" s="373" t="s">
         <v>497</v>
       </c>
-      <c r="C47" s="371"/>
-      <c r="D47" s="371"/>
-      <c r="E47" s="371"/>
-      <c r="F47" s="371"/>
+      <c r="C47" s="373"/>
+      <c r="D47" s="373"/>
+      <c r="E47" s="373"/>
+      <c r="F47" s="373"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -21288,13 +21288,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="373" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
+      <c r="C50" s="373"/>
+      <c r="D50" s="373"/>
+      <c r="E50" s="373"/>
+      <c r="F50" s="373"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>279.6110509210431</v>
+        <v>279.60915740585773</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>-523.3889490789569</v>
+        <v>-523.39084259414221</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21358,13 +21358,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="371" t="s">
+      <c r="B58" s="373" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="371"/>
-      <c r="D58" s="371"/>
-      <c r="E58" s="371"/>
-      <c r="F58" s="371"/>
+      <c r="C58" s="373"/>
+      <c r="D58" s="373"/>
+      <c r="E58" s="373"/>
+      <c r="F58" s="373"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-4449.7295773188016</v>
+        <v>-4449.7291039400052</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21380,7 +21380,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="371" t="s">
+      <c r="B61" s="373" t="s">
         <v>500</v>
       </c>
       <c r="C61" s="374"/>
@@ -21402,22 +21402,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="370" t="s">
+      <c r="B64" s="372" t="s">
         <v>501</v>
       </c>
-      <c r="C64" s="370"/>
-      <c r="D64" s="370"/>
-      <c r="E64" s="370"/>
-      <c r="F64" s="370"/>
+      <c r="C64" s="372"/>
+      <c r="D64" s="372"/>
+      <c r="E64" s="372"/>
+      <c r="F64" s="372"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="370" t="s">
+      <c r="B65" s="372" t="s">
         <v>502</v>
       </c>
-      <c r="C65" s="370"/>
-      <c r="D65" s="370"/>
-      <c r="E65" s="370"/>
-      <c r="F65" s="370"/>
+      <c r="C65" s="372"/>
+      <c r="D65" s="372"/>
+      <c r="E65" s="372"/>
+      <c r="F65" s="372"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>10305.046364726248</v>
+        <v>10305.04234186732</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>7230.3266620440008</v>
+        <v>7230.3252419076125</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.12603531807473087</v>
+        <v>0.12309697530348271</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -21461,14 +21461,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.766551203093921E-2</v>
+        <v>4.6554264307692307E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>504</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.4132783967654487</v>
+        <v>0.41312134681796203</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -21488,11 +21488,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.20035929880424613</v>
+        <v>0.20035927748927812</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.19114140107757358</v>
+        <v>0.19114135579295682</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -21502,11 +21502,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>9.7688904002608157E-2</v>
+        <v>9.7688893610098901E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>9.0780056054266048E-2</v>
+        <v>9.0780034546942029E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -21552,22 +21552,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="370" t="s">
+      <c r="B80" s="372" t="s">
         <v>507</v>
       </c>
-      <c r="C80" s="370"/>
-      <c r="D80" s="370"/>
-      <c r="E80" s="370"/>
-      <c r="F80" s="370"/>
+      <c r="C80" s="372"/>
+      <c r="D80" s="372"/>
+      <c r="E80" s="372"/>
+      <c r="F80" s="372"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="375" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="375"/>
+      <c r="D81" s="375"/>
+      <c r="E81" s="375"/>
+      <c r="F81" s="375"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -21611,22 +21611,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="370" t="s">
+      <c r="B89" s="372" t="s">
         <v>508</v>
       </c>
-      <c r="C89" s="370"/>
-      <c r="D89" s="370"/>
-      <c r="E89" s="370"/>
-      <c r="F89" s="370"/>
+      <c r="C89" s="372"/>
+      <c r="D89" s="372"/>
+      <c r="E89" s="372"/>
+      <c r="F89" s="372"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="370" t="s">
+      <c r="B90" s="372" t="s">
         <v>509</v>
       </c>
-      <c r="C90" s="370"/>
-      <c r="D90" s="370"/>
-      <c r="E90" s="370"/>
-      <c r="F90" s="370"/>
+      <c r="C90" s="372"/>
+      <c r="D90" s="372"/>
+      <c r="E90" s="372"/>
+      <c r="F90" s="372"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.166609371480687</v>
+        <v>12.161981159984091</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -21663,13 +21663,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="370" t="s">
+      <c r="B97" s="372" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="370"/>
-      <c r="D97" s="370"/>
-      <c r="E97" s="370"/>
-      <c r="F97" s="370"/>
+      <c r="C97" s="372"/>
+      <c r="D97" s="372"/>
+      <c r="E97" s="372"/>
+      <c r="F97" s="372"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -21682,13 +21682,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="370" t="s">
+      <c r="B101" s="372" t="s">
         <v>512</v>
       </c>
-      <c r="C101" s="370"/>
-      <c r="D101" s="370"/>
-      <c r="E101" s="370"/>
-      <c r="F101" s="370"/>
+      <c r="C101" s="372"/>
+      <c r="D101" s="372"/>
+      <c r="E101" s="372"/>
+      <c r="F101" s="372"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -21709,7 +21709,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0641054277761266</v>
+        <v>3.062940435291003</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>17130.89490789569</v>
+        <v>17131.08425941423</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.1619864108878288</v>
+        <v>2.1611882976455816</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.9990703890594277E-2</v>
+        <v>1.9983103297091926E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -21810,13 +21810,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="370" t="s">
+      <c r="B116" s="372" t="s">
         <v>517</v>
       </c>
-      <c r="C116" s="370"/>
-      <c r="D116" s="370"/>
-      <c r="E116" s="370"/>
-      <c r="F116" s="370"/>
+      <c r="C116" s="372"/>
+      <c r="D116" s="372"/>
+      <c r="E116" s="372"/>
+      <c r="F116" s="372"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>11.284481058482982</v>
+        <v>11.280212125635762</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-3.1912811368073881</v>
+        <v>-3.1900677913041315</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -21855,13 +21855,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="371" t="s">
+      <c r="B123" s="373" t="s">
         <v>520</v>
       </c>
-      <c r="C123" s="371"/>
-      <c r="D123" s="371"/>
-      <c r="E123" s="371"/>
-      <c r="F123" s="371"/>
+      <c r="C123" s="373"/>
+      <c r="D123" s="373"/>
+      <c r="E123" s="373"/>
+      <c r="F123" s="373"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>12.9 HKD</v>
+        <v>12.89 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -21961,7 +21961,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.12 HKD</v>
+        <v>12.11 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -21996,7 +21996,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.966172607509471</v>
+        <v>12.961263954595363</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -22004,13 +22004,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="376" t="s">
         <v>525</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="376"/>
+      <c r="D134" s="376"/>
+      <c r="E134" s="376"/>
+      <c r="F134" s="376"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -22023,22 +22023,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="377" t="s">
         <v>527</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="377"/>
+      <c r="D138" s="377"/>
+      <c r="E138" s="377"/>
+      <c r="F138" s="377"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="370" t="s">
+      <c r="B139" s="372" t="s">
         <v>528</v>
       </c>
-      <c r="C139" s="370"/>
-      <c r="D139" s="370"/>
-      <c r="E139" s="370"/>
-      <c r="F139" s="370"/>
+      <c r="C139" s="372"/>
+      <c r="D139" s="372"/>
+      <c r="E139" s="372"/>
+      <c r="F139" s="372"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.34509830710399991</v>
+        <v>0.34496709852000002</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.58524521115335659</v>
+        <v>0.58502269718018607</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.269998519538472</v>
+        <v>5.2680034363035562</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8552437306918286</v>
+        <v>5.8530261334837421</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54842158068289837</v>
+        <v>0.54842165440133828</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.67363189546700775</v>
+        <v>0.67337577631103995</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6386803750448493</v>
+        <v>6.6361671447528261</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3123122705118568</v>
+        <v>7.3095429210638656</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43604697455000185</v>
+        <v>0.43604705940177257</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.89743703041019007</v>
+        <v>0.89709581911020631</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.437257686500638</v>
+        <v>10.433306414455373</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.334694716910828</v>
+        <v>11.330402233565579</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.12582571125528264</v>
+        <v>0.12582582429791267</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>0.83258525447524612</v>
+        <v>0.83226870023533794</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>9.2936389740562557</v>
+        <v>9.2901206460643682</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.126224228531502</v>
+        <v>10.122389346299705</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -22357,7 +22357,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22261897541104037</v>
+        <v>0.2226190732616139</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -22371,13 +22371,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="371" t="s">
         <v>535</v>
       </c>
-      <c r="C179" s="370"/>
-      <c r="D179" s="370"/>
-      <c r="E179" s="370"/>
-      <c r="F179" s="370"/>
+      <c r="C179" s="372"/>
+      <c r="D179" s="372"/>
+      <c r="E179" s="372"/>
+      <c r="F179" s="372"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -22414,13 +22414,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="371" t="s">
+      <c r="B188" s="373" t="s">
         <v>542</v>
       </c>
-      <c r="C188" s="371"/>
-      <c r="D188" s="371"/>
-      <c r="E188" s="371"/>
-      <c r="F188" s="371"/>
+      <c r="C188" s="373"/>
+      <c r="D188" s="373"/>
+      <c r="E188" s="373"/>
+      <c r="F188" s="373"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -22428,22 +22428,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="376" t="s">
+      <c r="B191" s="370" t="s">
         <v>544</v>
       </c>
-      <c r="C191" s="376"/>
-      <c r="D191" s="376"/>
-      <c r="E191" s="376"/>
-      <c r="F191" s="376"/>
+      <c r="C191" s="370"/>
+      <c r="D191" s="370"/>
+      <c r="E191" s="370"/>
+      <c r="F191" s="370"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="376" t="s">
+      <c r="B192" s="370" t="s">
         <v>545</v>
       </c>
-      <c r="C192" s="376"/>
-      <c r="D192" s="376"/>
-      <c r="E192" s="376"/>
-      <c r="F192" s="376"/>
+      <c r="C192" s="370"/>
+      <c r="D192" s="370"/>
+      <c r="E192" s="370"/>
+      <c r="F192" s="370"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -22467,15 +22467,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -22488,12 +22485,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0135.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0135.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44ECE6C-E340-4224-A21F-DE0886E6FF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4759C160-0343-4D08-8298-E65F66283758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="560">
   <si>
     <t>Sales</t>
   </si>
@@ -2523,9 +2523,6 @@
     <t xml:space="preserve">Taxes = </t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -3260,6 +3257,24 @@
   </si>
   <si>
     <t>CNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天然氣銷售 </t>
+  </si>
+  <si>
+    <t>LPG銷售</t>
+  </si>
+  <si>
+    <t>LNG加工與儲運</t>
+  </si>
+  <si>
+    <t>原油銷售</t>
+  </si>
+  <si>
+    <t>Next</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -4003,7 +4018,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="473">
+  <cellXfs count="477">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4963,30 +4978,38 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4996,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5325,7 +5348,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F3" s="439">
         <v>45932</v>
@@ -5333,13 +5356,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C4" s="430" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E4" s="440" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F4" s="441" t="s">
         <v>327</v>
@@ -5350,13 +5373,13 @@
         <v>353</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>504</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5364,7 +5387,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5405,11 +5428,11 @@
         <v>60005.495836439994</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>0.38369191211394271</v>
+        <v>0.27869234727094133</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5417,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="455" t="s">
+      <c r="B12" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C12" s="455"/>
-      <c r="D12" s="455"/>
-      <c r="E12" s="455"/>
-      <c r="F12" s="455"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5463,7 +5486,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
@@ -5472,7 +5495,7 @@
         <v>276</v>
       </c>
       <c r="E17" s="228" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5482,7 +5505,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>12.445302783583385</v>
+        <v>10.622939875291571</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>351</v>
@@ -5497,7 +5520,7 @@
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">Low Growth </v>
+        <v>Low Growth Asset Play</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>352</v>
@@ -5532,7 +5555,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>7.2738380246452037</v>
+        <v>6.2293992812020962</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>412</v>
@@ -5547,7 +5570,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>8.4621105915013661</v>
+        <v>7.2460866491938063</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>413</v>
@@ -5562,7 +5585,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>10.552982187820145</v>
+        <v>9.0348931565705026</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>414</v>
@@ -5577,7 +5600,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>11.441599424464991</v>
+        <v>9.795088262511122</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>415</v>
@@ -5601,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="455" t="s">
+      <c r="B29" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C29" s="455"/>
-      <c r="D29" s="455"/>
-      <c r="E29" s="455"/>
-      <c r="F29" s="455"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="457" t="s">
+      <c r="B30" s="465" t="s">
         <v>268</v>
       </c>
-      <c r="C30" s="457"/>
-      <c r="D30" s="457"/>
-      <c r="E30" s="457"/>
-      <c r="F30" s="457"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5628,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="456" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="456"/>
-      <c r="D33" s="456"/>
-      <c r="E33" s="456"/>
-      <c r="F33" s="456"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5654,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="456" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="456"/>
-      <c r="D36" s="456"/>
-      <c r="E36" s="456"/>
-      <c r="F36" s="456"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5689,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="456" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="456"/>
-      <c r="D40" s="456"/>
-      <c r="E40" s="456"/>
-      <c r="F40" s="456"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5703,7 +5726,7 @@
       </c>
       <c r="C41" s="293">
         <f>Normalized_FCF!C9</f>
-        <v>1126</v>
+        <v>291.16000000000003</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5711,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="456" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="456"/>
-      <c r="D43" s="456"/>
-      <c r="E43" s="456"/>
-      <c r="F43" s="456"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5781,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="456" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s=